--- a/development/MS/spec/MSBB/Logic/MSBBLA0010_SlsSchdSrch.xlsx
+++ b/development/MS/spec/MSBB/Logic/MSBBLA0010_SlsSchdSrch.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\PJ\TK\dev\development\MS\spec\MSBB\Logic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8B95C61-C242-4A62-94CB-9FF0AB063887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32FBCFA7-7D7E-459E-8C90-F531A21FAB34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14955" yWindow="0" windowWidth="13860" windowHeight="15750" tabRatio="794" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="794" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LogicCommon" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="622">
   <si>
     <t>*</t>
   </si>
@@ -555,9 +555,6 @@
     <t>cst_grp_nm10</t>
   </si>
   <si>
-    <t>#MA.CST_FRCST_NO</t>
-  </si>
-  <si>
     <t>#MA.CST_FRCST_SLIP_NO</t>
   </si>
   <si>
@@ -625,10 +622,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>cst_frcst_no</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>frcst_usr_cd</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -654,10 +647,6 @@
   </si>
   <si>
     <t>dtl_intr_rmrks</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>cst_frcst_no</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -949,10 +938,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>顧客期間内示ＮＯ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>最新のみ</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -1629,9 +1614,6 @@
     <t>Forecast period TO</t>
   </si>
   <si>
-    <t>Sales forecast No.</t>
-  </si>
-  <si>
     <t>Latest only</t>
   </si>
   <si>
@@ -2191,6 +2173,24 @@
   </si>
   <si>
     <t>prd_itm_sub3</t>
+  </si>
+  <si>
+    <t>#MA.ZOHO_SLS_SCHD_NO</t>
+  </si>
+  <si>
+    <t>#MA.DEAL_CD</t>
+  </si>
+  <si>
+    <t>#MA.DEAL_NM</t>
+  </si>
+  <si>
+    <t>Deal cd.</t>
+  </si>
+  <si>
+    <t>Deal name</t>
+  </si>
+  <si>
+    <t>ＺＯＨＯ販売予定ＮＯ</t>
   </si>
 </sst>
 </file>
@@ -3423,13 +3423,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>20</v>
@@ -3453,7 +3453,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>22</v>
@@ -3471,13 +3471,13 @@
         <v>5</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>23</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="H4" s="19"/>
       <c r="I4" s="19"/>
@@ -3621,7 +3621,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U212"/>
+  <dimension ref="A1:U211"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4.875" style="4" customWidth="1"/>
@@ -3645,10 +3645,10 @@
   <sheetData>
     <row r="1" spans="1:21" s="9" customFormat="1">
       <c r="A1" s="53" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B1" s="53" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C1" s="53"/>
       <c r="D1" s="1" t="s">
@@ -3676,12 +3676,12 @@
     </row>
     <row r="2" spans="1:21" s="9" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A2" s="24" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="70" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>1</v>
@@ -3698,7 +3698,7 @@
         <v>MSBBLA0010</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>33</v>
@@ -3711,10 +3711,10 @@
         <v>MC</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="N2" s="26" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="O2" s="7"/>
       <c r="P2" s="7"/>
@@ -3726,7 +3726,7 @@
     </row>
     <row r="3" spans="1:21" s="9" customFormat="1">
       <c r="A3" s="55" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
@@ -3749,7 +3749,7 @@
         <v>MSBBLA_SlsSchdSrch</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>24</v>
@@ -3764,10 +3764,10 @@
       <c r="M3" s="58"/>
       <c r="N3" s="7"/>
       <c r="O3" s="7" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="Q3" s="4"/>
       <c r="R3" s="5"/>
@@ -3777,7 +3777,7 @@
     </row>
     <row r="4" spans="1:21" s="9" customFormat="1">
       <c r="A4" s="55" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B4" s="56"/>
       <c r="C4" s="56"/>
@@ -3786,7 +3786,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="59" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>5</v>
@@ -3796,7 +3796,7 @@
         <v>ZOHO販売予定一覧照会</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>34</v>
@@ -3809,7 +3809,7 @@
         <v>MS.MSUDL5010</v>
       </c>
       <c r="M4" s="60" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="N4" s="26"/>
       <c r="O4" s="61"/>
@@ -3822,13 +3822,13 @@
     </row>
     <row r="5" spans="1:21" s="9" customFormat="1">
       <c r="A5" s="62" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B5" s="53"/>
       <c r="C5" s="53"/>
       <c r="D5" s="23"/>
       <c r="E5" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F5" s="59"/>
       <c r="G5" s="63"/>
@@ -3849,7 +3849,7 @@
     </row>
     <row r="6" spans="1:21" s="9" customFormat="1">
       <c r="A6" s="55" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B6" s="56"/>
       <c r="C6" s="56"/>
@@ -3857,7 +3857,7 @@
         <v>13</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
@@ -3867,15 +3867,15 @@
       <c r="K6" s="12"/>
       <c r="L6" s="64"/>
       <c r="M6" s="48" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="N6" s="48"/>
       <c r="O6" s="48" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="P6" s="48"/>
       <c r="Q6" s="48" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
@@ -3924,17 +3924,17 @@
       <c r="B8" s="71"/>
       <c r="C8" s="72"/>
       <c r="D8" s="28" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="F8" s="64"/>
       <c r="G8" s="28" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="H8" s="28" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="I8" s="64"/>
       <c r="J8" s="3"/>
@@ -3946,17 +3946,17 @@
       </c>
       <c r="M8" s="29"/>
       <c r="N8" s="28" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="O8" s="29"/>
       <c r="P8" s="28" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="Q8" s="29"/>
       <c r="R8" s="3"/>
       <c r="S8" s="23"/>
       <c r="T8" s="74" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="U8" s="75"/>
     </row>
@@ -3967,25 +3967,25 @@
       <c r="B9" s="32"/>
       <c r="C9" s="33"/>
       <c r="D9" s="28" t="s">
+        <v>406</v>
+      </c>
+      <c r="E9" s="67" t="s">
+        <v>407</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>408</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>409</v>
+      </c>
+      <c r="H9" s="28" t="s">
         <v>410</v>
       </c>
-      <c r="E9" s="67" t="s">
+      <c r="I9" s="68" t="s">
         <v>411</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="J9" s="28" t="s">
         <v>412</v>
-      </c>
-      <c r="G9" s="28" t="s">
-        <v>413</v>
-      </c>
-      <c r="H9" s="28" t="s">
-        <v>414</v>
-      </c>
-      <c r="I9" s="68" t="s">
-        <v>415</v>
-      </c>
-      <c r="J9" s="28" t="s">
-        <v>416</v>
       </c>
       <c r="K9" s="70"/>
       <c r="L9" s="68"/>
@@ -3995,11 +3995,11 @@
       <c r="P9" s="28"/>
       <c r="Q9" s="28"/>
       <c r="R9" s="74" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="S9" s="75"/>
       <c r="T9" s="74" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="U9" s="75"/>
     </row>
@@ -4018,22 +4018,22 @@
       <c r="J10" s="34"/>
       <c r="K10" s="37"/>
       <c r="L10" s="28" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M10" s="28" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="N10" s="28" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="O10" s="28" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="P10" s="28" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="Q10" s="28" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="R10" s="34"/>
       <c r="S10" s="34"/>
@@ -4078,23 +4078,23 @@
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E12" s="29" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F12" s="29"/>
       <c r="G12" s="42" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="H12" s="42" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
@@ -4115,23 +4115,23 @@
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E13" s="29" t="s">
         <v>54</v>
       </c>
       <c r="F13" s="29"/>
       <c r="G13" s="42" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="H13" s="42" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
@@ -4152,23 +4152,23 @@
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
       <c r="D14" s="8" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E14" s="29" t="s">
         <v>54</v>
       </c>
       <c r="F14" s="29"/>
       <c r="G14" s="42" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="H14" s="42" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -4189,23 +4189,23 @@
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E15" s="29" t="s">
         <v>54</v>
       </c>
       <c r="F15" s="29"/>
       <c r="G15" s="42" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="H15" s="42" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
@@ -4226,23 +4226,23 @@
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E16" s="29" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="29"/>
       <c r="G16" s="42" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="H16" s="42" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -4270,16 +4270,16 @@
       </c>
       <c r="F17" s="29"/>
       <c r="G17" s="42" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="H17" s="42" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
@@ -4300,23 +4300,23 @@
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
       <c r="D18" s="8" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E18" s="29" t="s">
         <v>27</v>
       </c>
       <c r="F18" s="29"/>
       <c r="G18" s="42" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="H18" s="42" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
@@ -4337,23 +4337,23 @@
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
       <c r="D19" s="8" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E19" s="29" t="s">
         <v>27</v>
       </c>
       <c r="F19" s="29"/>
       <c r="G19" s="42" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="H19" s="42" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
@@ -4374,23 +4374,23 @@
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
       <c r="D20" s="8" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E20" s="29" t="s">
         <v>27</v>
       </c>
       <c r="F20" s="29"/>
       <c r="G20" s="42" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="H20" s="42" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
@@ -4411,23 +4411,23 @@
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E21" s="29" t="s">
         <v>27</v>
       </c>
       <c r="F21" s="29"/>
       <c r="G21" s="42" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="H21" s="42" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
@@ -4448,23 +4448,23 @@
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E22" s="29" t="s">
         <v>27</v>
       </c>
       <c r="F22" s="29"/>
       <c r="G22" s="42" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="H22" s="42" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>
@@ -4485,23 +4485,23 @@
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E23" s="29" t="s">
         <v>27</v>
       </c>
       <c r="F23" s="29"/>
       <c r="G23" s="42" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="H23" s="42" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
@@ -4522,23 +4522,23 @@
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E24" s="29" t="s">
         <v>27</v>
       </c>
       <c r="F24" s="29"/>
       <c r="G24" s="42" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="H24" s="42" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K24" s="8"/>
       <c r="L24" s="8"/>
@@ -4566,16 +4566,16 @@
       </c>
       <c r="F25" s="29"/>
       <c r="G25" s="42" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="H25" s="42" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
@@ -4589,30 +4589,30 @@
       <c r="T25" s="76"/>
       <c r="U25" s="77"/>
     </row>
-    <row r="26" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
+    <row r="26" spans="1:21" s="9" customFormat="1">
       <c r="A26" s="8">
         <v>10</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
       <c r="D26" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E26" s="29" t="s">
-        <v>151</v>
+        <v>54</v>
       </c>
       <c r="F26" s="29"/>
       <c r="G26" s="42" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="H26" s="42" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K26" s="8"/>
       <c r="L26" s="8"/>
@@ -4626,30 +4626,30 @@
       <c r="T26" s="76"/>
       <c r="U26" s="77"/>
     </row>
-    <row r="27" spans="1:21" s="9" customFormat="1">
+    <row r="27" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A27" s="8">
         <v>10</v>
       </c>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
       <c r="D27" s="8" t="s">
-        <v>184</v>
+        <v>608</v>
       </c>
       <c r="E27" s="29" t="s">
-        <v>54</v>
+        <v>152</v>
       </c>
       <c r="F27" s="29"/>
       <c r="G27" s="42" t="s">
-        <v>434</v>
+        <v>609</v>
       </c>
       <c r="H27" s="42" t="s">
-        <v>264</v>
+        <v>610</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K27" s="8"/>
       <c r="L27" s="8"/>
@@ -4670,23 +4670,23 @@
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
       <c r="D28" s="8" t="s">
-        <v>613</v>
+        <v>573</v>
       </c>
       <c r="E28" s="29" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F28" s="29"/>
       <c r="G28" s="42" t="s">
-        <v>614</v>
+        <v>432</v>
       </c>
       <c r="H28" s="42" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K28" s="8"/>
       <c r="L28" s="8"/>
@@ -4707,23 +4707,23 @@
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
       <c r="D29" s="8" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="E29" s="29" t="s">
         <v>153</v>
       </c>
       <c r="F29" s="29"/>
       <c r="G29" s="42" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="H29" s="42" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K29" s="8"/>
       <c r="L29" s="8"/>
@@ -4744,24 +4744,22 @@
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
       <c r="D30" s="8" t="s">
-        <v>579</v>
+        <v>116</v>
       </c>
       <c r="E30" s="29" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="F30" s="29"/>
       <c r="G30" s="42" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="H30" s="42" t="s">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="J30" s="8" t="s">
-        <v>249</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="J30" s="8"/>
       <c r="K30" s="8"/>
       <c r="L30" s="8"/>
       <c r="M30" s="8"/>
@@ -4769,10 +4767,10 @@
       <c r="O30" s="8"/>
       <c r="P30" s="8"/>
       <c r="Q30" s="8"/>
-      <c r="R30" s="74"/>
-      <c r="S30" s="75"/>
-      <c r="T30" s="76"/>
-      <c r="U30" s="77"/>
+      <c r="R30" s="67"/>
+      <c r="S30" s="68"/>
+      <c r="T30" s="65"/>
+      <c r="U30" s="66"/>
     </row>
     <row r="31" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A31" s="8">
@@ -4781,20 +4779,20 @@
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
       <c r="D31" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E31" s="29" t="s">
         <v>165</v>
       </c>
       <c r="F31" s="29"/>
       <c r="G31" s="42" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="H31" s="42" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J31" s="8"/>
       <c r="K31" s="8"/>
@@ -4816,20 +4814,20 @@
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8" t="s">
-        <v>117</v>
+        <v>591</v>
       </c>
       <c r="E32" s="29" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="F32" s="29"/>
       <c r="G32" s="42" t="s">
-        <v>462</v>
+        <v>440</v>
       </c>
       <c r="H32" s="42" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
@@ -4851,20 +4849,20 @@
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8" t="s">
-        <v>596</v>
+        <v>113</v>
       </c>
       <c r="E33" s="29" t="s">
         <v>157</v>
       </c>
       <c r="F33" s="29"/>
       <c r="G33" s="42" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="H33" s="42" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
@@ -4886,20 +4884,20 @@
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
       <c r="D34" s="8" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E34" s="29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F34" s="29"/>
       <c r="G34" s="42" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="H34" s="42" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J34" s="8"/>
       <c r="K34" s="8"/>
@@ -4921,20 +4919,20 @@
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
       <c r="D35" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E35" s="29" t="s">
         <v>157</v>
       </c>
       <c r="F35" s="29"/>
       <c r="G35" s="42" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="H35" s="42" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J35" s="8"/>
       <c r="K35" s="8"/>
@@ -4956,20 +4954,20 @@
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
       <c r="D36" s="8" t="s">
-        <v>108</v>
+        <v>577</v>
       </c>
       <c r="E36" s="29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F36" s="29"/>
       <c r="G36" s="42" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="H36" s="42" t="s">
-        <v>612</v>
+        <v>601</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J36" s="8"/>
       <c r="K36" s="8"/>
@@ -4991,20 +4989,20 @@
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
       <c r="D37" s="8" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="E37" s="29" t="s">
         <v>157</v>
       </c>
       <c r="F37" s="29"/>
       <c r="G37" s="42" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="H37" s="42" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J37" s="8"/>
       <c r="K37" s="8"/>
@@ -5026,20 +5024,20 @@
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
       <c r="D38" s="8" t="s">
-        <v>583</v>
+        <v>592</v>
       </c>
       <c r="E38" s="29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F38" s="29"/>
       <c r="G38" s="42" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="H38" s="42" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J38" s="8"/>
       <c r="K38" s="8"/>
@@ -5061,20 +5059,20 @@
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
       <c r="D39" s="8" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="E39" s="29" t="s">
         <v>157</v>
       </c>
       <c r="F39" s="29"/>
       <c r="G39" s="42" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="H39" s="42" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J39" s="8"/>
       <c r="K39" s="8"/>
@@ -5096,20 +5094,20 @@
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
       <c r="D40" s="8" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="E40" s="29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F40" s="29"/>
       <c r="G40" s="42" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="H40" s="42" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J40" s="8"/>
       <c r="K40" s="8"/>
@@ -5131,20 +5129,20 @@
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
       <c r="D41" s="8" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="E41" s="29" t="s">
         <v>157</v>
       </c>
       <c r="F41" s="29"/>
       <c r="G41" s="42" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="H41" s="42" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J41" s="8"/>
       <c r="K41" s="8"/>
@@ -5166,22 +5164,24 @@
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
       <c r="D42" s="8" t="s">
-        <v>600</v>
+        <v>173</v>
       </c>
       <c r="E42" s="29" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F42" s="29"/>
       <c r="G42" s="42" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="H42" s="42" t="s">
-        <v>611</v>
+        <v>265</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="J42" s="8"/>
+        <v>245</v>
+      </c>
+      <c r="J42" s="8" t="s">
+        <v>246</v>
+      </c>
       <c r="K42" s="8"/>
       <c r="L42" s="8"/>
       <c r="M42" s="8"/>
@@ -5189,10 +5189,10 @@
       <c r="O42" s="8"/>
       <c r="P42" s="8"/>
       <c r="Q42" s="8"/>
-      <c r="R42" s="67"/>
-      <c r="S42" s="68"/>
-      <c r="T42" s="65"/>
-      <c r="U42" s="66"/>
+      <c r="R42" s="74"/>
+      <c r="S42" s="75"/>
+      <c r="T42" s="76"/>
+      <c r="U42" s="77"/>
     </row>
     <row r="43" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A43" s="8">
@@ -5201,23 +5201,23 @@
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
       <c r="D43" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E43" s="29" t="s">
         <v>155</v>
       </c>
       <c r="F43" s="29"/>
       <c r="G43" s="42" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="H43" s="42" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K43" s="8"/>
       <c r="L43" s="8"/>
@@ -5238,23 +5238,23 @@
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
       <c r="D44" s="8" t="s">
-        <v>176</v>
+        <v>111</v>
       </c>
       <c r="E44" s="29" t="s">
-        <v>156</v>
+        <v>86</v>
       </c>
       <c r="F44" s="29"/>
       <c r="G44" s="42" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="H44" s="42" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K44" s="8"/>
       <c r="L44" s="8"/>
@@ -5275,23 +5275,23 @@
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
       <c r="D45" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E45" s="29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F45" s="29"/>
       <c r="G45" s="42" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="H45" s="42" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K45" s="8"/>
       <c r="L45" s="8"/>
@@ -5312,23 +5312,23 @@
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
       <c r="D46" s="8" t="s">
-        <v>112</v>
+        <v>225</v>
       </c>
       <c r="E46" s="29" t="s">
-        <v>87</v>
+        <v>231</v>
       </c>
       <c r="F46" s="29"/>
       <c r="G46" s="42" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="H46" s="42" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K46" s="8"/>
       <c r="L46" s="8"/>
@@ -5337,10 +5337,10 @@
       <c r="O46" s="8"/>
       <c r="P46" s="8"/>
       <c r="Q46" s="8"/>
-      <c r="R46" s="74"/>
-      <c r="S46" s="75"/>
-      <c r="T46" s="76"/>
-      <c r="U46" s="77"/>
+      <c r="R46" s="67"/>
+      <c r="S46" s="68"/>
+      <c r="T46" s="65"/>
+      <c r="U46" s="66"/>
     </row>
     <row r="47" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A47" s="8">
@@ -5349,23 +5349,23 @@
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
       <c r="D47" s="8" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E47" s="29" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F47" s="29"/>
       <c r="G47" s="42" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="H47" s="42" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K47" s="8"/>
       <c r="L47" s="8"/>
@@ -5386,23 +5386,23 @@
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
       <c r="D48" s="8" t="s">
-        <v>229</v>
+        <v>114</v>
       </c>
       <c r="E48" s="29" t="s">
-        <v>235</v>
+        <v>158</v>
       </c>
       <c r="F48" s="29"/>
       <c r="G48" s="42" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H48" s="42" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K48" s="8"/>
       <c r="L48" s="8"/>
@@ -5411,10 +5411,10 @@
       <c r="O48" s="8"/>
       <c r="P48" s="8"/>
       <c r="Q48" s="8"/>
-      <c r="R48" s="67"/>
-      <c r="S48" s="68"/>
-      <c r="T48" s="65"/>
-      <c r="U48" s="66"/>
+      <c r="R48" s="74"/>
+      <c r="S48" s="75"/>
+      <c r="T48" s="76"/>
+      <c r="U48" s="77"/>
     </row>
     <row r="49" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A49" s="8">
@@ -5423,23 +5423,23 @@
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
       <c r="D49" s="8" t="s">
-        <v>114</v>
+        <v>175</v>
       </c>
       <c r="E49" s="29" t="s">
         <v>159</v>
       </c>
       <c r="F49" s="29"/>
       <c r="G49" s="42" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="H49" s="42" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K49" s="8"/>
       <c r="L49" s="8"/>
@@ -5460,23 +5460,23 @@
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
       <c r="D50" s="8" t="s">
-        <v>177</v>
+        <v>35</v>
       </c>
       <c r="E50" s="29" t="s">
         <v>160</v>
       </c>
       <c r="F50" s="29"/>
       <c r="G50" s="42" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="H50" s="42" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K50" s="8"/>
       <c r="L50" s="8"/>
@@ -5497,23 +5497,23 @@
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
       <c r="D51" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E51" s="29" t="s">
         <v>161</v>
       </c>
       <c r="F51" s="29"/>
       <c r="G51" s="42" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="H51" s="42" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K51" s="8"/>
       <c r="L51" s="8"/>
@@ -5534,23 +5534,23 @@
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
       <c r="D52" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E52" s="29" t="s">
         <v>162</v>
       </c>
       <c r="F52" s="29"/>
       <c r="G52" s="42" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="H52" s="42" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J52" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K52" s="8"/>
       <c r="L52" s="8"/>
@@ -5571,23 +5571,23 @@
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
       <c r="D53" s="8" t="s">
-        <v>37</v>
+        <v>176</v>
       </c>
       <c r="E53" s="29" t="s">
         <v>163</v>
       </c>
       <c r="F53" s="29"/>
       <c r="G53" s="42" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="H53" s="42" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J53" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K53" s="8"/>
       <c r="L53" s="8"/>
@@ -5611,20 +5611,20 @@
         <v>178</v>
       </c>
       <c r="E54" s="29" t="s">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="F54" s="29"/>
       <c r="G54" s="42" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="H54" s="42" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J54" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K54" s="8"/>
       <c r="L54" s="8"/>
@@ -5645,23 +5645,23 @@
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
       <c r="D55" s="8" t="s">
-        <v>180</v>
+        <v>75</v>
       </c>
       <c r="E55" s="29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F55" s="29"/>
       <c r="G55" s="42" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="H55" s="42" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J55" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K55" s="8"/>
       <c r="L55" s="8"/>
@@ -5682,23 +5682,23 @@
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
       <c r="D56" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E56" s="29" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F56" s="29"/>
       <c r="G56" s="42" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="H56" s="42" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J56" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K56" s="8"/>
       <c r="L56" s="8"/>
@@ -5719,23 +5719,23 @@
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
       <c r="D57" s="8" t="s">
-        <v>76</v>
+        <v>585</v>
       </c>
       <c r="E57" s="29" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="F57" s="29"/>
       <c r="G57" s="42" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="H57" s="42" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J57" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K57" s="8"/>
       <c r="L57" s="8"/>
@@ -5756,23 +5756,23 @@
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
       <c r="D58" s="8" t="s">
-        <v>590</v>
+        <v>613</v>
       </c>
       <c r="E58" s="29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F58" s="29"/>
       <c r="G58" s="42" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="H58" s="42" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J58" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K58" s="8"/>
       <c r="L58" s="8"/>
@@ -5793,23 +5793,23 @@
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
       <c r="D59" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="E59" s="29" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="F59" s="29"/>
       <c r="G59" s="42" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="H59" s="42" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J59" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K59" s="8"/>
       <c r="L59" s="8"/>
@@ -5830,23 +5830,23 @@
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
       <c r="D60" s="8" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="E60" s="29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F60" s="29"/>
       <c r="G60" s="42" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="H60" s="42" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J60" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K60" s="8"/>
       <c r="L60" s="8"/>
@@ -5867,23 +5867,23 @@
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
       <c r="D61" s="8" t="s">
-        <v>620</v>
+        <v>586</v>
       </c>
       <c r="E61" s="29" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="F61" s="29"/>
       <c r="G61" s="42" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="H61" s="42" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J61" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K61" s="8"/>
       <c r="L61" s="8"/>
@@ -5904,23 +5904,23 @@
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
       <c r="D62" s="8" t="s">
-        <v>591</v>
+        <v>77</v>
       </c>
       <c r="E62" s="29" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="F62" s="29"/>
       <c r="G62" s="42" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="H62" s="42" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J62" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K62" s="8"/>
       <c r="L62" s="8"/>
@@ -5941,23 +5941,23 @@
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
       <c r="D63" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E63" s="29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F63" s="29"/>
       <c r="G63" s="42" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="H63" s="42" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J63" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K63" s="8"/>
       <c r="L63" s="8"/>
@@ -5978,23 +5978,23 @@
       <c r="B64" s="8"/>
       <c r="C64" s="8"/>
       <c r="D64" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E64" s="29" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="F64" s="29"/>
       <c r="G64" s="42" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="H64" s="42" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J64" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K64" s="8"/>
       <c r="L64" s="8"/>
@@ -6015,23 +6015,23 @@
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
       <c r="D65" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E65" s="29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F65" s="29"/>
       <c r="G65" s="42" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="H65" s="42" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K65" s="8"/>
       <c r="L65" s="8"/>
@@ -6052,23 +6052,23 @@
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
       <c r="D66" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E66" s="29" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="F66" s="29"/>
       <c r="G66" s="42" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="H66" s="42" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J66" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K66" s="8"/>
       <c r="L66" s="8"/>
@@ -6082,30 +6082,30 @@
       <c r="T66" s="76"/>
       <c r="U66" s="77"/>
     </row>
-    <row r="67" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
+    <row r="67" spans="1:21" s="9" customFormat="1">
       <c r="A67" s="8">
         <v>10</v>
       </c>
       <c r="B67" s="8"/>
       <c r="C67" s="8"/>
       <c r="D67" s="8" t="s">
-        <v>81</v>
+        <v>182</v>
       </c>
       <c r="E67" s="29" t="s">
-        <v>85</v>
+        <v>151</v>
       </c>
       <c r="F67" s="29"/>
       <c r="G67" s="42" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="H67" s="42" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="I67" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J67" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K67" s="8"/>
       <c r="L67" s="8"/>
@@ -6119,30 +6119,30 @@
       <c r="T67" s="76"/>
       <c r="U67" s="77"/>
     </row>
-    <row r="68" spans="1:21" s="9" customFormat="1">
+    <row r="68" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A68" s="8">
         <v>10</v>
       </c>
       <c r="B68" s="8"/>
       <c r="C68" s="8"/>
       <c r="D68" s="8" t="s">
-        <v>185</v>
+        <v>223</v>
       </c>
       <c r="E68" s="29" t="s">
-        <v>152</v>
+        <v>224</v>
       </c>
       <c r="F68" s="29"/>
       <c r="G68" s="42" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="H68" s="42" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J68" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K68" s="8"/>
       <c r="L68" s="8"/>
@@ -6163,23 +6163,23 @@
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
       <c r="D69" s="8" t="s">
-        <v>226</v>
+        <v>192</v>
       </c>
       <c r="E69" s="29" t="s">
-        <v>227</v>
+        <v>185</v>
       </c>
       <c r="F69" s="29"/>
       <c r="G69" s="42" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="H69" s="42" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K69" s="8"/>
       <c r="L69" s="8"/>
@@ -6200,23 +6200,23 @@
       <c r="B70" s="8"/>
       <c r="C70" s="8"/>
       <c r="D70" s="8" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="E70" s="29" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="F70" s="29"/>
       <c r="G70" s="42" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="H70" s="42" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K70" s="8"/>
       <c r="L70" s="8"/>
@@ -6237,23 +6237,23 @@
       <c r="B71" s="8"/>
       <c r="C71" s="8"/>
       <c r="D71" s="8" t="s">
-        <v>181</v>
+        <v>118</v>
       </c>
       <c r="E71" s="29" t="s">
         <v>167</v>
       </c>
       <c r="F71" s="29"/>
       <c r="G71" s="42" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="H71" s="42" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J71" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K71" s="8"/>
       <c r="L71" s="8"/>
@@ -6274,23 +6274,23 @@
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
       <c r="D72" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E72" s="29" t="s">
         <v>168</v>
       </c>
       <c r="F72" s="29"/>
       <c r="G72" s="42" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="H72" s="42" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J72" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K72" s="8"/>
       <c r="L72" s="8"/>
@@ -6311,23 +6311,23 @@
       <c r="B73" s="8"/>
       <c r="C73" s="8"/>
       <c r="D73" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E73" s="29" t="s">
         <v>169</v>
       </c>
       <c r="F73" s="29"/>
       <c r="G73" s="42" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="H73" s="42" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J73" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K73" s="8"/>
       <c r="L73" s="8"/>
@@ -6348,23 +6348,23 @@
       <c r="B74" s="8"/>
       <c r="C74" s="8"/>
       <c r="D74" s="8" t="s">
-        <v>120</v>
+        <v>398</v>
       </c>
       <c r="E74" s="29" t="s">
-        <v>170</v>
+        <v>54</v>
       </c>
       <c r="F74" s="29"/>
       <c r="G74" s="42" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="H74" s="42" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J74" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K74" s="8"/>
       <c r="L74" s="8"/>
@@ -6373,10 +6373,10 @@
       <c r="O74" s="8"/>
       <c r="P74" s="8"/>
       <c r="Q74" s="8"/>
-      <c r="R74" s="74"/>
-      <c r="S74" s="75"/>
-      <c r="T74" s="76"/>
-      <c r="U74" s="77"/>
+      <c r="R74" s="67"/>
+      <c r="S74" s="68"/>
+      <c r="T74" s="65"/>
+      <c r="U74" s="66"/>
     </row>
     <row r="75" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A75" s="8">
@@ -6385,23 +6385,23 @@
       <c r="B75" s="8"/>
       <c r="C75" s="8"/>
       <c r="D75" s="8" t="s">
-        <v>402</v>
+        <v>193</v>
       </c>
       <c r="E75" s="29" t="s">
         <v>54</v>
       </c>
       <c r="F75" s="29"/>
       <c r="G75" s="42" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="H75" s="42" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J75" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K75" s="8"/>
       <c r="L75" s="8"/>
@@ -6422,23 +6422,23 @@
       <c r="B76" s="8"/>
       <c r="C76" s="8"/>
       <c r="D76" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E76" s="29" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="F76" s="29"/>
       <c r="G76" s="42" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="H76" s="42" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J76" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K76" s="8"/>
       <c r="L76" s="8"/>
@@ -6459,23 +6459,23 @@
       <c r="B77" s="8"/>
       <c r="C77" s="8"/>
       <c r="D77" s="8" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E77" s="29" t="s">
         <v>171</v>
       </c>
       <c r="F77" s="29"/>
       <c r="G77" s="42" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="H77" s="42" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J77" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K77" s="8"/>
       <c r="L77" s="8"/>
@@ -6496,23 +6496,23 @@
       <c r="B78" s="8"/>
       <c r="C78" s="8"/>
       <c r="D78" s="8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E78" s="29" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="F78" s="29"/>
       <c r="G78" s="42" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="H78" s="42" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="I78" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J78" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K78" s="8"/>
       <c r="L78" s="8"/>
@@ -6533,23 +6533,23 @@
       <c r="B79" s="8"/>
       <c r="C79" s="8"/>
       <c r="D79" s="8" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E79" s="29" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="F79" s="29"/>
       <c r="G79" s="42" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H79" s="42" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J79" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K79" s="8"/>
       <c r="L79" s="8"/>
@@ -6570,23 +6570,23 @@
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
       <c r="D80" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E80" s="29" t="s">
         <v>171</v>
       </c>
       <c r="F80" s="29"/>
       <c r="G80" s="42" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="H80" s="42" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J80" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K80" s="8"/>
       <c r="L80" s="8"/>
@@ -6607,23 +6607,23 @@
       <c r="B81" s="8"/>
       <c r="C81" s="8"/>
       <c r="D81" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E81" s="29" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="F81" s="29"/>
       <c r="G81" s="42" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="H81" s="42" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J81" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K81" s="8"/>
       <c r="L81" s="8"/>
@@ -6644,23 +6644,23 @@
       <c r="B82" s="8"/>
       <c r="C82" s="8"/>
       <c r="D82" s="8" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E82" s="29" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="F82" s="29"/>
       <c r="G82" s="42" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="H82" s="42" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J82" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K82" s="8"/>
       <c r="L82" s="8"/>
@@ -6681,23 +6681,23 @@
       <c r="B83" s="8"/>
       <c r="C83" s="8"/>
       <c r="D83" s="8" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E83" s="29" t="s">
         <v>171</v>
       </c>
       <c r="F83" s="29"/>
       <c r="G83" s="42" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="H83" s="42" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J83" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K83" s="8"/>
       <c r="L83" s="8"/>
@@ -6718,23 +6718,23 @@
       <c r="B84" s="8"/>
       <c r="C84" s="8"/>
       <c r="D84" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E84" s="29" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="F84" s="29"/>
       <c r="G84" s="42" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="H84" s="42" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="I84" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J84" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K84" s="8"/>
       <c r="L84" s="8"/>
@@ -6755,23 +6755,23 @@
       <c r="B85" s="8"/>
       <c r="C85" s="8"/>
       <c r="D85" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E85" s="29" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="F85" s="29"/>
       <c r="G85" s="42" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="H85" s="42" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J85" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K85" s="8"/>
       <c r="L85" s="8"/>
@@ -6792,23 +6792,23 @@
       <c r="B86" s="8"/>
       <c r="C86" s="8"/>
       <c r="D86" s="8" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E86" s="29" t="s">
         <v>171</v>
       </c>
       <c r="F86" s="29"/>
       <c r="G86" s="42" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="H86" s="42" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="I86" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J86" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K86" s="8"/>
       <c r="L86" s="8"/>
@@ -6829,23 +6829,23 @@
       <c r="B87" s="8"/>
       <c r="C87" s="8"/>
       <c r="D87" s="8" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E87" s="29" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="F87" s="29"/>
       <c r="G87" s="42" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="H87" s="42" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="I87" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J87" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K87" s="8"/>
       <c r="L87" s="8"/>
@@ -6866,23 +6866,23 @@
       <c r="B88" s="8"/>
       <c r="C88" s="8"/>
       <c r="D88" s="8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E88" s="29" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="F88" s="29"/>
       <c r="G88" s="42" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="H88" s="42" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I88" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J88" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K88" s="8"/>
       <c r="L88" s="8"/>
@@ -6903,23 +6903,23 @@
       <c r="B89" s="8"/>
       <c r="C89" s="8"/>
       <c r="D89" s="8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E89" s="29" t="s">
         <v>171</v>
       </c>
       <c r="F89" s="29"/>
       <c r="G89" s="42" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="H89" s="42" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="I89" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J89" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K89" s="8"/>
       <c r="L89" s="8"/>
@@ -6940,23 +6940,23 @@
       <c r="B90" s="8"/>
       <c r="C90" s="8"/>
       <c r="D90" s="8" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E90" s="29" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="F90" s="29"/>
       <c r="G90" s="42" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="H90" s="42" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="I90" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J90" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K90" s="8"/>
       <c r="L90" s="8"/>
@@ -6977,23 +6977,23 @@
       <c r="B91" s="8"/>
       <c r="C91" s="8"/>
       <c r="D91" s="8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E91" s="29" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="F91" s="29"/>
       <c r="G91" s="42" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="H91" s="42" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="I91" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J91" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K91" s="8"/>
       <c r="L91" s="8"/>
@@ -7014,23 +7014,23 @@
       <c r="B92" s="8"/>
       <c r="C92" s="8"/>
       <c r="D92" s="8" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E92" s="29" t="s">
         <v>171</v>
       </c>
       <c r="F92" s="29"/>
       <c r="G92" s="42" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="H92" s="42" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I92" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J92" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K92" s="8"/>
       <c r="L92" s="8"/>
@@ -7051,23 +7051,23 @@
       <c r="B93" s="8"/>
       <c r="C93" s="8"/>
       <c r="D93" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E93" s="29" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="F93" s="29"/>
       <c r="G93" s="42" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="H93" s="42" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J93" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K93" s="8"/>
       <c r="L93" s="8"/>
@@ -7088,23 +7088,23 @@
       <c r="B94" s="8"/>
       <c r="C94" s="8"/>
       <c r="D94" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E94" s="29" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="F94" s="29"/>
       <c r="G94" s="42" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="H94" s="42" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I94" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J94" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K94" s="8"/>
       <c r="L94" s="8"/>
@@ -7125,23 +7125,23 @@
       <c r="B95" s="8"/>
       <c r="C95" s="8"/>
       <c r="D95" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E95" s="29" t="s">
         <v>171</v>
       </c>
       <c r="F95" s="29"/>
       <c r="G95" s="42" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="H95" s="42" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I95" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J95" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K95" s="8"/>
       <c r="L95" s="8"/>
@@ -7162,23 +7162,23 @@
       <c r="B96" s="8"/>
       <c r="C96" s="8"/>
       <c r="D96" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E96" s="29" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="F96" s="29"/>
       <c r="G96" s="42" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="H96" s="42" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I96" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J96" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K96" s="8"/>
       <c r="L96" s="8"/>
@@ -7199,23 +7199,23 @@
       <c r="B97" s="8"/>
       <c r="C97" s="8"/>
       <c r="D97" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E97" s="29" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="F97" s="29"/>
       <c r="G97" s="42" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="H97" s="42" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="I97" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J97" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K97" s="8"/>
       <c r="L97" s="8"/>
@@ -7236,23 +7236,23 @@
       <c r="B98" s="8"/>
       <c r="C98" s="8"/>
       <c r="D98" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E98" s="29" t="s">
         <v>171</v>
       </c>
       <c r="F98" s="29"/>
       <c r="G98" s="42" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="H98" s="42" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="I98" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J98" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K98" s="8"/>
       <c r="L98" s="8"/>
@@ -7273,23 +7273,23 @@
       <c r="B99" s="8"/>
       <c r="C99" s="8"/>
       <c r="D99" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E99" s="29" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="F99" s="29"/>
       <c r="G99" s="42" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="H99" s="42" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I99" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J99" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K99" s="8"/>
       <c r="L99" s="8"/>
@@ -7310,23 +7310,23 @@
       <c r="B100" s="8"/>
       <c r="C100" s="8"/>
       <c r="D100" s="8" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E100" s="29" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="F100" s="29"/>
       <c r="G100" s="42" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="H100" s="42" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="I100" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J100" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K100" s="8"/>
       <c r="L100" s="8"/>
@@ -7347,23 +7347,23 @@
       <c r="B101" s="8"/>
       <c r="C101" s="8"/>
       <c r="D101" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E101" s="29" t="s">
         <v>171</v>
       </c>
       <c r="F101" s="29"/>
       <c r="G101" s="42" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="H101" s="42" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J101" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K101" s="8"/>
       <c r="L101" s="8"/>
@@ -7384,23 +7384,23 @@
       <c r="B102" s="8"/>
       <c r="C102" s="8"/>
       <c r="D102" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E102" s="29" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="F102" s="29"/>
       <c r="G102" s="42" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="H102" s="42" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="I102" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J102" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K102" s="8"/>
       <c r="L102" s="8"/>
@@ -7421,23 +7421,23 @@
       <c r="B103" s="8"/>
       <c r="C103" s="8"/>
       <c r="D103" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E103" s="29" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="F103" s="29"/>
       <c r="G103" s="42" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="H103" s="42" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="I103" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J103" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K103" s="8"/>
       <c r="L103" s="8"/>
@@ -7458,23 +7458,23 @@
       <c r="B104" s="8"/>
       <c r="C104" s="8"/>
       <c r="D104" s="8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E104" s="29" t="s">
         <v>171</v>
       </c>
       <c r="F104" s="29"/>
       <c r="G104" s="42" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="H104" s="42" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I104" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J104" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K104" s="8"/>
       <c r="L104" s="8"/>
@@ -7495,23 +7495,23 @@
       <c r="B105" s="8"/>
       <c r="C105" s="8"/>
       <c r="D105" s="8" t="s">
-        <v>225</v>
+        <v>121</v>
       </c>
       <c r="E105" s="29" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="F105" s="29"/>
       <c r="G105" s="42" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="H105" s="42" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="I105" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J105" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K105" s="8"/>
       <c r="L105" s="8"/>
@@ -7532,23 +7532,23 @@
       <c r="B106" s="8"/>
       <c r="C106" s="8"/>
       <c r="D106" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E106" s="29" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="F106" s="29"/>
       <c r="G106" s="42" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="H106" s="42" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="I106" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J106" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K106" s="8"/>
       <c r="L106" s="8"/>
@@ -7569,23 +7569,23 @@
       <c r="B107" s="8"/>
       <c r="C107" s="8"/>
       <c r="D107" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E107" s="29" t="s">
         <v>171</v>
       </c>
       <c r="F107" s="29"/>
       <c r="G107" s="42" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="H107" s="42" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I107" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J107" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K107" s="8"/>
       <c r="L107" s="8"/>
@@ -7606,23 +7606,23 @@
       <c r="B108" s="8"/>
       <c r="C108" s="8"/>
       <c r="D108" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E108" s="29" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="F108" s="29"/>
       <c r="G108" s="42" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="H108" s="42" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="I108" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J108" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K108" s="8"/>
       <c r="L108" s="8"/>
@@ -7643,23 +7643,23 @@
       <c r="B109" s="8"/>
       <c r="C109" s="8"/>
       <c r="D109" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E109" s="29" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="F109" s="29"/>
       <c r="G109" s="42" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="H109" s="42" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="I109" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J109" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K109" s="8"/>
       <c r="L109" s="8"/>
@@ -7680,23 +7680,23 @@
       <c r="B110" s="8"/>
       <c r="C110" s="8"/>
       <c r="D110" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E110" s="29" t="s">
         <v>171</v>
       </c>
       <c r="F110" s="29"/>
       <c r="G110" s="42" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="H110" s="42" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="I110" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J110" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K110" s="8"/>
       <c r="L110" s="8"/>
@@ -7717,23 +7717,23 @@
       <c r="B111" s="8"/>
       <c r="C111" s="8"/>
       <c r="D111" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E111" s="29" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="F111" s="29"/>
       <c r="G111" s="42" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="H111" s="42" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="I111" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J111" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K111" s="8"/>
       <c r="L111" s="8"/>
@@ -7754,23 +7754,23 @@
       <c r="B112" s="8"/>
       <c r="C112" s="8"/>
       <c r="D112" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E112" s="29" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="F112" s="29"/>
       <c r="G112" s="42" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="H112" s="42" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="I112" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J112" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K112" s="8"/>
       <c r="L112" s="8"/>
@@ -7791,23 +7791,23 @@
       <c r="B113" s="8"/>
       <c r="C113" s="8"/>
       <c r="D113" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E113" s="29" t="s">
         <v>171</v>
       </c>
       <c r="F113" s="29"/>
       <c r="G113" s="42" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="H113" s="42" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J113" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K113" s="8"/>
       <c r="L113" s="8"/>
@@ -7828,23 +7828,23 @@
       <c r="B114" s="8"/>
       <c r="C114" s="8"/>
       <c r="D114" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E114" s="29" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="F114" s="29"/>
       <c r="G114" s="42" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="H114" s="42" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="I114" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J114" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K114" s="8"/>
       <c r="L114" s="8"/>
@@ -7865,23 +7865,23 @@
       <c r="B115" s="8"/>
       <c r="C115" s="8"/>
       <c r="D115" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E115" s="29" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="F115" s="29"/>
       <c r="G115" s="42" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="H115" s="42" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J115" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K115" s="8"/>
       <c r="L115" s="8"/>
@@ -7902,23 +7902,23 @@
       <c r="B116" s="8"/>
       <c r="C116" s="8"/>
       <c r="D116" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E116" s="29" t="s">
         <v>171</v>
       </c>
       <c r="F116" s="29"/>
       <c r="G116" s="42" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="H116" s="42" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="I116" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J116" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K116" s="8"/>
       <c r="L116" s="8"/>
@@ -7939,23 +7939,23 @@
       <c r="B117" s="8"/>
       <c r="C117" s="8"/>
       <c r="D117" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E117" s="29" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="F117" s="29"/>
       <c r="G117" s="42" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="H117" s="42" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J117" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K117" s="8"/>
       <c r="L117" s="8"/>
@@ -7976,23 +7976,23 @@
       <c r="B118" s="8"/>
       <c r="C118" s="8"/>
       <c r="D118" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E118" s="29" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="F118" s="29"/>
       <c r="G118" s="42" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="H118" s="42" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I118" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J118" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K118" s="8"/>
       <c r="L118" s="8"/>
@@ -8013,23 +8013,23 @@
       <c r="B119" s="8"/>
       <c r="C119" s="8"/>
       <c r="D119" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E119" s="29" t="s">
         <v>171</v>
       </c>
       <c r="F119" s="29"/>
       <c r="G119" s="42" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="H119" s="42" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="I119" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J119" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K119" s="8"/>
       <c r="L119" s="8"/>
@@ -8050,23 +8050,23 @@
       <c r="B120" s="8"/>
       <c r="C120" s="8"/>
       <c r="D120" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E120" s="29" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="F120" s="29"/>
       <c r="G120" s="42" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="H120" s="42" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I120" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J120" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K120" s="8"/>
       <c r="L120" s="8"/>
@@ -8087,23 +8087,23 @@
       <c r="B121" s="8"/>
       <c r="C121" s="8"/>
       <c r="D121" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E121" s="29" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="F121" s="29"/>
       <c r="G121" s="42" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="H121" s="42" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="I121" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J121" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K121" s="8"/>
       <c r="L121" s="8"/>
@@ -8124,23 +8124,23 @@
       <c r="B122" s="8"/>
       <c r="C122" s="8"/>
       <c r="D122" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E122" s="29" t="s">
         <v>171</v>
       </c>
       <c r="F122" s="29"/>
       <c r="G122" s="42" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="H122" s="42" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="I122" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J122" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K122" s="8"/>
       <c r="L122" s="8"/>
@@ -8161,23 +8161,23 @@
       <c r="B123" s="8"/>
       <c r="C123" s="8"/>
       <c r="D123" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E123" s="29" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="F123" s="29"/>
       <c r="G123" s="42" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="H123" s="42" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="I123" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J123" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K123" s="8"/>
       <c r="L123" s="8"/>
@@ -8198,23 +8198,23 @@
       <c r="B124" s="8"/>
       <c r="C124" s="8"/>
       <c r="D124" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E124" s="29" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="F124" s="29"/>
       <c r="G124" s="42" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="H124" s="42" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="I124" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J124" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K124" s="8"/>
       <c r="L124" s="8"/>
@@ -8235,23 +8235,23 @@
       <c r="B125" s="8"/>
       <c r="C125" s="8"/>
       <c r="D125" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E125" s="29" t="s">
         <v>171</v>
       </c>
       <c r="F125" s="29"/>
       <c r="G125" s="42" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="H125" s="42" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J125" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K125" s="8"/>
       <c r="L125" s="8"/>
@@ -8272,23 +8272,23 @@
       <c r="B126" s="8"/>
       <c r="C126" s="8"/>
       <c r="D126" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E126" s="29" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="F126" s="29"/>
       <c r="G126" s="42" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="H126" s="42" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="I126" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J126" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K126" s="8"/>
       <c r="L126" s="8"/>
@@ -8309,23 +8309,23 @@
       <c r="B127" s="8"/>
       <c r="C127" s="8"/>
       <c r="D127" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E127" s="29" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="F127" s="29"/>
       <c r="G127" s="42" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="H127" s="42" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="I127" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J127" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K127" s="8"/>
       <c r="L127" s="8"/>
@@ -8346,23 +8346,23 @@
       <c r="B128" s="8"/>
       <c r="C128" s="8"/>
       <c r="D128" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E128" s="29" t="s">
         <v>171</v>
       </c>
       <c r="F128" s="29"/>
       <c r="G128" s="42" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="H128" s="42" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="I128" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J128" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K128" s="8"/>
       <c r="L128" s="8"/>
@@ -8383,23 +8383,23 @@
       <c r="B129" s="8"/>
       <c r="C129" s="8"/>
       <c r="D129" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E129" s="29" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="F129" s="29"/>
       <c r="G129" s="42" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="H129" s="42" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="I129" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J129" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K129" s="8"/>
       <c r="L129" s="8"/>
@@ -8420,23 +8420,23 @@
       <c r="B130" s="8"/>
       <c r="C130" s="8"/>
       <c r="D130" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E130" s="29" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="F130" s="29"/>
       <c r="G130" s="42" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="H130" s="42" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="I130" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J130" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K130" s="8"/>
       <c r="L130" s="8"/>
@@ -8457,23 +8457,23 @@
       <c r="B131" s="8"/>
       <c r="C131" s="8"/>
       <c r="D131" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E131" s="29" t="s">
         <v>171</v>
       </c>
       <c r="F131" s="29"/>
       <c r="G131" s="42" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="H131" s="42" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="I131" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J131" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K131" s="8"/>
       <c r="L131" s="8"/>
@@ -8494,23 +8494,23 @@
       <c r="B132" s="8"/>
       <c r="C132" s="8"/>
       <c r="D132" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E132" s="29" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="F132" s="29"/>
       <c r="G132" s="42" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="H132" s="42" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="I132" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J132" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K132" s="8"/>
       <c r="L132" s="8"/>
@@ -8531,23 +8531,23 @@
       <c r="B133" s="8"/>
       <c r="C133" s="8"/>
       <c r="D133" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E133" s="29" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="F133" s="29"/>
       <c r="G133" s="42" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="H133" s="42" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="I133" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J133" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K133" s="8"/>
       <c r="L133" s="8"/>
@@ -8568,23 +8568,23 @@
       <c r="B134" s="8"/>
       <c r="C134" s="8"/>
       <c r="D134" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E134" s="29" t="s">
         <v>171</v>
       </c>
       <c r="F134" s="29"/>
       <c r="G134" s="42" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="H134" s="42" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="I134" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J134" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K134" s="8"/>
       <c r="L134" s="8"/>
@@ -8605,23 +8605,23 @@
       <c r="B135" s="8"/>
       <c r="C135" s="8"/>
       <c r="D135" s="8" t="s">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="E135" s="29" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="F135" s="29"/>
       <c r="G135" s="42" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="H135" s="42" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="I135" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J135" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K135" s="8"/>
       <c r="L135" s="8"/>
@@ -8642,23 +8642,23 @@
       <c r="B136" s="8"/>
       <c r="C136" s="8"/>
       <c r="D136" s="8" t="s">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="E136" s="29" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="F136" s="29"/>
       <c r="G136" s="42" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="H136" s="42" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="I136" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J136" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K136" s="8"/>
       <c r="L136" s="8"/>
@@ -8679,23 +8679,23 @@
       <c r="B137" s="8"/>
       <c r="C137" s="8"/>
       <c r="D137" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E137" s="29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F137" s="29"/>
       <c r="G137" s="42" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="H137" s="42" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="I137" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J137" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K137" s="8"/>
       <c r="L137" s="8"/>
@@ -8716,23 +8716,23 @@
       <c r="B138" s="8"/>
       <c r="C138" s="8"/>
       <c r="D138" s="8" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="E138" s="29" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="F138" s="29"/>
       <c r="G138" s="42" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="H138" s="42" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="I138" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J138" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K138" s="8"/>
       <c r="L138" s="8"/>
@@ -8741,10 +8741,10 @@
       <c r="O138" s="8"/>
       <c r="P138" s="8"/>
       <c r="Q138" s="8"/>
-      <c r="R138" s="67"/>
-      <c r="S138" s="68"/>
-      <c r="T138" s="65"/>
-      <c r="U138" s="66"/>
+      <c r="R138" s="74"/>
+      <c r="S138" s="75"/>
+      <c r="T138" s="76"/>
+      <c r="U138" s="77"/>
     </row>
     <row r="139" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A139" s="8">
@@ -8753,23 +8753,23 @@
       <c r="B139" s="8"/>
       <c r="C139" s="8"/>
       <c r="D139" s="8" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="E139" s="29" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="F139" s="29"/>
       <c r="G139" s="42" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="H139" s="42" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J139" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K139" s="8"/>
       <c r="L139" s="8"/>
@@ -8778,10 +8778,10 @@
       <c r="O139" s="8"/>
       <c r="P139" s="8"/>
       <c r="Q139" s="8"/>
-      <c r="R139" s="74"/>
-      <c r="S139" s="75"/>
-      <c r="T139" s="76"/>
-      <c r="U139" s="77"/>
+      <c r="R139" s="67"/>
+      <c r="S139" s="68"/>
+      <c r="T139" s="65"/>
+      <c r="U139" s="66"/>
     </row>
     <row r="140" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A140" s="8">
@@ -8790,23 +8790,23 @@
       <c r="B140" s="8"/>
       <c r="C140" s="8"/>
       <c r="D140" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E140" s="29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F140" s="29"/>
       <c r="G140" s="42" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="H140" s="42" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="I140" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J140" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K140" s="8"/>
       <c r="L140" s="8"/>
@@ -8827,23 +8827,23 @@
       <c r="B141" s="8"/>
       <c r="C141" s="8"/>
       <c r="D141" s="8" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="E141" s="29" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="F141" s="29"/>
       <c r="G141" s="42" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="H141" s="42" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="I141" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J141" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K141" s="8"/>
       <c r="L141" s="8"/>
@@ -8852,10 +8852,10 @@
       <c r="O141" s="8"/>
       <c r="P141" s="8"/>
       <c r="Q141" s="8"/>
-      <c r="R141" s="67"/>
-      <c r="S141" s="68"/>
-      <c r="T141" s="65"/>
-      <c r="U141" s="66"/>
+      <c r="R141" s="74"/>
+      <c r="S141" s="75"/>
+      <c r="T141" s="76"/>
+      <c r="U141" s="77"/>
     </row>
     <row r="142" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A142" s="8">
@@ -8864,23 +8864,23 @@
       <c r="B142" s="8"/>
       <c r="C142" s="8"/>
       <c r="D142" s="8" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="E142" s="29" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="F142" s="29"/>
       <c r="G142" s="42" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="H142" s="42" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="I142" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J142" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K142" s="8"/>
       <c r="L142" s="8"/>
@@ -8889,10 +8889,10 @@
       <c r="O142" s="8"/>
       <c r="P142" s="8"/>
       <c r="Q142" s="8"/>
-      <c r="R142" s="74"/>
-      <c r="S142" s="75"/>
-      <c r="T142" s="76"/>
-      <c r="U142" s="77"/>
+      <c r="R142" s="67"/>
+      <c r="S142" s="68"/>
+      <c r="T142" s="65"/>
+      <c r="U142" s="66"/>
     </row>
     <row r="143" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A143" s="8">
@@ -8901,23 +8901,23 @@
       <c r="B143" s="8"/>
       <c r="C143" s="8"/>
       <c r="D143" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E143" s="29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F143" s="29"/>
       <c r="G143" s="42" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="H143" s="42" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="I143" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J143" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K143" s="8"/>
       <c r="L143" s="8"/>
@@ -8938,23 +8938,23 @@
       <c r="B144" s="8"/>
       <c r="C144" s="8"/>
       <c r="D144" s="8" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="E144" s="29" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="F144" s="29"/>
       <c r="G144" s="42" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="H144" s="42" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="I144" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J144" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K144" s="8"/>
       <c r="L144" s="8"/>
@@ -8963,10 +8963,10 @@
       <c r="O144" s="8"/>
       <c r="P144" s="8"/>
       <c r="Q144" s="8"/>
-      <c r="R144" s="67"/>
-      <c r="S144" s="68"/>
-      <c r="T144" s="65"/>
-      <c r="U144" s="66"/>
+      <c r="R144" s="74"/>
+      <c r="S144" s="75"/>
+      <c r="T144" s="76"/>
+      <c r="U144" s="77"/>
     </row>
     <row r="145" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A145" s="8">
@@ -8975,23 +8975,23 @@
       <c r="B145" s="8"/>
       <c r="C145" s="8"/>
       <c r="D145" s="8" t="s">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="E145" s="29" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="F145" s="29"/>
       <c r="G145" s="42" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="H145" s="42" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="I145" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J145" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K145" s="8"/>
       <c r="L145" s="8"/>
@@ -9000,10 +9000,10 @@
       <c r="O145" s="8"/>
       <c r="P145" s="8"/>
       <c r="Q145" s="8"/>
-      <c r="R145" s="74"/>
-      <c r="S145" s="75"/>
-      <c r="T145" s="76"/>
-      <c r="U145" s="77"/>
+      <c r="R145" s="67"/>
+      <c r="S145" s="68"/>
+      <c r="T145" s="65"/>
+      <c r="U145" s="66"/>
     </row>
     <row r="146" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A146" s="8">
@@ -9012,23 +9012,23 @@
       <c r="B146" s="8"/>
       <c r="C146" s="8"/>
       <c r="D146" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E146" s="29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F146" s="29"/>
       <c r="G146" s="42" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="H146" s="42" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="I146" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J146" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K146" s="8"/>
       <c r="L146" s="8"/>
@@ -9049,23 +9049,23 @@
       <c r="B147" s="8"/>
       <c r="C147" s="8"/>
       <c r="D147" s="8" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="E147" s="29" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="F147" s="29"/>
       <c r="G147" s="42" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="H147" s="42" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="I147" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J147" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K147" s="8"/>
       <c r="L147" s="8"/>
@@ -9074,10 +9074,10 @@
       <c r="O147" s="8"/>
       <c r="P147" s="8"/>
       <c r="Q147" s="8"/>
-      <c r="R147" s="67"/>
-      <c r="S147" s="68"/>
-      <c r="T147" s="65"/>
-      <c r="U147" s="66"/>
+      <c r="R147" s="74"/>
+      <c r="S147" s="75"/>
+      <c r="T147" s="76"/>
+      <c r="U147" s="77"/>
     </row>
     <row r="148" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A148" s="8">
@@ -9086,23 +9086,23 @@
       <c r="B148" s="8"/>
       <c r="C148" s="8"/>
       <c r="D148" s="8" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="E148" s="29" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="F148" s="29"/>
       <c r="G148" s="42" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="H148" s="42" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I148" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J148" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K148" s="8"/>
       <c r="L148" s="8"/>
@@ -9111,10 +9111,10 @@
       <c r="O148" s="8"/>
       <c r="P148" s="8"/>
       <c r="Q148" s="8"/>
-      <c r="R148" s="74"/>
-      <c r="S148" s="75"/>
-      <c r="T148" s="76"/>
-      <c r="U148" s="77"/>
+      <c r="R148" s="67"/>
+      <c r="S148" s="68"/>
+      <c r="T148" s="65"/>
+      <c r="U148" s="66"/>
     </row>
     <row r="149" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A149" s="8">
@@ -9123,23 +9123,23 @@
       <c r="B149" s="8"/>
       <c r="C149" s="8"/>
       <c r="D149" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E149" s="29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F149" s="29"/>
       <c r="G149" s="42" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="H149" s="42" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="I149" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J149" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K149" s="8"/>
       <c r="L149" s="8"/>
@@ -9160,23 +9160,23 @@
       <c r="B150" s="8"/>
       <c r="C150" s="8"/>
       <c r="D150" s="8" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="E150" s="29" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="F150" s="29"/>
       <c r="G150" s="42" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="H150" s="42" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="I150" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J150" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K150" s="8"/>
       <c r="L150" s="8"/>
@@ -9185,10 +9185,10 @@
       <c r="O150" s="8"/>
       <c r="P150" s="8"/>
       <c r="Q150" s="8"/>
-      <c r="R150" s="67"/>
-      <c r="S150" s="68"/>
-      <c r="T150" s="65"/>
-      <c r="U150" s="66"/>
+      <c r="R150" s="74"/>
+      <c r="S150" s="75"/>
+      <c r="T150" s="76"/>
+      <c r="U150" s="77"/>
     </row>
     <row r="151" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A151" s="8">
@@ -9197,23 +9197,23 @@
       <c r="B151" s="8"/>
       <c r="C151" s="8"/>
       <c r="D151" s="8" t="s">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="E151" s="29" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="F151" s="29"/>
       <c r="G151" s="42" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="H151" s="42" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I151" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J151" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K151" s="8"/>
       <c r="L151" s="8"/>
@@ -9222,10 +9222,10 @@
       <c r="O151" s="8"/>
       <c r="P151" s="8"/>
       <c r="Q151" s="8"/>
-      <c r="R151" s="74"/>
-      <c r="S151" s="75"/>
-      <c r="T151" s="76"/>
-      <c r="U151" s="77"/>
+      <c r="R151" s="67"/>
+      <c r="S151" s="68"/>
+      <c r="T151" s="65"/>
+      <c r="U151" s="66"/>
     </row>
     <row r="152" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A152" s="8">
@@ -9234,23 +9234,23 @@
       <c r="B152" s="8"/>
       <c r="C152" s="8"/>
       <c r="D152" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E152" s="29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F152" s="29"/>
       <c r="G152" s="42" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="H152" s="42" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I152" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J152" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K152" s="8"/>
       <c r="L152" s="8"/>
@@ -9271,23 +9271,23 @@
       <c r="B153" s="8"/>
       <c r="C153" s="8"/>
       <c r="D153" s="8" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E153" s="29" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="F153" s="29"/>
       <c r="G153" s="42" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="H153" s="42" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="I153" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J153" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K153" s="8"/>
       <c r="L153" s="8"/>
@@ -9296,10 +9296,10 @@
       <c r="O153" s="8"/>
       <c r="P153" s="8"/>
       <c r="Q153" s="8"/>
-      <c r="R153" s="67"/>
-      <c r="S153" s="68"/>
-      <c r="T153" s="65"/>
-      <c r="U153" s="66"/>
+      <c r="R153" s="74"/>
+      <c r="S153" s="75"/>
+      <c r="T153" s="76"/>
+      <c r="U153" s="77"/>
     </row>
     <row r="154" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A154" s="8">
@@ -9308,23 +9308,23 @@
       <c r="B154" s="8"/>
       <c r="C154" s="8"/>
       <c r="D154" s="8" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="E154" s="29" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="F154" s="29"/>
       <c r="G154" s="42" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="H154" s="42" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I154" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J154" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K154" s="8"/>
       <c r="L154" s="8"/>
@@ -9333,10 +9333,10 @@
       <c r="O154" s="8"/>
       <c r="P154" s="8"/>
       <c r="Q154" s="8"/>
-      <c r="R154" s="74"/>
-      <c r="S154" s="75"/>
-      <c r="T154" s="76"/>
-      <c r="U154" s="77"/>
+      <c r="R154" s="67"/>
+      <c r="S154" s="68"/>
+      <c r="T154" s="65"/>
+      <c r="U154" s="66"/>
     </row>
     <row r="155" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A155" s="8">
@@ -9345,23 +9345,23 @@
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
       <c r="D155" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E155" s="29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F155" s="29"/>
       <c r="G155" s="42" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="H155" s="42" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="I155" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J155" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K155" s="8"/>
       <c r="L155" s="8"/>
@@ -9382,23 +9382,23 @@
       <c r="B156" s="8"/>
       <c r="C156" s="8"/>
       <c r="D156" s="8" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="E156" s="29" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="F156" s="29"/>
       <c r="G156" s="42" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="H156" s="42" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="I156" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J156" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K156" s="8"/>
       <c r="L156" s="8"/>
@@ -9407,10 +9407,10 @@
       <c r="O156" s="8"/>
       <c r="P156" s="8"/>
       <c r="Q156" s="8"/>
-      <c r="R156" s="67"/>
-      <c r="S156" s="68"/>
-      <c r="T156" s="65"/>
-      <c r="U156" s="66"/>
+      <c r="R156" s="74"/>
+      <c r="S156" s="75"/>
+      <c r="T156" s="76"/>
+      <c r="U156" s="77"/>
     </row>
     <row r="157" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A157" s="8">
@@ -9419,23 +9419,23 @@
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
       <c r="D157" s="8" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="E157" s="29" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="F157" s="29"/>
       <c r="G157" s="42" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="H157" s="42" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="I157" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J157" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K157" s="8"/>
       <c r="L157" s="8"/>
@@ -9444,10 +9444,10 @@
       <c r="O157" s="8"/>
       <c r="P157" s="8"/>
       <c r="Q157" s="8"/>
-      <c r="R157" s="74"/>
-      <c r="S157" s="75"/>
-      <c r="T157" s="76"/>
-      <c r="U157" s="77"/>
+      <c r="R157" s="67"/>
+      <c r="S157" s="68"/>
+      <c r="T157" s="65"/>
+      <c r="U157" s="66"/>
     </row>
     <row r="158" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A158" s="8">
@@ -9456,23 +9456,23 @@
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
       <c r="D158" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E158" s="29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F158" s="29"/>
       <c r="G158" s="42" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="H158" s="42" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I158" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J158" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K158" s="8"/>
       <c r="L158" s="8"/>
@@ -9493,23 +9493,23 @@
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
       <c r="D159" s="8" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="E159" s="29" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="F159" s="29"/>
       <c r="G159" s="42" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="H159" s="42" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="I159" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J159" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K159" s="8"/>
       <c r="L159" s="8"/>
@@ -9518,10 +9518,10 @@
       <c r="O159" s="8"/>
       <c r="P159" s="8"/>
       <c r="Q159" s="8"/>
-      <c r="R159" s="67"/>
-      <c r="S159" s="68"/>
-      <c r="T159" s="65"/>
-      <c r="U159" s="66"/>
+      <c r="R159" s="74"/>
+      <c r="S159" s="75"/>
+      <c r="T159" s="76"/>
+      <c r="U159" s="77"/>
     </row>
     <row r="160" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A160" s="8">
@@ -9530,23 +9530,23 @@
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
       <c r="D160" s="8" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="E160" s="29" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="F160" s="29"/>
       <c r="G160" s="42" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="H160" s="42" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="I160" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J160" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K160" s="8"/>
       <c r="L160" s="8"/>
@@ -9555,10 +9555,10 @@
       <c r="O160" s="8"/>
       <c r="P160" s="8"/>
       <c r="Q160" s="8"/>
-      <c r="R160" s="74"/>
-      <c r="S160" s="75"/>
-      <c r="T160" s="76"/>
-      <c r="U160" s="77"/>
+      <c r="R160" s="67"/>
+      <c r="S160" s="68"/>
+      <c r="T160" s="65"/>
+      <c r="U160" s="66"/>
     </row>
     <row r="161" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A161" s="8">
@@ -9567,23 +9567,23 @@
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
       <c r="D161" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E161" s="29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F161" s="29"/>
       <c r="G161" s="42" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="H161" s="42" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="I161" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J161" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K161" s="8"/>
       <c r="L161" s="8"/>
@@ -9604,23 +9604,23 @@
       <c r="B162" s="8"/>
       <c r="C162" s="8"/>
       <c r="D162" s="8" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="E162" s="29" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="F162" s="29"/>
       <c r="G162" s="42" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="H162" s="42" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I162" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J162" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K162" s="8"/>
       <c r="L162" s="8"/>
@@ -9629,10 +9629,10 @@
       <c r="O162" s="8"/>
       <c r="P162" s="8"/>
       <c r="Q162" s="8"/>
-      <c r="R162" s="67"/>
-      <c r="S162" s="68"/>
-      <c r="T162" s="65"/>
-      <c r="U162" s="66"/>
+      <c r="R162" s="74"/>
+      <c r="S162" s="75"/>
+      <c r="T162" s="76"/>
+      <c r="U162" s="77"/>
     </row>
     <row r="163" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A163" s="8">
@@ -9641,23 +9641,23 @@
       <c r="B163" s="8"/>
       <c r="C163" s="8"/>
       <c r="D163" s="8" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="E163" s="29" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="F163" s="29"/>
       <c r="G163" s="42" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="H163" s="42" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="I163" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J163" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K163" s="8"/>
       <c r="L163" s="8"/>
@@ -9666,10 +9666,10 @@
       <c r="O163" s="8"/>
       <c r="P163" s="8"/>
       <c r="Q163" s="8"/>
-      <c r="R163" s="74"/>
-      <c r="S163" s="75"/>
-      <c r="T163" s="76"/>
-      <c r="U163" s="77"/>
+      <c r="R163" s="67"/>
+      <c r="S163" s="68"/>
+      <c r="T163" s="65"/>
+      <c r="U163" s="66"/>
     </row>
     <row r="164" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A164" s="8">
@@ -9678,23 +9678,23 @@
       <c r="B164" s="8"/>
       <c r="C164" s="8"/>
       <c r="D164" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E164" s="29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F164" s="29"/>
       <c r="G164" s="42" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="H164" s="42" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I164" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J164" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K164" s="8"/>
       <c r="L164" s="8"/>
@@ -9703,80 +9703,80 @@
       <c r="O164" s="8"/>
       <c r="P164" s="8"/>
       <c r="Q164" s="8"/>
-      <c r="R164" s="67"/>
-      <c r="S164" s="68"/>
-      <c r="T164" s="65"/>
-      <c r="U164" s="66"/>
+      <c r="R164" s="74"/>
+      <c r="S164" s="75"/>
+      <c r="T164" s="76"/>
+      <c r="U164" s="77"/>
     </row>
     <row r="165" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A165" s="8">
-        <v>10</v>
-      </c>
-      <c r="B165" s="8"/>
-      <c r="C165" s="8"/>
-      <c r="D165" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="E165" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="F165" s="29"/>
-      <c r="G165" s="42" t="s">
-        <v>560</v>
-      </c>
-      <c r="H165" s="42" t="s">
-        <v>386</v>
-      </c>
-      <c r="I165" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="J165" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="K165" s="8"/>
-      <c r="L165" s="8"/>
-      <c r="M165" s="8"/>
-      <c r="N165" s="8"/>
-      <c r="O165" s="8"/>
-      <c r="P165" s="8"/>
-      <c r="Q165" s="8"/>
-      <c r="R165" s="74"/>
-      <c r="S165" s="75"/>
-      <c r="T165" s="76"/>
-      <c r="U165" s="77"/>
+      <c r="A165" s="55"/>
+      <c r="U165" s="43"/>
     </row>
     <row r="166" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A166" s="55"/>
-      <c r="U166" s="43"/>
+      <c r="A166" s="8">
+        <v>20</v>
+      </c>
+      <c r="B166" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="C166" s="33"/>
+      <c r="D166" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="E166" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="F166" s="44"/>
+      <c r="G166" s="31"/>
+      <c r="H166" s="31"/>
+      <c r="I166" s="45"/>
+      <c r="J166" s="46"/>
+      <c r="K166" s="46"/>
+      <c r="L166" s="30"/>
+      <c r="M166" s="30"/>
+      <c r="N166" s="30"/>
+      <c r="O166" s="30"/>
+      <c r="P166" s="30"/>
+      <c r="Q166" s="30"/>
+      <c r="R166" s="41"/>
+      <c r="S166" s="40"/>
+      <c r="T166" s="76"/>
+      <c r="U166" s="77"/>
     </row>
     <row r="167" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A167" s="8">
         <v>20</v>
       </c>
-      <c r="B167" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="C167" s="33"/>
-      <c r="D167" s="26" t="s">
-        <v>173</v>
-      </c>
-      <c r="E167" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F167" s="44"/>
-      <c r="G167" s="31"/>
-      <c r="H167" s="31"/>
-      <c r="I167" s="45"/>
-      <c r="J167" s="46"/>
-      <c r="K167" s="46"/>
-      <c r="L167" s="30"/>
-      <c r="M167" s="30"/>
-      <c r="N167" s="30"/>
-      <c r="O167" s="30"/>
-      <c r="P167" s="30"/>
-      <c r="Q167" s="30"/>
-      <c r="R167" s="41"/>
-      <c r="S167" s="40"/>
+      <c r="B167" s="8"/>
+      <c r="C167" s="8"/>
+      <c r="D167" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="E167" s="29" t="s">
+        <v>616</v>
+      </c>
+      <c r="F167" s="29"/>
+      <c r="G167" s="42" t="s">
+        <v>609</v>
+      </c>
+      <c r="H167" s="42" t="s">
+        <v>621</v>
+      </c>
+      <c r="I167" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="J167" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K167" s="8"/>
+      <c r="L167" s="8"/>
+      <c r="M167" s="8"/>
+      <c r="N167" s="8"/>
+      <c r="O167" s="8"/>
+      <c r="P167" s="8"/>
+      <c r="Q167" s="8"/>
+      <c r="R167" s="74"/>
+      <c r="S167" s="75"/>
       <c r="T167" s="76"/>
       <c r="U167" s="77"/>
     </row>
@@ -9787,23 +9787,23 @@
       <c r="B168" s="8"/>
       <c r="C168" s="8"/>
       <c r="D168" s="8" t="s">
-        <v>174</v>
+        <v>573</v>
       </c>
       <c r="E168" s="29" t="s">
-        <v>151</v>
+        <v>617</v>
       </c>
       <c r="F168" s="29"/>
       <c r="G168" s="42" t="s">
-        <v>433</v>
+        <v>619</v>
       </c>
       <c r="H168" s="42" t="s">
-        <v>263</v>
+        <v>611</v>
       </c>
       <c r="I168" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J168" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K168" s="8"/>
       <c r="L168" s="8"/>
@@ -9824,23 +9824,23 @@
       <c r="B169" s="8"/>
       <c r="C169" s="8"/>
       <c r="D169" s="8" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="E169" s="29" t="s">
-        <v>153</v>
+        <v>618</v>
       </c>
       <c r="F169" s="29"/>
       <c r="G169" s="42" t="s">
-        <v>435</v>
+        <v>620</v>
       </c>
       <c r="H169" s="42" t="s">
-        <v>265</v>
+        <v>612</v>
       </c>
       <c r="I169" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J169" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K169" s="8"/>
       <c r="L169" s="8"/>
@@ -9861,23 +9861,23 @@
       <c r="B170" s="8"/>
       <c r="C170" s="8"/>
       <c r="D170" s="8" t="s">
-        <v>579</v>
+        <v>105</v>
       </c>
       <c r="E170" s="29" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F170" s="29"/>
       <c r="G170" s="42" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="H170" s="42" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="I170" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J170" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K170" s="8"/>
       <c r="L170" s="8"/>
@@ -9898,23 +9898,23 @@
       <c r="B171" s="8"/>
       <c r="C171" s="8"/>
       <c r="D171" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E171" s="29" t="s">
         <v>153</v>
       </c>
       <c r="F171" s="29"/>
       <c r="G171" s="42" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="H171" s="42" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="I171" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J171" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K171" s="8"/>
       <c r="L171" s="8"/>
@@ -9935,23 +9935,23 @@
       <c r="B172" s="8"/>
       <c r="C172" s="8"/>
       <c r="D172" s="8" t="s">
-        <v>106</v>
+        <v>575</v>
       </c>
       <c r="E172" s="29" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F172" s="29"/>
       <c r="G172" s="42" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="H172" s="42" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I172" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J172" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K172" s="8"/>
       <c r="L172" s="8"/>
@@ -9972,23 +9972,23 @@
       <c r="B173" s="8"/>
       <c r="C173" s="8"/>
       <c r="D173" s="8" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="E173" s="29" t="s">
         <v>153</v>
       </c>
       <c r="F173" s="29"/>
       <c r="G173" s="42" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="H173" s="42" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I173" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J173" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K173" s="8"/>
       <c r="L173" s="8"/>
@@ -10009,23 +10009,23 @@
       <c r="B174" s="8"/>
       <c r="C174" s="8"/>
       <c r="D174" s="8" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="E174" s="29" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F174" s="29"/>
       <c r="G174" s="42" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="H174" s="42" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="I174" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J174" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K174" s="8"/>
       <c r="L174" s="8"/>
@@ -10046,23 +10046,23 @@
       <c r="B175" s="8"/>
       <c r="C175" s="8"/>
       <c r="D175" s="8" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="E175" s="29" t="s">
         <v>153</v>
       </c>
       <c r="F175" s="29"/>
       <c r="G175" s="42" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="H175" s="42" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I175" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J175" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K175" s="8"/>
       <c r="L175" s="8"/>
@@ -10083,23 +10083,23 @@
       <c r="B176" s="8"/>
       <c r="C176" s="8"/>
       <c r="D176" s="8" t="s">
-        <v>583</v>
+        <v>111</v>
       </c>
       <c r="E176" s="29" t="s">
-        <v>154</v>
+        <v>86</v>
       </c>
       <c r="F176" s="29"/>
       <c r="G176" s="42" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="H176" s="42" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I176" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J176" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K176" s="8"/>
       <c r="L176" s="8"/>
@@ -10120,23 +10120,23 @@
       <c r="B177" s="8"/>
       <c r="C177" s="8"/>
       <c r="D177" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E177" s="29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F177" s="29"/>
       <c r="G177" s="42" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="H177" s="42" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="I177" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J177" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K177" s="8"/>
       <c r="L177" s="8"/>
@@ -10157,23 +10157,23 @@
       <c r="B178" s="8"/>
       <c r="C178" s="8"/>
       <c r="D178" s="8" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E178" s="29" t="s">
-        <v>87</v>
+        <v>154</v>
       </c>
       <c r="F178" s="29"/>
       <c r="G178" s="42" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="H178" s="42" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="I178" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J178" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K178" s="8"/>
       <c r="L178" s="8"/>
@@ -10194,23 +10194,23 @@
       <c r="B179" s="8"/>
       <c r="C179" s="8"/>
       <c r="D179" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E179" s="29" t="s">
         <v>155</v>
       </c>
       <c r="F179" s="29"/>
       <c r="G179" s="42" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="H179" s="42" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I179" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J179" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K179" s="8"/>
       <c r="L179" s="8"/>
@@ -10231,23 +10231,23 @@
       <c r="B180" s="8"/>
       <c r="C180" s="8"/>
       <c r="D180" s="8" t="s">
-        <v>110</v>
+        <v>225</v>
       </c>
       <c r="E180" s="29" t="s">
-        <v>156</v>
+        <v>227</v>
       </c>
       <c r="F180" s="29"/>
       <c r="G180" s="42" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="H180" s="42" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I180" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J180" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K180" s="8"/>
       <c r="L180" s="8"/>
@@ -10256,10 +10256,10 @@
       <c r="O180" s="8"/>
       <c r="P180" s="8"/>
       <c r="Q180" s="8"/>
-      <c r="R180" s="74"/>
-      <c r="S180" s="75"/>
-      <c r="T180" s="76"/>
-      <c r="U180" s="77"/>
+      <c r="R180" s="67"/>
+      <c r="S180" s="68"/>
+      <c r="T180" s="65"/>
+      <c r="U180" s="66"/>
     </row>
     <row r="181" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A181" s="8">
@@ -10268,23 +10268,23 @@
       <c r="B181" s="8"/>
       <c r="C181" s="8"/>
       <c r="D181" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="E181" s="29" t="s">
         <v>228</v>
-      </c>
-      <c r="E181" s="29" t="s">
-        <v>230</v>
       </c>
       <c r="F181" s="29"/>
       <c r="G181" s="42" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="H181" s="42" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="I181" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J181" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K181" s="8"/>
       <c r="L181" s="8"/>
@@ -10304,24 +10304,24 @@
       </c>
       <c r="B182" s="8"/>
       <c r="C182" s="8"/>
-      <c r="D182" s="8" t="s">
-        <v>229</v>
+      <c r="D182" s="73" t="s">
+        <v>585</v>
       </c>
       <c r="E182" s="29" t="s">
-        <v>231</v>
+        <v>49</v>
       </c>
       <c r="F182" s="29"/>
       <c r="G182" s="42" t="s">
-        <v>444</v>
+        <v>587</v>
       </c>
       <c r="H182" s="42" t="s">
-        <v>274</v>
+        <v>589</v>
       </c>
       <c r="I182" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J182" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K182" s="8"/>
       <c r="L182" s="8"/>
@@ -10330,35 +10330,35 @@
       <c r="O182" s="8"/>
       <c r="P182" s="8"/>
       <c r="Q182" s="8"/>
-      <c r="R182" s="67"/>
-      <c r="S182" s="68"/>
-      <c r="T182" s="65"/>
-      <c r="U182" s="66"/>
-    </row>
-    <row r="183" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
+      <c r="R182" s="74"/>
+      <c r="S182" s="75"/>
+      <c r="T182" s="76"/>
+      <c r="U182" s="77"/>
+    </row>
+    <row r="183" spans="1:21" s="9" customFormat="1">
       <c r="A183" s="8">
         <v>20</v>
       </c>
       <c r="B183" s="8"/>
       <c r="C183" s="8"/>
       <c r="D183" s="73" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="E183" s="29" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="F183" s="29"/>
       <c r="G183" s="42" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="H183" s="42" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="I183" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J183" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K183" s="8"/>
       <c r="L183" s="8"/>
@@ -10372,30 +10372,30 @@
       <c r="T183" s="76"/>
       <c r="U183" s="77"/>
     </row>
-    <row r="184" spans="1:21" s="9" customFormat="1">
+    <row r="184" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A184" s="8">
         <v>20</v>
       </c>
       <c r="B184" s="8"/>
       <c r="C184" s="8"/>
       <c r="D184" s="73" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="E184" s="29" t="s">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="F184" s="29"/>
       <c r="G184" s="42" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="H184" s="42" t="s">
-        <v>595</v>
+        <v>582</v>
       </c>
       <c r="I184" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J184" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K184" s="8"/>
       <c r="L184" s="8"/>
@@ -10416,23 +10416,23 @@
       <c r="B185" s="8"/>
       <c r="C185" s="8"/>
       <c r="D185" s="73" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="E185" s="29" t="s">
         <v>27</v>
       </c>
       <c r="F185" s="29"/>
       <c r="G185" s="42" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="H185" s="42" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="I185" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J185" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K185" s="8"/>
       <c r="L185" s="8"/>
@@ -10452,24 +10452,24 @@
       </c>
       <c r="B186" s="8"/>
       <c r="C186" s="8"/>
-      <c r="D186" s="73" t="s">
-        <v>585</v>
+      <c r="D186" s="8" t="s">
+        <v>38</v>
       </c>
       <c r="E186" s="29" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="F186" s="29"/>
       <c r="G186" s="42" t="s">
-        <v>588</v>
+        <v>556</v>
       </c>
       <c r="H186" s="42" t="s">
-        <v>589</v>
+        <v>383</v>
       </c>
       <c r="I186" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J186" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K186" s="8"/>
       <c r="L186" s="8"/>
@@ -10490,23 +10490,23 @@
       <c r="B187" s="8"/>
       <c r="C187" s="8"/>
       <c r="D187" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E187" s="29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F187" s="29"/>
       <c r="G187" s="42" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="H187" s="42" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="I187" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J187" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K187" s="8"/>
       <c r="L187" s="8"/>
@@ -10527,23 +10527,23 @@
       <c r="B188" s="8"/>
       <c r="C188" s="8"/>
       <c r="D188" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E188" s="29" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="F188" s="29"/>
       <c r="G188" s="42" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="H188" s="42" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="I188" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J188" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K188" s="8"/>
       <c r="L188" s="8"/>
@@ -10564,23 +10564,23 @@
       <c r="B189" s="8"/>
       <c r="C189" s="8"/>
       <c r="D189" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E189" s="29" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="F189" s="29"/>
       <c r="G189" s="42" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="H189" s="42" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="I189" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J189" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K189" s="8"/>
       <c r="L189" s="8"/>
@@ -10601,23 +10601,23 @@
       <c r="B190" s="8"/>
       <c r="C190" s="8"/>
       <c r="D190" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E190" s="29" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="F190" s="29"/>
       <c r="G190" s="42" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="H190" s="42" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="I190" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J190" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K190" s="8"/>
       <c r="L190" s="8"/>
@@ -10638,23 +10638,23 @@
       <c r="B191" s="8"/>
       <c r="C191" s="8"/>
       <c r="D191" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E191" s="29" t="s">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="F191" s="29"/>
       <c r="G191" s="42" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="H191" s="42" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="I191" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J191" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K191" s="8"/>
       <c r="L191" s="8"/>
@@ -10675,23 +10675,23 @@
       <c r="B192" s="8"/>
       <c r="C192" s="8"/>
       <c r="D192" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E192" s="29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F192" s="29"/>
       <c r="G192" s="42" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="H192" s="42" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="I192" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J192" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K192" s="8"/>
       <c r="L192" s="8"/>
@@ -10712,23 +10712,23 @@
       <c r="B193" s="8"/>
       <c r="C193" s="8"/>
       <c r="D193" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E193" s="29" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="F193" s="29"/>
       <c r="G193" s="42" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="H193" s="42" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="I193" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J193" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K193" s="8"/>
       <c r="L193" s="8"/>
@@ -10749,23 +10749,23 @@
       <c r="B194" s="8"/>
       <c r="C194" s="8"/>
       <c r="D194" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E194" s="29" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="F194" s="29"/>
       <c r="G194" s="42" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="H194" s="42" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="I194" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J194" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K194" s="8"/>
       <c r="L194" s="8"/>
@@ -10786,23 +10786,23 @@
       <c r="B195" s="8"/>
       <c r="C195" s="8"/>
       <c r="D195" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E195" s="29" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="F195" s="29"/>
       <c r="G195" s="42" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="H195" s="42" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="I195" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J195" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K195" s="8"/>
       <c r="L195" s="8"/>
@@ -10823,23 +10823,23 @@
       <c r="B196" s="8"/>
       <c r="C196" s="8"/>
       <c r="D196" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E196" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F196" s="29"/>
       <c r="G196" s="42" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="H196" s="42" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="I196" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J196" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K196" s="8"/>
       <c r="L196" s="8"/>
@@ -10853,67 +10853,34 @@
       <c r="T196" s="76"/>
       <c r="U196" s="77"/>
     </row>
-    <row r="197" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A197" s="8">
-        <v>20</v>
-      </c>
-      <c r="B197" s="8"/>
-      <c r="C197" s="8"/>
-      <c r="D197" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E197" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="F197" s="29"/>
-      <c r="G197" s="42" t="s">
-        <v>571</v>
-      </c>
-      <c r="H197" s="42" t="s">
-        <v>397</v>
-      </c>
-      <c r="I197" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="J197" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="K197" s="8"/>
-      <c r="L197" s="8"/>
-      <c r="M197" s="8"/>
-      <c r="N197" s="8"/>
-      <c r="O197" s="8"/>
-      <c r="P197" s="8"/>
-      <c r="Q197" s="8"/>
-      <c r="R197" s="74"/>
-      <c r="S197" s="75"/>
-      <c r="T197" s="76"/>
-      <c r="U197" s="77"/>
+    <row r="197" spans="1:21" s="9" customFormat="1">
+      <c r="A197" s="24"/>
+      <c r="B197" s="25"/>
+      <c r="C197" s="25"/>
+      <c r="D197" s="47" t="s">
+        <v>6</v>
+      </c>
+      <c r="E197" s="6"/>
+      <c r="F197" s="6"/>
+      <c r="G197" s="6"/>
+      <c r="H197" s="6"/>
+      <c r="I197" s="6"/>
+      <c r="J197" s="6"/>
+      <c r="K197" s="6"/>
+      <c r="L197" s="6"/>
+      <c r="M197" s="6"/>
+      <c r="N197" s="6"/>
+      <c r="O197" s="6"/>
+      <c r="P197" s="6"/>
+      <c r="Q197" s="6"/>
+      <c r="R197" s="6"/>
+      <c r="S197" s="6"/>
+      <c r="T197" s="6"/>
+      <c r="U197" s="18"/>
     </row>
     <row r="198" spans="1:21" s="9" customFormat="1">
-      <c r="A198" s="24"/>
-      <c r="B198" s="25"/>
-      <c r="C198" s="25"/>
-      <c r="D198" s="47" t="s">
-        <v>6</v>
-      </c>
-      <c r="E198" s="6"/>
-      <c r="F198" s="6"/>
-      <c r="G198" s="6"/>
-      <c r="H198" s="6"/>
-      <c r="I198" s="6"/>
-      <c r="J198" s="6"/>
-      <c r="K198" s="6"/>
-      <c r="L198" s="6"/>
-      <c r="M198" s="6"/>
-      <c r="N198" s="6"/>
-      <c r="O198" s="6"/>
-      <c r="P198" s="6"/>
-      <c r="Q198" s="6"/>
-      <c r="R198" s="6"/>
-      <c r="S198" s="6"/>
-      <c r="T198" s="6"/>
-      <c r="U198" s="18"/>
+      <c r="A198" s="55"/>
+      <c r="U198" s="43"/>
     </row>
     <row r="199" spans="1:21" s="9" customFormat="1">
       <c r="A199" s="55"/>
@@ -10964,209 +10931,203 @@
       <c r="U210" s="43"/>
     </row>
     <row r="211" spans="1:21" s="9" customFormat="1">
-      <c r="A211" s="55"/>
-      <c r="U211" s="43"/>
-    </row>
-    <row r="212" spans="1:21" s="9" customFormat="1">
-      <c r="A212" s="62"/>
-      <c r="B212" s="48"/>
-      <c r="C212" s="48"/>
-      <c r="D212" s="48"/>
-      <c r="E212" s="48"/>
-      <c r="F212" s="48"/>
-      <c r="G212" s="48"/>
-      <c r="H212" s="48"/>
-      <c r="I212" s="48"/>
-      <c r="J212" s="48"/>
-      <c r="K212" s="48"/>
-      <c r="L212" s="48"/>
-      <c r="M212" s="48"/>
-      <c r="N212" s="48"/>
-      <c r="O212" s="48"/>
-      <c r="P212" s="48"/>
-      <c r="Q212" s="48"/>
-      <c r="R212" s="48"/>
-      <c r="S212" s="48"/>
-      <c r="T212" s="48"/>
-      <c r="U212" s="49"/>
+      <c r="A211" s="62"/>
+      <c r="B211" s="48"/>
+      <c r="C211" s="48"/>
+      <c r="D211" s="48"/>
+      <c r="E211" s="48"/>
+      <c r="F211" s="48"/>
+      <c r="G211" s="48"/>
+      <c r="H211" s="48"/>
+      <c r="I211" s="48"/>
+      <c r="J211" s="48"/>
+      <c r="K211" s="48"/>
+      <c r="L211" s="48"/>
+      <c r="M211" s="48"/>
+      <c r="N211" s="48"/>
+      <c r="O211" s="48"/>
+      <c r="P211" s="48"/>
+      <c r="Q211" s="48"/>
+      <c r="R211" s="48"/>
+      <c r="S211" s="48"/>
+      <c r="T211" s="48"/>
+      <c r="U211" s="49"/>
     </row>
   </sheetData>
-  <mergeCells count="175">
-    <mergeCell ref="T30:U30"/>
+  <mergeCells count="173">
+    <mergeCell ref="R186:S186"/>
+    <mergeCell ref="T186:U186"/>
+    <mergeCell ref="T29:U29"/>
     <mergeCell ref="R21:S21"/>
-    <mergeCell ref="T51:U51"/>
+    <mergeCell ref="T50:U50"/>
     <mergeCell ref="R25:S25"/>
-    <mergeCell ref="T148:U148"/>
+    <mergeCell ref="T147:U147"/>
     <mergeCell ref="R20:S20"/>
-    <mergeCell ref="R59:S59"/>
-    <mergeCell ref="T59:U59"/>
+    <mergeCell ref="R58:S58"/>
+    <mergeCell ref="T58:U58"/>
     <mergeCell ref="R22:S22"/>
     <mergeCell ref="T22:U22"/>
     <mergeCell ref="R23:S23"/>
     <mergeCell ref="T23:U23"/>
-    <mergeCell ref="T49:U49"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="T48:U48"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="T27:U27"/>
+    <mergeCell ref="R68:S68"/>
+    <mergeCell ref="T68:U68"/>
+    <mergeCell ref="T190:U190"/>
+    <mergeCell ref="R191:S191"/>
+    <mergeCell ref="T191:U191"/>
+    <mergeCell ref="R187:S187"/>
+    <mergeCell ref="T187:U187"/>
     <mergeCell ref="R194:S194"/>
     <mergeCell ref="T194:U194"/>
     <mergeCell ref="R193:S193"/>
     <mergeCell ref="T193:U193"/>
-    <mergeCell ref="R190:S190"/>
-    <mergeCell ref="T190:U190"/>
+    <mergeCell ref="R192:S192"/>
+    <mergeCell ref="T192:U192"/>
     <mergeCell ref="R189:S189"/>
     <mergeCell ref="T189:U189"/>
-    <mergeCell ref="R187:S187"/>
-    <mergeCell ref="T187:U187"/>
-    <mergeCell ref="R196:S196"/>
-    <mergeCell ref="T196:U196"/>
-    <mergeCell ref="R191:S191"/>
-    <mergeCell ref="T191:U191"/>
-    <mergeCell ref="R192:S192"/>
-    <mergeCell ref="T192:U192"/>
     <mergeCell ref="R188:S188"/>
     <mergeCell ref="T188:U188"/>
-    <mergeCell ref="R195:S195"/>
-    <mergeCell ref="T195:U195"/>
     <mergeCell ref="T8:U8"/>
-    <mergeCell ref="T70:U70"/>
+    <mergeCell ref="T69:U69"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="R73:S73"/>
+    <mergeCell ref="T73:U73"/>
+    <mergeCell ref="T60:U60"/>
+    <mergeCell ref="T56:U56"/>
+    <mergeCell ref="R57:S57"/>
+    <mergeCell ref="T57:U57"/>
+    <mergeCell ref="T43:U43"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="T44:U44"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="T52:U52"/>
     <mergeCell ref="R29:S29"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="T74:U74"/>
-    <mergeCell ref="T61:U61"/>
-    <mergeCell ref="T57:U57"/>
-    <mergeCell ref="R58:S58"/>
-    <mergeCell ref="T58:U58"/>
-    <mergeCell ref="T44:U44"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="T45:U45"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="R53:S53"/>
-    <mergeCell ref="T53:U53"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="R50:S50"/>
     <mergeCell ref="R15:S15"/>
     <mergeCell ref="T25:U25"/>
-    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="R26:S26"/>
     <mergeCell ref="T21:U21"/>
-    <mergeCell ref="T72:U72"/>
+    <mergeCell ref="T71:U71"/>
     <mergeCell ref="R13:S13"/>
     <mergeCell ref="T15:U15"/>
-    <mergeCell ref="R151:S151"/>
-    <mergeCell ref="T50:U50"/>
-    <mergeCell ref="T68:U68"/>
-    <mergeCell ref="T27:U27"/>
+    <mergeCell ref="R150:S150"/>
+    <mergeCell ref="T49:U49"/>
+    <mergeCell ref="T67:U67"/>
+    <mergeCell ref="T26:U26"/>
     <mergeCell ref="T9:U9"/>
-    <mergeCell ref="R54:S54"/>
+    <mergeCell ref="R53:S53"/>
     <mergeCell ref="T11:U11"/>
-    <mergeCell ref="T54:U54"/>
+    <mergeCell ref="T53:U53"/>
     <mergeCell ref="T20:U20"/>
     <mergeCell ref="R9:S9"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="T26:U26"/>
     <mergeCell ref="R16:S16"/>
     <mergeCell ref="T16:U16"/>
     <mergeCell ref="R17:S17"/>
     <mergeCell ref="T17:U17"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="T46:U46"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="T43:U43"/>
-    <mergeCell ref="T52:U52"/>
-    <mergeCell ref="R197:S197"/>
-    <mergeCell ref="T197:U197"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="T45:U45"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="T42:U42"/>
+    <mergeCell ref="T51:U51"/>
+    <mergeCell ref="R60:S60"/>
+    <mergeCell ref="T66:U66"/>
+    <mergeCell ref="R147:S147"/>
+    <mergeCell ref="R196:S196"/>
+    <mergeCell ref="T196:U196"/>
+    <mergeCell ref="T172:U172"/>
+    <mergeCell ref="R172:S172"/>
+    <mergeCell ref="R173:S173"/>
     <mergeCell ref="T173:U173"/>
-    <mergeCell ref="R173:S173"/>
+    <mergeCell ref="R176:S176"/>
+    <mergeCell ref="R178:S178"/>
+    <mergeCell ref="T178:U178"/>
+    <mergeCell ref="T176:U176"/>
+    <mergeCell ref="R177:S177"/>
+    <mergeCell ref="T177:U177"/>
+    <mergeCell ref="T182:U182"/>
+    <mergeCell ref="R179:S179"/>
+    <mergeCell ref="T179:U179"/>
+    <mergeCell ref="R185:S185"/>
+    <mergeCell ref="T185:U185"/>
+    <mergeCell ref="R183:S183"/>
+    <mergeCell ref="T183:U183"/>
+    <mergeCell ref="R195:S195"/>
+    <mergeCell ref="T195:U195"/>
+    <mergeCell ref="R190:S190"/>
+    <mergeCell ref="R164:S164"/>
+    <mergeCell ref="T164:U164"/>
+    <mergeCell ref="R144:S144"/>
+    <mergeCell ref="T150:U150"/>
+    <mergeCell ref="R153:S153"/>
+    <mergeCell ref="T144:U144"/>
+    <mergeCell ref="R168:S168"/>
+    <mergeCell ref="T168:U168"/>
+    <mergeCell ref="R182:S182"/>
+    <mergeCell ref="R170:S170"/>
+    <mergeCell ref="T170:U170"/>
+    <mergeCell ref="R171:S171"/>
+    <mergeCell ref="T171:U171"/>
     <mergeCell ref="R174:S174"/>
     <mergeCell ref="T174:U174"/>
-    <mergeCell ref="R177:S177"/>
-    <mergeCell ref="R179:S179"/>
-    <mergeCell ref="T179:U179"/>
-    <mergeCell ref="T177:U177"/>
-    <mergeCell ref="R178:S178"/>
-    <mergeCell ref="T178:U178"/>
-    <mergeCell ref="T183:U183"/>
-    <mergeCell ref="R180:S180"/>
-    <mergeCell ref="T180:U180"/>
-    <mergeCell ref="R61:S61"/>
-    <mergeCell ref="R69:S69"/>
-    <mergeCell ref="T69:U69"/>
-    <mergeCell ref="R157:S157"/>
-    <mergeCell ref="T157:U157"/>
+    <mergeCell ref="R175:S175"/>
+    <mergeCell ref="T175:U175"/>
+    <mergeCell ref="T153:U153"/>
+    <mergeCell ref="R156:S156"/>
+    <mergeCell ref="T156:U156"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="T162:U162"/>
+    <mergeCell ref="R162:S162"/>
+    <mergeCell ref="R159:S159"/>
+    <mergeCell ref="T159:U159"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="T24:U24"/>
+    <mergeCell ref="R141:S141"/>
+    <mergeCell ref="R67:S67"/>
+    <mergeCell ref="T141:U141"/>
     <mergeCell ref="R71:S71"/>
-    <mergeCell ref="T71:U71"/>
+    <mergeCell ref="T138:U138"/>
+    <mergeCell ref="R62:S62"/>
+    <mergeCell ref="R70:S70"/>
+    <mergeCell ref="T70:U70"/>
+    <mergeCell ref="T62:U62"/>
+    <mergeCell ref="R63:S63"/>
     <mergeCell ref="T63:U63"/>
     <mergeCell ref="R64:S64"/>
     <mergeCell ref="T64:U64"/>
     <mergeCell ref="R65:S65"/>
     <mergeCell ref="T65:U65"/>
     <mergeCell ref="R66:S66"/>
-    <mergeCell ref="T66:U66"/>
-    <mergeCell ref="R67:S67"/>
-    <mergeCell ref="T67:U67"/>
-    <mergeCell ref="R148:S148"/>
-    <mergeCell ref="R165:S165"/>
-    <mergeCell ref="T165:U165"/>
-    <mergeCell ref="R145:S145"/>
-    <mergeCell ref="T151:U151"/>
-    <mergeCell ref="R154:S154"/>
-    <mergeCell ref="T145:U145"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="R184:S184"/>
+    <mergeCell ref="T184:U184"/>
     <mergeCell ref="R169:S169"/>
     <mergeCell ref="T169:U169"/>
-    <mergeCell ref="R183:S183"/>
-    <mergeCell ref="R171:S171"/>
-    <mergeCell ref="T171:U171"/>
-    <mergeCell ref="R172:S172"/>
-    <mergeCell ref="T172:U172"/>
-    <mergeCell ref="R175:S175"/>
-    <mergeCell ref="T175:U175"/>
-    <mergeCell ref="R176:S176"/>
-    <mergeCell ref="T176:U176"/>
-    <mergeCell ref="T154:U154"/>
-    <mergeCell ref="R186:S186"/>
-    <mergeCell ref="T186:U186"/>
-    <mergeCell ref="R184:S184"/>
-    <mergeCell ref="T184:U184"/>
+    <mergeCell ref="R69:S69"/>
+    <mergeCell ref="R54:S54"/>
+    <mergeCell ref="T54:U54"/>
+    <mergeCell ref="R55:S55"/>
+    <mergeCell ref="T55:U55"/>
+    <mergeCell ref="R56:S56"/>
+    <mergeCell ref="T59:U59"/>
+    <mergeCell ref="R59:S59"/>
+    <mergeCell ref="R61:S61"/>
+    <mergeCell ref="T61:U61"/>
+    <mergeCell ref="T72:U72"/>
+    <mergeCell ref="R138:S138"/>
     <mergeCell ref="T13:U13"/>
     <mergeCell ref="R14:S14"/>
     <mergeCell ref="T14:U14"/>
+    <mergeCell ref="T166:U166"/>
+    <mergeCell ref="R167:S167"/>
     <mergeCell ref="T167:U167"/>
-    <mergeCell ref="R168:S168"/>
-    <mergeCell ref="T168:U168"/>
-    <mergeCell ref="R73:S73"/>
-    <mergeCell ref="T163:U163"/>
-    <mergeCell ref="R163:S163"/>
-    <mergeCell ref="R160:S160"/>
-    <mergeCell ref="T160:U160"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="T24:U24"/>
-    <mergeCell ref="R142:S142"/>
-    <mergeCell ref="R68:S68"/>
-    <mergeCell ref="T142:U142"/>
-    <mergeCell ref="R72:S72"/>
-    <mergeCell ref="T139:U139"/>
-    <mergeCell ref="R63:S63"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="T12:U12"/>
-    <mergeCell ref="R185:S185"/>
-    <mergeCell ref="T185:U185"/>
-    <mergeCell ref="R170:S170"/>
-    <mergeCell ref="T170:U170"/>
-    <mergeCell ref="R70:S70"/>
-    <mergeCell ref="R55:S55"/>
-    <mergeCell ref="T55:U55"/>
-    <mergeCell ref="R56:S56"/>
-    <mergeCell ref="T56:U56"/>
-    <mergeCell ref="R57:S57"/>
-    <mergeCell ref="T60:U60"/>
-    <mergeCell ref="R60:S60"/>
-    <mergeCell ref="R62:S62"/>
-    <mergeCell ref="T62:U62"/>
-    <mergeCell ref="T73:U73"/>
-    <mergeCell ref="R139:S139"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.47244094488188981" right="0.43307086614173229" top="0.55118110236220474" bottom="0.59055118110236227" header="0.55118110236220474" footer="0.11811023622047245"/>
@@ -11572,7 +11533,7 @@
       <c r="M5" s="106"/>
       <c r="N5" s="107"/>
       <c r="O5" s="112" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="P5" s="113"/>
       <c r="Q5" s="113"/>
@@ -11602,7 +11563,7 @@
       <c r="AO5" s="113"/>
       <c r="AP5" s="114"/>
       <c r="AQ5" s="115" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="AR5" s="116"/>
       <c r="AS5" s="116"/>

--- a/development/MS/spec/MSBB/Logic/MSBBLA0010_SlsSchdSrch.xlsx
+++ b/development/MS/spec/MSBB/Logic/MSBBLA0010_SlsSchdSrch.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\PJ\TK\dev\development\MS\spec\MSBB\Logic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32FBCFA7-7D7E-459E-8C90-F531A21FAB34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65E6AA2D-0E29-4316-8ACE-AE5FB2D517FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="794" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1230" uniqueCount="644">
   <si>
     <t>*</t>
   </si>
@@ -2052,24 +2052,12 @@
     <t>deal_nm</t>
   </si>
   <si>
-    <t>bill_cst_cd</t>
-  </si>
-  <si>
-    <t>bill_cst_nm</t>
-  </si>
-  <si>
     <t>sls_dpt_cd</t>
   </si>
   <si>
     <t>sls_dpt_nm</t>
   </si>
   <si>
-    <t>order_dlv_dt</t>
-  </si>
-  <si>
-    <t>pst_inst_sls_dt</t>
-  </si>
-  <si>
     <t>Order delivery date</t>
   </si>
   <si>
@@ -2191,6 +2179,84 @@
   </si>
   <si>
     <t>ＺＯＨＯ販売予定ＮＯ</t>
+  </si>
+  <si>
+    <t>bcst_cd</t>
+  </si>
+  <si>
+    <t>bcst_nm</t>
+  </si>
+  <si>
+    <t>Billing customer cd.</t>
+  </si>
+  <si>
+    <t>Billing customer name</t>
+  </si>
+  <si>
+    <t>qty</t>
+  </si>
+  <si>
+    <t>金額</t>
+  </si>
+  <si>
+    <t>数量</t>
+  </si>
+  <si>
+    <t>#MA.MONEY</t>
+  </si>
+  <si>
+    <t>#MA.QTY</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Currency cd.</t>
+  </si>
+  <si>
+    <t>外貨ＣＤ</t>
+  </si>
+  <si>
+    <t>cur_cd</t>
+  </si>
+  <si>
+    <t>#MA.CUR_CD</t>
+  </si>
+  <si>
+    <t>prd_amt</t>
+  </si>
+  <si>
+    <t>prd_qty</t>
+  </si>
+  <si>
+    <t>upri</t>
+  </si>
+  <si>
+    <t>単価</t>
+  </si>
+  <si>
+    <t>Unit price</t>
+  </si>
+  <si>
+    <t>品目CD</t>
+  </si>
+  <si>
+    <t>prod_itm_cd</t>
+  </si>
+  <si>
+    <t>prod_itm_nm</t>
+  </si>
+  <si>
+    <t>ord_dlv_dt</t>
+  </si>
+  <si>
+    <t>post_inst_sls_dt</t>
+  </si>
+  <si>
+    <t>品名</t>
   </si>
 </sst>
 </file>
@@ -3621,7 +3687,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U211"/>
+  <dimension ref="A1:U218"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4.875" style="4" customWidth="1"/>
@@ -4633,17 +4699,17 @@
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
       <c r="D27" s="8" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="E27" s="29" t="s">
         <v>152</v>
       </c>
       <c r="F27" s="29"/>
       <c r="G27" s="42" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="H27" s="42" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="I27" s="8" t="s">
         <v>245</v>
@@ -4680,7 +4746,7 @@
         <v>432</v>
       </c>
       <c r="H28" s="42" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="I28" s="8" t="s">
         <v>245</v>
@@ -4717,7 +4783,7 @@
         <v>433</v>
       </c>
       <c r="H29" s="42" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="I29" s="8" t="s">
         <v>245</v>
@@ -4754,7 +4820,7 @@
         <v>456</v>
       </c>
       <c r="H30" s="42" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="I30" s="8" t="s">
         <v>245</v>
@@ -4789,7 +4855,7 @@
         <v>457</v>
       </c>
       <c r="H31" s="42" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="I31" s="8" t="s">
         <v>245</v>
@@ -4814,7 +4880,7 @@
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="E32" s="29" t="s">
         <v>156</v>
@@ -4824,7 +4890,7 @@
         <v>440</v>
       </c>
       <c r="H32" s="42" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="I32" s="8" t="s">
         <v>245</v>
@@ -4859,7 +4925,7 @@
         <v>441</v>
       </c>
       <c r="H33" s="42" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="I33" s="8" t="s">
         <v>245</v>
@@ -4894,7 +4960,7 @@
         <v>440</v>
       </c>
       <c r="H34" s="42" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="I34" s="8" t="s">
         <v>245</v>
@@ -4929,7 +4995,7 @@
         <v>441</v>
       </c>
       <c r="H35" s="42" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="I35" s="8" t="s">
         <v>245</v>
@@ -4954,7 +5020,7 @@
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
       <c r="D36" s="8" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E36" s="29" t="s">
         <v>156</v>
@@ -4964,7 +5030,7 @@
         <v>440</v>
       </c>
       <c r="H36" s="42" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="I36" s="8" t="s">
         <v>245</v>
@@ -4989,7 +5055,7 @@
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
       <c r="D37" s="8" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E37" s="29" t="s">
         <v>157</v>
@@ -4999,7 +5065,7 @@
         <v>441</v>
       </c>
       <c r="H37" s="42" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="I37" s="8" t="s">
         <v>245</v>
@@ -5024,7 +5090,7 @@
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
       <c r="D38" s="8" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="E38" s="29" t="s">
         <v>156</v>
@@ -5034,7 +5100,7 @@
         <v>440</v>
       </c>
       <c r="H38" s="42" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="I38" s="8" t="s">
         <v>245</v>
@@ -5059,7 +5125,7 @@
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
       <c r="D39" s="8" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="E39" s="29" t="s">
         <v>157</v>
@@ -5069,7 +5135,7 @@
         <v>441</v>
       </c>
       <c r="H39" s="42" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="I39" s="8" t="s">
         <v>245</v>
@@ -5094,7 +5160,7 @@
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
       <c r="D40" s="8" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="E40" s="29" t="s">
         <v>156</v>
@@ -5104,7 +5170,7 @@
         <v>440</v>
       </c>
       <c r="H40" s="42" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="I40" s="8" t="s">
         <v>245</v>
@@ -5129,7 +5195,7 @@
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
       <c r="D41" s="8" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="E41" s="29" t="s">
         <v>157</v>
@@ -5139,7 +5205,7 @@
         <v>441</v>
       </c>
       <c r="H41" s="42" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="I41" s="8" t="s">
         <v>245</v>
@@ -5719,7 +5785,7 @@
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
       <c r="D57" s="8" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="E57" s="29" t="s">
         <v>49</v>
@@ -5756,7 +5822,7 @@
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
       <c r="D58" s="8" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="E58" s="29" t="s">
         <v>50</v>
@@ -5793,7 +5859,7 @@
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
       <c r="D59" s="8" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="E59" s="29" t="s">
         <v>28</v>
@@ -5830,7 +5896,7 @@
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
       <c r="D60" s="8" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="E60" s="29" t="s">
         <v>29</v>
@@ -5867,7 +5933,7 @@
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
       <c r="D61" s="8" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="E61" s="29" t="s">
         <v>85</v>
@@ -9750,17 +9816,17 @@
       <c r="B167" s="8"/>
       <c r="C167" s="8"/>
       <c r="D167" s="8" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="E167" s="29" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="F167" s="29"/>
       <c r="G167" s="42" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="H167" s="42" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="I167" s="8" t="s">
         <v>246</v>
@@ -9790,14 +9856,14 @@
         <v>573</v>
       </c>
       <c r="E168" s="29" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="F168" s="29"/>
       <c r="G168" s="42" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="H168" s="42" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="I168" s="8" t="s">
         <v>246</v>
@@ -9827,14 +9893,14 @@
         <v>574</v>
       </c>
       <c r="E169" s="29" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="F169" s="29"/>
       <c r="G169" s="42" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="H169" s="42" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="I169" s="8" t="s">
         <v>246</v>
@@ -9935,17 +10001,17 @@
       <c r="B172" s="8"/>
       <c r="C172" s="8"/>
       <c r="D172" s="8" t="s">
-        <v>575</v>
+        <v>618</v>
       </c>
       <c r="E172" s="29" t="s">
         <v>152</v>
       </c>
       <c r="F172" s="29"/>
       <c r="G172" s="42" t="s">
-        <v>432</v>
+        <v>620</v>
       </c>
       <c r="H172" s="42" t="s">
-        <v>263</v>
+        <v>594</v>
       </c>
       <c r="I172" s="8" t="s">
         <v>246</v>
@@ -9972,17 +10038,17 @@
       <c r="B173" s="8"/>
       <c r="C173" s="8"/>
       <c r="D173" s="8" t="s">
-        <v>576</v>
+        <v>619</v>
       </c>
       <c r="E173" s="29" t="s">
         <v>153</v>
       </c>
       <c r="F173" s="29"/>
       <c r="G173" s="42" t="s">
-        <v>433</v>
+        <v>621</v>
       </c>
       <c r="H173" s="42" t="s">
-        <v>264</v>
+        <v>595</v>
       </c>
       <c r="I173" s="8" t="s">
         <v>246</v>
@@ -10009,7 +10075,7 @@
       <c r="B174" s="8"/>
       <c r="C174" s="8"/>
       <c r="D174" s="8" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E174" s="29" t="s">
         <v>152</v>
@@ -10046,7 +10112,7 @@
       <c r="B175" s="8"/>
       <c r="C175" s="8"/>
       <c r="D175" s="8" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E175" s="29" t="s">
         <v>153</v>
@@ -10305,17 +10371,17 @@
       <c r="B182" s="8"/>
       <c r="C182" s="8"/>
       <c r="D182" s="73" t="s">
-        <v>585</v>
+        <v>639</v>
       </c>
       <c r="E182" s="29" t="s">
         <v>49</v>
       </c>
       <c r="F182" s="29"/>
       <c r="G182" s="42" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="H182" s="42" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="I182" s="8" t="s">
         <v>246</v>
@@ -10342,17 +10408,17 @@
       <c r="B183" s="8"/>
       <c r="C183" s="8"/>
       <c r="D183" s="73" t="s">
-        <v>586</v>
+        <v>640</v>
       </c>
       <c r="E183" s="29" t="s">
         <v>85</v>
       </c>
       <c r="F183" s="29"/>
       <c r="G183" s="42" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="H183" s="42" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="I183" s="8" t="s">
         <v>246</v>
@@ -10379,17 +10445,17 @@
       <c r="B184" s="8"/>
       <c r="C184" s="8"/>
       <c r="D184" s="73" t="s">
-        <v>579</v>
+        <v>641</v>
       </c>
       <c r="E184" s="29" t="s">
         <v>27</v>
       </c>
       <c r="F184" s="29"/>
       <c r="G184" s="42" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="H184" s="42" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="I184" s="8" t="s">
         <v>246</v>
@@ -10416,17 +10482,17 @@
       <c r="B185" s="8"/>
       <c r="C185" s="8"/>
       <c r="D185" s="73" t="s">
-        <v>580</v>
+        <v>642</v>
       </c>
       <c r="E185" s="29" t="s">
         <v>27</v>
       </c>
       <c r="F185" s="29"/>
       <c r="G185" s="42" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="H185" s="42" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="I185" s="8" t="s">
         <v>246</v>
@@ -10452,18 +10518,18 @@
       </c>
       <c r="B186" s="8"/>
       <c r="C186" s="8"/>
-      <c r="D186" s="8" t="s">
-        <v>38</v>
+      <c r="D186" s="73" t="s">
+        <v>633</v>
       </c>
       <c r="E186" s="29" t="s">
-        <v>100</v>
+        <v>625</v>
       </c>
       <c r="F186" s="29"/>
       <c r="G186" s="42" t="s">
-        <v>556</v>
+        <v>627</v>
       </c>
       <c r="H186" s="42" t="s">
-        <v>383</v>
+        <v>623</v>
       </c>
       <c r="I186" s="8" t="s">
         <v>246</v>
@@ -10478,10 +10544,10 @@
       <c r="O186" s="8"/>
       <c r="P186" s="8"/>
       <c r="Q186" s="8"/>
-      <c r="R186" s="74"/>
-      <c r="S186" s="75"/>
-      <c r="T186" s="76"/>
-      <c r="U186" s="77"/>
+      <c r="R186" s="67"/>
+      <c r="S186" s="68"/>
+      <c r="T186" s="65"/>
+      <c r="U186" s="66"/>
     </row>
     <row r="187" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A187" s="8">
@@ -10489,18 +10555,18 @@
       </c>
       <c r="B187" s="8"/>
       <c r="C187" s="8"/>
-      <c r="D187" s="8" t="s">
-        <v>39</v>
+      <c r="D187" s="73" t="s">
+        <v>634</v>
       </c>
       <c r="E187" s="29" t="s">
-        <v>101</v>
+        <v>626</v>
       </c>
       <c r="F187" s="29"/>
       <c r="G187" s="42" t="s">
-        <v>557</v>
+        <v>628</v>
       </c>
       <c r="H187" s="42" t="s">
-        <v>384</v>
+        <v>624</v>
       </c>
       <c r="I187" s="8" t="s">
         <v>246</v>
@@ -10515,10 +10581,10 @@
       <c r="O187" s="8"/>
       <c r="P187" s="8"/>
       <c r="Q187" s="8"/>
-      <c r="R187" s="74"/>
-      <c r="S187" s="75"/>
-      <c r="T187" s="76"/>
-      <c r="U187" s="77"/>
+      <c r="R187" s="67"/>
+      <c r="S187" s="68"/>
+      <c r="T187" s="65"/>
+      <c r="U187" s="66"/>
     </row>
     <row r="188" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A188" s="8">
@@ -10526,18 +10592,18 @@
       </c>
       <c r="B188" s="8"/>
       <c r="C188" s="8"/>
-      <c r="D188" s="8" t="s">
-        <v>40</v>
+      <c r="D188" s="73" t="s">
+        <v>631</v>
       </c>
       <c r="E188" s="29" t="s">
-        <v>51</v>
+        <v>632</v>
       </c>
       <c r="F188" s="29"/>
       <c r="G188" s="42" t="s">
-        <v>558</v>
+        <v>629</v>
       </c>
       <c r="H188" s="42" t="s">
-        <v>385</v>
+        <v>630</v>
       </c>
       <c r="I188" s="8" t="s">
         <v>246</v>
@@ -10552,10 +10618,10 @@
       <c r="O188" s="8"/>
       <c r="P188" s="8"/>
       <c r="Q188" s="8"/>
-      <c r="R188" s="74"/>
-      <c r="S188" s="75"/>
-      <c r="T188" s="76"/>
-      <c r="U188" s="77"/>
+      <c r="R188" s="67"/>
+      <c r="S188" s="68"/>
+      <c r="T188" s="65"/>
+      <c r="U188" s="66"/>
     </row>
     <row r="189" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A189" s="8">
@@ -10563,18 +10629,18 @@
       </c>
       <c r="B189" s="8"/>
       <c r="C189" s="8"/>
-      <c r="D189" s="8" t="s">
-        <v>41</v>
+      <c r="D189" s="73" t="s">
+        <v>77</v>
       </c>
       <c r="E189" s="29" t="s">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="F189" s="29"/>
       <c r="G189" s="42" t="s">
-        <v>559</v>
+        <v>451</v>
       </c>
       <c r="H189" s="42" t="s">
-        <v>386</v>
+        <v>638</v>
       </c>
       <c r="I189" s="8" t="s">
         <v>246</v>
@@ -10589,29 +10655,29 @@
       <c r="O189" s="8"/>
       <c r="P189" s="8"/>
       <c r="Q189" s="8"/>
-      <c r="R189" s="74"/>
-      <c r="S189" s="75"/>
-      <c r="T189" s="76"/>
-      <c r="U189" s="77"/>
-    </row>
-    <row r="190" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
+      <c r="R189" s="67"/>
+      <c r="S189" s="68"/>
+      <c r="T189" s="65"/>
+      <c r="U189" s="66"/>
+    </row>
+    <row r="190" spans="1:21" s="9" customFormat="1">
       <c r="A190" s="8">
         <v>20</v>
       </c>
       <c r="B190" s="8"/>
       <c r="C190" s="8"/>
-      <c r="D190" s="8" t="s">
-        <v>42</v>
+      <c r="D190" s="73" t="s">
+        <v>81</v>
       </c>
       <c r="E190" s="29" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F190" s="29"/>
       <c r="G190" s="42" t="s">
-        <v>560</v>
+        <v>455</v>
       </c>
       <c r="H190" s="42" t="s">
-        <v>387</v>
+        <v>643</v>
       </c>
       <c r="I190" s="8" t="s">
         <v>246</v>
@@ -10637,18 +10703,18 @@
       </c>
       <c r="B191" s="8"/>
       <c r="C191" s="8"/>
-      <c r="D191" s="8" t="s">
-        <v>43</v>
+      <c r="D191" s="73" t="s">
+        <v>622</v>
       </c>
       <c r="E191" s="29" t="s">
-        <v>100</v>
+        <v>626</v>
       </c>
       <c r="F191" s="29"/>
       <c r="G191" s="42" t="s">
-        <v>561</v>
+        <v>628</v>
       </c>
       <c r="H191" s="42" t="s">
-        <v>388</v>
+        <v>624</v>
       </c>
       <c r="I191" s="8" t="s">
         <v>246</v>
@@ -10663,10 +10729,10 @@
       <c r="O191" s="8"/>
       <c r="P191" s="8"/>
       <c r="Q191" s="8"/>
-      <c r="R191" s="74"/>
-      <c r="S191" s="75"/>
-      <c r="T191" s="76"/>
-      <c r="U191" s="77"/>
+      <c r="R191" s="67"/>
+      <c r="S191" s="68"/>
+      <c r="T191" s="65"/>
+      <c r="U191" s="66"/>
     </row>
     <row r="192" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A192" s="8">
@@ -10674,18 +10740,18 @@
       </c>
       <c r="B192" s="8"/>
       <c r="C192" s="8"/>
-      <c r="D192" s="8" t="s">
-        <v>44</v>
+      <c r="D192" s="73" t="s">
+        <v>635</v>
       </c>
       <c r="E192" s="29" t="s">
-        <v>101</v>
+        <v>625</v>
       </c>
       <c r="F192" s="29"/>
       <c r="G192" s="42" t="s">
-        <v>562</v>
+        <v>637</v>
       </c>
       <c r="H192" s="42" t="s">
-        <v>389</v>
+        <v>636</v>
       </c>
       <c r="I192" s="8" t="s">
         <v>246</v>
@@ -10700,10 +10766,10 @@
       <c r="O192" s="8"/>
       <c r="P192" s="8"/>
       <c r="Q192" s="8"/>
-      <c r="R192" s="74"/>
-      <c r="S192" s="75"/>
-      <c r="T192" s="76"/>
-      <c r="U192" s="77"/>
+      <c r="R192" s="67"/>
+      <c r="S192" s="68"/>
+      <c r="T192" s="65"/>
+      <c r="U192" s="66"/>
     </row>
     <row r="193" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A193" s="8">
@@ -10712,17 +10778,17 @@
       <c r="B193" s="8"/>
       <c r="C193" s="8"/>
       <c r="D193" s="8" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E193" s="29" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="F193" s="29"/>
       <c r="G193" s="42" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="H193" s="42" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="I193" s="8" t="s">
         <v>246</v>
@@ -10749,17 +10815,17 @@
       <c r="B194" s="8"/>
       <c r="C194" s="8"/>
       <c r="D194" s="8" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E194" s="29" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F194" s="29"/>
       <c r="G194" s="42" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="H194" s="42" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="I194" s="8" t="s">
         <v>246</v>
@@ -10786,17 +10852,17 @@
       <c r="B195" s="8"/>
       <c r="C195" s="8"/>
       <c r="D195" s="8" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E195" s="29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F195" s="29"/>
       <c r="G195" s="42" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="H195" s="42" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="I195" s="8" t="s">
         <v>246</v>
@@ -10823,17 +10889,17 @@
       <c r="B196" s="8"/>
       <c r="C196" s="8"/>
       <c r="D196" s="8" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E196" s="29" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="F196" s="29"/>
       <c r="G196" s="42" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="H196" s="42" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="I196" s="8" t="s">
         <v>246</v>
@@ -10853,58 +10919,289 @@
       <c r="T196" s="76"/>
       <c r="U196" s="77"/>
     </row>
-    <row r="197" spans="1:21" s="9" customFormat="1">
-      <c r="A197" s="24"/>
-      <c r="B197" s="25"/>
-      <c r="C197" s="25"/>
-      <c r="D197" s="47" t="s">
+    <row r="197" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A197" s="8">
+        <v>20</v>
+      </c>
+      <c r="B197" s="8"/>
+      <c r="C197" s="8"/>
+      <c r="D197" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E197" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="F197" s="29"/>
+      <c r="G197" s="42" t="s">
+        <v>560</v>
+      </c>
+      <c r="H197" s="42" t="s">
+        <v>387</v>
+      </c>
+      <c r="I197" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="J197" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K197" s="8"/>
+      <c r="L197" s="8"/>
+      <c r="M197" s="8"/>
+      <c r="N197" s="8"/>
+      <c r="O197" s="8"/>
+      <c r="P197" s="8"/>
+      <c r="Q197" s="8"/>
+      <c r="R197" s="74"/>
+      <c r="S197" s="75"/>
+      <c r="T197" s="76"/>
+      <c r="U197" s="77"/>
+    </row>
+    <row r="198" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A198" s="8">
+        <v>20</v>
+      </c>
+      <c r="B198" s="8"/>
+      <c r="C198" s="8"/>
+      <c r="D198" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E198" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="F198" s="29"/>
+      <c r="G198" s="42" t="s">
+        <v>561</v>
+      </c>
+      <c r="H198" s="42" t="s">
+        <v>388</v>
+      </c>
+      <c r="I198" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="J198" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K198" s="8"/>
+      <c r="L198" s="8"/>
+      <c r="M198" s="8"/>
+      <c r="N198" s="8"/>
+      <c r="O198" s="8"/>
+      <c r="P198" s="8"/>
+      <c r="Q198" s="8"/>
+      <c r="R198" s="74"/>
+      <c r="S198" s="75"/>
+      <c r="T198" s="76"/>
+      <c r="U198" s="77"/>
+    </row>
+    <row r="199" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A199" s="8">
+        <v>20</v>
+      </c>
+      <c r="B199" s="8"/>
+      <c r="C199" s="8"/>
+      <c r="D199" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E199" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="F199" s="29"/>
+      <c r="G199" s="42" t="s">
+        <v>562</v>
+      </c>
+      <c r="H199" s="42" t="s">
+        <v>389</v>
+      </c>
+      <c r="I199" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="J199" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K199" s="8"/>
+      <c r="L199" s="8"/>
+      <c r="M199" s="8"/>
+      <c r="N199" s="8"/>
+      <c r="O199" s="8"/>
+      <c r="P199" s="8"/>
+      <c r="Q199" s="8"/>
+      <c r="R199" s="74"/>
+      <c r="S199" s="75"/>
+      <c r="T199" s="76"/>
+      <c r="U199" s="77"/>
+    </row>
+    <row r="200" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A200" s="8">
+        <v>20</v>
+      </c>
+      <c r="B200" s="8"/>
+      <c r="C200" s="8"/>
+      <c r="D200" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E200" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="F200" s="29"/>
+      <c r="G200" s="42" t="s">
+        <v>563</v>
+      </c>
+      <c r="H200" s="42" t="s">
+        <v>390</v>
+      </c>
+      <c r="I200" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="J200" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K200" s="8"/>
+      <c r="L200" s="8"/>
+      <c r="M200" s="8"/>
+      <c r="N200" s="8"/>
+      <c r="O200" s="8"/>
+      <c r="P200" s="8"/>
+      <c r="Q200" s="8"/>
+      <c r="R200" s="74"/>
+      <c r="S200" s="75"/>
+      <c r="T200" s="76"/>
+      <c r="U200" s="77"/>
+    </row>
+    <row r="201" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A201" s="8">
+        <v>20</v>
+      </c>
+      <c r="B201" s="8"/>
+      <c r="C201" s="8"/>
+      <c r="D201" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E201" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="F201" s="29"/>
+      <c r="G201" s="42" t="s">
+        <v>564</v>
+      </c>
+      <c r="H201" s="42" t="s">
+        <v>391</v>
+      </c>
+      <c r="I201" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="J201" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K201" s="8"/>
+      <c r="L201" s="8"/>
+      <c r="M201" s="8"/>
+      <c r="N201" s="8"/>
+      <c r="O201" s="8"/>
+      <c r="P201" s="8"/>
+      <c r="Q201" s="8"/>
+      <c r="R201" s="74"/>
+      <c r="S201" s="75"/>
+      <c r="T201" s="76"/>
+      <c r="U201" s="77"/>
+    </row>
+    <row r="202" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A202" s="8">
+        <v>20</v>
+      </c>
+      <c r="B202" s="8"/>
+      <c r="C202" s="8"/>
+      <c r="D202" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E202" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="F202" s="29"/>
+      <c r="G202" s="42" t="s">
+        <v>565</v>
+      </c>
+      <c r="H202" s="42" t="s">
+        <v>392</v>
+      </c>
+      <c r="I202" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="J202" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K202" s="8"/>
+      <c r="L202" s="8"/>
+      <c r="M202" s="8"/>
+      <c r="N202" s="8"/>
+      <c r="O202" s="8"/>
+      <c r="P202" s="8"/>
+      <c r="Q202" s="8"/>
+      <c r="R202" s="74"/>
+      <c r="S202" s="75"/>
+      <c r="T202" s="76"/>
+      <c r="U202" s="77"/>
+    </row>
+    <row r="203" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A203" s="8">
+        <v>20</v>
+      </c>
+      <c r="B203" s="8"/>
+      <c r="C203" s="8"/>
+      <c r="D203" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E203" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="F203" s="29"/>
+      <c r="G203" s="42" t="s">
+        <v>566</v>
+      </c>
+      <c r="H203" s="42" t="s">
+        <v>393</v>
+      </c>
+      <c r="I203" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="J203" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K203" s="8"/>
+      <c r="L203" s="8"/>
+      <c r="M203" s="8"/>
+      <c r="N203" s="8"/>
+      <c r="O203" s="8"/>
+      <c r="P203" s="8"/>
+      <c r="Q203" s="8"/>
+      <c r="R203" s="74"/>
+      <c r="S203" s="75"/>
+      <c r="T203" s="76"/>
+      <c r="U203" s="77"/>
+    </row>
+    <row r="204" spans="1:21" s="9" customFormat="1">
+      <c r="A204" s="24"/>
+      <c r="B204" s="25"/>
+      <c r="C204" s="25"/>
+      <c r="D204" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="E197" s="6"/>
-      <c r="F197" s="6"/>
-      <c r="G197" s="6"/>
-      <c r="H197" s="6"/>
-      <c r="I197" s="6"/>
-      <c r="J197" s="6"/>
-      <c r="K197" s="6"/>
-      <c r="L197" s="6"/>
-      <c r="M197" s="6"/>
-      <c r="N197" s="6"/>
-      <c r="O197" s="6"/>
-      <c r="P197" s="6"/>
-      <c r="Q197" s="6"/>
-      <c r="R197" s="6"/>
-      <c r="S197" s="6"/>
-      <c r="T197" s="6"/>
-      <c r="U197" s="18"/>
-    </row>
-    <row r="198" spans="1:21" s="9" customFormat="1">
-      <c r="A198" s="55"/>
-      <c r="U198" s="43"/>
-    </row>
-    <row r="199" spans="1:21" s="9" customFormat="1">
-      <c r="A199" s="55"/>
-      <c r="U199" s="43"/>
-    </row>
-    <row r="200" spans="1:21" s="9" customFormat="1">
-      <c r="A200" s="55"/>
-      <c r="U200" s="43"/>
-    </row>
-    <row r="201" spans="1:21" s="9" customFormat="1">
-      <c r="A201" s="55"/>
-      <c r="U201" s="43"/>
-    </row>
-    <row r="202" spans="1:21" s="9" customFormat="1">
-      <c r="A202" s="55"/>
-      <c r="U202" s="43"/>
-    </row>
-    <row r="203" spans="1:21" s="9" customFormat="1">
-      <c r="A203" s="55"/>
-      <c r="U203" s="43"/>
-    </row>
-    <row r="204" spans="1:21" s="9" customFormat="1">
-      <c r="A204" s="55"/>
-      <c r="U204" s="43"/>
+      <c r="E204" s="6"/>
+      <c r="F204" s="6"/>
+      <c r="G204" s="6"/>
+      <c r="H204" s="6"/>
+      <c r="I204" s="6"/>
+      <c r="J204" s="6"/>
+      <c r="K204" s="6"/>
+      <c r="L204" s="6"/>
+      <c r="M204" s="6"/>
+      <c r="N204" s="6"/>
+      <c r="O204" s="6"/>
+      <c r="P204" s="6"/>
+      <c r="Q204" s="6"/>
+      <c r="R204" s="6"/>
+      <c r="S204" s="6"/>
+      <c r="T204" s="6"/>
+      <c r="U204" s="18"/>
     </row>
     <row r="205" spans="1:21" s="9" customFormat="1">
       <c r="A205" s="55"/>
@@ -10931,32 +11228,62 @@
       <c r="U210" s="43"/>
     </row>
     <row r="211" spans="1:21" s="9" customFormat="1">
-      <c r="A211" s="62"/>
-      <c r="B211" s="48"/>
-      <c r="C211" s="48"/>
-      <c r="D211" s="48"/>
-      <c r="E211" s="48"/>
-      <c r="F211" s="48"/>
-      <c r="G211" s="48"/>
-      <c r="H211" s="48"/>
-      <c r="I211" s="48"/>
-      <c r="J211" s="48"/>
-      <c r="K211" s="48"/>
-      <c r="L211" s="48"/>
-      <c r="M211" s="48"/>
-      <c r="N211" s="48"/>
-      <c r="O211" s="48"/>
-      <c r="P211" s="48"/>
-      <c r="Q211" s="48"/>
-      <c r="R211" s="48"/>
-      <c r="S211" s="48"/>
-      <c r="T211" s="48"/>
-      <c r="U211" s="49"/>
+      <c r="A211" s="55"/>
+      <c r="U211" s="43"/>
+    </row>
+    <row r="212" spans="1:21" s="9" customFormat="1">
+      <c r="A212" s="55"/>
+      <c r="U212" s="43"/>
+    </row>
+    <row r="213" spans="1:21" s="9" customFormat="1">
+      <c r="A213" s="55"/>
+      <c r="U213" s="43"/>
+    </row>
+    <row r="214" spans="1:21" s="9" customFormat="1">
+      <c r="A214" s="55"/>
+      <c r="U214" s="43"/>
+    </row>
+    <row r="215" spans="1:21" s="9" customFormat="1">
+      <c r="A215" s="55"/>
+      <c r="U215" s="43"/>
+    </row>
+    <row r="216" spans="1:21" s="9" customFormat="1">
+      <c r="A216" s="55"/>
+      <c r="U216" s="43"/>
+    </row>
+    <row r="217" spans="1:21" s="9" customFormat="1">
+      <c r="A217" s="55"/>
+      <c r="U217" s="43"/>
+    </row>
+    <row r="218" spans="1:21" s="9" customFormat="1">
+      <c r="A218" s="62"/>
+      <c r="B218" s="48"/>
+      <c r="C218" s="48"/>
+      <c r="D218" s="48"/>
+      <c r="E218" s="48"/>
+      <c r="F218" s="48"/>
+      <c r="G218" s="48"/>
+      <c r="H218" s="48"/>
+      <c r="I218" s="48"/>
+      <c r="J218" s="48"/>
+      <c r="K218" s="48"/>
+      <c r="L218" s="48"/>
+      <c r="M218" s="48"/>
+      <c r="N218" s="48"/>
+      <c r="O218" s="48"/>
+      <c r="P218" s="48"/>
+      <c r="Q218" s="48"/>
+      <c r="R218" s="48"/>
+      <c r="S218" s="48"/>
+      <c r="T218" s="48"/>
+      <c r="U218" s="49"/>
     </row>
   </sheetData>
-  <mergeCells count="173">
-    <mergeCell ref="R186:S186"/>
-    <mergeCell ref="T186:U186"/>
+  <mergeCells count="175">
+    <mergeCell ref="R190:S190"/>
+    <mergeCell ref="T190:U190"/>
+    <mergeCell ref="R193:S193"/>
+    <mergeCell ref="T193:U193"/>
     <mergeCell ref="T29:U29"/>
     <mergeCell ref="R21:S21"/>
     <mergeCell ref="T50:U50"/>
@@ -10975,21 +11302,23 @@
     <mergeCell ref="T27:U27"/>
     <mergeCell ref="R68:S68"/>
     <mergeCell ref="T68:U68"/>
-    <mergeCell ref="T190:U190"/>
-    <mergeCell ref="R191:S191"/>
-    <mergeCell ref="T191:U191"/>
-    <mergeCell ref="R187:S187"/>
-    <mergeCell ref="T187:U187"/>
+    <mergeCell ref="R164:S164"/>
+    <mergeCell ref="T164:U164"/>
+    <mergeCell ref="R144:S144"/>
+    <mergeCell ref="T150:U150"/>
+    <mergeCell ref="T198:U198"/>
     <mergeCell ref="R194:S194"/>
     <mergeCell ref="T194:U194"/>
-    <mergeCell ref="R193:S193"/>
-    <mergeCell ref="T193:U193"/>
-    <mergeCell ref="R192:S192"/>
-    <mergeCell ref="T192:U192"/>
-    <mergeCell ref="R189:S189"/>
-    <mergeCell ref="T189:U189"/>
-    <mergeCell ref="R188:S188"/>
-    <mergeCell ref="T188:U188"/>
+    <mergeCell ref="R201:S201"/>
+    <mergeCell ref="T201:U201"/>
+    <mergeCell ref="R200:S200"/>
+    <mergeCell ref="T200:U200"/>
+    <mergeCell ref="R199:S199"/>
+    <mergeCell ref="T199:U199"/>
+    <mergeCell ref="R196:S196"/>
+    <mergeCell ref="T196:U196"/>
+    <mergeCell ref="R195:S195"/>
+    <mergeCell ref="T195:U195"/>
     <mergeCell ref="T8:U8"/>
     <mergeCell ref="T69:U69"/>
     <mergeCell ref="R28:S28"/>
@@ -11038,8 +11367,8 @@
     <mergeCell ref="R60:S60"/>
     <mergeCell ref="T66:U66"/>
     <mergeCell ref="R147:S147"/>
-    <mergeCell ref="R196:S196"/>
-    <mergeCell ref="T196:U196"/>
+    <mergeCell ref="R203:S203"/>
+    <mergeCell ref="T203:U203"/>
     <mergeCell ref="T172:U172"/>
     <mergeCell ref="R172:S172"/>
     <mergeCell ref="R173:S173"/>
@@ -11057,13 +11386,11 @@
     <mergeCell ref="T185:U185"/>
     <mergeCell ref="R183:S183"/>
     <mergeCell ref="T183:U183"/>
-    <mergeCell ref="R195:S195"/>
-    <mergeCell ref="T195:U195"/>
-    <mergeCell ref="R190:S190"/>
-    <mergeCell ref="R164:S164"/>
-    <mergeCell ref="T164:U164"/>
-    <mergeCell ref="R144:S144"/>
-    <mergeCell ref="T150:U150"/>
+    <mergeCell ref="R202:S202"/>
+    <mergeCell ref="T202:U202"/>
+    <mergeCell ref="R197:S197"/>
+    <mergeCell ref="T197:U197"/>
+    <mergeCell ref="R198:S198"/>
     <mergeCell ref="R153:S153"/>
     <mergeCell ref="T144:U144"/>
     <mergeCell ref="R168:S168"/>

--- a/development/MS/spec/MSBB/Logic/MSBBLA0010_SlsSchdSrch.xlsx
+++ b/development/MS/spec/MSBB/Logic/MSBBLA0010_SlsSchdSrch.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\PJ\TK\dev\development\MS\spec\MSBB\Logic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65E6AA2D-0E29-4316-8ACE-AE5FB2D517FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C01B90B-16B3-4152-83A0-5AFE1485E054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="794" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1230" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="650">
   <si>
     <t>*</t>
   </si>
@@ -2257,6 +2257,24 @@
   </si>
   <si>
     <t>品名</t>
+  </si>
+  <si>
+    <t>枝番１</t>
+  </si>
+  <si>
+    <t>枝番２</t>
+  </si>
+  <si>
+    <t>枝番３</t>
+  </si>
+  <si>
+    <t>prod_itm_sub1</t>
+  </si>
+  <si>
+    <t>prod_itm_sub2</t>
+  </si>
+  <si>
+    <t>prod_itm_sub3</t>
   </si>
 </sst>
 </file>
@@ -2990,6 +3008,93 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3051,93 +3156,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3687,7 +3705,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U218"/>
+  <dimension ref="A1:U224"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4.875" style="4" customWidth="1"/>
@@ -10401,24 +10419,24 @@
       <c r="T182" s="76"/>
       <c r="U182" s="77"/>
     </row>
-    <row r="183" spans="1:21" s="9" customFormat="1">
+    <row r="183" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A183" s="8">
         <v>20</v>
       </c>
       <c r="B183" s="8"/>
       <c r="C183" s="8"/>
       <c r="D183" s="73" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="E183" s="29" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="F183" s="29"/>
       <c r="G183" s="42" t="s">
-        <v>584</v>
+        <v>452</v>
       </c>
       <c r="H183" s="42" t="s">
-        <v>586</v>
+        <v>644</v>
       </c>
       <c r="I183" s="8" t="s">
         <v>246</v>
@@ -10433,10 +10451,10 @@
       <c r="O183" s="8"/>
       <c r="P183" s="8"/>
       <c r="Q183" s="8"/>
-      <c r="R183" s="74"/>
-      <c r="S183" s="75"/>
-      <c r="T183" s="76"/>
-      <c r="U183" s="77"/>
+      <c r="R183" s="67"/>
+      <c r="S183" s="68"/>
+      <c r="T183" s="65"/>
+      <c r="U183" s="66"/>
     </row>
     <row r="184" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A184" s="8">
@@ -10445,17 +10463,17 @@
       <c r="B184" s="8"/>
       <c r="C184" s="8"/>
       <c r="D184" s="73" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="E184" s="29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F184" s="29"/>
       <c r="G184" s="42" t="s">
-        <v>577</v>
+        <v>453</v>
       </c>
       <c r="H184" s="42" t="s">
-        <v>578</v>
+        <v>645</v>
       </c>
       <c r="I184" s="8" t="s">
         <v>246</v>
@@ -10470,10 +10488,10 @@
       <c r="O184" s="8"/>
       <c r="P184" s="8"/>
       <c r="Q184" s="8"/>
-      <c r="R184" s="74"/>
-      <c r="S184" s="75"/>
-      <c r="T184" s="76"/>
-      <c r="U184" s="77"/>
+      <c r="R184" s="67"/>
+      <c r="S184" s="68"/>
+      <c r="T184" s="65"/>
+      <c r="U184" s="66"/>
     </row>
     <row r="185" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A185" s="8">
@@ -10482,17 +10500,17 @@
       <c r="B185" s="8"/>
       <c r="C185" s="8"/>
       <c r="D185" s="73" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="E185" s="29" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F185" s="29"/>
       <c r="G185" s="42" t="s">
-        <v>579</v>
+        <v>454</v>
       </c>
       <c r="H185" s="42" t="s">
-        <v>580</v>
+        <v>646</v>
       </c>
       <c r="I185" s="8" t="s">
         <v>246</v>
@@ -10507,29 +10525,29 @@
       <c r="O185" s="8"/>
       <c r="P185" s="8"/>
       <c r="Q185" s="8"/>
-      <c r="R185" s="74"/>
-      <c r="S185" s="75"/>
-      <c r="T185" s="76"/>
-      <c r="U185" s="77"/>
-    </row>
-    <row r="186" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
+      <c r="R185" s="67"/>
+      <c r="S185" s="68"/>
+      <c r="T185" s="65"/>
+      <c r="U185" s="66"/>
+    </row>
+    <row r="186" spans="1:21" s="9" customFormat="1">
       <c r="A186" s="8">
         <v>20</v>
       </c>
       <c r="B186" s="8"/>
       <c r="C186" s="8"/>
       <c r="D186" s="73" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="E186" s="29" t="s">
-        <v>625</v>
+        <v>85</v>
       </c>
       <c r="F186" s="29"/>
       <c r="G186" s="42" t="s">
-        <v>627</v>
+        <v>584</v>
       </c>
       <c r="H186" s="42" t="s">
-        <v>623</v>
+        <v>586</v>
       </c>
       <c r="I186" s="8" t="s">
         <v>246</v>
@@ -10544,10 +10562,10 @@
       <c r="O186" s="8"/>
       <c r="P186" s="8"/>
       <c r="Q186" s="8"/>
-      <c r="R186" s="67"/>
-      <c r="S186" s="68"/>
-      <c r="T186" s="65"/>
-      <c r="U186" s="66"/>
+      <c r="R186" s="74"/>
+      <c r="S186" s="75"/>
+      <c r="T186" s="76"/>
+      <c r="U186" s="77"/>
     </row>
     <row r="187" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A187" s="8">
@@ -10556,17 +10574,17 @@
       <c r="B187" s="8"/>
       <c r="C187" s="8"/>
       <c r="D187" s="73" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="E187" s="29" t="s">
-        <v>626</v>
+        <v>27</v>
       </c>
       <c r="F187" s="29"/>
       <c r="G187" s="42" t="s">
-        <v>628</v>
+        <v>577</v>
       </c>
       <c r="H187" s="42" t="s">
-        <v>624</v>
+        <v>578</v>
       </c>
       <c r="I187" s="8" t="s">
         <v>246</v>
@@ -10581,10 +10599,10 @@
       <c r="O187" s="8"/>
       <c r="P187" s="8"/>
       <c r="Q187" s="8"/>
-      <c r="R187" s="67"/>
-      <c r="S187" s="68"/>
-      <c r="T187" s="65"/>
-      <c r="U187" s="66"/>
+      <c r="R187" s="74"/>
+      <c r="S187" s="75"/>
+      <c r="T187" s="76"/>
+      <c r="U187" s="77"/>
     </row>
     <row r="188" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A188" s="8">
@@ -10593,17 +10611,17 @@
       <c r="B188" s="8"/>
       <c r="C188" s="8"/>
       <c r="D188" s="73" t="s">
-        <v>631</v>
+        <v>642</v>
       </c>
       <c r="E188" s="29" t="s">
-        <v>632</v>
+        <v>27</v>
       </c>
       <c r="F188" s="29"/>
       <c r="G188" s="42" t="s">
-        <v>629</v>
+        <v>579</v>
       </c>
       <c r="H188" s="42" t="s">
-        <v>630</v>
+        <v>580</v>
       </c>
       <c r="I188" s="8" t="s">
         <v>246</v>
@@ -10618,10 +10636,10 @@
       <c r="O188" s="8"/>
       <c r="P188" s="8"/>
       <c r="Q188" s="8"/>
-      <c r="R188" s="67"/>
-      <c r="S188" s="68"/>
-      <c r="T188" s="65"/>
-      <c r="U188" s="66"/>
+      <c r="R188" s="74"/>
+      <c r="S188" s="75"/>
+      <c r="T188" s="76"/>
+      <c r="U188" s="77"/>
     </row>
     <row r="189" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A189" s="8">
@@ -10630,17 +10648,17 @@
       <c r="B189" s="8"/>
       <c r="C189" s="8"/>
       <c r="D189" s="73" t="s">
-        <v>77</v>
+        <v>633</v>
       </c>
       <c r="E189" s="29" t="s">
-        <v>49</v>
+        <v>625</v>
       </c>
       <c r="F189" s="29"/>
       <c r="G189" s="42" t="s">
-        <v>451</v>
+        <v>627</v>
       </c>
       <c r="H189" s="42" t="s">
-        <v>638</v>
+        <v>623</v>
       </c>
       <c r="I189" s="8" t="s">
         <v>246</v>
@@ -10660,24 +10678,24 @@
       <c r="T189" s="65"/>
       <c r="U189" s="66"/>
     </row>
-    <row r="190" spans="1:21" s="9" customFormat="1">
+    <row r="190" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A190" s="8">
         <v>20</v>
       </c>
       <c r="B190" s="8"/>
       <c r="C190" s="8"/>
       <c r="D190" s="73" t="s">
-        <v>81</v>
+        <v>634</v>
       </c>
       <c r="E190" s="29" t="s">
-        <v>85</v>
+        <v>626</v>
       </c>
       <c r="F190" s="29"/>
       <c r="G190" s="42" t="s">
-        <v>455</v>
+        <v>628</v>
       </c>
       <c r="H190" s="42" t="s">
-        <v>643</v>
+        <v>624</v>
       </c>
       <c r="I190" s="8" t="s">
         <v>246</v>
@@ -10692,10 +10710,10 @@
       <c r="O190" s="8"/>
       <c r="P190" s="8"/>
       <c r="Q190" s="8"/>
-      <c r="R190" s="74"/>
-      <c r="S190" s="75"/>
-      <c r="T190" s="76"/>
-      <c r="U190" s="77"/>
+      <c r="R190" s="67"/>
+      <c r="S190" s="68"/>
+      <c r="T190" s="65"/>
+      <c r="U190" s="66"/>
     </row>
     <row r="191" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A191" s="8">
@@ -10704,17 +10722,17 @@
       <c r="B191" s="8"/>
       <c r="C191" s="8"/>
       <c r="D191" s="73" t="s">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="E191" s="29" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="F191" s="29"/>
       <c r="G191" s="42" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H191" s="42" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="I191" s="8" t="s">
         <v>246</v>
@@ -10741,17 +10759,17 @@
       <c r="B192" s="8"/>
       <c r="C192" s="8"/>
       <c r="D192" s="73" t="s">
-        <v>635</v>
+        <v>77</v>
       </c>
       <c r="E192" s="29" t="s">
-        <v>625</v>
+        <v>49</v>
       </c>
       <c r="F192" s="29"/>
       <c r="G192" s="42" t="s">
-        <v>637</v>
+        <v>451</v>
       </c>
       <c r="H192" s="42" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="I192" s="8" t="s">
         <v>246</v>
@@ -10777,18 +10795,18 @@
       </c>
       <c r="B193" s="8"/>
       <c r="C193" s="8"/>
-      <c r="D193" s="8" t="s">
-        <v>38</v>
+      <c r="D193" s="73" t="s">
+        <v>78</v>
       </c>
       <c r="E193" s="29" t="s">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F193" s="29"/>
       <c r="G193" s="42" t="s">
-        <v>556</v>
+        <v>452</v>
       </c>
       <c r="H193" s="42" t="s">
-        <v>383</v>
+        <v>644</v>
       </c>
       <c r="I193" s="8" t="s">
         <v>246</v>
@@ -10803,10 +10821,10 @@
       <c r="O193" s="8"/>
       <c r="P193" s="8"/>
       <c r="Q193" s="8"/>
-      <c r="R193" s="74"/>
-      <c r="S193" s="75"/>
-      <c r="T193" s="76"/>
-      <c r="U193" s="77"/>
+      <c r="R193" s="67"/>
+      <c r="S193" s="68"/>
+      <c r="T193" s="65"/>
+      <c r="U193" s="66"/>
     </row>
     <row r="194" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A194" s="8">
@@ -10814,18 +10832,18 @@
       </c>
       <c r="B194" s="8"/>
       <c r="C194" s="8"/>
-      <c r="D194" s="8" t="s">
-        <v>39</v>
+      <c r="D194" s="73" t="s">
+        <v>79</v>
       </c>
       <c r="E194" s="29" t="s">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="F194" s="29"/>
       <c r="G194" s="42" t="s">
-        <v>557</v>
+        <v>453</v>
       </c>
       <c r="H194" s="42" t="s">
-        <v>384</v>
+        <v>645</v>
       </c>
       <c r="I194" s="8" t="s">
         <v>246</v>
@@ -10840,10 +10858,10 @@
       <c r="O194" s="8"/>
       <c r="P194" s="8"/>
       <c r="Q194" s="8"/>
-      <c r="R194" s="74"/>
-      <c r="S194" s="75"/>
-      <c r="T194" s="76"/>
-      <c r="U194" s="77"/>
+      <c r="R194" s="67"/>
+      <c r="S194" s="68"/>
+      <c r="T194" s="65"/>
+      <c r="U194" s="66"/>
     </row>
     <row r="195" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A195" s="8">
@@ -10851,18 +10869,18 @@
       </c>
       <c r="B195" s="8"/>
       <c r="C195" s="8"/>
-      <c r="D195" s="8" t="s">
-        <v>40</v>
+      <c r="D195" s="73" t="s">
+        <v>80</v>
       </c>
       <c r="E195" s="29" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="F195" s="29"/>
       <c r="G195" s="42" t="s">
-        <v>558</v>
+        <v>454</v>
       </c>
       <c r="H195" s="42" t="s">
-        <v>385</v>
+        <v>646</v>
       </c>
       <c r="I195" s="8" t="s">
         <v>246</v>
@@ -10877,29 +10895,29 @@
       <c r="O195" s="8"/>
       <c r="P195" s="8"/>
       <c r="Q195" s="8"/>
-      <c r="R195" s="74"/>
-      <c r="S195" s="75"/>
-      <c r="T195" s="76"/>
-      <c r="U195" s="77"/>
-    </row>
-    <row r="196" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
+      <c r="R195" s="67"/>
+      <c r="S195" s="68"/>
+      <c r="T195" s="65"/>
+      <c r="U195" s="66"/>
+    </row>
+    <row r="196" spans="1:21" s="9" customFormat="1">
       <c r="A196" s="8">
         <v>20</v>
       </c>
       <c r="B196" s="8"/>
       <c r="C196" s="8"/>
-      <c r="D196" s="8" t="s">
-        <v>41</v>
+      <c r="D196" s="73" t="s">
+        <v>81</v>
       </c>
       <c r="E196" s="29" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="F196" s="29"/>
       <c r="G196" s="42" t="s">
-        <v>559</v>
+        <v>455</v>
       </c>
       <c r="H196" s="42" t="s">
-        <v>386</v>
+        <v>643</v>
       </c>
       <c r="I196" s="8" t="s">
         <v>246</v>
@@ -10925,18 +10943,18 @@
       </c>
       <c r="B197" s="8"/>
       <c r="C197" s="8"/>
-      <c r="D197" s="8" t="s">
-        <v>42</v>
+      <c r="D197" s="73" t="s">
+        <v>622</v>
       </c>
       <c r="E197" s="29" t="s">
-        <v>52</v>
+        <v>626</v>
       </c>
       <c r="F197" s="29"/>
       <c r="G197" s="42" t="s">
-        <v>560</v>
+        <v>628</v>
       </c>
       <c r="H197" s="42" t="s">
-        <v>387</v>
+        <v>624</v>
       </c>
       <c r="I197" s="8" t="s">
         <v>246</v>
@@ -10951,10 +10969,10 @@
       <c r="O197" s="8"/>
       <c r="P197" s="8"/>
       <c r="Q197" s="8"/>
-      <c r="R197" s="74"/>
-      <c r="S197" s="75"/>
-      <c r="T197" s="76"/>
-      <c r="U197" s="77"/>
+      <c r="R197" s="67"/>
+      <c r="S197" s="68"/>
+      <c r="T197" s="65"/>
+      <c r="U197" s="66"/>
     </row>
     <row r="198" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A198" s="8">
@@ -10962,18 +10980,18 @@
       </c>
       <c r="B198" s="8"/>
       <c r="C198" s="8"/>
-      <c r="D198" s="8" t="s">
-        <v>43</v>
+      <c r="D198" s="73" t="s">
+        <v>635</v>
       </c>
       <c r="E198" s="29" t="s">
-        <v>100</v>
+        <v>625</v>
       </c>
       <c r="F198" s="29"/>
       <c r="G198" s="42" t="s">
-        <v>561</v>
+        <v>637</v>
       </c>
       <c r="H198" s="42" t="s">
-        <v>388</v>
+        <v>636</v>
       </c>
       <c r="I198" s="8" t="s">
         <v>246</v>
@@ -10988,10 +11006,10 @@
       <c r="O198" s="8"/>
       <c r="P198" s="8"/>
       <c r="Q198" s="8"/>
-      <c r="R198" s="74"/>
-      <c r="S198" s="75"/>
-      <c r="T198" s="76"/>
-      <c r="U198" s="77"/>
+      <c r="R198" s="67"/>
+      <c r="S198" s="68"/>
+      <c r="T198" s="65"/>
+      <c r="U198" s="66"/>
     </row>
     <row r="199" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
       <c r="A199" s="8">
@@ -11000,17 +11018,17 @@
       <c r="B199" s="8"/>
       <c r="C199" s="8"/>
       <c r="D199" s="8" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E199" s="29" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F199" s="29"/>
       <c r="G199" s="42" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="H199" s="42" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I199" s="8" t="s">
         <v>246</v>
@@ -11037,17 +11055,17 @@
       <c r="B200" s="8"/>
       <c r="C200" s="8"/>
       <c r="D200" s="8" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E200" s="29" t="s">
-        <v>51</v>
+        <v>101</v>
       </c>
       <c r="F200" s="29"/>
       <c r="G200" s="42" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="H200" s="42" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="I200" s="8" t="s">
         <v>246</v>
@@ -11074,17 +11092,17 @@
       <c r="B201" s="8"/>
       <c r="C201" s="8"/>
       <c r="D201" s="8" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E201" s="29" t="s">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="F201" s="29"/>
       <c r="G201" s="42" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="H201" s="42" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="I201" s="8" t="s">
         <v>246</v>
@@ -11111,17 +11129,17 @@
       <c r="B202" s="8"/>
       <c r="C202" s="8"/>
       <c r="D202" s="8" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E202" s="29" t="s">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="F202" s="29"/>
       <c r="G202" s="42" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="H202" s="42" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="I202" s="8" t="s">
         <v>246</v>
@@ -11148,17 +11166,17 @@
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
       <c r="D203" s="8" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E203" s="29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F203" s="29"/>
       <c r="G203" s="42" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="H203" s="42" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="I203" s="8" t="s">
         <v>246</v>
@@ -11178,54 +11196,252 @@
       <c r="T203" s="76"/>
       <c r="U203" s="77"/>
     </row>
-    <row r="204" spans="1:21" s="9" customFormat="1">
-      <c r="A204" s="24"/>
-      <c r="B204" s="25"/>
-      <c r="C204" s="25"/>
-      <c r="D204" s="47" t="s">
+    <row r="204" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A204" s="8">
+        <v>20</v>
+      </c>
+      <c r="B204" s="8"/>
+      <c r="C204" s="8"/>
+      <c r="D204" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E204" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="F204" s="29"/>
+      <c r="G204" s="42" t="s">
+        <v>561</v>
+      </c>
+      <c r="H204" s="42" t="s">
+        <v>388</v>
+      </c>
+      <c r="I204" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="J204" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K204" s="8"/>
+      <c r="L204" s="8"/>
+      <c r="M204" s="8"/>
+      <c r="N204" s="8"/>
+      <c r="O204" s="8"/>
+      <c r="P204" s="8"/>
+      <c r="Q204" s="8"/>
+      <c r="R204" s="74"/>
+      <c r="S204" s="75"/>
+      <c r="T204" s="76"/>
+      <c r="U204" s="77"/>
+    </row>
+    <row r="205" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A205" s="8">
+        <v>20</v>
+      </c>
+      <c r="B205" s="8"/>
+      <c r="C205" s="8"/>
+      <c r="D205" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E205" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="F205" s="29"/>
+      <c r="G205" s="42" t="s">
+        <v>562</v>
+      </c>
+      <c r="H205" s="42" t="s">
+        <v>389</v>
+      </c>
+      <c r="I205" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="J205" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K205" s="8"/>
+      <c r="L205" s="8"/>
+      <c r="M205" s="8"/>
+      <c r="N205" s="8"/>
+      <c r="O205" s="8"/>
+      <c r="P205" s="8"/>
+      <c r="Q205" s="8"/>
+      <c r="R205" s="74"/>
+      <c r="S205" s="75"/>
+      <c r="T205" s="76"/>
+      <c r="U205" s="77"/>
+    </row>
+    <row r="206" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A206" s="8">
+        <v>20</v>
+      </c>
+      <c r="B206" s="8"/>
+      <c r="C206" s="8"/>
+      <c r="D206" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E206" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="F206" s="29"/>
+      <c r="G206" s="42" t="s">
+        <v>563</v>
+      </c>
+      <c r="H206" s="42" t="s">
+        <v>390</v>
+      </c>
+      <c r="I206" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="J206" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K206" s="8"/>
+      <c r="L206" s="8"/>
+      <c r="M206" s="8"/>
+      <c r="N206" s="8"/>
+      <c r="O206" s="8"/>
+      <c r="P206" s="8"/>
+      <c r="Q206" s="8"/>
+      <c r="R206" s="74"/>
+      <c r="S206" s="75"/>
+      <c r="T206" s="76"/>
+      <c r="U206" s="77"/>
+    </row>
+    <row r="207" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A207" s="8">
+        <v>20</v>
+      </c>
+      <c r="B207" s="8"/>
+      <c r="C207" s="8"/>
+      <c r="D207" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E207" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="F207" s="29"/>
+      <c r="G207" s="42" t="s">
+        <v>564</v>
+      </c>
+      <c r="H207" s="42" t="s">
+        <v>391</v>
+      </c>
+      <c r="I207" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="J207" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K207" s="8"/>
+      <c r="L207" s="8"/>
+      <c r="M207" s="8"/>
+      <c r="N207" s="8"/>
+      <c r="O207" s="8"/>
+      <c r="P207" s="8"/>
+      <c r="Q207" s="8"/>
+      <c r="R207" s="74"/>
+      <c r="S207" s="75"/>
+      <c r="T207" s="76"/>
+      <c r="U207" s="77"/>
+    </row>
+    <row r="208" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A208" s="8">
+        <v>20</v>
+      </c>
+      <c r="B208" s="8"/>
+      <c r="C208" s="8"/>
+      <c r="D208" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E208" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="F208" s="29"/>
+      <c r="G208" s="42" t="s">
+        <v>565</v>
+      </c>
+      <c r="H208" s="42" t="s">
+        <v>392</v>
+      </c>
+      <c r="I208" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="J208" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K208" s="8"/>
+      <c r="L208" s="8"/>
+      <c r="M208" s="8"/>
+      <c r="N208" s="8"/>
+      <c r="O208" s="8"/>
+      <c r="P208" s="8"/>
+      <c r="Q208" s="8"/>
+      <c r="R208" s="74"/>
+      <c r="S208" s="75"/>
+      <c r="T208" s="76"/>
+      <c r="U208" s="77"/>
+    </row>
+    <row r="209" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A209" s="8">
+        <v>20</v>
+      </c>
+      <c r="B209" s="8"/>
+      <c r="C209" s="8"/>
+      <c r="D209" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E209" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="F209" s="29"/>
+      <c r="G209" s="42" t="s">
+        <v>566</v>
+      </c>
+      <c r="H209" s="42" t="s">
+        <v>393</v>
+      </c>
+      <c r="I209" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="J209" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K209" s="8"/>
+      <c r="L209" s="8"/>
+      <c r="M209" s="8"/>
+      <c r="N209" s="8"/>
+      <c r="O209" s="8"/>
+      <c r="P209" s="8"/>
+      <c r="Q209" s="8"/>
+      <c r="R209" s="74"/>
+      <c r="S209" s="75"/>
+      <c r="T209" s="76"/>
+      <c r="U209" s="77"/>
+    </row>
+    <row r="210" spans="1:21" s="9" customFormat="1">
+      <c r="A210" s="24"/>
+      <c r="B210" s="25"/>
+      <c r="C210" s="25"/>
+      <c r="D210" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="E204" s="6"/>
-      <c r="F204" s="6"/>
-      <c r="G204" s="6"/>
-      <c r="H204" s="6"/>
-      <c r="I204" s="6"/>
-      <c r="J204" s="6"/>
-      <c r="K204" s="6"/>
-      <c r="L204" s="6"/>
-      <c r="M204" s="6"/>
-      <c r="N204" s="6"/>
-      <c r="O204" s="6"/>
-      <c r="P204" s="6"/>
-      <c r="Q204" s="6"/>
-      <c r="R204" s="6"/>
-      <c r="S204" s="6"/>
-      <c r="T204" s="6"/>
-      <c r="U204" s="18"/>
-    </row>
-    <row r="205" spans="1:21" s="9" customFormat="1">
-      <c r="A205" s="55"/>
-      <c r="U205" s="43"/>
-    </row>
-    <row r="206" spans="1:21" s="9" customFormat="1">
-      <c r="A206" s="55"/>
-      <c r="U206" s="43"/>
-    </row>
-    <row r="207" spans="1:21" s="9" customFormat="1">
-      <c r="A207" s="55"/>
-      <c r="U207" s="43"/>
-    </row>
-    <row r="208" spans="1:21" s="9" customFormat="1">
-      <c r="A208" s="55"/>
-      <c r="U208" s="43"/>
-    </row>
-    <row r="209" spans="1:21" s="9" customFormat="1">
-      <c r="A209" s="55"/>
-      <c r="U209" s="43"/>
-    </row>
-    <row r="210" spans="1:21" s="9" customFormat="1">
-      <c r="A210" s="55"/>
-      <c r="U210" s="43"/>
+      <c r="E210" s="6"/>
+      <c r="F210" s="6"/>
+      <c r="G210" s="6"/>
+      <c r="H210" s="6"/>
+      <c r="I210" s="6"/>
+      <c r="J210" s="6"/>
+      <c r="K210" s="6"/>
+      <c r="L210" s="6"/>
+      <c r="M210" s="6"/>
+      <c r="N210" s="6"/>
+      <c r="O210" s="6"/>
+      <c r="P210" s="6"/>
+      <c r="Q210" s="6"/>
+      <c r="R210" s="6"/>
+      <c r="S210" s="6"/>
+      <c r="T210" s="6"/>
+      <c r="U210" s="18"/>
     </row>
     <row r="211" spans="1:21" s="9" customFormat="1">
       <c r="A211" s="55"/>
@@ -11256,69 +11472,154 @@
       <c r="U217" s="43"/>
     </row>
     <row r="218" spans="1:21" s="9" customFormat="1">
-      <c r="A218" s="62"/>
-      <c r="B218" s="48"/>
-      <c r="C218" s="48"/>
-      <c r="D218" s="48"/>
-      <c r="E218" s="48"/>
-      <c r="F218" s="48"/>
-      <c r="G218" s="48"/>
-      <c r="H218" s="48"/>
-      <c r="I218" s="48"/>
-      <c r="J218" s="48"/>
-      <c r="K218" s="48"/>
-      <c r="L218" s="48"/>
-      <c r="M218" s="48"/>
-      <c r="N218" s="48"/>
-      <c r="O218" s="48"/>
-      <c r="P218" s="48"/>
-      <c r="Q218" s="48"/>
-      <c r="R218" s="48"/>
-      <c r="S218" s="48"/>
-      <c r="T218" s="48"/>
-      <c r="U218" s="49"/>
+      <c r="A218" s="55"/>
+      <c r="U218" s="43"/>
+    </row>
+    <row r="219" spans="1:21" s="9" customFormat="1">
+      <c r="A219" s="55"/>
+      <c r="U219" s="43"/>
+    </row>
+    <row r="220" spans="1:21" s="9" customFormat="1">
+      <c r="A220" s="55"/>
+      <c r="U220" s="43"/>
+    </row>
+    <row r="221" spans="1:21" s="9" customFormat="1">
+      <c r="A221" s="55"/>
+      <c r="U221" s="43"/>
+    </row>
+    <row r="222" spans="1:21" s="9" customFormat="1">
+      <c r="A222" s="55"/>
+      <c r="U222" s="43"/>
+    </row>
+    <row r="223" spans="1:21" s="9" customFormat="1">
+      <c r="A223" s="55"/>
+      <c r="U223" s="43"/>
+    </row>
+    <row r="224" spans="1:21" s="9" customFormat="1">
+      <c r="A224" s="62"/>
+      <c r="B224" s="48"/>
+      <c r="C224" s="48"/>
+      <c r="D224" s="48"/>
+      <c r="E224" s="48"/>
+      <c r="F224" s="48"/>
+      <c r="G224" s="48"/>
+      <c r="H224" s="48"/>
+      <c r="I224" s="48"/>
+      <c r="J224" s="48"/>
+      <c r="K224" s="48"/>
+      <c r="L224" s="48"/>
+      <c r="M224" s="48"/>
+      <c r="N224" s="48"/>
+      <c r="O224" s="48"/>
+      <c r="P224" s="48"/>
+      <c r="Q224" s="48"/>
+      <c r="R224" s="48"/>
+      <c r="S224" s="48"/>
+      <c r="T224" s="48"/>
+      <c r="U224" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="175">
-    <mergeCell ref="R190:S190"/>
-    <mergeCell ref="T190:U190"/>
-    <mergeCell ref="R193:S193"/>
-    <mergeCell ref="T193:U193"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="T50:U50"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="T147:U147"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="R58:S58"/>
-    <mergeCell ref="T58:U58"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="T48:U48"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="T27:U27"/>
-    <mergeCell ref="R68:S68"/>
-    <mergeCell ref="T68:U68"/>
-    <mergeCell ref="R164:S164"/>
-    <mergeCell ref="T164:U164"/>
-    <mergeCell ref="R144:S144"/>
-    <mergeCell ref="T150:U150"/>
-    <mergeCell ref="T198:U198"/>
-    <mergeCell ref="R194:S194"/>
-    <mergeCell ref="T194:U194"/>
-    <mergeCell ref="R201:S201"/>
-    <mergeCell ref="T201:U201"/>
-    <mergeCell ref="R200:S200"/>
-    <mergeCell ref="T200:U200"/>
-    <mergeCell ref="R199:S199"/>
-    <mergeCell ref="T199:U199"/>
-    <mergeCell ref="R196:S196"/>
-    <mergeCell ref="T196:U196"/>
-    <mergeCell ref="R195:S195"/>
-    <mergeCell ref="T195:U195"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="R187:S187"/>
+    <mergeCell ref="T187:U187"/>
+    <mergeCell ref="R169:S169"/>
+    <mergeCell ref="T169:U169"/>
+    <mergeCell ref="R69:S69"/>
+    <mergeCell ref="R54:S54"/>
+    <mergeCell ref="T54:U54"/>
+    <mergeCell ref="R55:S55"/>
+    <mergeCell ref="T55:U55"/>
+    <mergeCell ref="R56:S56"/>
+    <mergeCell ref="T59:U59"/>
+    <mergeCell ref="R59:S59"/>
+    <mergeCell ref="R61:S61"/>
+    <mergeCell ref="T61:U61"/>
+    <mergeCell ref="T72:U72"/>
+    <mergeCell ref="R138:S138"/>
+    <mergeCell ref="T13:U13"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="T14:U14"/>
+    <mergeCell ref="T166:U166"/>
+    <mergeCell ref="R167:S167"/>
+    <mergeCell ref="T167:U167"/>
+    <mergeCell ref="R67:S67"/>
+    <mergeCell ref="T141:U141"/>
+    <mergeCell ref="R71:S71"/>
+    <mergeCell ref="T138:U138"/>
+    <mergeCell ref="R62:S62"/>
+    <mergeCell ref="R70:S70"/>
+    <mergeCell ref="T70:U70"/>
+    <mergeCell ref="T62:U62"/>
+    <mergeCell ref="R63:S63"/>
+    <mergeCell ref="T63:U63"/>
+    <mergeCell ref="R64:S64"/>
+    <mergeCell ref="T64:U64"/>
+    <mergeCell ref="R65:S65"/>
+    <mergeCell ref="T65:U65"/>
+    <mergeCell ref="R66:S66"/>
+    <mergeCell ref="R174:S174"/>
+    <mergeCell ref="T174:U174"/>
+    <mergeCell ref="R175:S175"/>
+    <mergeCell ref="T175:U175"/>
+    <mergeCell ref="T153:U153"/>
+    <mergeCell ref="R156:S156"/>
+    <mergeCell ref="T156:U156"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="T162:U162"/>
+    <mergeCell ref="R162:S162"/>
+    <mergeCell ref="R159:S159"/>
+    <mergeCell ref="T159:U159"/>
+    <mergeCell ref="R141:S141"/>
+    <mergeCell ref="R209:S209"/>
+    <mergeCell ref="T209:U209"/>
+    <mergeCell ref="T172:U172"/>
+    <mergeCell ref="R172:S172"/>
+    <mergeCell ref="R173:S173"/>
+    <mergeCell ref="T173:U173"/>
+    <mergeCell ref="R176:S176"/>
+    <mergeCell ref="R178:S178"/>
+    <mergeCell ref="T178:U178"/>
+    <mergeCell ref="T176:U176"/>
+    <mergeCell ref="R177:S177"/>
+    <mergeCell ref="T177:U177"/>
+    <mergeCell ref="T182:U182"/>
+    <mergeCell ref="R179:S179"/>
+    <mergeCell ref="T179:U179"/>
+    <mergeCell ref="R188:S188"/>
+    <mergeCell ref="T188:U188"/>
+    <mergeCell ref="R186:S186"/>
+    <mergeCell ref="T186:U186"/>
+    <mergeCell ref="R208:S208"/>
+    <mergeCell ref="T208:U208"/>
+    <mergeCell ref="R203:S203"/>
+    <mergeCell ref="T203:U203"/>
+    <mergeCell ref="R204:S204"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="R150:S150"/>
+    <mergeCell ref="T49:U49"/>
+    <mergeCell ref="T67:U67"/>
+    <mergeCell ref="T26:U26"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="R53:S53"/>
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="T53:U53"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="T45:U45"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="T42:U42"/>
+    <mergeCell ref="T51:U51"/>
+    <mergeCell ref="R60:S60"/>
+    <mergeCell ref="T66:U66"/>
+    <mergeCell ref="R147:S147"/>
     <mergeCell ref="T8:U8"/>
     <mergeCell ref="T69:U69"/>
     <mergeCell ref="R28:S28"/>
@@ -11343,54 +11644,48 @@
     <mergeCell ref="T21:U21"/>
     <mergeCell ref="T71:U71"/>
     <mergeCell ref="R13:S13"/>
-    <mergeCell ref="T15:U15"/>
-    <mergeCell ref="R150:S150"/>
-    <mergeCell ref="T49:U49"/>
-    <mergeCell ref="T67:U67"/>
-    <mergeCell ref="T26:U26"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="R53:S53"/>
-    <mergeCell ref="T11:U11"/>
-    <mergeCell ref="T53:U53"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="T45:U45"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="T42:U42"/>
-    <mergeCell ref="T51:U51"/>
-    <mergeCell ref="R60:S60"/>
-    <mergeCell ref="T66:U66"/>
-    <mergeCell ref="R147:S147"/>
-    <mergeCell ref="R203:S203"/>
-    <mergeCell ref="T203:U203"/>
-    <mergeCell ref="T172:U172"/>
-    <mergeCell ref="R172:S172"/>
-    <mergeCell ref="R173:S173"/>
-    <mergeCell ref="T173:U173"/>
-    <mergeCell ref="R176:S176"/>
-    <mergeCell ref="R178:S178"/>
-    <mergeCell ref="T178:U178"/>
-    <mergeCell ref="T176:U176"/>
-    <mergeCell ref="R177:S177"/>
-    <mergeCell ref="T177:U177"/>
-    <mergeCell ref="T182:U182"/>
-    <mergeCell ref="R179:S179"/>
-    <mergeCell ref="T179:U179"/>
-    <mergeCell ref="R185:S185"/>
-    <mergeCell ref="T185:U185"/>
-    <mergeCell ref="R183:S183"/>
-    <mergeCell ref="T183:U183"/>
+    <mergeCell ref="T204:U204"/>
+    <mergeCell ref="R200:S200"/>
+    <mergeCell ref="T200:U200"/>
+    <mergeCell ref="R207:S207"/>
+    <mergeCell ref="T207:U207"/>
+    <mergeCell ref="R206:S206"/>
+    <mergeCell ref="T206:U206"/>
+    <mergeCell ref="R205:S205"/>
+    <mergeCell ref="T205:U205"/>
     <mergeCell ref="R202:S202"/>
     <mergeCell ref="T202:U202"/>
-    <mergeCell ref="R197:S197"/>
-    <mergeCell ref="T197:U197"/>
-    <mergeCell ref="R198:S198"/>
+    <mergeCell ref="R201:S201"/>
+    <mergeCell ref="T201:U201"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="R58:S58"/>
+    <mergeCell ref="T58:U58"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="T48:U48"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="T27:U27"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="T24:U24"/>
+    <mergeCell ref="R196:S196"/>
+    <mergeCell ref="T196:U196"/>
+    <mergeCell ref="R199:S199"/>
+    <mergeCell ref="T199:U199"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="T50:U50"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="T147:U147"/>
+    <mergeCell ref="R68:S68"/>
+    <mergeCell ref="T68:U68"/>
+    <mergeCell ref="R164:S164"/>
+    <mergeCell ref="T164:U164"/>
+    <mergeCell ref="R144:S144"/>
+    <mergeCell ref="T150:U150"/>
     <mergeCell ref="R153:S153"/>
     <mergeCell ref="T144:U144"/>
     <mergeCell ref="R168:S168"/>
@@ -11400,61 +11695,6 @@
     <mergeCell ref="T170:U170"/>
     <mergeCell ref="R171:S171"/>
     <mergeCell ref="T171:U171"/>
-    <mergeCell ref="R174:S174"/>
-    <mergeCell ref="T174:U174"/>
-    <mergeCell ref="R175:S175"/>
-    <mergeCell ref="T175:U175"/>
-    <mergeCell ref="T153:U153"/>
-    <mergeCell ref="R156:S156"/>
-    <mergeCell ref="T156:U156"/>
-    <mergeCell ref="R72:S72"/>
-    <mergeCell ref="T162:U162"/>
-    <mergeCell ref="R162:S162"/>
-    <mergeCell ref="R159:S159"/>
-    <mergeCell ref="T159:U159"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="T24:U24"/>
-    <mergeCell ref="R141:S141"/>
-    <mergeCell ref="R67:S67"/>
-    <mergeCell ref="T141:U141"/>
-    <mergeCell ref="R71:S71"/>
-    <mergeCell ref="T138:U138"/>
-    <mergeCell ref="R62:S62"/>
-    <mergeCell ref="R70:S70"/>
-    <mergeCell ref="T70:U70"/>
-    <mergeCell ref="T62:U62"/>
-    <mergeCell ref="R63:S63"/>
-    <mergeCell ref="T63:U63"/>
-    <mergeCell ref="R64:S64"/>
-    <mergeCell ref="T64:U64"/>
-    <mergeCell ref="R65:S65"/>
-    <mergeCell ref="T65:U65"/>
-    <mergeCell ref="R66:S66"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="T12:U12"/>
-    <mergeCell ref="R184:S184"/>
-    <mergeCell ref="T184:U184"/>
-    <mergeCell ref="R169:S169"/>
-    <mergeCell ref="T169:U169"/>
-    <mergeCell ref="R69:S69"/>
-    <mergeCell ref="R54:S54"/>
-    <mergeCell ref="T54:U54"/>
-    <mergeCell ref="R55:S55"/>
-    <mergeCell ref="T55:U55"/>
-    <mergeCell ref="R56:S56"/>
-    <mergeCell ref="T59:U59"/>
-    <mergeCell ref="R59:S59"/>
-    <mergeCell ref="R61:S61"/>
-    <mergeCell ref="T61:U61"/>
-    <mergeCell ref="T72:U72"/>
-    <mergeCell ref="R138:S138"/>
-    <mergeCell ref="T13:U13"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="T14:U14"/>
-    <mergeCell ref="T166:U166"/>
-    <mergeCell ref="R167:S167"/>
-    <mergeCell ref="T167:U167"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.47244094488188981" right="0.43307086614173229" top="0.55118110236220474" bottom="0.59055118110236227" header="0.55118110236220474" footer="0.11811023622047245"/>
@@ -11608,65 +11848,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="107" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="79"/>
-      <c r="P1" s="79"/>
-      <c r="Q1" s="79"/>
-      <c r="R1" s="79"/>
-      <c r="S1" s="79"/>
-      <c r="T1" s="79"/>
-      <c r="U1" s="79"/>
-      <c r="V1" s="79"/>
-      <c r="W1" s="79"/>
-      <c r="X1" s="79"/>
-      <c r="Y1" s="79"/>
-      <c r="Z1" s="79"/>
-      <c r="AA1" s="79"/>
-      <c r="AB1" s="79"/>
-      <c r="AC1" s="79"/>
-      <c r="AD1" s="79"/>
-      <c r="AE1" s="79"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="79"/>
-      <c r="AH1" s="79"/>
-      <c r="AI1" s="79"/>
-      <c r="AJ1" s="79"/>
-      <c r="AK1" s="79"/>
-      <c r="AL1" s="79"/>
-      <c r="AM1" s="79"/>
-      <c r="AN1" s="79"/>
-      <c r="AO1" s="79"/>
-      <c r="AP1" s="79"/>
-      <c r="AQ1" s="79"/>
-      <c r="AR1" s="79"/>
-      <c r="AS1" s="79"/>
-      <c r="AT1" s="79"/>
-      <c r="AU1" s="79"/>
-      <c r="AV1" s="79"/>
-      <c r="AW1" s="79"/>
-      <c r="AX1" s="79"/>
-      <c r="AY1" s="79"/>
-      <c r="AZ1" s="79"/>
-      <c r="BA1" s="79"/>
-      <c r="BB1" s="79"/>
-      <c r="BC1" s="79"/>
-      <c r="BD1" s="79"/>
-      <c r="BE1" s="80"/>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
+      <c r="V1" s="108"/>
+      <c r="W1" s="108"/>
+      <c r="X1" s="108"/>
+      <c r="Y1" s="108"/>
+      <c r="Z1" s="108"/>
+      <c r="AA1" s="108"/>
+      <c r="AB1" s="108"/>
+      <c r="AC1" s="108"/>
+      <c r="AD1" s="108"/>
+      <c r="AE1" s="108"/>
+      <c r="AF1" s="108"/>
+      <c r="AG1" s="108"/>
+      <c r="AH1" s="108"/>
+      <c r="AI1" s="108"/>
+      <c r="AJ1" s="108"/>
+      <c r="AK1" s="108"/>
+      <c r="AL1" s="108"/>
+      <c r="AM1" s="108"/>
+      <c r="AN1" s="108"/>
+      <c r="AO1" s="108"/>
+      <c r="AP1" s="108"/>
+      <c r="AQ1" s="108"/>
+      <c r="AR1" s="108"/>
+      <c r="AS1" s="108"/>
+      <c r="AT1" s="108"/>
+      <c r="AU1" s="108"/>
+      <c r="AV1" s="108"/>
+      <c r="AW1" s="108"/>
+      <c r="AX1" s="108"/>
+      <c r="AY1" s="108"/>
+      <c r="AZ1" s="108"/>
+      <c r="BA1" s="108"/>
+      <c r="BB1" s="108"/>
+      <c r="BC1" s="108"/>
+      <c r="BD1" s="108"/>
+      <c r="BE1" s="109"/>
     </row>
     <row r="2" spans="1:57" ht="12" customHeight="1" thickBot="1">
       <c r="A2" s="51"/>
@@ -11713,1984 +11953,2077 @@
       <c r="AP2" s="51"/>
     </row>
     <row r="3" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="110" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="84" t="s">
+      <c r="B3" s="111"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="111"/>
+      <c r="F3" s="111"/>
+      <c r="G3" s="112"/>
+      <c r="H3" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="82"/>
-      <c r="J3" s="82"/>
-      <c r="K3" s="82"/>
-      <c r="L3" s="82"/>
-      <c r="M3" s="82"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="84" t="s">
+      <c r="I3" s="111"/>
+      <c r="J3" s="111"/>
+      <c r="K3" s="111"/>
+      <c r="L3" s="111"/>
+      <c r="M3" s="111"/>
+      <c r="N3" s="112"/>
+      <c r="O3" s="113" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="85"/>
-      <c r="Q3" s="85"/>
-      <c r="R3" s="85"/>
-      <c r="S3" s="85"/>
-      <c r="T3" s="85"/>
-      <c r="U3" s="85"/>
-      <c r="V3" s="85"/>
-      <c r="W3" s="85"/>
-      <c r="X3" s="85"/>
-      <c r="Y3" s="85"/>
-      <c r="Z3" s="85"/>
-      <c r="AA3" s="85"/>
-      <c r="AB3" s="85"/>
-      <c r="AC3" s="85"/>
-      <c r="AD3" s="85"/>
-      <c r="AE3" s="85"/>
-      <c r="AF3" s="85"/>
-      <c r="AG3" s="85"/>
-      <c r="AH3" s="85"/>
-      <c r="AI3" s="85"/>
-      <c r="AJ3" s="85"/>
-      <c r="AK3" s="85"/>
-      <c r="AL3" s="85"/>
-      <c r="AM3" s="85"/>
-      <c r="AN3" s="85"/>
-      <c r="AO3" s="85"/>
-      <c r="AP3" s="86"/>
-      <c r="AQ3" s="84" t="s">
+      <c r="P3" s="114"/>
+      <c r="Q3" s="114"/>
+      <c r="R3" s="114"/>
+      <c r="S3" s="114"/>
+      <c r="T3" s="114"/>
+      <c r="U3" s="114"/>
+      <c r="V3" s="114"/>
+      <c r="W3" s="114"/>
+      <c r="X3" s="114"/>
+      <c r="Y3" s="114"/>
+      <c r="Z3" s="114"/>
+      <c r="AA3" s="114"/>
+      <c r="AB3" s="114"/>
+      <c r="AC3" s="114"/>
+      <c r="AD3" s="114"/>
+      <c r="AE3" s="114"/>
+      <c r="AF3" s="114"/>
+      <c r="AG3" s="114"/>
+      <c r="AH3" s="114"/>
+      <c r="AI3" s="114"/>
+      <c r="AJ3" s="114"/>
+      <c r="AK3" s="114"/>
+      <c r="AL3" s="114"/>
+      <c r="AM3" s="114"/>
+      <c r="AN3" s="114"/>
+      <c r="AO3" s="114"/>
+      <c r="AP3" s="115"/>
+      <c r="AQ3" s="113" t="s">
         <v>18</v>
       </c>
-      <c r="AR3" s="87"/>
-      <c r="AS3" s="87"/>
-      <c r="AT3" s="87"/>
-      <c r="AU3" s="87"/>
-      <c r="AV3" s="87"/>
-      <c r="AW3" s="87"/>
-      <c r="AX3" s="87"/>
-      <c r="AY3" s="87"/>
-      <c r="AZ3" s="87"/>
-      <c r="BA3" s="87"/>
-      <c r="BB3" s="87"/>
-      <c r="BC3" s="87"/>
-      <c r="BD3" s="87"/>
-      <c r="BE3" s="88"/>
+      <c r="AR3" s="116"/>
+      <c r="AS3" s="116"/>
+      <c r="AT3" s="116"/>
+      <c r="AU3" s="116"/>
+      <c r="AV3" s="116"/>
+      <c r="AW3" s="116"/>
+      <c r="AX3" s="116"/>
+      <c r="AY3" s="116"/>
+      <c r="AZ3" s="116"/>
+      <c r="BA3" s="116"/>
+      <c r="BB3" s="116"/>
+      <c r="BC3" s="116"/>
+      <c r="BD3" s="116"/>
+      <c r="BE3" s="117"/>
     </row>
     <row r="4" spans="1:57" ht="15" customHeight="1">
-      <c r="A4" s="89">
+      <c r="A4" s="118">
         <v>1</v>
       </c>
-      <c r="B4" s="90"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="92"/>
-      <c r="I4" s="93"/>
-      <c r="J4" s="93"/>
-      <c r="K4" s="93"/>
-      <c r="L4" s="93"/>
-      <c r="M4" s="93"/>
-      <c r="N4" s="94"/>
-      <c r="O4" s="92" t="s">
+      <c r="B4" s="119"/>
+      <c r="C4" s="119"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="122"/>
+      <c r="L4" s="122"/>
+      <c r="M4" s="122"/>
+      <c r="N4" s="123"/>
+      <c r="O4" s="121" t="s">
         <v>19</v>
       </c>
-      <c r="P4" s="95"/>
-      <c r="Q4" s="95"/>
-      <c r="R4" s="95"/>
-      <c r="S4" s="95"/>
-      <c r="T4" s="95"/>
-      <c r="U4" s="95"/>
-      <c r="V4" s="95"/>
-      <c r="W4" s="95"/>
-      <c r="X4" s="95"/>
-      <c r="Y4" s="95"/>
-      <c r="Z4" s="95"/>
-      <c r="AA4" s="95"/>
-      <c r="AB4" s="95"/>
-      <c r="AC4" s="95"/>
-      <c r="AD4" s="95"/>
-      <c r="AE4" s="95"/>
-      <c r="AF4" s="95"/>
-      <c r="AG4" s="95"/>
-      <c r="AH4" s="95"/>
-      <c r="AI4" s="95"/>
-      <c r="AJ4" s="95"/>
-      <c r="AK4" s="95"/>
-      <c r="AL4" s="95"/>
-      <c r="AM4" s="95"/>
-      <c r="AN4" s="95"/>
-      <c r="AO4" s="95"/>
-      <c r="AP4" s="96"/>
-      <c r="AQ4" s="97"/>
-      <c r="AR4" s="95"/>
-      <c r="AS4" s="95"/>
-      <c r="AT4" s="95"/>
-      <c r="AU4" s="95"/>
-      <c r="AV4" s="95"/>
-      <c r="AW4" s="95"/>
-      <c r="AX4" s="95"/>
-      <c r="AY4" s="95"/>
-      <c r="AZ4" s="95"/>
-      <c r="BA4" s="95"/>
-      <c r="BB4" s="95"/>
-      <c r="BC4" s="95"/>
-      <c r="BD4" s="95"/>
-      <c r="BE4" s="98"/>
+      <c r="P4" s="124"/>
+      <c r="Q4" s="124"/>
+      <c r="R4" s="124"/>
+      <c r="S4" s="124"/>
+      <c r="T4" s="124"/>
+      <c r="U4" s="124"/>
+      <c r="V4" s="124"/>
+      <c r="W4" s="124"/>
+      <c r="X4" s="124"/>
+      <c r="Y4" s="124"/>
+      <c r="Z4" s="124"/>
+      <c r="AA4" s="124"/>
+      <c r="AB4" s="124"/>
+      <c r="AC4" s="124"/>
+      <c r="AD4" s="124"/>
+      <c r="AE4" s="124"/>
+      <c r="AF4" s="124"/>
+      <c r="AG4" s="124"/>
+      <c r="AH4" s="124"/>
+      <c r="AI4" s="124"/>
+      <c r="AJ4" s="124"/>
+      <c r="AK4" s="124"/>
+      <c r="AL4" s="124"/>
+      <c r="AM4" s="124"/>
+      <c r="AN4" s="124"/>
+      <c r="AO4" s="124"/>
+      <c r="AP4" s="125"/>
+      <c r="AQ4" s="126"/>
+      <c r="AR4" s="124"/>
+      <c r="AS4" s="124"/>
+      <c r="AT4" s="124"/>
+      <c r="AU4" s="124"/>
+      <c r="AV4" s="124"/>
+      <c r="AW4" s="124"/>
+      <c r="AX4" s="124"/>
+      <c r="AY4" s="124"/>
+      <c r="AZ4" s="124"/>
+      <c r="BA4" s="124"/>
+      <c r="BB4" s="124"/>
+      <c r="BC4" s="124"/>
+      <c r="BD4" s="124"/>
+      <c r="BE4" s="127"/>
     </row>
     <row r="5" spans="1:57" ht="15" customHeight="1">
-      <c r="A5" s="99">
+      <c r="A5" s="88">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B5" s="100"/>
-      <c r="C5" s="100"/>
-      <c r="D5" s="100"/>
-      <c r="E5" s="100"/>
-      <c r="F5" s="100"/>
-      <c r="G5" s="101"/>
-      <c r="H5" s="105"/>
-      <c r="I5" s="106"/>
-      <c r="J5" s="106"/>
-      <c r="K5" s="106"/>
-      <c r="L5" s="106"/>
-      <c r="M5" s="106"/>
-      <c r="N5" s="107"/>
-      <c r="O5" s="112" t="s">
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="91"/>
+      <c r="I5" s="92"/>
+      <c r="J5" s="92"/>
+      <c r="K5" s="92"/>
+      <c r="L5" s="92"/>
+      <c r="M5" s="92"/>
+      <c r="N5" s="93"/>
+      <c r="O5" s="101" t="s">
         <v>567</v>
       </c>
-      <c r="P5" s="113"/>
-      <c r="Q5" s="113"/>
-      <c r="R5" s="113"/>
-      <c r="S5" s="113"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="113"/>
-      <c r="V5" s="113"/>
-      <c r="W5" s="113"/>
-      <c r="X5" s="113"/>
-      <c r="Y5" s="113"/>
-      <c r="Z5" s="113"/>
-      <c r="AA5" s="113"/>
-      <c r="AB5" s="113"/>
-      <c r="AC5" s="113"/>
-      <c r="AD5" s="113"/>
-      <c r="AE5" s="113"/>
-      <c r="AF5" s="113"/>
-      <c r="AG5" s="113"/>
-      <c r="AH5" s="113"/>
-      <c r="AI5" s="113"/>
-      <c r="AJ5" s="113"/>
-      <c r="AK5" s="113"/>
-      <c r="AL5" s="113"/>
-      <c r="AM5" s="113"/>
-      <c r="AN5" s="113"/>
-      <c r="AO5" s="113"/>
-      <c r="AP5" s="114"/>
-      <c r="AQ5" s="115" t="s">
+      <c r="P5" s="102"/>
+      <c r="Q5" s="102"/>
+      <c r="R5" s="102"/>
+      <c r="S5" s="102"/>
+      <c r="T5" s="102"/>
+      <c r="U5" s="102"/>
+      <c r="V5" s="102"/>
+      <c r="W5" s="102"/>
+      <c r="X5" s="102"/>
+      <c r="Y5" s="102"/>
+      <c r="Z5" s="102"/>
+      <c r="AA5" s="102"/>
+      <c r="AB5" s="102"/>
+      <c r="AC5" s="102"/>
+      <c r="AD5" s="102"/>
+      <c r="AE5" s="102"/>
+      <c r="AF5" s="102"/>
+      <c r="AG5" s="102"/>
+      <c r="AH5" s="102"/>
+      <c r="AI5" s="102"/>
+      <c r="AJ5" s="102"/>
+      <c r="AK5" s="102"/>
+      <c r="AL5" s="102"/>
+      <c r="AM5" s="102"/>
+      <c r="AN5" s="102"/>
+      <c r="AO5" s="102"/>
+      <c r="AP5" s="103"/>
+      <c r="AQ5" s="104" t="s">
         <v>568</v>
       </c>
-      <c r="AR5" s="116"/>
-      <c r="AS5" s="116"/>
-      <c r="AT5" s="116"/>
-      <c r="AU5" s="116"/>
-      <c r="AV5" s="116"/>
-      <c r="AW5" s="116"/>
-      <c r="AX5" s="116"/>
-      <c r="AY5" s="116"/>
-      <c r="AZ5" s="116"/>
-      <c r="BA5" s="116"/>
-      <c r="BB5" s="116"/>
-      <c r="BC5" s="116"/>
-      <c r="BD5" s="116"/>
-      <c r="BE5" s="117"/>
+      <c r="AR5" s="105"/>
+      <c r="AS5" s="105"/>
+      <c r="AT5" s="105"/>
+      <c r="AU5" s="105"/>
+      <c r="AV5" s="105"/>
+      <c r="AW5" s="105"/>
+      <c r="AX5" s="105"/>
+      <c r="AY5" s="105"/>
+      <c r="AZ5" s="105"/>
+      <c r="BA5" s="105"/>
+      <c r="BB5" s="105"/>
+      <c r="BC5" s="105"/>
+      <c r="BD5" s="105"/>
+      <c r="BE5" s="106"/>
     </row>
     <row r="6" spans="1:57" ht="15" customHeight="1">
-      <c r="A6" s="99"/>
-      <c r="B6" s="100"/>
-      <c r="C6" s="100"/>
-      <c r="D6" s="100"/>
-      <c r="E6" s="100"/>
-      <c r="F6" s="100"/>
-      <c r="G6" s="101"/>
-      <c r="H6" s="102"/>
-      <c r="I6" s="103"/>
-      <c r="J6" s="103"/>
-      <c r="K6" s="103"/>
-      <c r="L6" s="103"/>
-      <c r="M6" s="103"/>
-      <c r="N6" s="104"/>
-      <c r="O6" s="105"/>
-      <c r="P6" s="109"/>
-      <c r="Q6" s="109"/>
-      <c r="R6" s="109"/>
-      <c r="S6" s="109"/>
-      <c r="T6" s="109"/>
-      <c r="U6" s="109"/>
-      <c r="V6" s="109"/>
-      <c r="W6" s="109"/>
-      <c r="X6" s="109"/>
-      <c r="Y6" s="109"/>
-      <c r="Z6" s="109"/>
-      <c r="AA6" s="109"/>
-      <c r="AB6" s="109"/>
-      <c r="AC6" s="109"/>
-      <c r="AD6" s="109"/>
-      <c r="AE6" s="109"/>
-      <c r="AF6" s="109"/>
-      <c r="AG6" s="109"/>
-      <c r="AH6" s="109"/>
-      <c r="AI6" s="109"/>
-      <c r="AJ6" s="109"/>
-      <c r="AK6" s="109"/>
-      <c r="AL6" s="109"/>
-      <c r="AM6" s="109"/>
-      <c r="AN6" s="109"/>
-      <c r="AO6" s="109"/>
-      <c r="AP6" s="111"/>
-      <c r="AQ6" s="108"/>
-      <c r="AR6" s="109"/>
-      <c r="AS6" s="109"/>
-      <c r="AT6" s="109"/>
-      <c r="AU6" s="109"/>
-      <c r="AV6" s="109"/>
-      <c r="AW6" s="109"/>
-      <c r="AX6" s="109"/>
-      <c r="AY6" s="109"/>
-      <c r="AZ6" s="109"/>
-      <c r="BA6" s="109"/>
-      <c r="BB6" s="109"/>
-      <c r="BC6" s="109"/>
-      <c r="BD6" s="109"/>
-      <c r="BE6" s="110"/>
+      <c r="A6" s="88"/>
+      <c r="B6" s="89"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="90"/>
+      <c r="H6" s="98"/>
+      <c r="I6" s="99"/>
+      <c r="J6" s="99"/>
+      <c r="K6" s="99"/>
+      <c r="L6" s="99"/>
+      <c r="M6" s="99"/>
+      <c r="N6" s="100"/>
+      <c r="O6" s="91"/>
+      <c r="P6" s="94"/>
+      <c r="Q6" s="94"/>
+      <c r="R6" s="94"/>
+      <c r="S6" s="94"/>
+      <c r="T6" s="94"/>
+      <c r="U6" s="94"/>
+      <c r="V6" s="94"/>
+      <c r="W6" s="94"/>
+      <c r="X6" s="94"/>
+      <c r="Y6" s="94"/>
+      <c r="Z6" s="94"/>
+      <c r="AA6" s="94"/>
+      <c r="AB6" s="94"/>
+      <c r="AC6" s="94"/>
+      <c r="AD6" s="94"/>
+      <c r="AE6" s="94"/>
+      <c r="AF6" s="94"/>
+      <c r="AG6" s="94"/>
+      <c r="AH6" s="94"/>
+      <c r="AI6" s="94"/>
+      <c r="AJ6" s="94"/>
+      <c r="AK6" s="94"/>
+      <c r="AL6" s="94"/>
+      <c r="AM6" s="94"/>
+      <c r="AN6" s="94"/>
+      <c r="AO6" s="94"/>
+      <c r="AP6" s="95"/>
+      <c r="AQ6" s="96"/>
+      <c r="AR6" s="94"/>
+      <c r="AS6" s="94"/>
+      <c r="AT6" s="94"/>
+      <c r="AU6" s="94"/>
+      <c r="AV6" s="94"/>
+      <c r="AW6" s="94"/>
+      <c r="AX6" s="94"/>
+      <c r="AY6" s="94"/>
+      <c r="AZ6" s="94"/>
+      <c r="BA6" s="94"/>
+      <c r="BB6" s="94"/>
+      <c r="BC6" s="94"/>
+      <c r="BD6" s="94"/>
+      <c r="BE6" s="97"/>
     </row>
     <row r="7" spans="1:57" ht="15" customHeight="1">
-      <c r="A7" s="99"/>
-      <c r="B7" s="100"/>
-      <c r="C7" s="100"/>
-      <c r="D7" s="100"/>
-      <c r="E7" s="100"/>
-      <c r="F7" s="100"/>
-      <c r="G7" s="101"/>
-      <c r="H7" s="102"/>
-      <c r="I7" s="103"/>
-      <c r="J7" s="103"/>
-      <c r="K7" s="103"/>
-      <c r="L7" s="103"/>
-      <c r="M7" s="103"/>
-      <c r="N7" s="104"/>
-      <c r="O7" s="105"/>
-      <c r="P7" s="106"/>
-      <c r="Q7" s="106"/>
-      <c r="R7" s="106"/>
-      <c r="S7" s="106"/>
-      <c r="T7" s="106"/>
-      <c r="U7" s="106"/>
-      <c r="V7" s="106"/>
-      <c r="W7" s="106"/>
-      <c r="X7" s="106"/>
-      <c r="Y7" s="106"/>
-      <c r="Z7" s="106"/>
-      <c r="AA7" s="106"/>
-      <c r="AB7" s="106"/>
-      <c r="AC7" s="106"/>
-      <c r="AD7" s="106"/>
-      <c r="AE7" s="106"/>
-      <c r="AF7" s="106"/>
-      <c r="AG7" s="106"/>
-      <c r="AH7" s="106"/>
-      <c r="AI7" s="106"/>
-      <c r="AJ7" s="106"/>
-      <c r="AK7" s="106"/>
-      <c r="AL7" s="106"/>
-      <c r="AM7" s="106"/>
-      <c r="AN7" s="106"/>
-      <c r="AO7" s="106"/>
-      <c r="AP7" s="107"/>
-      <c r="AQ7" s="108"/>
-      <c r="AR7" s="109"/>
-      <c r="AS7" s="109"/>
-      <c r="AT7" s="109"/>
-      <c r="AU7" s="109"/>
-      <c r="AV7" s="109"/>
-      <c r="AW7" s="109"/>
-      <c r="AX7" s="109"/>
-      <c r="AY7" s="109"/>
-      <c r="AZ7" s="109"/>
-      <c r="BA7" s="109"/>
-      <c r="BB7" s="109"/>
-      <c r="BC7" s="109"/>
-      <c r="BD7" s="109"/>
-      <c r="BE7" s="110"/>
+      <c r="A7" s="88"/>
+      <c r="B7" s="89"/>
+      <c r="C7" s="89"/>
+      <c r="D7" s="89"/>
+      <c r="E7" s="89"/>
+      <c r="F7" s="89"/>
+      <c r="G7" s="90"/>
+      <c r="H7" s="98"/>
+      <c r="I7" s="99"/>
+      <c r="J7" s="99"/>
+      <c r="K7" s="99"/>
+      <c r="L7" s="99"/>
+      <c r="M7" s="99"/>
+      <c r="N7" s="100"/>
+      <c r="O7" s="91"/>
+      <c r="P7" s="92"/>
+      <c r="Q7" s="92"/>
+      <c r="R7" s="92"/>
+      <c r="S7" s="92"/>
+      <c r="T7" s="92"/>
+      <c r="U7" s="92"/>
+      <c r="V7" s="92"/>
+      <c r="W7" s="92"/>
+      <c r="X7" s="92"/>
+      <c r="Y7" s="92"/>
+      <c r="Z7" s="92"/>
+      <c r="AA7" s="92"/>
+      <c r="AB7" s="92"/>
+      <c r="AC7" s="92"/>
+      <c r="AD7" s="92"/>
+      <c r="AE7" s="92"/>
+      <c r="AF7" s="92"/>
+      <c r="AG7" s="92"/>
+      <c r="AH7" s="92"/>
+      <c r="AI7" s="92"/>
+      <c r="AJ7" s="92"/>
+      <c r="AK7" s="92"/>
+      <c r="AL7" s="92"/>
+      <c r="AM7" s="92"/>
+      <c r="AN7" s="92"/>
+      <c r="AO7" s="92"/>
+      <c r="AP7" s="93"/>
+      <c r="AQ7" s="96"/>
+      <c r="AR7" s="94"/>
+      <c r="AS7" s="94"/>
+      <c r="AT7" s="94"/>
+      <c r="AU7" s="94"/>
+      <c r="AV7" s="94"/>
+      <c r="AW7" s="94"/>
+      <c r="AX7" s="94"/>
+      <c r="AY7" s="94"/>
+      <c r="AZ7" s="94"/>
+      <c r="BA7" s="94"/>
+      <c r="BB7" s="94"/>
+      <c r="BC7" s="94"/>
+      <c r="BD7" s="94"/>
+      <c r="BE7" s="97"/>
     </row>
     <row r="8" spans="1:57" ht="15" customHeight="1">
-      <c r="A8" s="99"/>
-      <c r="B8" s="100"/>
-      <c r="C8" s="100"/>
-      <c r="D8" s="100"/>
-      <c r="E8" s="100"/>
-      <c r="F8" s="100"/>
-      <c r="G8" s="101"/>
-      <c r="H8" s="105"/>
-      <c r="I8" s="106"/>
-      <c r="J8" s="106"/>
-      <c r="K8" s="106"/>
-      <c r="L8" s="106"/>
-      <c r="M8" s="106"/>
-      <c r="N8" s="107"/>
-      <c r="O8" s="105"/>
-      <c r="P8" s="109"/>
-      <c r="Q8" s="109"/>
-      <c r="R8" s="109"/>
-      <c r="S8" s="109"/>
-      <c r="T8" s="109"/>
-      <c r="U8" s="109"/>
-      <c r="V8" s="109"/>
-      <c r="W8" s="109"/>
-      <c r="X8" s="109"/>
-      <c r="Y8" s="109"/>
-      <c r="Z8" s="109"/>
-      <c r="AA8" s="109"/>
-      <c r="AB8" s="109"/>
-      <c r="AC8" s="109"/>
-      <c r="AD8" s="109"/>
-      <c r="AE8" s="109"/>
-      <c r="AF8" s="109"/>
-      <c r="AG8" s="109"/>
-      <c r="AH8" s="109"/>
-      <c r="AI8" s="109"/>
-      <c r="AJ8" s="109"/>
-      <c r="AK8" s="109"/>
-      <c r="AL8" s="109"/>
-      <c r="AM8" s="109"/>
-      <c r="AN8" s="109"/>
-      <c r="AO8" s="109"/>
-      <c r="AP8" s="111"/>
-      <c r="AQ8" s="108"/>
-      <c r="AR8" s="109"/>
-      <c r="AS8" s="109"/>
-      <c r="AT8" s="109"/>
-      <c r="AU8" s="109"/>
-      <c r="AV8" s="109"/>
-      <c r="AW8" s="109"/>
-      <c r="AX8" s="109"/>
-      <c r="AY8" s="109"/>
-      <c r="AZ8" s="109"/>
-      <c r="BA8" s="109"/>
-      <c r="BB8" s="109"/>
-      <c r="BC8" s="109"/>
-      <c r="BD8" s="109"/>
-      <c r="BE8" s="110"/>
+      <c r="A8" s="88"/>
+      <c r="B8" s="89"/>
+      <c r="C8" s="89"/>
+      <c r="D8" s="89"/>
+      <c r="E8" s="89"/>
+      <c r="F8" s="89"/>
+      <c r="G8" s="90"/>
+      <c r="H8" s="91"/>
+      <c r="I8" s="92"/>
+      <c r="J8" s="92"/>
+      <c r="K8" s="92"/>
+      <c r="L8" s="92"/>
+      <c r="M8" s="92"/>
+      <c r="N8" s="93"/>
+      <c r="O8" s="91"/>
+      <c r="P8" s="94"/>
+      <c r="Q8" s="94"/>
+      <c r="R8" s="94"/>
+      <c r="S8" s="94"/>
+      <c r="T8" s="94"/>
+      <c r="U8" s="94"/>
+      <c r="V8" s="94"/>
+      <c r="W8" s="94"/>
+      <c r="X8" s="94"/>
+      <c r="Y8" s="94"/>
+      <c r="Z8" s="94"/>
+      <c r="AA8" s="94"/>
+      <c r="AB8" s="94"/>
+      <c r="AC8" s="94"/>
+      <c r="AD8" s="94"/>
+      <c r="AE8" s="94"/>
+      <c r="AF8" s="94"/>
+      <c r="AG8" s="94"/>
+      <c r="AH8" s="94"/>
+      <c r="AI8" s="94"/>
+      <c r="AJ8" s="94"/>
+      <c r="AK8" s="94"/>
+      <c r="AL8" s="94"/>
+      <c r="AM8" s="94"/>
+      <c r="AN8" s="94"/>
+      <c r="AO8" s="94"/>
+      <c r="AP8" s="95"/>
+      <c r="AQ8" s="96"/>
+      <c r="AR8" s="94"/>
+      <c r="AS8" s="94"/>
+      <c r="AT8" s="94"/>
+      <c r="AU8" s="94"/>
+      <c r="AV8" s="94"/>
+      <c r="AW8" s="94"/>
+      <c r="AX8" s="94"/>
+      <c r="AY8" s="94"/>
+      <c r="AZ8" s="94"/>
+      <c r="BA8" s="94"/>
+      <c r="BB8" s="94"/>
+      <c r="BC8" s="94"/>
+      <c r="BD8" s="94"/>
+      <c r="BE8" s="97"/>
     </row>
     <row r="9" spans="1:57" ht="15" customHeight="1">
-      <c r="A9" s="99"/>
-      <c r="B9" s="100"/>
-      <c r="C9" s="100"/>
-      <c r="D9" s="100"/>
-      <c r="E9" s="100"/>
-      <c r="F9" s="100"/>
-      <c r="G9" s="101"/>
-      <c r="H9" s="105"/>
-      <c r="I9" s="106"/>
-      <c r="J9" s="106"/>
-      <c r="K9" s="106"/>
-      <c r="L9" s="106"/>
-      <c r="M9" s="106"/>
-      <c r="N9" s="107"/>
-      <c r="O9" s="105"/>
-      <c r="P9" s="109"/>
-      <c r="Q9" s="109"/>
-      <c r="R9" s="109"/>
-      <c r="S9" s="109"/>
-      <c r="T9" s="109"/>
-      <c r="U9" s="109"/>
-      <c r="V9" s="109"/>
-      <c r="W9" s="109"/>
-      <c r="X9" s="109"/>
-      <c r="Y9" s="109"/>
-      <c r="Z9" s="109"/>
-      <c r="AA9" s="109"/>
-      <c r="AB9" s="109"/>
-      <c r="AC9" s="109"/>
-      <c r="AD9" s="109"/>
-      <c r="AE9" s="109"/>
-      <c r="AF9" s="109"/>
-      <c r="AG9" s="109"/>
-      <c r="AH9" s="109"/>
-      <c r="AI9" s="109"/>
-      <c r="AJ9" s="109"/>
-      <c r="AK9" s="109"/>
-      <c r="AL9" s="109"/>
-      <c r="AM9" s="109"/>
-      <c r="AN9" s="109"/>
-      <c r="AO9" s="109"/>
-      <c r="AP9" s="111"/>
-      <c r="AQ9" s="108"/>
-      <c r="AR9" s="109"/>
-      <c r="AS9" s="109"/>
-      <c r="AT9" s="109"/>
-      <c r="AU9" s="109"/>
-      <c r="AV9" s="109"/>
-      <c r="AW9" s="109"/>
-      <c r="AX9" s="109"/>
-      <c r="AY9" s="109"/>
-      <c r="AZ9" s="109"/>
-      <c r="BA9" s="109"/>
-      <c r="BB9" s="109"/>
-      <c r="BC9" s="109"/>
-      <c r="BD9" s="109"/>
-      <c r="BE9" s="110"/>
+      <c r="A9" s="88"/>
+      <c r="B9" s="89"/>
+      <c r="C9" s="89"/>
+      <c r="D9" s="89"/>
+      <c r="E9" s="89"/>
+      <c r="F9" s="89"/>
+      <c r="G9" s="90"/>
+      <c r="H9" s="91"/>
+      <c r="I9" s="92"/>
+      <c r="J9" s="92"/>
+      <c r="K9" s="92"/>
+      <c r="L9" s="92"/>
+      <c r="M9" s="92"/>
+      <c r="N9" s="93"/>
+      <c r="O9" s="91"/>
+      <c r="P9" s="94"/>
+      <c r="Q9" s="94"/>
+      <c r="R9" s="94"/>
+      <c r="S9" s="94"/>
+      <c r="T9" s="94"/>
+      <c r="U9" s="94"/>
+      <c r="V9" s="94"/>
+      <c r="W9" s="94"/>
+      <c r="X9" s="94"/>
+      <c r="Y9" s="94"/>
+      <c r="Z9" s="94"/>
+      <c r="AA9" s="94"/>
+      <c r="AB9" s="94"/>
+      <c r="AC9" s="94"/>
+      <c r="AD9" s="94"/>
+      <c r="AE9" s="94"/>
+      <c r="AF9" s="94"/>
+      <c r="AG9" s="94"/>
+      <c r="AH9" s="94"/>
+      <c r="AI9" s="94"/>
+      <c r="AJ9" s="94"/>
+      <c r="AK9" s="94"/>
+      <c r="AL9" s="94"/>
+      <c r="AM9" s="94"/>
+      <c r="AN9" s="94"/>
+      <c r="AO9" s="94"/>
+      <c r="AP9" s="95"/>
+      <c r="AQ9" s="96"/>
+      <c r="AR9" s="94"/>
+      <c r="AS9" s="94"/>
+      <c r="AT9" s="94"/>
+      <c r="AU9" s="94"/>
+      <c r="AV9" s="94"/>
+      <c r="AW9" s="94"/>
+      <c r="AX9" s="94"/>
+      <c r="AY9" s="94"/>
+      <c r="AZ9" s="94"/>
+      <c r="BA9" s="94"/>
+      <c r="BB9" s="94"/>
+      <c r="BC9" s="94"/>
+      <c r="BD9" s="94"/>
+      <c r="BE9" s="97"/>
     </row>
     <row r="10" spans="1:57" ht="15" customHeight="1">
-      <c r="A10" s="99"/>
-      <c r="B10" s="100"/>
-      <c r="C10" s="100"/>
-      <c r="D10" s="100"/>
-      <c r="E10" s="100"/>
-      <c r="F10" s="100"/>
-      <c r="G10" s="101"/>
-      <c r="H10" s="105"/>
-      <c r="I10" s="106"/>
-      <c r="J10" s="106"/>
-      <c r="K10" s="106"/>
-      <c r="L10" s="106"/>
-      <c r="M10" s="106"/>
-      <c r="N10" s="107"/>
-      <c r="O10" s="105"/>
-      <c r="P10" s="109"/>
-      <c r="Q10" s="109"/>
-      <c r="R10" s="109"/>
-      <c r="S10" s="109"/>
-      <c r="T10" s="109"/>
-      <c r="U10" s="109"/>
-      <c r="V10" s="109"/>
-      <c r="W10" s="109"/>
-      <c r="X10" s="109"/>
-      <c r="Y10" s="109"/>
-      <c r="Z10" s="109"/>
-      <c r="AA10" s="109"/>
-      <c r="AB10" s="109"/>
-      <c r="AC10" s="109"/>
-      <c r="AD10" s="109"/>
-      <c r="AE10" s="109"/>
-      <c r="AF10" s="109"/>
-      <c r="AG10" s="109"/>
-      <c r="AH10" s="109"/>
-      <c r="AI10" s="109"/>
-      <c r="AJ10" s="109"/>
-      <c r="AK10" s="109"/>
-      <c r="AL10" s="109"/>
-      <c r="AM10" s="109"/>
-      <c r="AN10" s="109"/>
-      <c r="AO10" s="109"/>
-      <c r="AP10" s="111"/>
-      <c r="AQ10" s="108"/>
-      <c r="AR10" s="109"/>
-      <c r="AS10" s="109"/>
-      <c r="AT10" s="109"/>
-      <c r="AU10" s="109"/>
-      <c r="AV10" s="109"/>
-      <c r="AW10" s="109"/>
-      <c r="AX10" s="109"/>
-      <c r="AY10" s="109"/>
-      <c r="AZ10" s="109"/>
-      <c r="BA10" s="109"/>
-      <c r="BB10" s="109"/>
-      <c r="BC10" s="109"/>
-      <c r="BD10" s="109"/>
-      <c r="BE10" s="110"/>
+      <c r="A10" s="88"/>
+      <c r="B10" s="89"/>
+      <c r="C10" s="89"/>
+      <c r="D10" s="89"/>
+      <c r="E10" s="89"/>
+      <c r="F10" s="89"/>
+      <c r="G10" s="90"/>
+      <c r="H10" s="91"/>
+      <c r="I10" s="92"/>
+      <c r="J10" s="92"/>
+      <c r="K10" s="92"/>
+      <c r="L10" s="92"/>
+      <c r="M10" s="92"/>
+      <c r="N10" s="93"/>
+      <c r="O10" s="91"/>
+      <c r="P10" s="94"/>
+      <c r="Q10" s="94"/>
+      <c r="R10" s="94"/>
+      <c r="S10" s="94"/>
+      <c r="T10" s="94"/>
+      <c r="U10" s="94"/>
+      <c r="V10" s="94"/>
+      <c r="W10" s="94"/>
+      <c r="X10" s="94"/>
+      <c r="Y10" s="94"/>
+      <c r="Z10" s="94"/>
+      <c r="AA10" s="94"/>
+      <c r="AB10" s="94"/>
+      <c r="AC10" s="94"/>
+      <c r="AD10" s="94"/>
+      <c r="AE10" s="94"/>
+      <c r="AF10" s="94"/>
+      <c r="AG10" s="94"/>
+      <c r="AH10" s="94"/>
+      <c r="AI10" s="94"/>
+      <c r="AJ10" s="94"/>
+      <c r="AK10" s="94"/>
+      <c r="AL10" s="94"/>
+      <c r="AM10" s="94"/>
+      <c r="AN10" s="94"/>
+      <c r="AO10" s="94"/>
+      <c r="AP10" s="95"/>
+      <c r="AQ10" s="96"/>
+      <c r="AR10" s="94"/>
+      <c r="AS10" s="94"/>
+      <c r="AT10" s="94"/>
+      <c r="AU10" s="94"/>
+      <c r="AV10" s="94"/>
+      <c r="AW10" s="94"/>
+      <c r="AX10" s="94"/>
+      <c r="AY10" s="94"/>
+      <c r="AZ10" s="94"/>
+      <c r="BA10" s="94"/>
+      <c r="BB10" s="94"/>
+      <c r="BC10" s="94"/>
+      <c r="BD10" s="94"/>
+      <c r="BE10" s="97"/>
     </row>
     <row r="11" spans="1:57" ht="15" customHeight="1">
-      <c r="A11" s="99"/>
-      <c r="B11" s="100"/>
-      <c r="C11" s="100"/>
-      <c r="D11" s="100"/>
-      <c r="E11" s="100"/>
-      <c r="F11" s="100"/>
-      <c r="G11" s="101"/>
-      <c r="H11" s="105"/>
-      <c r="I11" s="106"/>
-      <c r="J11" s="106"/>
-      <c r="K11" s="106"/>
-      <c r="L11" s="106"/>
-      <c r="M11" s="106"/>
-      <c r="N11" s="107"/>
-      <c r="O11" s="105"/>
-      <c r="P11" s="109"/>
-      <c r="Q11" s="109"/>
-      <c r="R11" s="109"/>
-      <c r="S11" s="109"/>
-      <c r="T11" s="109"/>
-      <c r="U11" s="109"/>
-      <c r="V11" s="109"/>
-      <c r="W11" s="109"/>
-      <c r="X11" s="109"/>
-      <c r="Y11" s="109"/>
-      <c r="Z11" s="109"/>
-      <c r="AA11" s="109"/>
-      <c r="AB11" s="109"/>
-      <c r="AC11" s="109"/>
-      <c r="AD11" s="109"/>
-      <c r="AE11" s="109"/>
-      <c r="AF11" s="109"/>
-      <c r="AG11" s="109"/>
-      <c r="AH11" s="109"/>
-      <c r="AI11" s="109"/>
-      <c r="AJ11" s="109"/>
-      <c r="AK11" s="109"/>
-      <c r="AL11" s="109"/>
-      <c r="AM11" s="109"/>
-      <c r="AN11" s="109"/>
-      <c r="AO11" s="109"/>
-      <c r="AP11" s="111"/>
-      <c r="AQ11" s="108"/>
-      <c r="AR11" s="109"/>
-      <c r="AS11" s="109"/>
-      <c r="AT11" s="109"/>
-      <c r="AU11" s="109"/>
-      <c r="AV11" s="109"/>
-      <c r="AW11" s="109"/>
-      <c r="AX11" s="109"/>
-      <c r="AY11" s="109"/>
-      <c r="AZ11" s="109"/>
-      <c r="BA11" s="109"/>
-      <c r="BB11" s="109"/>
-      <c r="BC11" s="109"/>
-      <c r="BD11" s="109"/>
-      <c r="BE11" s="110"/>
+      <c r="A11" s="88"/>
+      <c r="B11" s="89"/>
+      <c r="C11" s="89"/>
+      <c r="D11" s="89"/>
+      <c r="E11" s="89"/>
+      <c r="F11" s="89"/>
+      <c r="G11" s="90"/>
+      <c r="H11" s="91"/>
+      <c r="I11" s="92"/>
+      <c r="J11" s="92"/>
+      <c r="K11" s="92"/>
+      <c r="L11" s="92"/>
+      <c r="M11" s="92"/>
+      <c r="N11" s="93"/>
+      <c r="O11" s="91"/>
+      <c r="P11" s="94"/>
+      <c r="Q11" s="94"/>
+      <c r="R11" s="94"/>
+      <c r="S11" s="94"/>
+      <c r="T11" s="94"/>
+      <c r="U11" s="94"/>
+      <c r="V11" s="94"/>
+      <c r="W11" s="94"/>
+      <c r="X11" s="94"/>
+      <c r="Y11" s="94"/>
+      <c r="Z11" s="94"/>
+      <c r="AA11" s="94"/>
+      <c r="AB11" s="94"/>
+      <c r="AC11" s="94"/>
+      <c r="AD11" s="94"/>
+      <c r="AE11" s="94"/>
+      <c r="AF11" s="94"/>
+      <c r="AG11" s="94"/>
+      <c r="AH11" s="94"/>
+      <c r="AI11" s="94"/>
+      <c r="AJ11" s="94"/>
+      <c r="AK11" s="94"/>
+      <c r="AL11" s="94"/>
+      <c r="AM11" s="94"/>
+      <c r="AN11" s="94"/>
+      <c r="AO11" s="94"/>
+      <c r="AP11" s="95"/>
+      <c r="AQ11" s="96"/>
+      <c r="AR11" s="94"/>
+      <c r="AS11" s="94"/>
+      <c r="AT11" s="94"/>
+      <c r="AU11" s="94"/>
+      <c r="AV11" s="94"/>
+      <c r="AW11" s="94"/>
+      <c r="AX11" s="94"/>
+      <c r="AY11" s="94"/>
+      <c r="AZ11" s="94"/>
+      <c r="BA11" s="94"/>
+      <c r="BB11" s="94"/>
+      <c r="BC11" s="94"/>
+      <c r="BD11" s="94"/>
+      <c r="BE11" s="97"/>
     </row>
     <row r="12" spans="1:57" ht="15" customHeight="1">
-      <c r="A12" s="99"/>
-      <c r="B12" s="100"/>
-      <c r="C12" s="100"/>
-      <c r="D12" s="100"/>
-      <c r="E12" s="100"/>
-      <c r="F12" s="100"/>
-      <c r="G12" s="101"/>
-      <c r="H12" s="105"/>
-      <c r="I12" s="106"/>
-      <c r="J12" s="106"/>
-      <c r="K12" s="106"/>
-      <c r="L12" s="106"/>
-      <c r="M12" s="106"/>
-      <c r="N12" s="107"/>
-      <c r="O12" s="105"/>
-      <c r="P12" s="109"/>
-      <c r="Q12" s="109"/>
-      <c r="R12" s="109"/>
-      <c r="S12" s="109"/>
-      <c r="T12" s="109"/>
-      <c r="U12" s="109"/>
-      <c r="V12" s="109"/>
-      <c r="W12" s="109"/>
-      <c r="X12" s="109"/>
-      <c r="Y12" s="109"/>
-      <c r="Z12" s="109"/>
-      <c r="AA12" s="109"/>
-      <c r="AB12" s="109"/>
-      <c r="AC12" s="109"/>
-      <c r="AD12" s="109"/>
-      <c r="AE12" s="109"/>
-      <c r="AF12" s="109"/>
-      <c r="AG12" s="109"/>
-      <c r="AH12" s="109"/>
-      <c r="AI12" s="109"/>
-      <c r="AJ12" s="109"/>
-      <c r="AK12" s="109"/>
-      <c r="AL12" s="109"/>
-      <c r="AM12" s="109"/>
-      <c r="AN12" s="109"/>
-      <c r="AO12" s="109"/>
-      <c r="AP12" s="111"/>
-      <c r="AQ12" s="108"/>
-      <c r="AR12" s="109"/>
-      <c r="AS12" s="109"/>
-      <c r="AT12" s="109"/>
-      <c r="AU12" s="109"/>
-      <c r="AV12" s="109"/>
-      <c r="AW12" s="109"/>
-      <c r="AX12" s="109"/>
-      <c r="AY12" s="109"/>
-      <c r="AZ12" s="109"/>
-      <c r="BA12" s="109"/>
-      <c r="BB12" s="109"/>
-      <c r="BC12" s="109"/>
-      <c r="BD12" s="109"/>
-      <c r="BE12" s="110"/>
+      <c r="A12" s="88"/>
+      <c r="B12" s="89"/>
+      <c r="C12" s="89"/>
+      <c r="D12" s="89"/>
+      <c r="E12" s="89"/>
+      <c r="F12" s="89"/>
+      <c r="G12" s="90"/>
+      <c r="H12" s="91"/>
+      <c r="I12" s="92"/>
+      <c r="J12" s="92"/>
+      <c r="K12" s="92"/>
+      <c r="L12" s="92"/>
+      <c r="M12" s="92"/>
+      <c r="N12" s="93"/>
+      <c r="O12" s="91"/>
+      <c r="P12" s="94"/>
+      <c r="Q12" s="94"/>
+      <c r="R12" s="94"/>
+      <c r="S12" s="94"/>
+      <c r="T12" s="94"/>
+      <c r="U12" s="94"/>
+      <c r="V12" s="94"/>
+      <c r="W12" s="94"/>
+      <c r="X12" s="94"/>
+      <c r="Y12" s="94"/>
+      <c r="Z12" s="94"/>
+      <c r="AA12" s="94"/>
+      <c r="AB12" s="94"/>
+      <c r="AC12" s="94"/>
+      <c r="AD12" s="94"/>
+      <c r="AE12" s="94"/>
+      <c r="AF12" s="94"/>
+      <c r="AG12" s="94"/>
+      <c r="AH12" s="94"/>
+      <c r="AI12" s="94"/>
+      <c r="AJ12" s="94"/>
+      <c r="AK12" s="94"/>
+      <c r="AL12" s="94"/>
+      <c r="AM12" s="94"/>
+      <c r="AN12" s="94"/>
+      <c r="AO12" s="94"/>
+      <c r="AP12" s="95"/>
+      <c r="AQ12" s="96"/>
+      <c r="AR12" s="94"/>
+      <c r="AS12" s="94"/>
+      <c r="AT12" s="94"/>
+      <c r="AU12" s="94"/>
+      <c r="AV12" s="94"/>
+      <c r="AW12" s="94"/>
+      <c r="AX12" s="94"/>
+      <c r="AY12" s="94"/>
+      <c r="AZ12" s="94"/>
+      <c r="BA12" s="94"/>
+      <c r="BB12" s="94"/>
+      <c r="BC12" s="94"/>
+      <c r="BD12" s="94"/>
+      <c r="BE12" s="97"/>
     </row>
     <row r="13" spans="1:57" ht="15" customHeight="1">
-      <c r="A13" s="99"/>
-      <c r="B13" s="100"/>
-      <c r="C13" s="100"/>
-      <c r="D13" s="100"/>
-      <c r="E13" s="100"/>
-      <c r="F13" s="100"/>
-      <c r="G13" s="101"/>
-      <c r="H13" s="105"/>
-      <c r="I13" s="106"/>
-      <c r="J13" s="106"/>
-      <c r="K13" s="106"/>
-      <c r="L13" s="106"/>
-      <c r="M13" s="106"/>
-      <c r="N13" s="107"/>
-      <c r="O13" s="105"/>
-      <c r="P13" s="109"/>
-      <c r="Q13" s="109"/>
-      <c r="R13" s="109"/>
-      <c r="S13" s="109"/>
-      <c r="T13" s="109"/>
-      <c r="U13" s="109"/>
-      <c r="V13" s="109"/>
-      <c r="W13" s="109"/>
-      <c r="X13" s="109"/>
-      <c r="Y13" s="109"/>
-      <c r="Z13" s="109"/>
-      <c r="AA13" s="109"/>
-      <c r="AB13" s="109"/>
-      <c r="AC13" s="109"/>
-      <c r="AD13" s="109"/>
-      <c r="AE13" s="109"/>
-      <c r="AF13" s="109"/>
-      <c r="AG13" s="109"/>
-      <c r="AH13" s="109"/>
-      <c r="AI13" s="109"/>
-      <c r="AJ13" s="109"/>
-      <c r="AK13" s="109"/>
-      <c r="AL13" s="109"/>
-      <c r="AM13" s="109"/>
-      <c r="AN13" s="109"/>
-      <c r="AO13" s="109"/>
-      <c r="AP13" s="111"/>
-      <c r="AQ13" s="108"/>
-      <c r="AR13" s="109"/>
-      <c r="AS13" s="109"/>
-      <c r="AT13" s="109"/>
-      <c r="AU13" s="109"/>
-      <c r="AV13" s="109"/>
-      <c r="AW13" s="109"/>
-      <c r="AX13" s="109"/>
-      <c r="AY13" s="109"/>
-      <c r="AZ13" s="109"/>
-      <c r="BA13" s="109"/>
-      <c r="BB13" s="109"/>
-      <c r="BC13" s="109"/>
-      <c r="BD13" s="109"/>
-      <c r="BE13" s="110"/>
+      <c r="A13" s="88"/>
+      <c r="B13" s="89"/>
+      <c r="C13" s="89"/>
+      <c r="D13" s="89"/>
+      <c r="E13" s="89"/>
+      <c r="F13" s="89"/>
+      <c r="G13" s="90"/>
+      <c r="H13" s="91"/>
+      <c r="I13" s="92"/>
+      <c r="J13" s="92"/>
+      <c r="K13" s="92"/>
+      <c r="L13" s="92"/>
+      <c r="M13" s="92"/>
+      <c r="N13" s="93"/>
+      <c r="O13" s="91"/>
+      <c r="P13" s="94"/>
+      <c r="Q13" s="94"/>
+      <c r="R13" s="94"/>
+      <c r="S13" s="94"/>
+      <c r="T13" s="94"/>
+      <c r="U13" s="94"/>
+      <c r="V13" s="94"/>
+      <c r="W13" s="94"/>
+      <c r="X13" s="94"/>
+      <c r="Y13" s="94"/>
+      <c r="Z13" s="94"/>
+      <c r="AA13" s="94"/>
+      <c r="AB13" s="94"/>
+      <c r="AC13" s="94"/>
+      <c r="AD13" s="94"/>
+      <c r="AE13" s="94"/>
+      <c r="AF13" s="94"/>
+      <c r="AG13" s="94"/>
+      <c r="AH13" s="94"/>
+      <c r="AI13" s="94"/>
+      <c r="AJ13" s="94"/>
+      <c r="AK13" s="94"/>
+      <c r="AL13" s="94"/>
+      <c r="AM13" s="94"/>
+      <c r="AN13" s="94"/>
+      <c r="AO13" s="94"/>
+      <c r="AP13" s="95"/>
+      <c r="AQ13" s="96"/>
+      <c r="AR13" s="94"/>
+      <c r="AS13" s="94"/>
+      <c r="AT13" s="94"/>
+      <c r="AU13" s="94"/>
+      <c r="AV13" s="94"/>
+      <c r="AW13" s="94"/>
+      <c r="AX13" s="94"/>
+      <c r="AY13" s="94"/>
+      <c r="AZ13" s="94"/>
+      <c r="BA13" s="94"/>
+      <c r="BB13" s="94"/>
+      <c r="BC13" s="94"/>
+      <c r="BD13" s="94"/>
+      <c r="BE13" s="97"/>
     </row>
     <row r="14" spans="1:57" ht="15" customHeight="1">
-      <c r="A14" s="99"/>
-      <c r="B14" s="100"/>
-      <c r="C14" s="100"/>
-      <c r="D14" s="100"/>
-      <c r="E14" s="100"/>
-      <c r="F14" s="100"/>
-      <c r="G14" s="101"/>
-      <c r="H14" s="105"/>
-      <c r="I14" s="106"/>
-      <c r="J14" s="106"/>
-      <c r="K14" s="106"/>
-      <c r="L14" s="106"/>
-      <c r="M14" s="106"/>
-      <c r="N14" s="107"/>
-      <c r="O14" s="105"/>
-      <c r="P14" s="109"/>
-      <c r="Q14" s="109"/>
-      <c r="R14" s="109"/>
-      <c r="S14" s="109"/>
-      <c r="T14" s="109"/>
-      <c r="U14" s="109"/>
-      <c r="V14" s="109"/>
-      <c r="W14" s="109"/>
-      <c r="X14" s="109"/>
-      <c r="Y14" s="109"/>
-      <c r="Z14" s="109"/>
-      <c r="AA14" s="109"/>
-      <c r="AB14" s="109"/>
-      <c r="AC14" s="109"/>
-      <c r="AD14" s="109"/>
-      <c r="AE14" s="109"/>
-      <c r="AF14" s="109"/>
-      <c r="AG14" s="109"/>
-      <c r="AH14" s="109"/>
-      <c r="AI14" s="109"/>
-      <c r="AJ14" s="109"/>
-      <c r="AK14" s="109"/>
-      <c r="AL14" s="109"/>
-      <c r="AM14" s="109"/>
-      <c r="AN14" s="109"/>
-      <c r="AO14" s="109"/>
-      <c r="AP14" s="111"/>
-      <c r="AQ14" s="108"/>
-      <c r="AR14" s="109"/>
-      <c r="AS14" s="109"/>
-      <c r="AT14" s="109"/>
-      <c r="AU14" s="109"/>
-      <c r="AV14" s="109"/>
-      <c r="AW14" s="109"/>
-      <c r="AX14" s="109"/>
-      <c r="AY14" s="109"/>
-      <c r="AZ14" s="109"/>
-      <c r="BA14" s="109"/>
-      <c r="BB14" s="109"/>
-      <c r="BC14" s="109"/>
-      <c r="BD14" s="109"/>
-      <c r="BE14" s="110"/>
+      <c r="A14" s="88"/>
+      <c r="B14" s="89"/>
+      <c r="C14" s="89"/>
+      <c r="D14" s="89"/>
+      <c r="E14" s="89"/>
+      <c r="F14" s="89"/>
+      <c r="G14" s="90"/>
+      <c r="H14" s="91"/>
+      <c r="I14" s="92"/>
+      <c r="J14" s="92"/>
+      <c r="K14" s="92"/>
+      <c r="L14" s="92"/>
+      <c r="M14" s="92"/>
+      <c r="N14" s="93"/>
+      <c r="O14" s="91"/>
+      <c r="P14" s="94"/>
+      <c r="Q14" s="94"/>
+      <c r="R14" s="94"/>
+      <c r="S14" s="94"/>
+      <c r="T14" s="94"/>
+      <c r="U14" s="94"/>
+      <c r="V14" s="94"/>
+      <c r="W14" s="94"/>
+      <c r="X14" s="94"/>
+      <c r="Y14" s="94"/>
+      <c r="Z14" s="94"/>
+      <c r="AA14" s="94"/>
+      <c r="AB14" s="94"/>
+      <c r="AC14" s="94"/>
+      <c r="AD14" s="94"/>
+      <c r="AE14" s="94"/>
+      <c r="AF14" s="94"/>
+      <c r="AG14" s="94"/>
+      <c r="AH14" s="94"/>
+      <c r="AI14" s="94"/>
+      <c r="AJ14" s="94"/>
+      <c r="AK14" s="94"/>
+      <c r="AL14" s="94"/>
+      <c r="AM14" s="94"/>
+      <c r="AN14" s="94"/>
+      <c r="AO14" s="94"/>
+      <c r="AP14" s="95"/>
+      <c r="AQ14" s="96"/>
+      <c r="AR14" s="94"/>
+      <c r="AS14" s="94"/>
+      <c r="AT14" s="94"/>
+      <c r="AU14" s="94"/>
+      <c r="AV14" s="94"/>
+      <c r="AW14" s="94"/>
+      <c r="AX14" s="94"/>
+      <c r="AY14" s="94"/>
+      <c r="AZ14" s="94"/>
+      <c r="BA14" s="94"/>
+      <c r="BB14" s="94"/>
+      <c r="BC14" s="94"/>
+      <c r="BD14" s="94"/>
+      <c r="BE14" s="97"/>
     </row>
     <row r="15" spans="1:57" ht="15" customHeight="1">
-      <c r="A15" s="99"/>
-      <c r="B15" s="100"/>
-      <c r="C15" s="100"/>
-      <c r="D15" s="100"/>
-      <c r="E15" s="100"/>
-      <c r="F15" s="100"/>
-      <c r="G15" s="101"/>
-      <c r="H15" s="105"/>
-      <c r="I15" s="106"/>
-      <c r="J15" s="106"/>
-      <c r="K15" s="106"/>
-      <c r="L15" s="106"/>
-      <c r="M15" s="106"/>
-      <c r="N15" s="107"/>
-      <c r="O15" s="105"/>
-      <c r="P15" s="109"/>
-      <c r="Q15" s="109"/>
-      <c r="R15" s="109"/>
-      <c r="S15" s="109"/>
-      <c r="T15" s="109"/>
-      <c r="U15" s="109"/>
-      <c r="V15" s="109"/>
-      <c r="W15" s="109"/>
-      <c r="X15" s="109"/>
-      <c r="Y15" s="109"/>
-      <c r="Z15" s="109"/>
-      <c r="AA15" s="109"/>
-      <c r="AB15" s="109"/>
-      <c r="AC15" s="109"/>
-      <c r="AD15" s="109"/>
-      <c r="AE15" s="109"/>
-      <c r="AF15" s="109"/>
-      <c r="AG15" s="109"/>
-      <c r="AH15" s="109"/>
-      <c r="AI15" s="109"/>
-      <c r="AJ15" s="109"/>
-      <c r="AK15" s="109"/>
-      <c r="AL15" s="109"/>
-      <c r="AM15" s="109"/>
-      <c r="AN15" s="109"/>
-      <c r="AO15" s="109"/>
-      <c r="AP15" s="111"/>
-      <c r="AQ15" s="108"/>
-      <c r="AR15" s="109"/>
-      <c r="AS15" s="109"/>
-      <c r="AT15" s="109"/>
-      <c r="AU15" s="109"/>
-      <c r="AV15" s="109"/>
-      <c r="AW15" s="109"/>
-      <c r="AX15" s="109"/>
-      <c r="AY15" s="109"/>
-      <c r="AZ15" s="109"/>
-      <c r="BA15" s="109"/>
-      <c r="BB15" s="109"/>
-      <c r="BC15" s="109"/>
-      <c r="BD15" s="109"/>
-      <c r="BE15" s="110"/>
+      <c r="A15" s="88"/>
+      <c r="B15" s="89"/>
+      <c r="C15" s="89"/>
+      <c r="D15" s="89"/>
+      <c r="E15" s="89"/>
+      <c r="F15" s="89"/>
+      <c r="G15" s="90"/>
+      <c r="H15" s="91"/>
+      <c r="I15" s="92"/>
+      <c r="J15" s="92"/>
+      <c r="K15" s="92"/>
+      <c r="L15" s="92"/>
+      <c r="M15" s="92"/>
+      <c r="N15" s="93"/>
+      <c r="O15" s="91"/>
+      <c r="P15" s="94"/>
+      <c r="Q15" s="94"/>
+      <c r="R15" s="94"/>
+      <c r="S15" s="94"/>
+      <c r="T15" s="94"/>
+      <c r="U15" s="94"/>
+      <c r="V15" s="94"/>
+      <c r="W15" s="94"/>
+      <c r="X15" s="94"/>
+      <c r="Y15" s="94"/>
+      <c r="Z15" s="94"/>
+      <c r="AA15" s="94"/>
+      <c r="AB15" s="94"/>
+      <c r="AC15" s="94"/>
+      <c r="AD15" s="94"/>
+      <c r="AE15" s="94"/>
+      <c r="AF15" s="94"/>
+      <c r="AG15" s="94"/>
+      <c r="AH15" s="94"/>
+      <c r="AI15" s="94"/>
+      <c r="AJ15" s="94"/>
+      <c r="AK15" s="94"/>
+      <c r="AL15" s="94"/>
+      <c r="AM15" s="94"/>
+      <c r="AN15" s="94"/>
+      <c r="AO15" s="94"/>
+      <c r="AP15" s="95"/>
+      <c r="AQ15" s="96"/>
+      <c r="AR15" s="94"/>
+      <c r="AS15" s="94"/>
+      <c r="AT15" s="94"/>
+      <c r="AU15" s="94"/>
+      <c r="AV15" s="94"/>
+      <c r="AW15" s="94"/>
+      <c r="AX15" s="94"/>
+      <c r="AY15" s="94"/>
+      <c r="AZ15" s="94"/>
+      <c r="BA15" s="94"/>
+      <c r="BB15" s="94"/>
+      <c r="BC15" s="94"/>
+      <c r="BD15" s="94"/>
+      <c r="BE15" s="97"/>
     </row>
     <row r="16" spans="1:57" ht="15" customHeight="1">
-      <c r="A16" s="99"/>
-      <c r="B16" s="100"/>
-      <c r="C16" s="100"/>
-      <c r="D16" s="100"/>
-      <c r="E16" s="100"/>
-      <c r="F16" s="100"/>
-      <c r="G16" s="101"/>
-      <c r="H16" s="105"/>
-      <c r="I16" s="106"/>
-      <c r="J16" s="106"/>
-      <c r="K16" s="106"/>
-      <c r="L16" s="106"/>
-      <c r="M16" s="106"/>
-      <c r="N16" s="107"/>
-      <c r="O16" s="105"/>
-      <c r="P16" s="109"/>
-      <c r="Q16" s="109"/>
-      <c r="R16" s="109"/>
-      <c r="S16" s="109"/>
-      <c r="T16" s="109"/>
-      <c r="U16" s="109"/>
-      <c r="V16" s="109"/>
-      <c r="W16" s="109"/>
-      <c r="X16" s="109"/>
-      <c r="Y16" s="109"/>
-      <c r="Z16" s="109"/>
-      <c r="AA16" s="109"/>
-      <c r="AB16" s="109"/>
-      <c r="AC16" s="109"/>
-      <c r="AD16" s="109"/>
-      <c r="AE16" s="109"/>
-      <c r="AF16" s="109"/>
-      <c r="AG16" s="109"/>
-      <c r="AH16" s="109"/>
-      <c r="AI16" s="109"/>
-      <c r="AJ16" s="109"/>
-      <c r="AK16" s="109"/>
-      <c r="AL16" s="109"/>
-      <c r="AM16" s="109"/>
-      <c r="AN16" s="109"/>
-      <c r="AO16" s="109"/>
-      <c r="AP16" s="111"/>
-      <c r="AQ16" s="108"/>
-      <c r="AR16" s="109"/>
-      <c r="AS16" s="109"/>
-      <c r="AT16" s="109"/>
-      <c r="AU16" s="109"/>
-      <c r="AV16" s="109"/>
-      <c r="AW16" s="109"/>
-      <c r="AX16" s="109"/>
-      <c r="AY16" s="109"/>
-      <c r="AZ16" s="109"/>
-      <c r="BA16" s="109"/>
-      <c r="BB16" s="109"/>
-      <c r="BC16" s="109"/>
-      <c r="BD16" s="109"/>
-      <c r="BE16" s="110"/>
+      <c r="A16" s="88"/>
+      <c r="B16" s="89"/>
+      <c r="C16" s="89"/>
+      <c r="D16" s="89"/>
+      <c r="E16" s="89"/>
+      <c r="F16" s="89"/>
+      <c r="G16" s="90"/>
+      <c r="H16" s="91"/>
+      <c r="I16" s="92"/>
+      <c r="J16" s="92"/>
+      <c r="K16" s="92"/>
+      <c r="L16" s="92"/>
+      <c r="M16" s="92"/>
+      <c r="N16" s="93"/>
+      <c r="O16" s="91"/>
+      <c r="P16" s="94"/>
+      <c r="Q16" s="94"/>
+      <c r="R16" s="94"/>
+      <c r="S16" s="94"/>
+      <c r="T16" s="94"/>
+      <c r="U16" s="94"/>
+      <c r="V16" s="94"/>
+      <c r="W16" s="94"/>
+      <c r="X16" s="94"/>
+      <c r="Y16" s="94"/>
+      <c r="Z16" s="94"/>
+      <c r="AA16" s="94"/>
+      <c r="AB16" s="94"/>
+      <c r="AC16" s="94"/>
+      <c r="AD16" s="94"/>
+      <c r="AE16" s="94"/>
+      <c r="AF16" s="94"/>
+      <c r="AG16" s="94"/>
+      <c r="AH16" s="94"/>
+      <c r="AI16" s="94"/>
+      <c r="AJ16" s="94"/>
+      <c r="AK16" s="94"/>
+      <c r="AL16" s="94"/>
+      <c r="AM16" s="94"/>
+      <c r="AN16" s="94"/>
+      <c r="AO16" s="94"/>
+      <c r="AP16" s="95"/>
+      <c r="AQ16" s="96"/>
+      <c r="AR16" s="94"/>
+      <c r="AS16" s="94"/>
+      <c r="AT16" s="94"/>
+      <c r="AU16" s="94"/>
+      <c r="AV16" s="94"/>
+      <c r="AW16" s="94"/>
+      <c r="AX16" s="94"/>
+      <c r="AY16" s="94"/>
+      <c r="AZ16" s="94"/>
+      <c r="BA16" s="94"/>
+      <c r="BB16" s="94"/>
+      <c r="BC16" s="94"/>
+      <c r="BD16" s="94"/>
+      <c r="BE16" s="97"/>
     </row>
     <row r="17" spans="1:57" ht="15" customHeight="1">
-      <c r="A17" s="99"/>
-      <c r="B17" s="100"/>
-      <c r="C17" s="100"/>
-      <c r="D17" s="100"/>
-      <c r="E17" s="100"/>
-      <c r="F17" s="100"/>
-      <c r="G17" s="101"/>
-      <c r="H17" s="105"/>
-      <c r="I17" s="106"/>
-      <c r="J17" s="106"/>
-      <c r="K17" s="106"/>
-      <c r="L17" s="106"/>
-      <c r="M17" s="106"/>
-      <c r="N17" s="107"/>
-      <c r="O17" s="105"/>
-      <c r="P17" s="109"/>
-      <c r="Q17" s="109"/>
-      <c r="R17" s="109"/>
-      <c r="S17" s="109"/>
-      <c r="T17" s="109"/>
-      <c r="U17" s="109"/>
-      <c r="V17" s="109"/>
-      <c r="W17" s="109"/>
-      <c r="X17" s="109"/>
-      <c r="Y17" s="109"/>
-      <c r="Z17" s="109"/>
-      <c r="AA17" s="109"/>
-      <c r="AB17" s="109"/>
-      <c r="AC17" s="109"/>
-      <c r="AD17" s="109"/>
-      <c r="AE17" s="109"/>
-      <c r="AF17" s="109"/>
-      <c r="AG17" s="109"/>
-      <c r="AH17" s="109"/>
-      <c r="AI17" s="109"/>
-      <c r="AJ17" s="109"/>
-      <c r="AK17" s="109"/>
-      <c r="AL17" s="109"/>
-      <c r="AM17" s="109"/>
-      <c r="AN17" s="109"/>
-      <c r="AO17" s="109"/>
-      <c r="AP17" s="111"/>
-      <c r="AQ17" s="108"/>
-      <c r="AR17" s="109"/>
-      <c r="AS17" s="109"/>
-      <c r="AT17" s="109"/>
-      <c r="AU17" s="109"/>
-      <c r="AV17" s="109"/>
-      <c r="AW17" s="109"/>
-      <c r="AX17" s="109"/>
-      <c r="AY17" s="109"/>
-      <c r="AZ17" s="109"/>
-      <c r="BA17" s="109"/>
-      <c r="BB17" s="109"/>
-      <c r="BC17" s="109"/>
-      <c r="BD17" s="109"/>
-      <c r="BE17" s="110"/>
+      <c r="A17" s="88"/>
+      <c r="B17" s="89"/>
+      <c r="C17" s="89"/>
+      <c r="D17" s="89"/>
+      <c r="E17" s="89"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="90"/>
+      <c r="H17" s="91"/>
+      <c r="I17" s="92"/>
+      <c r="J17" s="92"/>
+      <c r="K17" s="92"/>
+      <c r="L17" s="92"/>
+      <c r="M17" s="92"/>
+      <c r="N17" s="93"/>
+      <c r="O17" s="91"/>
+      <c r="P17" s="94"/>
+      <c r="Q17" s="94"/>
+      <c r="R17" s="94"/>
+      <c r="S17" s="94"/>
+      <c r="T17" s="94"/>
+      <c r="U17" s="94"/>
+      <c r="V17" s="94"/>
+      <c r="W17" s="94"/>
+      <c r="X17" s="94"/>
+      <c r="Y17" s="94"/>
+      <c r="Z17" s="94"/>
+      <c r="AA17" s="94"/>
+      <c r="AB17" s="94"/>
+      <c r="AC17" s="94"/>
+      <c r="AD17" s="94"/>
+      <c r="AE17" s="94"/>
+      <c r="AF17" s="94"/>
+      <c r="AG17" s="94"/>
+      <c r="AH17" s="94"/>
+      <c r="AI17" s="94"/>
+      <c r="AJ17" s="94"/>
+      <c r="AK17" s="94"/>
+      <c r="AL17" s="94"/>
+      <c r="AM17" s="94"/>
+      <c r="AN17" s="94"/>
+      <c r="AO17" s="94"/>
+      <c r="AP17" s="95"/>
+      <c r="AQ17" s="96"/>
+      <c r="AR17" s="94"/>
+      <c r="AS17" s="94"/>
+      <c r="AT17" s="94"/>
+      <c r="AU17" s="94"/>
+      <c r="AV17" s="94"/>
+      <c r="AW17" s="94"/>
+      <c r="AX17" s="94"/>
+      <c r="AY17" s="94"/>
+      <c r="AZ17" s="94"/>
+      <c r="BA17" s="94"/>
+      <c r="BB17" s="94"/>
+      <c r="BC17" s="94"/>
+      <c r="BD17" s="94"/>
+      <c r="BE17" s="97"/>
     </row>
     <row r="18" spans="1:57" ht="15" customHeight="1">
-      <c r="A18" s="99"/>
-      <c r="B18" s="100"/>
-      <c r="C18" s="100"/>
-      <c r="D18" s="100"/>
-      <c r="E18" s="100"/>
-      <c r="F18" s="100"/>
-      <c r="G18" s="101"/>
-      <c r="H18" s="105"/>
-      <c r="I18" s="106"/>
-      <c r="J18" s="106"/>
-      <c r="K18" s="106"/>
-      <c r="L18" s="106"/>
-      <c r="M18" s="106"/>
-      <c r="N18" s="107"/>
-      <c r="O18" s="105"/>
-      <c r="P18" s="109"/>
-      <c r="Q18" s="109"/>
-      <c r="R18" s="109"/>
-      <c r="S18" s="109"/>
-      <c r="T18" s="109"/>
-      <c r="U18" s="109"/>
-      <c r="V18" s="109"/>
-      <c r="W18" s="109"/>
-      <c r="X18" s="109"/>
-      <c r="Y18" s="109"/>
-      <c r="Z18" s="109"/>
-      <c r="AA18" s="109"/>
-      <c r="AB18" s="109"/>
-      <c r="AC18" s="109"/>
-      <c r="AD18" s="109"/>
-      <c r="AE18" s="109"/>
-      <c r="AF18" s="109"/>
-      <c r="AG18" s="109"/>
-      <c r="AH18" s="109"/>
-      <c r="AI18" s="109"/>
-      <c r="AJ18" s="109"/>
-      <c r="AK18" s="109"/>
-      <c r="AL18" s="109"/>
-      <c r="AM18" s="109"/>
-      <c r="AN18" s="109"/>
-      <c r="AO18" s="109"/>
-      <c r="AP18" s="111"/>
-      <c r="AQ18" s="108"/>
-      <c r="AR18" s="109"/>
-      <c r="AS18" s="109"/>
-      <c r="AT18" s="109"/>
-      <c r="AU18" s="109"/>
-      <c r="AV18" s="109"/>
-      <c r="AW18" s="109"/>
-      <c r="AX18" s="109"/>
-      <c r="AY18" s="109"/>
-      <c r="AZ18" s="109"/>
-      <c r="BA18" s="109"/>
-      <c r="BB18" s="109"/>
-      <c r="BC18" s="109"/>
-      <c r="BD18" s="109"/>
-      <c r="BE18" s="110"/>
+      <c r="A18" s="88"/>
+      <c r="B18" s="89"/>
+      <c r="C18" s="89"/>
+      <c r="D18" s="89"/>
+      <c r="E18" s="89"/>
+      <c r="F18" s="89"/>
+      <c r="G18" s="90"/>
+      <c r="H18" s="91"/>
+      <c r="I18" s="92"/>
+      <c r="J18" s="92"/>
+      <c r="K18" s="92"/>
+      <c r="L18" s="92"/>
+      <c r="M18" s="92"/>
+      <c r="N18" s="93"/>
+      <c r="O18" s="91"/>
+      <c r="P18" s="94"/>
+      <c r="Q18" s="94"/>
+      <c r="R18" s="94"/>
+      <c r="S18" s="94"/>
+      <c r="T18" s="94"/>
+      <c r="U18" s="94"/>
+      <c r="V18" s="94"/>
+      <c r="W18" s="94"/>
+      <c r="X18" s="94"/>
+      <c r="Y18" s="94"/>
+      <c r="Z18" s="94"/>
+      <c r="AA18" s="94"/>
+      <c r="AB18" s="94"/>
+      <c r="AC18" s="94"/>
+      <c r="AD18" s="94"/>
+      <c r="AE18" s="94"/>
+      <c r="AF18" s="94"/>
+      <c r="AG18" s="94"/>
+      <c r="AH18" s="94"/>
+      <c r="AI18" s="94"/>
+      <c r="AJ18" s="94"/>
+      <c r="AK18" s="94"/>
+      <c r="AL18" s="94"/>
+      <c r="AM18" s="94"/>
+      <c r="AN18" s="94"/>
+      <c r="AO18" s="94"/>
+      <c r="AP18" s="95"/>
+      <c r="AQ18" s="96"/>
+      <c r="AR18" s="94"/>
+      <c r="AS18" s="94"/>
+      <c r="AT18" s="94"/>
+      <c r="AU18" s="94"/>
+      <c r="AV18" s="94"/>
+      <c r="AW18" s="94"/>
+      <c r="AX18" s="94"/>
+      <c r="AY18" s="94"/>
+      <c r="AZ18" s="94"/>
+      <c r="BA18" s="94"/>
+      <c r="BB18" s="94"/>
+      <c r="BC18" s="94"/>
+      <c r="BD18" s="94"/>
+      <c r="BE18" s="97"/>
     </row>
     <row r="19" spans="1:57" ht="15" customHeight="1">
-      <c r="A19" s="99"/>
-      <c r="B19" s="100"/>
-      <c r="C19" s="100"/>
-      <c r="D19" s="100"/>
-      <c r="E19" s="100"/>
-      <c r="F19" s="100"/>
-      <c r="G19" s="101"/>
-      <c r="H19" s="105"/>
-      <c r="I19" s="106"/>
-      <c r="J19" s="106"/>
-      <c r="K19" s="106"/>
-      <c r="L19" s="106"/>
-      <c r="M19" s="106"/>
-      <c r="N19" s="107"/>
-      <c r="O19" s="105"/>
-      <c r="P19" s="109"/>
-      <c r="Q19" s="109"/>
-      <c r="R19" s="109"/>
-      <c r="S19" s="109"/>
-      <c r="T19" s="109"/>
-      <c r="U19" s="109"/>
-      <c r="V19" s="109"/>
-      <c r="W19" s="109"/>
-      <c r="X19" s="109"/>
-      <c r="Y19" s="109"/>
-      <c r="Z19" s="109"/>
-      <c r="AA19" s="109"/>
-      <c r="AB19" s="109"/>
-      <c r="AC19" s="109"/>
-      <c r="AD19" s="109"/>
-      <c r="AE19" s="109"/>
-      <c r="AF19" s="109"/>
-      <c r="AG19" s="109"/>
-      <c r="AH19" s="109"/>
-      <c r="AI19" s="109"/>
-      <c r="AJ19" s="109"/>
-      <c r="AK19" s="109"/>
-      <c r="AL19" s="109"/>
-      <c r="AM19" s="109"/>
-      <c r="AN19" s="109"/>
-      <c r="AO19" s="109"/>
-      <c r="AP19" s="111"/>
-      <c r="AQ19" s="108"/>
-      <c r="AR19" s="109"/>
-      <c r="AS19" s="109"/>
-      <c r="AT19" s="109"/>
-      <c r="AU19" s="109"/>
-      <c r="AV19" s="109"/>
-      <c r="AW19" s="109"/>
-      <c r="AX19" s="109"/>
-      <c r="AY19" s="109"/>
-      <c r="AZ19" s="109"/>
-      <c r="BA19" s="109"/>
-      <c r="BB19" s="109"/>
-      <c r="BC19" s="109"/>
-      <c r="BD19" s="109"/>
-      <c r="BE19" s="110"/>
+      <c r="A19" s="88"/>
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="90"/>
+      <c r="H19" s="91"/>
+      <c r="I19" s="92"/>
+      <c r="J19" s="92"/>
+      <c r="K19" s="92"/>
+      <c r="L19" s="92"/>
+      <c r="M19" s="92"/>
+      <c r="N19" s="93"/>
+      <c r="O19" s="91"/>
+      <c r="P19" s="94"/>
+      <c r="Q19" s="94"/>
+      <c r="R19" s="94"/>
+      <c r="S19" s="94"/>
+      <c r="T19" s="94"/>
+      <c r="U19" s="94"/>
+      <c r="V19" s="94"/>
+      <c r="W19" s="94"/>
+      <c r="X19" s="94"/>
+      <c r="Y19" s="94"/>
+      <c r="Z19" s="94"/>
+      <c r="AA19" s="94"/>
+      <c r="AB19" s="94"/>
+      <c r="AC19" s="94"/>
+      <c r="AD19" s="94"/>
+      <c r="AE19" s="94"/>
+      <c r="AF19" s="94"/>
+      <c r="AG19" s="94"/>
+      <c r="AH19" s="94"/>
+      <c r="AI19" s="94"/>
+      <c r="AJ19" s="94"/>
+      <c r="AK19" s="94"/>
+      <c r="AL19" s="94"/>
+      <c r="AM19" s="94"/>
+      <c r="AN19" s="94"/>
+      <c r="AO19" s="94"/>
+      <c r="AP19" s="95"/>
+      <c r="AQ19" s="96"/>
+      <c r="AR19" s="94"/>
+      <c r="AS19" s="94"/>
+      <c r="AT19" s="94"/>
+      <c r="AU19" s="94"/>
+      <c r="AV19" s="94"/>
+      <c r="AW19" s="94"/>
+      <c r="AX19" s="94"/>
+      <c r="AY19" s="94"/>
+      <c r="AZ19" s="94"/>
+      <c r="BA19" s="94"/>
+      <c r="BB19" s="94"/>
+      <c r="BC19" s="94"/>
+      <c r="BD19" s="94"/>
+      <c r="BE19" s="97"/>
     </row>
     <row r="20" spans="1:57" ht="15" customHeight="1">
-      <c r="A20" s="99"/>
-      <c r="B20" s="100"/>
-      <c r="C20" s="100"/>
-      <c r="D20" s="100"/>
-      <c r="E20" s="100"/>
-      <c r="F20" s="100"/>
-      <c r="G20" s="101"/>
-      <c r="H20" s="105"/>
-      <c r="I20" s="106"/>
-      <c r="J20" s="106"/>
-      <c r="K20" s="106"/>
-      <c r="L20" s="106"/>
-      <c r="M20" s="106"/>
-      <c r="N20" s="107"/>
-      <c r="O20" s="105"/>
-      <c r="P20" s="109"/>
-      <c r="Q20" s="109"/>
-      <c r="R20" s="109"/>
-      <c r="S20" s="109"/>
-      <c r="T20" s="109"/>
-      <c r="U20" s="109"/>
-      <c r="V20" s="109"/>
-      <c r="W20" s="109"/>
-      <c r="X20" s="109"/>
-      <c r="Y20" s="109"/>
-      <c r="Z20" s="109"/>
-      <c r="AA20" s="109"/>
-      <c r="AB20" s="109"/>
-      <c r="AC20" s="109"/>
-      <c r="AD20" s="109"/>
-      <c r="AE20" s="109"/>
-      <c r="AF20" s="109"/>
-      <c r="AG20" s="109"/>
-      <c r="AH20" s="109"/>
-      <c r="AI20" s="109"/>
-      <c r="AJ20" s="109"/>
-      <c r="AK20" s="109"/>
-      <c r="AL20" s="109"/>
-      <c r="AM20" s="109"/>
-      <c r="AN20" s="109"/>
-      <c r="AO20" s="109"/>
-      <c r="AP20" s="111"/>
-      <c r="AQ20" s="108"/>
-      <c r="AR20" s="109"/>
-      <c r="AS20" s="109"/>
-      <c r="AT20" s="109"/>
-      <c r="AU20" s="109"/>
-      <c r="AV20" s="109"/>
-      <c r="AW20" s="109"/>
-      <c r="AX20" s="109"/>
-      <c r="AY20" s="109"/>
-      <c r="AZ20" s="109"/>
-      <c r="BA20" s="109"/>
-      <c r="BB20" s="109"/>
-      <c r="BC20" s="109"/>
-      <c r="BD20" s="109"/>
-      <c r="BE20" s="110"/>
+      <c r="A20" s="88"/>
+      <c r="B20" s="89"/>
+      <c r="C20" s="89"/>
+      <c r="D20" s="89"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="90"/>
+      <c r="H20" s="91"/>
+      <c r="I20" s="92"/>
+      <c r="J20" s="92"/>
+      <c r="K20" s="92"/>
+      <c r="L20" s="92"/>
+      <c r="M20" s="92"/>
+      <c r="N20" s="93"/>
+      <c r="O20" s="91"/>
+      <c r="P20" s="94"/>
+      <c r="Q20" s="94"/>
+      <c r="R20" s="94"/>
+      <c r="S20" s="94"/>
+      <c r="T20" s="94"/>
+      <c r="U20" s="94"/>
+      <c r="V20" s="94"/>
+      <c r="W20" s="94"/>
+      <c r="X20" s="94"/>
+      <c r="Y20" s="94"/>
+      <c r="Z20" s="94"/>
+      <c r="AA20" s="94"/>
+      <c r="AB20" s="94"/>
+      <c r="AC20" s="94"/>
+      <c r="AD20" s="94"/>
+      <c r="AE20" s="94"/>
+      <c r="AF20" s="94"/>
+      <c r="AG20" s="94"/>
+      <c r="AH20" s="94"/>
+      <c r="AI20" s="94"/>
+      <c r="AJ20" s="94"/>
+      <c r="AK20" s="94"/>
+      <c r="AL20" s="94"/>
+      <c r="AM20" s="94"/>
+      <c r="AN20" s="94"/>
+      <c r="AO20" s="94"/>
+      <c r="AP20" s="95"/>
+      <c r="AQ20" s="96"/>
+      <c r="AR20" s="94"/>
+      <c r="AS20" s="94"/>
+      <c r="AT20" s="94"/>
+      <c r="AU20" s="94"/>
+      <c r="AV20" s="94"/>
+      <c r="AW20" s="94"/>
+      <c r="AX20" s="94"/>
+      <c r="AY20" s="94"/>
+      <c r="AZ20" s="94"/>
+      <c r="BA20" s="94"/>
+      <c r="BB20" s="94"/>
+      <c r="BC20" s="94"/>
+      <c r="BD20" s="94"/>
+      <c r="BE20" s="97"/>
     </row>
     <row r="21" spans="1:57" ht="15" customHeight="1">
-      <c r="A21" s="99"/>
-      <c r="B21" s="100"/>
-      <c r="C21" s="100"/>
-      <c r="D21" s="100"/>
-      <c r="E21" s="100"/>
-      <c r="F21" s="100"/>
-      <c r="G21" s="101"/>
-      <c r="H21" s="105"/>
-      <c r="I21" s="106"/>
-      <c r="J21" s="106"/>
-      <c r="K21" s="106"/>
-      <c r="L21" s="106"/>
-      <c r="M21" s="106"/>
-      <c r="N21" s="107"/>
-      <c r="O21" s="105"/>
-      <c r="P21" s="109"/>
-      <c r="Q21" s="109"/>
-      <c r="R21" s="109"/>
-      <c r="S21" s="109"/>
-      <c r="T21" s="109"/>
-      <c r="U21" s="109"/>
-      <c r="V21" s="109"/>
-      <c r="W21" s="109"/>
-      <c r="X21" s="109"/>
-      <c r="Y21" s="109"/>
-      <c r="Z21" s="109"/>
-      <c r="AA21" s="109"/>
-      <c r="AB21" s="109"/>
-      <c r="AC21" s="109"/>
-      <c r="AD21" s="109"/>
-      <c r="AE21" s="109"/>
-      <c r="AF21" s="109"/>
-      <c r="AG21" s="109"/>
-      <c r="AH21" s="109"/>
-      <c r="AI21" s="109"/>
-      <c r="AJ21" s="109"/>
-      <c r="AK21" s="109"/>
-      <c r="AL21" s="109"/>
-      <c r="AM21" s="109"/>
-      <c r="AN21" s="109"/>
-      <c r="AO21" s="109"/>
-      <c r="AP21" s="111"/>
-      <c r="AQ21" s="108"/>
-      <c r="AR21" s="109"/>
-      <c r="AS21" s="109"/>
-      <c r="AT21" s="109"/>
-      <c r="AU21" s="109"/>
-      <c r="AV21" s="109"/>
-      <c r="AW21" s="109"/>
-      <c r="AX21" s="109"/>
-      <c r="AY21" s="109"/>
-      <c r="AZ21" s="109"/>
-      <c r="BA21" s="109"/>
-      <c r="BB21" s="109"/>
-      <c r="BC21" s="109"/>
-      <c r="BD21" s="109"/>
-      <c r="BE21" s="110"/>
+      <c r="A21" s="88"/>
+      <c r="B21" s="89"/>
+      <c r="C21" s="89"/>
+      <c r="D21" s="89"/>
+      <c r="E21" s="89"/>
+      <c r="F21" s="89"/>
+      <c r="G21" s="90"/>
+      <c r="H21" s="91"/>
+      <c r="I21" s="92"/>
+      <c r="J21" s="92"/>
+      <c r="K21" s="92"/>
+      <c r="L21" s="92"/>
+      <c r="M21" s="92"/>
+      <c r="N21" s="93"/>
+      <c r="O21" s="91"/>
+      <c r="P21" s="94"/>
+      <c r="Q21" s="94"/>
+      <c r="R21" s="94"/>
+      <c r="S21" s="94"/>
+      <c r="T21" s="94"/>
+      <c r="U21" s="94"/>
+      <c r="V21" s="94"/>
+      <c r="W21" s="94"/>
+      <c r="X21" s="94"/>
+      <c r="Y21" s="94"/>
+      <c r="Z21" s="94"/>
+      <c r="AA21" s="94"/>
+      <c r="AB21" s="94"/>
+      <c r="AC21" s="94"/>
+      <c r="AD21" s="94"/>
+      <c r="AE21" s="94"/>
+      <c r="AF21" s="94"/>
+      <c r="AG21" s="94"/>
+      <c r="AH21" s="94"/>
+      <c r="AI21" s="94"/>
+      <c r="AJ21" s="94"/>
+      <c r="AK21" s="94"/>
+      <c r="AL21" s="94"/>
+      <c r="AM21" s="94"/>
+      <c r="AN21" s="94"/>
+      <c r="AO21" s="94"/>
+      <c r="AP21" s="95"/>
+      <c r="AQ21" s="96"/>
+      <c r="AR21" s="94"/>
+      <c r="AS21" s="94"/>
+      <c r="AT21" s="94"/>
+      <c r="AU21" s="94"/>
+      <c r="AV21" s="94"/>
+      <c r="AW21" s="94"/>
+      <c r="AX21" s="94"/>
+      <c r="AY21" s="94"/>
+      <c r="AZ21" s="94"/>
+      <c r="BA21" s="94"/>
+      <c r="BB21" s="94"/>
+      <c r="BC21" s="94"/>
+      <c r="BD21" s="94"/>
+      <c r="BE21" s="97"/>
     </row>
     <row r="22" spans="1:57" ht="15" customHeight="1">
-      <c r="A22" s="99"/>
-      <c r="B22" s="100"/>
-      <c r="C22" s="100"/>
-      <c r="D22" s="100"/>
-      <c r="E22" s="100"/>
-      <c r="F22" s="100"/>
-      <c r="G22" s="101"/>
-      <c r="H22" s="105"/>
-      <c r="I22" s="106"/>
-      <c r="J22" s="106"/>
-      <c r="K22" s="106"/>
-      <c r="L22" s="106"/>
-      <c r="M22" s="106"/>
-      <c r="N22" s="107"/>
-      <c r="O22" s="105"/>
-      <c r="P22" s="109"/>
-      <c r="Q22" s="109"/>
-      <c r="R22" s="109"/>
-      <c r="S22" s="109"/>
-      <c r="T22" s="109"/>
-      <c r="U22" s="109"/>
-      <c r="V22" s="109"/>
-      <c r="W22" s="109"/>
-      <c r="X22" s="109"/>
-      <c r="Y22" s="109"/>
-      <c r="Z22" s="109"/>
-      <c r="AA22" s="109"/>
-      <c r="AB22" s="109"/>
-      <c r="AC22" s="109"/>
-      <c r="AD22" s="109"/>
-      <c r="AE22" s="109"/>
-      <c r="AF22" s="109"/>
-      <c r="AG22" s="109"/>
-      <c r="AH22" s="109"/>
-      <c r="AI22" s="109"/>
-      <c r="AJ22" s="109"/>
-      <c r="AK22" s="109"/>
-      <c r="AL22" s="109"/>
-      <c r="AM22" s="109"/>
-      <c r="AN22" s="109"/>
-      <c r="AO22" s="109"/>
-      <c r="AP22" s="111"/>
-      <c r="AQ22" s="108"/>
-      <c r="AR22" s="109"/>
-      <c r="AS22" s="109"/>
-      <c r="AT22" s="109"/>
-      <c r="AU22" s="109"/>
-      <c r="AV22" s="109"/>
-      <c r="AW22" s="109"/>
-      <c r="AX22" s="109"/>
-      <c r="AY22" s="109"/>
-      <c r="AZ22" s="109"/>
-      <c r="BA22" s="109"/>
-      <c r="BB22" s="109"/>
-      <c r="BC22" s="109"/>
-      <c r="BD22" s="109"/>
-      <c r="BE22" s="110"/>
+      <c r="A22" s="88"/>
+      <c r="B22" s="89"/>
+      <c r="C22" s="89"/>
+      <c r="D22" s="89"/>
+      <c r="E22" s="89"/>
+      <c r="F22" s="89"/>
+      <c r="G22" s="90"/>
+      <c r="H22" s="91"/>
+      <c r="I22" s="92"/>
+      <c r="J22" s="92"/>
+      <c r="K22" s="92"/>
+      <c r="L22" s="92"/>
+      <c r="M22" s="92"/>
+      <c r="N22" s="93"/>
+      <c r="O22" s="91"/>
+      <c r="P22" s="94"/>
+      <c r="Q22" s="94"/>
+      <c r="R22" s="94"/>
+      <c r="S22" s="94"/>
+      <c r="T22" s="94"/>
+      <c r="U22" s="94"/>
+      <c r="V22" s="94"/>
+      <c r="W22" s="94"/>
+      <c r="X22" s="94"/>
+      <c r="Y22" s="94"/>
+      <c r="Z22" s="94"/>
+      <c r="AA22" s="94"/>
+      <c r="AB22" s="94"/>
+      <c r="AC22" s="94"/>
+      <c r="AD22" s="94"/>
+      <c r="AE22" s="94"/>
+      <c r="AF22" s="94"/>
+      <c r="AG22" s="94"/>
+      <c r="AH22" s="94"/>
+      <c r="AI22" s="94"/>
+      <c r="AJ22" s="94"/>
+      <c r="AK22" s="94"/>
+      <c r="AL22" s="94"/>
+      <c r="AM22" s="94"/>
+      <c r="AN22" s="94"/>
+      <c r="AO22" s="94"/>
+      <c r="AP22" s="95"/>
+      <c r="AQ22" s="96"/>
+      <c r="AR22" s="94"/>
+      <c r="AS22" s="94"/>
+      <c r="AT22" s="94"/>
+      <c r="AU22" s="94"/>
+      <c r="AV22" s="94"/>
+      <c r="AW22" s="94"/>
+      <c r="AX22" s="94"/>
+      <c r="AY22" s="94"/>
+      <c r="AZ22" s="94"/>
+      <c r="BA22" s="94"/>
+      <c r="BB22" s="94"/>
+      <c r="BC22" s="94"/>
+      <c r="BD22" s="94"/>
+      <c r="BE22" s="97"/>
     </row>
     <row r="23" spans="1:57" ht="15" customHeight="1">
-      <c r="A23" s="99"/>
-      <c r="B23" s="100"/>
-      <c r="C23" s="100"/>
-      <c r="D23" s="100"/>
-      <c r="E23" s="100"/>
-      <c r="F23" s="100"/>
-      <c r="G23" s="101"/>
-      <c r="H23" s="105"/>
-      <c r="I23" s="106"/>
-      <c r="J23" s="106"/>
-      <c r="K23" s="106"/>
-      <c r="L23" s="106"/>
-      <c r="M23" s="106"/>
-      <c r="N23" s="107"/>
-      <c r="O23" s="105"/>
-      <c r="P23" s="109"/>
-      <c r="Q23" s="109"/>
-      <c r="R23" s="109"/>
-      <c r="S23" s="109"/>
-      <c r="T23" s="109"/>
-      <c r="U23" s="109"/>
-      <c r="V23" s="109"/>
-      <c r="W23" s="109"/>
-      <c r="X23" s="109"/>
-      <c r="Y23" s="109"/>
-      <c r="Z23" s="109"/>
-      <c r="AA23" s="109"/>
-      <c r="AB23" s="109"/>
-      <c r="AC23" s="109"/>
-      <c r="AD23" s="109"/>
-      <c r="AE23" s="109"/>
-      <c r="AF23" s="109"/>
-      <c r="AG23" s="109"/>
-      <c r="AH23" s="109"/>
-      <c r="AI23" s="109"/>
-      <c r="AJ23" s="109"/>
-      <c r="AK23" s="109"/>
-      <c r="AL23" s="109"/>
-      <c r="AM23" s="109"/>
-      <c r="AN23" s="109"/>
-      <c r="AO23" s="109"/>
-      <c r="AP23" s="111"/>
-      <c r="AQ23" s="108"/>
-      <c r="AR23" s="109"/>
-      <c r="AS23" s="109"/>
-      <c r="AT23" s="109"/>
-      <c r="AU23" s="109"/>
-      <c r="AV23" s="109"/>
-      <c r="AW23" s="109"/>
-      <c r="AX23" s="109"/>
-      <c r="AY23" s="109"/>
-      <c r="AZ23" s="109"/>
-      <c r="BA23" s="109"/>
-      <c r="BB23" s="109"/>
-      <c r="BC23" s="109"/>
-      <c r="BD23" s="109"/>
-      <c r="BE23" s="110"/>
+      <c r="A23" s="88"/>
+      <c r="B23" s="89"/>
+      <c r="C23" s="89"/>
+      <c r="D23" s="89"/>
+      <c r="E23" s="89"/>
+      <c r="F23" s="89"/>
+      <c r="G23" s="90"/>
+      <c r="H23" s="91"/>
+      <c r="I23" s="92"/>
+      <c r="J23" s="92"/>
+      <c r="K23" s="92"/>
+      <c r="L23" s="92"/>
+      <c r="M23" s="92"/>
+      <c r="N23" s="93"/>
+      <c r="O23" s="91"/>
+      <c r="P23" s="94"/>
+      <c r="Q23" s="94"/>
+      <c r="R23" s="94"/>
+      <c r="S23" s="94"/>
+      <c r="T23" s="94"/>
+      <c r="U23" s="94"/>
+      <c r="V23" s="94"/>
+      <c r="W23" s="94"/>
+      <c r="X23" s="94"/>
+      <c r="Y23" s="94"/>
+      <c r="Z23" s="94"/>
+      <c r="AA23" s="94"/>
+      <c r="AB23" s="94"/>
+      <c r="AC23" s="94"/>
+      <c r="AD23" s="94"/>
+      <c r="AE23" s="94"/>
+      <c r="AF23" s="94"/>
+      <c r="AG23" s="94"/>
+      <c r="AH23" s="94"/>
+      <c r="AI23" s="94"/>
+      <c r="AJ23" s="94"/>
+      <c r="AK23" s="94"/>
+      <c r="AL23" s="94"/>
+      <c r="AM23" s="94"/>
+      <c r="AN23" s="94"/>
+      <c r="AO23" s="94"/>
+      <c r="AP23" s="95"/>
+      <c r="AQ23" s="96"/>
+      <c r="AR23" s="94"/>
+      <c r="AS23" s="94"/>
+      <c r="AT23" s="94"/>
+      <c r="AU23" s="94"/>
+      <c r="AV23" s="94"/>
+      <c r="AW23" s="94"/>
+      <c r="AX23" s="94"/>
+      <c r="AY23" s="94"/>
+      <c r="AZ23" s="94"/>
+      <c r="BA23" s="94"/>
+      <c r="BB23" s="94"/>
+      <c r="BC23" s="94"/>
+      <c r="BD23" s="94"/>
+      <c r="BE23" s="97"/>
     </row>
     <row r="24" spans="1:57" ht="15" customHeight="1">
-      <c r="A24" s="99"/>
-      <c r="B24" s="100"/>
-      <c r="C24" s="100"/>
-      <c r="D24" s="100"/>
-      <c r="E24" s="100"/>
-      <c r="F24" s="100"/>
-      <c r="G24" s="101"/>
-      <c r="H24" s="105"/>
-      <c r="I24" s="106"/>
-      <c r="J24" s="106"/>
-      <c r="K24" s="106"/>
-      <c r="L24" s="106"/>
-      <c r="M24" s="106"/>
-      <c r="N24" s="107"/>
-      <c r="O24" s="105"/>
-      <c r="P24" s="109"/>
-      <c r="Q24" s="109"/>
-      <c r="R24" s="109"/>
-      <c r="S24" s="109"/>
-      <c r="T24" s="109"/>
-      <c r="U24" s="109"/>
-      <c r="V24" s="109"/>
-      <c r="W24" s="109"/>
-      <c r="X24" s="109"/>
-      <c r="Y24" s="109"/>
-      <c r="Z24" s="109"/>
-      <c r="AA24" s="109"/>
-      <c r="AB24" s="109"/>
-      <c r="AC24" s="109"/>
-      <c r="AD24" s="109"/>
-      <c r="AE24" s="109"/>
-      <c r="AF24" s="109"/>
-      <c r="AG24" s="109"/>
-      <c r="AH24" s="109"/>
-      <c r="AI24" s="109"/>
-      <c r="AJ24" s="109"/>
-      <c r="AK24" s="109"/>
-      <c r="AL24" s="109"/>
-      <c r="AM24" s="109"/>
-      <c r="AN24" s="109"/>
-      <c r="AO24" s="109"/>
-      <c r="AP24" s="111"/>
-      <c r="AQ24" s="108"/>
-      <c r="AR24" s="109"/>
-      <c r="AS24" s="109"/>
-      <c r="AT24" s="109"/>
-      <c r="AU24" s="109"/>
-      <c r="AV24" s="109"/>
-      <c r="AW24" s="109"/>
-      <c r="AX24" s="109"/>
-      <c r="AY24" s="109"/>
-      <c r="AZ24" s="109"/>
-      <c r="BA24" s="109"/>
-      <c r="BB24" s="109"/>
-      <c r="BC24" s="109"/>
-      <c r="BD24" s="109"/>
-      <c r="BE24" s="110"/>
+      <c r="A24" s="88"/>
+      <c r="B24" s="89"/>
+      <c r="C24" s="89"/>
+      <c r="D24" s="89"/>
+      <c r="E24" s="89"/>
+      <c r="F24" s="89"/>
+      <c r="G24" s="90"/>
+      <c r="H24" s="91"/>
+      <c r="I24" s="92"/>
+      <c r="J24" s="92"/>
+      <c r="K24" s="92"/>
+      <c r="L24" s="92"/>
+      <c r="M24" s="92"/>
+      <c r="N24" s="93"/>
+      <c r="O24" s="91"/>
+      <c r="P24" s="94"/>
+      <c r="Q24" s="94"/>
+      <c r="R24" s="94"/>
+      <c r="S24" s="94"/>
+      <c r="T24" s="94"/>
+      <c r="U24" s="94"/>
+      <c r="V24" s="94"/>
+      <c r="W24" s="94"/>
+      <c r="X24" s="94"/>
+      <c r="Y24" s="94"/>
+      <c r="Z24" s="94"/>
+      <c r="AA24" s="94"/>
+      <c r="AB24" s="94"/>
+      <c r="AC24" s="94"/>
+      <c r="AD24" s="94"/>
+      <c r="AE24" s="94"/>
+      <c r="AF24" s="94"/>
+      <c r="AG24" s="94"/>
+      <c r="AH24" s="94"/>
+      <c r="AI24" s="94"/>
+      <c r="AJ24" s="94"/>
+      <c r="AK24" s="94"/>
+      <c r="AL24" s="94"/>
+      <c r="AM24" s="94"/>
+      <c r="AN24" s="94"/>
+      <c r="AO24" s="94"/>
+      <c r="AP24" s="95"/>
+      <c r="AQ24" s="96"/>
+      <c r="AR24" s="94"/>
+      <c r="AS24" s="94"/>
+      <c r="AT24" s="94"/>
+      <c r="AU24" s="94"/>
+      <c r="AV24" s="94"/>
+      <c r="AW24" s="94"/>
+      <c r="AX24" s="94"/>
+      <c r="AY24" s="94"/>
+      <c r="AZ24" s="94"/>
+      <c r="BA24" s="94"/>
+      <c r="BB24" s="94"/>
+      <c r="BC24" s="94"/>
+      <c r="BD24" s="94"/>
+      <c r="BE24" s="97"/>
     </row>
     <row r="25" spans="1:57" ht="15" customHeight="1">
-      <c r="A25" s="99"/>
-      <c r="B25" s="100"/>
-      <c r="C25" s="100"/>
-      <c r="D25" s="100"/>
-      <c r="E25" s="100"/>
-      <c r="F25" s="100"/>
-      <c r="G25" s="101"/>
-      <c r="H25" s="105"/>
-      <c r="I25" s="106"/>
-      <c r="J25" s="106"/>
-      <c r="K25" s="106"/>
-      <c r="L25" s="106"/>
-      <c r="M25" s="106"/>
-      <c r="N25" s="107"/>
-      <c r="O25" s="105"/>
-      <c r="P25" s="109"/>
-      <c r="Q25" s="109"/>
-      <c r="R25" s="109"/>
-      <c r="S25" s="109"/>
-      <c r="T25" s="109"/>
-      <c r="U25" s="109"/>
-      <c r="V25" s="109"/>
-      <c r="W25" s="109"/>
-      <c r="X25" s="109"/>
-      <c r="Y25" s="109"/>
-      <c r="Z25" s="109"/>
-      <c r="AA25" s="109"/>
-      <c r="AB25" s="109"/>
-      <c r="AC25" s="109"/>
-      <c r="AD25" s="109"/>
-      <c r="AE25" s="109"/>
-      <c r="AF25" s="109"/>
-      <c r="AG25" s="109"/>
-      <c r="AH25" s="109"/>
-      <c r="AI25" s="109"/>
-      <c r="AJ25" s="109"/>
-      <c r="AK25" s="109"/>
-      <c r="AL25" s="109"/>
-      <c r="AM25" s="109"/>
-      <c r="AN25" s="109"/>
-      <c r="AO25" s="109"/>
-      <c r="AP25" s="111"/>
-      <c r="AQ25" s="108"/>
-      <c r="AR25" s="109"/>
-      <c r="AS25" s="109"/>
-      <c r="AT25" s="109"/>
-      <c r="AU25" s="109"/>
-      <c r="AV25" s="109"/>
-      <c r="AW25" s="109"/>
-      <c r="AX25" s="109"/>
-      <c r="AY25" s="109"/>
-      <c r="AZ25" s="109"/>
-      <c r="BA25" s="109"/>
-      <c r="BB25" s="109"/>
-      <c r="BC25" s="109"/>
-      <c r="BD25" s="109"/>
-      <c r="BE25" s="110"/>
+      <c r="A25" s="88"/>
+      <c r="B25" s="89"/>
+      <c r="C25" s="89"/>
+      <c r="D25" s="89"/>
+      <c r="E25" s="89"/>
+      <c r="F25" s="89"/>
+      <c r="G25" s="90"/>
+      <c r="H25" s="91"/>
+      <c r="I25" s="92"/>
+      <c r="J25" s="92"/>
+      <c r="K25" s="92"/>
+      <c r="L25" s="92"/>
+      <c r="M25" s="92"/>
+      <c r="N25" s="93"/>
+      <c r="O25" s="91"/>
+      <c r="P25" s="94"/>
+      <c r="Q25" s="94"/>
+      <c r="R25" s="94"/>
+      <c r="S25" s="94"/>
+      <c r="T25" s="94"/>
+      <c r="U25" s="94"/>
+      <c r="V25" s="94"/>
+      <c r="W25" s="94"/>
+      <c r="X25" s="94"/>
+      <c r="Y25" s="94"/>
+      <c r="Z25" s="94"/>
+      <c r="AA25" s="94"/>
+      <c r="AB25" s="94"/>
+      <c r="AC25" s="94"/>
+      <c r="AD25" s="94"/>
+      <c r="AE25" s="94"/>
+      <c r="AF25" s="94"/>
+      <c r="AG25" s="94"/>
+      <c r="AH25" s="94"/>
+      <c r="AI25" s="94"/>
+      <c r="AJ25" s="94"/>
+      <c r="AK25" s="94"/>
+      <c r="AL25" s="94"/>
+      <c r="AM25" s="94"/>
+      <c r="AN25" s="94"/>
+      <c r="AO25" s="94"/>
+      <c r="AP25" s="95"/>
+      <c r="AQ25" s="96"/>
+      <c r="AR25" s="94"/>
+      <c r="AS25" s="94"/>
+      <c r="AT25" s="94"/>
+      <c r="AU25" s="94"/>
+      <c r="AV25" s="94"/>
+      <c r="AW25" s="94"/>
+      <c r="AX25" s="94"/>
+      <c r="AY25" s="94"/>
+      <c r="AZ25" s="94"/>
+      <c r="BA25" s="94"/>
+      <c r="BB25" s="94"/>
+      <c r="BC25" s="94"/>
+      <c r="BD25" s="94"/>
+      <c r="BE25" s="97"/>
     </row>
     <row r="26" spans="1:57" ht="15" customHeight="1">
-      <c r="A26" s="99"/>
-      <c r="B26" s="100"/>
-      <c r="C26" s="100"/>
-      <c r="D26" s="100"/>
-      <c r="E26" s="100"/>
-      <c r="F26" s="100"/>
-      <c r="G26" s="101"/>
-      <c r="H26" s="105"/>
-      <c r="I26" s="106"/>
-      <c r="J26" s="106"/>
-      <c r="K26" s="106"/>
-      <c r="L26" s="106"/>
-      <c r="M26" s="106"/>
-      <c r="N26" s="107"/>
-      <c r="O26" s="105"/>
-      <c r="P26" s="109"/>
-      <c r="Q26" s="109"/>
-      <c r="R26" s="109"/>
-      <c r="S26" s="109"/>
-      <c r="T26" s="109"/>
-      <c r="U26" s="109"/>
-      <c r="V26" s="109"/>
-      <c r="W26" s="109"/>
-      <c r="X26" s="109"/>
-      <c r="Y26" s="109"/>
-      <c r="Z26" s="109"/>
-      <c r="AA26" s="109"/>
-      <c r="AB26" s="109"/>
-      <c r="AC26" s="109"/>
-      <c r="AD26" s="109"/>
-      <c r="AE26" s="109"/>
-      <c r="AF26" s="109"/>
-      <c r="AG26" s="109"/>
-      <c r="AH26" s="109"/>
-      <c r="AI26" s="109"/>
-      <c r="AJ26" s="109"/>
-      <c r="AK26" s="109"/>
-      <c r="AL26" s="109"/>
-      <c r="AM26" s="109"/>
-      <c r="AN26" s="109"/>
-      <c r="AO26" s="109"/>
-      <c r="AP26" s="111"/>
-      <c r="AQ26" s="108"/>
-      <c r="AR26" s="109"/>
-      <c r="AS26" s="109"/>
-      <c r="AT26" s="109"/>
-      <c r="AU26" s="109"/>
-      <c r="AV26" s="109"/>
-      <c r="AW26" s="109"/>
-      <c r="AX26" s="109"/>
-      <c r="AY26" s="109"/>
-      <c r="AZ26" s="109"/>
-      <c r="BA26" s="109"/>
-      <c r="BB26" s="109"/>
-      <c r="BC26" s="109"/>
-      <c r="BD26" s="109"/>
-      <c r="BE26" s="110"/>
+      <c r="A26" s="88"/>
+      <c r="B26" s="89"/>
+      <c r="C26" s="89"/>
+      <c r="D26" s="89"/>
+      <c r="E26" s="89"/>
+      <c r="F26" s="89"/>
+      <c r="G26" s="90"/>
+      <c r="H26" s="91"/>
+      <c r="I26" s="92"/>
+      <c r="J26" s="92"/>
+      <c r="K26" s="92"/>
+      <c r="L26" s="92"/>
+      <c r="M26" s="92"/>
+      <c r="N26" s="93"/>
+      <c r="O26" s="91"/>
+      <c r="P26" s="94"/>
+      <c r="Q26" s="94"/>
+      <c r="R26" s="94"/>
+      <c r="S26" s="94"/>
+      <c r="T26" s="94"/>
+      <c r="U26" s="94"/>
+      <c r="V26" s="94"/>
+      <c r="W26" s="94"/>
+      <c r="X26" s="94"/>
+      <c r="Y26" s="94"/>
+      <c r="Z26" s="94"/>
+      <c r="AA26" s="94"/>
+      <c r="AB26" s="94"/>
+      <c r="AC26" s="94"/>
+      <c r="AD26" s="94"/>
+      <c r="AE26" s="94"/>
+      <c r="AF26" s="94"/>
+      <c r="AG26" s="94"/>
+      <c r="AH26" s="94"/>
+      <c r="AI26" s="94"/>
+      <c r="AJ26" s="94"/>
+      <c r="AK26" s="94"/>
+      <c r="AL26" s="94"/>
+      <c r="AM26" s="94"/>
+      <c r="AN26" s="94"/>
+      <c r="AO26" s="94"/>
+      <c r="AP26" s="95"/>
+      <c r="AQ26" s="96"/>
+      <c r="AR26" s="94"/>
+      <c r="AS26" s="94"/>
+      <c r="AT26" s="94"/>
+      <c r="AU26" s="94"/>
+      <c r="AV26" s="94"/>
+      <c r="AW26" s="94"/>
+      <c r="AX26" s="94"/>
+      <c r="AY26" s="94"/>
+      <c r="AZ26" s="94"/>
+      <c r="BA26" s="94"/>
+      <c r="BB26" s="94"/>
+      <c r="BC26" s="94"/>
+      <c r="BD26" s="94"/>
+      <c r="BE26" s="97"/>
     </row>
     <row r="27" spans="1:57" ht="15" customHeight="1">
-      <c r="A27" s="99"/>
-      <c r="B27" s="100"/>
-      <c r="C27" s="100"/>
-      <c r="D27" s="100"/>
-      <c r="E27" s="100"/>
-      <c r="F27" s="100"/>
-      <c r="G27" s="101"/>
-      <c r="H27" s="105"/>
-      <c r="I27" s="106"/>
-      <c r="J27" s="106"/>
-      <c r="K27" s="106"/>
-      <c r="L27" s="106"/>
-      <c r="M27" s="106"/>
-      <c r="N27" s="107"/>
-      <c r="O27" s="105"/>
-      <c r="P27" s="109"/>
-      <c r="Q27" s="109"/>
-      <c r="R27" s="109"/>
-      <c r="S27" s="109"/>
-      <c r="T27" s="109"/>
-      <c r="U27" s="109"/>
-      <c r="V27" s="109"/>
-      <c r="W27" s="109"/>
-      <c r="X27" s="109"/>
-      <c r="Y27" s="109"/>
-      <c r="Z27" s="109"/>
-      <c r="AA27" s="109"/>
-      <c r="AB27" s="109"/>
-      <c r="AC27" s="109"/>
-      <c r="AD27" s="109"/>
-      <c r="AE27" s="109"/>
-      <c r="AF27" s="109"/>
-      <c r="AG27" s="109"/>
-      <c r="AH27" s="109"/>
-      <c r="AI27" s="109"/>
-      <c r="AJ27" s="109"/>
-      <c r="AK27" s="109"/>
-      <c r="AL27" s="109"/>
-      <c r="AM27" s="109"/>
-      <c r="AN27" s="109"/>
-      <c r="AO27" s="109"/>
-      <c r="AP27" s="111"/>
-      <c r="AQ27" s="108"/>
-      <c r="AR27" s="109"/>
-      <c r="AS27" s="109"/>
-      <c r="AT27" s="109"/>
-      <c r="AU27" s="109"/>
-      <c r="AV27" s="109"/>
-      <c r="AW27" s="109"/>
-      <c r="AX27" s="109"/>
-      <c r="AY27" s="109"/>
-      <c r="AZ27" s="109"/>
-      <c r="BA27" s="109"/>
-      <c r="BB27" s="109"/>
-      <c r="BC27" s="109"/>
-      <c r="BD27" s="109"/>
-      <c r="BE27" s="110"/>
+      <c r="A27" s="88"/>
+      <c r="B27" s="89"/>
+      <c r="C27" s="89"/>
+      <c r="D27" s="89"/>
+      <c r="E27" s="89"/>
+      <c r="F27" s="89"/>
+      <c r="G27" s="90"/>
+      <c r="H27" s="91"/>
+      <c r="I27" s="92"/>
+      <c r="J27" s="92"/>
+      <c r="K27" s="92"/>
+      <c r="L27" s="92"/>
+      <c r="M27" s="92"/>
+      <c r="N27" s="93"/>
+      <c r="O27" s="91"/>
+      <c r="P27" s="94"/>
+      <c r="Q27" s="94"/>
+      <c r="R27" s="94"/>
+      <c r="S27" s="94"/>
+      <c r="T27" s="94"/>
+      <c r="U27" s="94"/>
+      <c r="V27" s="94"/>
+      <c r="W27" s="94"/>
+      <c r="X27" s="94"/>
+      <c r="Y27" s="94"/>
+      <c r="Z27" s="94"/>
+      <c r="AA27" s="94"/>
+      <c r="AB27" s="94"/>
+      <c r="AC27" s="94"/>
+      <c r="AD27" s="94"/>
+      <c r="AE27" s="94"/>
+      <c r="AF27" s="94"/>
+      <c r="AG27" s="94"/>
+      <c r="AH27" s="94"/>
+      <c r="AI27" s="94"/>
+      <c r="AJ27" s="94"/>
+      <c r="AK27" s="94"/>
+      <c r="AL27" s="94"/>
+      <c r="AM27" s="94"/>
+      <c r="AN27" s="94"/>
+      <c r="AO27" s="94"/>
+      <c r="AP27" s="95"/>
+      <c r="AQ27" s="96"/>
+      <c r="AR27" s="94"/>
+      <c r="AS27" s="94"/>
+      <c r="AT27" s="94"/>
+      <c r="AU27" s="94"/>
+      <c r="AV27" s="94"/>
+      <c r="AW27" s="94"/>
+      <c r="AX27" s="94"/>
+      <c r="AY27" s="94"/>
+      <c r="AZ27" s="94"/>
+      <c r="BA27" s="94"/>
+      <c r="BB27" s="94"/>
+      <c r="BC27" s="94"/>
+      <c r="BD27" s="94"/>
+      <c r="BE27" s="97"/>
     </row>
     <row r="28" spans="1:57" ht="15" customHeight="1">
-      <c r="A28" s="99"/>
-      <c r="B28" s="100"/>
-      <c r="C28" s="100"/>
-      <c r="D28" s="100"/>
-      <c r="E28" s="100"/>
-      <c r="F28" s="100"/>
-      <c r="G28" s="101"/>
-      <c r="H28" s="105"/>
-      <c r="I28" s="106"/>
-      <c r="J28" s="106"/>
-      <c r="K28" s="106"/>
-      <c r="L28" s="106"/>
-      <c r="M28" s="106"/>
-      <c r="N28" s="107"/>
-      <c r="O28" s="105"/>
-      <c r="P28" s="109"/>
-      <c r="Q28" s="109"/>
-      <c r="R28" s="109"/>
-      <c r="S28" s="109"/>
-      <c r="T28" s="109"/>
-      <c r="U28" s="109"/>
-      <c r="V28" s="109"/>
-      <c r="W28" s="109"/>
-      <c r="X28" s="109"/>
-      <c r="Y28" s="109"/>
-      <c r="Z28" s="109"/>
-      <c r="AA28" s="109"/>
-      <c r="AB28" s="109"/>
-      <c r="AC28" s="109"/>
-      <c r="AD28" s="109"/>
-      <c r="AE28" s="109"/>
-      <c r="AF28" s="109"/>
-      <c r="AG28" s="109"/>
-      <c r="AH28" s="109"/>
-      <c r="AI28" s="109"/>
-      <c r="AJ28" s="109"/>
-      <c r="AK28" s="109"/>
-      <c r="AL28" s="109"/>
-      <c r="AM28" s="109"/>
-      <c r="AN28" s="109"/>
-      <c r="AO28" s="109"/>
-      <c r="AP28" s="111"/>
-      <c r="AQ28" s="108"/>
-      <c r="AR28" s="109"/>
-      <c r="AS28" s="109"/>
-      <c r="AT28" s="109"/>
-      <c r="AU28" s="109"/>
-      <c r="AV28" s="109"/>
-      <c r="AW28" s="109"/>
-      <c r="AX28" s="109"/>
-      <c r="AY28" s="109"/>
-      <c r="AZ28" s="109"/>
-      <c r="BA28" s="109"/>
-      <c r="BB28" s="109"/>
-      <c r="BC28" s="109"/>
-      <c r="BD28" s="109"/>
-      <c r="BE28" s="110"/>
+      <c r="A28" s="88"/>
+      <c r="B28" s="89"/>
+      <c r="C28" s="89"/>
+      <c r="D28" s="89"/>
+      <c r="E28" s="89"/>
+      <c r="F28" s="89"/>
+      <c r="G28" s="90"/>
+      <c r="H28" s="91"/>
+      <c r="I28" s="92"/>
+      <c r="J28" s="92"/>
+      <c r="K28" s="92"/>
+      <c r="L28" s="92"/>
+      <c r="M28" s="92"/>
+      <c r="N28" s="93"/>
+      <c r="O28" s="91"/>
+      <c r="P28" s="94"/>
+      <c r="Q28" s="94"/>
+      <c r="R28" s="94"/>
+      <c r="S28" s="94"/>
+      <c r="T28" s="94"/>
+      <c r="U28" s="94"/>
+      <c r="V28" s="94"/>
+      <c r="W28" s="94"/>
+      <c r="X28" s="94"/>
+      <c r="Y28" s="94"/>
+      <c r="Z28" s="94"/>
+      <c r="AA28" s="94"/>
+      <c r="AB28" s="94"/>
+      <c r="AC28" s="94"/>
+      <c r="AD28" s="94"/>
+      <c r="AE28" s="94"/>
+      <c r="AF28" s="94"/>
+      <c r="AG28" s="94"/>
+      <c r="AH28" s="94"/>
+      <c r="AI28" s="94"/>
+      <c r="AJ28" s="94"/>
+      <c r="AK28" s="94"/>
+      <c r="AL28" s="94"/>
+      <c r="AM28" s="94"/>
+      <c r="AN28" s="94"/>
+      <c r="AO28" s="94"/>
+      <c r="AP28" s="95"/>
+      <c r="AQ28" s="96"/>
+      <c r="AR28" s="94"/>
+      <c r="AS28" s="94"/>
+      <c r="AT28" s="94"/>
+      <c r="AU28" s="94"/>
+      <c r="AV28" s="94"/>
+      <c r="AW28" s="94"/>
+      <c r="AX28" s="94"/>
+      <c r="AY28" s="94"/>
+      <c r="AZ28" s="94"/>
+      <c r="BA28" s="94"/>
+      <c r="BB28" s="94"/>
+      <c r="BC28" s="94"/>
+      <c r="BD28" s="94"/>
+      <c r="BE28" s="97"/>
     </row>
     <row r="29" spans="1:57" ht="15" customHeight="1">
-      <c r="A29" s="99"/>
-      <c r="B29" s="100"/>
-      <c r="C29" s="100"/>
-      <c r="D29" s="100"/>
-      <c r="E29" s="100"/>
-      <c r="F29" s="100"/>
-      <c r="G29" s="101"/>
-      <c r="H29" s="105"/>
-      <c r="I29" s="106"/>
-      <c r="J29" s="106"/>
-      <c r="K29" s="106"/>
-      <c r="L29" s="106"/>
-      <c r="M29" s="106"/>
-      <c r="N29" s="107"/>
-      <c r="O29" s="105"/>
-      <c r="P29" s="109"/>
-      <c r="Q29" s="109"/>
-      <c r="R29" s="109"/>
-      <c r="S29" s="109"/>
-      <c r="T29" s="109"/>
-      <c r="U29" s="109"/>
-      <c r="V29" s="109"/>
-      <c r="W29" s="109"/>
-      <c r="X29" s="109"/>
-      <c r="Y29" s="109"/>
-      <c r="Z29" s="109"/>
-      <c r="AA29" s="109"/>
-      <c r="AB29" s="109"/>
-      <c r="AC29" s="109"/>
-      <c r="AD29" s="109"/>
-      <c r="AE29" s="109"/>
-      <c r="AF29" s="109"/>
-      <c r="AG29" s="109"/>
-      <c r="AH29" s="109"/>
-      <c r="AI29" s="109"/>
-      <c r="AJ29" s="109"/>
-      <c r="AK29" s="109"/>
-      <c r="AL29" s="109"/>
-      <c r="AM29" s="109"/>
-      <c r="AN29" s="109"/>
-      <c r="AO29" s="109"/>
-      <c r="AP29" s="111"/>
-      <c r="AQ29" s="108"/>
-      <c r="AR29" s="109"/>
-      <c r="AS29" s="109"/>
-      <c r="AT29" s="109"/>
-      <c r="AU29" s="109"/>
-      <c r="AV29" s="109"/>
-      <c r="AW29" s="109"/>
-      <c r="AX29" s="109"/>
-      <c r="AY29" s="109"/>
-      <c r="AZ29" s="109"/>
-      <c r="BA29" s="109"/>
-      <c r="BB29" s="109"/>
-      <c r="BC29" s="109"/>
-      <c r="BD29" s="109"/>
-      <c r="BE29" s="110"/>
+      <c r="A29" s="88"/>
+      <c r="B29" s="89"/>
+      <c r="C29" s="89"/>
+      <c r="D29" s="89"/>
+      <c r="E29" s="89"/>
+      <c r="F29" s="89"/>
+      <c r="G29" s="90"/>
+      <c r="H29" s="91"/>
+      <c r="I29" s="92"/>
+      <c r="J29" s="92"/>
+      <c r="K29" s="92"/>
+      <c r="L29" s="92"/>
+      <c r="M29" s="92"/>
+      <c r="N29" s="93"/>
+      <c r="O29" s="91"/>
+      <c r="P29" s="94"/>
+      <c r="Q29" s="94"/>
+      <c r="R29" s="94"/>
+      <c r="S29" s="94"/>
+      <c r="T29" s="94"/>
+      <c r="U29" s="94"/>
+      <c r="V29" s="94"/>
+      <c r="W29" s="94"/>
+      <c r="X29" s="94"/>
+      <c r="Y29" s="94"/>
+      <c r="Z29" s="94"/>
+      <c r="AA29" s="94"/>
+      <c r="AB29" s="94"/>
+      <c r="AC29" s="94"/>
+      <c r="AD29" s="94"/>
+      <c r="AE29" s="94"/>
+      <c r="AF29" s="94"/>
+      <c r="AG29" s="94"/>
+      <c r="AH29" s="94"/>
+      <c r="AI29" s="94"/>
+      <c r="AJ29" s="94"/>
+      <c r="AK29" s="94"/>
+      <c r="AL29" s="94"/>
+      <c r="AM29" s="94"/>
+      <c r="AN29" s="94"/>
+      <c r="AO29" s="94"/>
+      <c r="AP29" s="95"/>
+      <c r="AQ29" s="96"/>
+      <c r="AR29" s="94"/>
+      <c r="AS29" s="94"/>
+      <c r="AT29" s="94"/>
+      <c r="AU29" s="94"/>
+      <c r="AV29" s="94"/>
+      <c r="AW29" s="94"/>
+      <c r="AX29" s="94"/>
+      <c r="AY29" s="94"/>
+      <c r="AZ29" s="94"/>
+      <c r="BA29" s="94"/>
+      <c r="BB29" s="94"/>
+      <c r="BC29" s="94"/>
+      <c r="BD29" s="94"/>
+      <c r="BE29" s="97"/>
     </row>
     <row r="30" spans="1:57" ht="15" customHeight="1">
-      <c r="A30" s="99"/>
-      <c r="B30" s="100"/>
-      <c r="C30" s="100"/>
-      <c r="D30" s="100"/>
-      <c r="E30" s="100"/>
-      <c r="F30" s="100"/>
-      <c r="G30" s="101"/>
-      <c r="H30" s="105"/>
-      <c r="I30" s="106"/>
-      <c r="J30" s="106"/>
-      <c r="K30" s="106"/>
-      <c r="L30" s="106"/>
-      <c r="M30" s="106"/>
-      <c r="N30" s="107"/>
-      <c r="O30" s="105"/>
-      <c r="P30" s="109"/>
-      <c r="Q30" s="109"/>
-      <c r="R30" s="109"/>
-      <c r="S30" s="109"/>
-      <c r="T30" s="109"/>
-      <c r="U30" s="109"/>
-      <c r="V30" s="109"/>
-      <c r="W30" s="109"/>
-      <c r="X30" s="109"/>
-      <c r="Y30" s="109"/>
-      <c r="Z30" s="109"/>
-      <c r="AA30" s="109"/>
-      <c r="AB30" s="109"/>
-      <c r="AC30" s="109"/>
-      <c r="AD30" s="109"/>
-      <c r="AE30" s="109"/>
-      <c r="AF30" s="109"/>
-      <c r="AG30" s="109"/>
-      <c r="AH30" s="109"/>
-      <c r="AI30" s="109"/>
-      <c r="AJ30" s="109"/>
-      <c r="AK30" s="109"/>
-      <c r="AL30" s="109"/>
-      <c r="AM30" s="109"/>
-      <c r="AN30" s="109"/>
-      <c r="AO30" s="109"/>
-      <c r="AP30" s="111"/>
-      <c r="AQ30" s="108"/>
-      <c r="AR30" s="109"/>
-      <c r="AS30" s="109"/>
-      <c r="AT30" s="109"/>
-      <c r="AU30" s="109"/>
-      <c r="AV30" s="109"/>
-      <c r="AW30" s="109"/>
-      <c r="AX30" s="109"/>
-      <c r="AY30" s="109"/>
-      <c r="AZ30" s="109"/>
-      <c r="BA30" s="109"/>
-      <c r="BB30" s="109"/>
-      <c r="BC30" s="109"/>
-      <c r="BD30" s="109"/>
-      <c r="BE30" s="110"/>
+      <c r="A30" s="88"/>
+      <c r="B30" s="89"/>
+      <c r="C30" s="89"/>
+      <c r="D30" s="89"/>
+      <c r="E30" s="89"/>
+      <c r="F30" s="89"/>
+      <c r="G30" s="90"/>
+      <c r="H30" s="91"/>
+      <c r="I30" s="92"/>
+      <c r="J30" s="92"/>
+      <c r="K30" s="92"/>
+      <c r="L30" s="92"/>
+      <c r="M30" s="92"/>
+      <c r="N30" s="93"/>
+      <c r="O30" s="91"/>
+      <c r="P30" s="94"/>
+      <c r="Q30" s="94"/>
+      <c r="R30" s="94"/>
+      <c r="S30" s="94"/>
+      <c r="T30" s="94"/>
+      <c r="U30" s="94"/>
+      <c r="V30" s="94"/>
+      <c r="W30" s="94"/>
+      <c r="X30" s="94"/>
+      <c r="Y30" s="94"/>
+      <c r="Z30" s="94"/>
+      <c r="AA30" s="94"/>
+      <c r="AB30" s="94"/>
+      <c r="AC30" s="94"/>
+      <c r="AD30" s="94"/>
+      <c r="AE30" s="94"/>
+      <c r="AF30" s="94"/>
+      <c r="AG30" s="94"/>
+      <c r="AH30" s="94"/>
+      <c r="AI30" s="94"/>
+      <c r="AJ30" s="94"/>
+      <c r="AK30" s="94"/>
+      <c r="AL30" s="94"/>
+      <c r="AM30" s="94"/>
+      <c r="AN30" s="94"/>
+      <c r="AO30" s="94"/>
+      <c r="AP30" s="95"/>
+      <c r="AQ30" s="96"/>
+      <c r="AR30" s="94"/>
+      <c r="AS30" s="94"/>
+      <c r="AT30" s="94"/>
+      <c r="AU30" s="94"/>
+      <c r="AV30" s="94"/>
+      <c r="AW30" s="94"/>
+      <c r="AX30" s="94"/>
+      <c r="AY30" s="94"/>
+      <c r="AZ30" s="94"/>
+      <c r="BA30" s="94"/>
+      <c r="BB30" s="94"/>
+      <c r="BC30" s="94"/>
+      <c r="BD30" s="94"/>
+      <c r="BE30" s="97"/>
     </row>
     <row r="31" spans="1:57" ht="15" customHeight="1">
-      <c r="A31" s="99"/>
-      <c r="B31" s="100"/>
-      <c r="C31" s="100"/>
-      <c r="D31" s="100"/>
-      <c r="E31" s="100"/>
-      <c r="F31" s="100"/>
-      <c r="G31" s="101"/>
-      <c r="H31" s="105"/>
-      <c r="I31" s="106"/>
-      <c r="J31" s="106"/>
-      <c r="K31" s="106"/>
-      <c r="L31" s="106"/>
-      <c r="M31" s="106"/>
-      <c r="N31" s="107"/>
-      <c r="O31" s="105"/>
-      <c r="P31" s="109"/>
-      <c r="Q31" s="109"/>
-      <c r="R31" s="109"/>
-      <c r="S31" s="109"/>
-      <c r="T31" s="109"/>
-      <c r="U31" s="109"/>
-      <c r="V31" s="109"/>
-      <c r="W31" s="109"/>
-      <c r="X31" s="109"/>
-      <c r="Y31" s="109"/>
-      <c r="Z31" s="109"/>
-      <c r="AA31" s="109"/>
-      <c r="AB31" s="109"/>
-      <c r="AC31" s="109"/>
-      <c r="AD31" s="109"/>
-      <c r="AE31" s="109"/>
-      <c r="AF31" s="109"/>
-      <c r="AG31" s="109"/>
-      <c r="AH31" s="109"/>
-      <c r="AI31" s="109"/>
-      <c r="AJ31" s="109"/>
-      <c r="AK31" s="109"/>
-      <c r="AL31" s="109"/>
-      <c r="AM31" s="109"/>
-      <c r="AN31" s="109"/>
-      <c r="AO31" s="109"/>
-      <c r="AP31" s="111"/>
-      <c r="AQ31" s="108"/>
-      <c r="AR31" s="109"/>
-      <c r="AS31" s="109"/>
-      <c r="AT31" s="109"/>
-      <c r="AU31" s="109"/>
-      <c r="AV31" s="109"/>
-      <c r="AW31" s="109"/>
-      <c r="AX31" s="109"/>
-      <c r="AY31" s="109"/>
-      <c r="AZ31" s="109"/>
-      <c r="BA31" s="109"/>
-      <c r="BB31" s="109"/>
-      <c r="BC31" s="109"/>
-      <c r="BD31" s="109"/>
-      <c r="BE31" s="110"/>
+      <c r="A31" s="88"/>
+      <c r="B31" s="89"/>
+      <c r="C31" s="89"/>
+      <c r="D31" s="89"/>
+      <c r="E31" s="89"/>
+      <c r="F31" s="89"/>
+      <c r="G31" s="90"/>
+      <c r="H31" s="91"/>
+      <c r="I31" s="92"/>
+      <c r="J31" s="92"/>
+      <c r="K31" s="92"/>
+      <c r="L31" s="92"/>
+      <c r="M31" s="92"/>
+      <c r="N31" s="93"/>
+      <c r="O31" s="91"/>
+      <c r="P31" s="94"/>
+      <c r="Q31" s="94"/>
+      <c r="R31" s="94"/>
+      <c r="S31" s="94"/>
+      <c r="T31" s="94"/>
+      <c r="U31" s="94"/>
+      <c r="V31" s="94"/>
+      <c r="W31" s="94"/>
+      <c r="X31" s="94"/>
+      <c r="Y31" s="94"/>
+      <c r="Z31" s="94"/>
+      <c r="AA31" s="94"/>
+      <c r="AB31" s="94"/>
+      <c r="AC31" s="94"/>
+      <c r="AD31" s="94"/>
+      <c r="AE31" s="94"/>
+      <c r="AF31" s="94"/>
+      <c r="AG31" s="94"/>
+      <c r="AH31" s="94"/>
+      <c r="AI31" s="94"/>
+      <c r="AJ31" s="94"/>
+      <c r="AK31" s="94"/>
+      <c r="AL31" s="94"/>
+      <c r="AM31" s="94"/>
+      <c r="AN31" s="94"/>
+      <c r="AO31" s="94"/>
+      <c r="AP31" s="95"/>
+      <c r="AQ31" s="96"/>
+      <c r="AR31" s="94"/>
+      <c r="AS31" s="94"/>
+      <c r="AT31" s="94"/>
+      <c r="AU31" s="94"/>
+      <c r="AV31" s="94"/>
+      <c r="AW31" s="94"/>
+      <c r="AX31" s="94"/>
+      <c r="AY31" s="94"/>
+      <c r="AZ31" s="94"/>
+      <c r="BA31" s="94"/>
+      <c r="BB31" s="94"/>
+      <c r="BC31" s="94"/>
+      <c r="BD31" s="94"/>
+      <c r="BE31" s="97"/>
     </row>
     <row r="32" spans="1:57" ht="15" customHeight="1">
-      <c r="A32" s="99"/>
-      <c r="B32" s="100"/>
-      <c r="C32" s="100"/>
-      <c r="D32" s="100"/>
-      <c r="E32" s="100"/>
-      <c r="F32" s="100"/>
-      <c r="G32" s="101"/>
-      <c r="H32" s="105"/>
-      <c r="I32" s="106"/>
-      <c r="J32" s="106"/>
-      <c r="K32" s="106"/>
-      <c r="L32" s="106"/>
-      <c r="M32" s="106"/>
-      <c r="N32" s="107"/>
-      <c r="O32" s="105"/>
-      <c r="P32" s="109"/>
-      <c r="Q32" s="109"/>
-      <c r="R32" s="109"/>
-      <c r="S32" s="109"/>
-      <c r="T32" s="109"/>
-      <c r="U32" s="109"/>
-      <c r="V32" s="109"/>
-      <c r="W32" s="109"/>
-      <c r="X32" s="109"/>
-      <c r="Y32" s="109"/>
-      <c r="Z32" s="109"/>
-      <c r="AA32" s="109"/>
-      <c r="AB32" s="109"/>
-      <c r="AC32" s="109"/>
-      <c r="AD32" s="109"/>
-      <c r="AE32" s="109"/>
-      <c r="AF32" s="109"/>
-      <c r="AG32" s="109"/>
-      <c r="AH32" s="109"/>
-      <c r="AI32" s="109"/>
-      <c r="AJ32" s="109"/>
-      <c r="AK32" s="109"/>
-      <c r="AL32" s="109"/>
-      <c r="AM32" s="109"/>
-      <c r="AN32" s="109"/>
-      <c r="AO32" s="109"/>
-      <c r="AP32" s="111"/>
-      <c r="AQ32" s="108"/>
-      <c r="AR32" s="109"/>
-      <c r="AS32" s="109"/>
-      <c r="AT32" s="109"/>
-      <c r="AU32" s="109"/>
-      <c r="AV32" s="109"/>
-      <c r="AW32" s="109"/>
-      <c r="AX32" s="109"/>
-      <c r="AY32" s="109"/>
-      <c r="AZ32" s="109"/>
-      <c r="BA32" s="109"/>
-      <c r="BB32" s="109"/>
-      <c r="BC32" s="109"/>
-      <c r="BD32" s="109"/>
-      <c r="BE32" s="110"/>
+      <c r="A32" s="88"/>
+      <c r="B32" s="89"/>
+      <c r="C32" s="89"/>
+      <c r="D32" s="89"/>
+      <c r="E32" s="89"/>
+      <c r="F32" s="89"/>
+      <c r="G32" s="90"/>
+      <c r="H32" s="91"/>
+      <c r="I32" s="92"/>
+      <c r="J32" s="92"/>
+      <c r="K32" s="92"/>
+      <c r="L32" s="92"/>
+      <c r="M32" s="92"/>
+      <c r="N32" s="93"/>
+      <c r="O32" s="91"/>
+      <c r="P32" s="94"/>
+      <c r="Q32" s="94"/>
+      <c r="R32" s="94"/>
+      <c r="S32" s="94"/>
+      <c r="T32" s="94"/>
+      <c r="U32" s="94"/>
+      <c r="V32" s="94"/>
+      <c r="W32" s="94"/>
+      <c r="X32" s="94"/>
+      <c r="Y32" s="94"/>
+      <c r="Z32" s="94"/>
+      <c r="AA32" s="94"/>
+      <c r="AB32" s="94"/>
+      <c r="AC32" s="94"/>
+      <c r="AD32" s="94"/>
+      <c r="AE32" s="94"/>
+      <c r="AF32" s="94"/>
+      <c r="AG32" s="94"/>
+      <c r="AH32" s="94"/>
+      <c r="AI32" s="94"/>
+      <c r="AJ32" s="94"/>
+      <c r="AK32" s="94"/>
+      <c r="AL32" s="94"/>
+      <c r="AM32" s="94"/>
+      <c r="AN32" s="94"/>
+      <c r="AO32" s="94"/>
+      <c r="AP32" s="95"/>
+      <c r="AQ32" s="96"/>
+      <c r="AR32" s="94"/>
+      <c r="AS32" s="94"/>
+      <c r="AT32" s="94"/>
+      <c r="AU32" s="94"/>
+      <c r="AV32" s="94"/>
+      <c r="AW32" s="94"/>
+      <c r="AX32" s="94"/>
+      <c r="AY32" s="94"/>
+      <c r="AZ32" s="94"/>
+      <c r="BA32" s="94"/>
+      <c r="BB32" s="94"/>
+      <c r="BC32" s="94"/>
+      <c r="BD32" s="94"/>
+      <c r="BE32" s="97"/>
     </row>
     <row r="33" spans="1:57" ht="15" customHeight="1">
-      <c r="A33" s="99"/>
-      <c r="B33" s="100"/>
-      <c r="C33" s="100"/>
-      <c r="D33" s="100"/>
-      <c r="E33" s="100"/>
-      <c r="F33" s="100"/>
-      <c r="G33" s="101"/>
-      <c r="H33" s="105"/>
-      <c r="I33" s="106"/>
-      <c r="J33" s="106"/>
-      <c r="K33" s="106"/>
-      <c r="L33" s="106"/>
-      <c r="M33" s="106"/>
-      <c r="N33" s="107"/>
-      <c r="O33" s="105"/>
-      <c r="P33" s="109"/>
-      <c r="Q33" s="109"/>
-      <c r="R33" s="109"/>
-      <c r="S33" s="109"/>
-      <c r="T33" s="109"/>
-      <c r="U33" s="109"/>
-      <c r="V33" s="109"/>
-      <c r="W33" s="109"/>
-      <c r="X33" s="109"/>
-      <c r="Y33" s="109"/>
-      <c r="Z33" s="109"/>
-      <c r="AA33" s="109"/>
-      <c r="AB33" s="109"/>
-      <c r="AC33" s="109"/>
-      <c r="AD33" s="109"/>
-      <c r="AE33" s="109"/>
-      <c r="AF33" s="109"/>
-      <c r="AG33" s="109"/>
-      <c r="AH33" s="109"/>
-      <c r="AI33" s="109"/>
-      <c r="AJ33" s="109"/>
-      <c r="AK33" s="109"/>
-      <c r="AL33" s="109"/>
-      <c r="AM33" s="109"/>
-      <c r="AN33" s="109"/>
-      <c r="AO33" s="109"/>
-      <c r="AP33" s="111"/>
-      <c r="AQ33" s="108"/>
-      <c r="AR33" s="109"/>
-      <c r="AS33" s="109"/>
-      <c r="AT33" s="109"/>
-      <c r="AU33" s="109"/>
-      <c r="AV33" s="109"/>
-      <c r="AW33" s="109"/>
-      <c r="AX33" s="109"/>
-      <c r="AY33" s="109"/>
-      <c r="AZ33" s="109"/>
-      <c r="BA33" s="109"/>
-      <c r="BB33" s="109"/>
-      <c r="BC33" s="109"/>
-      <c r="BD33" s="109"/>
-      <c r="BE33" s="110"/>
+      <c r="A33" s="88"/>
+      <c r="B33" s="89"/>
+      <c r="C33" s="89"/>
+      <c r="D33" s="89"/>
+      <c r="E33" s="89"/>
+      <c r="F33" s="89"/>
+      <c r="G33" s="90"/>
+      <c r="H33" s="91"/>
+      <c r="I33" s="92"/>
+      <c r="J33" s="92"/>
+      <c r="K33" s="92"/>
+      <c r="L33" s="92"/>
+      <c r="M33" s="92"/>
+      <c r="N33" s="93"/>
+      <c r="O33" s="91"/>
+      <c r="P33" s="94"/>
+      <c r="Q33" s="94"/>
+      <c r="R33" s="94"/>
+      <c r="S33" s="94"/>
+      <c r="T33" s="94"/>
+      <c r="U33" s="94"/>
+      <c r="V33" s="94"/>
+      <c r="W33" s="94"/>
+      <c r="X33" s="94"/>
+      <c r="Y33" s="94"/>
+      <c r="Z33" s="94"/>
+      <c r="AA33" s="94"/>
+      <c r="AB33" s="94"/>
+      <c r="AC33" s="94"/>
+      <c r="AD33" s="94"/>
+      <c r="AE33" s="94"/>
+      <c r="AF33" s="94"/>
+      <c r="AG33" s="94"/>
+      <c r="AH33" s="94"/>
+      <c r="AI33" s="94"/>
+      <c r="AJ33" s="94"/>
+      <c r="AK33" s="94"/>
+      <c r="AL33" s="94"/>
+      <c r="AM33" s="94"/>
+      <c r="AN33" s="94"/>
+      <c r="AO33" s="94"/>
+      <c r="AP33" s="95"/>
+      <c r="AQ33" s="96"/>
+      <c r="AR33" s="94"/>
+      <c r="AS33" s="94"/>
+      <c r="AT33" s="94"/>
+      <c r="AU33" s="94"/>
+      <c r="AV33" s="94"/>
+      <c r="AW33" s="94"/>
+      <c r="AX33" s="94"/>
+      <c r="AY33" s="94"/>
+      <c r="AZ33" s="94"/>
+      <c r="BA33" s="94"/>
+      <c r="BB33" s="94"/>
+      <c r="BC33" s="94"/>
+      <c r="BD33" s="94"/>
+      <c r="BE33" s="97"/>
     </row>
     <row r="34" spans="1:57" ht="15" customHeight="1">
-      <c r="A34" s="99"/>
-      <c r="B34" s="100"/>
-      <c r="C34" s="100"/>
-      <c r="D34" s="100"/>
-      <c r="E34" s="100"/>
-      <c r="F34" s="100"/>
-      <c r="G34" s="101"/>
-      <c r="H34" s="105"/>
-      <c r="I34" s="106"/>
-      <c r="J34" s="106"/>
-      <c r="K34" s="106"/>
-      <c r="L34" s="106"/>
-      <c r="M34" s="106"/>
-      <c r="N34" s="107"/>
-      <c r="O34" s="105"/>
-      <c r="P34" s="109"/>
-      <c r="Q34" s="109"/>
-      <c r="R34" s="109"/>
-      <c r="S34" s="109"/>
-      <c r="T34" s="109"/>
-      <c r="U34" s="109"/>
-      <c r="V34" s="109"/>
-      <c r="W34" s="109"/>
-      <c r="X34" s="109"/>
-      <c r="Y34" s="109"/>
-      <c r="Z34" s="109"/>
-      <c r="AA34" s="109"/>
-      <c r="AB34" s="109"/>
-      <c r="AC34" s="109"/>
-      <c r="AD34" s="109"/>
-      <c r="AE34" s="109"/>
-      <c r="AF34" s="109"/>
-      <c r="AG34" s="109"/>
-      <c r="AH34" s="109"/>
-      <c r="AI34" s="109"/>
-      <c r="AJ34" s="109"/>
-      <c r="AK34" s="109"/>
-      <c r="AL34" s="109"/>
-      <c r="AM34" s="109"/>
-      <c r="AN34" s="109"/>
-      <c r="AO34" s="109"/>
-      <c r="AP34" s="111"/>
-      <c r="AQ34" s="108"/>
-      <c r="AR34" s="109"/>
-      <c r="AS34" s="109"/>
-      <c r="AT34" s="109"/>
-      <c r="AU34" s="109"/>
-      <c r="AV34" s="109"/>
-      <c r="AW34" s="109"/>
-      <c r="AX34" s="109"/>
-      <c r="AY34" s="109"/>
-      <c r="AZ34" s="109"/>
-      <c r="BA34" s="109"/>
-      <c r="BB34" s="109"/>
-      <c r="BC34" s="109"/>
-      <c r="BD34" s="109"/>
-      <c r="BE34" s="110"/>
+      <c r="A34" s="88"/>
+      <c r="B34" s="89"/>
+      <c r="C34" s="89"/>
+      <c r="D34" s="89"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="89"/>
+      <c r="G34" s="90"/>
+      <c r="H34" s="91"/>
+      <c r="I34" s="92"/>
+      <c r="J34" s="92"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="92"/>
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="91"/>
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="94"/>
+      <c r="S34" s="94"/>
+      <c r="T34" s="94"/>
+      <c r="U34" s="94"/>
+      <c r="V34" s="94"/>
+      <c r="W34" s="94"/>
+      <c r="X34" s="94"/>
+      <c r="Y34" s="94"/>
+      <c r="Z34" s="94"/>
+      <c r="AA34" s="94"/>
+      <c r="AB34" s="94"/>
+      <c r="AC34" s="94"/>
+      <c r="AD34" s="94"/>
+      <c r="AE34" s="94"/>
+      <c r="AF34" s="94"/>
+      <c r="AG34" s="94"/>
+      <c r="AH34" s="94"/>
+      <c r="AI34" s="94"/>
+      <c r="AJ34" s="94"/>
+      <c r="AK34" s="94"/>
+      <c r="AL34" s="94"/>
+      <c r="AM34" s="94"/>
+      <c r="AN34" s="94"/>
+      <c r="AO34" s="94"/>
+      <c r="AP34" s="95"/>
+      <c r="AQ34" s="96"/>
+      <c r="AR34" s="94"/>
+      <c r="AS34" s="94"/>
+      <c r="AT34" s="94"/>
+      <c r="AU34" s="94"/>
+      <c r="AV34" s="94"/>
+      <c r="AW34" s="94"/>
+      <c r="AX34" s="94"/>
+      <c r="AY34" s="94"/>
+      <c r="AZ34" s="94"/>
+      <c r="BA34" s="94"/>
+      <c r="BB34" s="94"/>
+      <c r="BC34" s="94"/>
+      <c r="BD34" s="94"/>
+      <c r="BE34" s="97"/>
     </row>
     <row r="35" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="118"/>
-      <c r="B35" s="119"/>
-      <c r="C35" s="119"/>
-      <c r="D35" s="119"/>
-      <c r="E35" s="119"/>
-      <c r="F35" s="119"/>
-      <c r="G35" s="120"/>
-      <c r="H35" s="121"/>
-      <c r="I35" s="122"/>
-      <c r="J35" s="122"/>
-      <c r="K35" s="122"/>
-      <c r="L35" s="122"/>
-      <c r="M35" s="122"/>
-      <c r="N35" s="123"/>
-      <c r="O35" s="121"/>
-      <c r="P35" s="124"/>
-      <c r="Q35" s="124"/>
-      <c r="R35" s="124"/>
-      <c r="S35" s="124"/>
-      <c r="T35" s="124"/>
-      <c r="U35" s="124"/>
-      <c r="V35" s="124"/>
-      <c r="W35" s="124"/>
-      <c r="X35" s="124"/>
-      <c r="Y35" s="124"/>
-      <c r="Z35" s="124"/>
-      <c r="AA35" s="124"/>
-      <c r="AB35" s="124"/>
-      <c r="AC35" s="124"/>
-      <c r="AD35" s="124"/>
-      <c r="AE35" s="124"/>
-      <c r="AF35" s="124"/>
-      <c r="AG35" s="124"/>
-      <c r="AH35" s="124"/>
-      <c r="AI35" s="124"/>
-      <c r="AJ35" s="124"/>
-      <c r="AK35" s="124"/>
-      <c r="AL35" s="124"/>
-      <c r="AM35" s="124"/>
-      <c r="AN35" s="124"/>
-      <c r="AO35" s="124"/>
-      <c r="AP35" s="125"/>
-      <c r="AQ35" s="126"/>
-      <c r="AR35" s="124"/>
-      <c r="AS35" s="124"/>
-      <c r="AT35" s="124"/>
-      <c r="AU35" s="124"/>
-      <c r="AV35" s="124"/>
-      <c r="AW35" s="124"/>
-      <c r="AX35" s="124"/>
-      <c r="AY35" s="124"/>
-      <c r="AZ35" s="124"/>
-      <c r="BA35" s="124"/>
-      <c r="BB35" s="124"/>
-      <c r="BC35" s="124"/>
-      <c r="BD35" s="124"/>
-      <c r="BE35" s="127"/>
+      <c r="A35" s="78"/>
+      <c r="B35" s="79"/>
+      <c r="C35" s="79"/>
+      <c r="D35" s="79"/>
+      <c r="E35" s="79"/>
+      <c r="F35" s="79"/>
+      <c r="G35" s="80"/>
+      <c r="H35" s="81"/>
+      <c r="I35" s="82"/>
+      <c r="J35" s="82"/>
+      <c r="K35" s="82"/>
+      <c r="L35" s="82"/>
+      <c r="M35" s="82"/>
+      <c r="N35" s="83"/>
+      <c r="O35" s="81"/>
+      <c r="P35" s="84"/>
+      <c r="Q35" s="84"/>
+      <c r="R35" s="84"/>
+      <c r="S35" s="84"/>
+      <c r="T35" s="84"/>
+      <c r="U35" s="84"/>
+      <c r="V35" s="84"/>
+      <c r="W35" s="84"/>
+      <c r="X35" s="84"/>
+      <c r="Y35" s="84"/>
+      <c r="Z35" s="84"/>
+      <c r="AA35" s="84"/>
+      <c r="AB35" s="84"/>
+      <c r="AC35" s="84"/>
+      <c r="AD35" s="84"/>
+      <c r="AE35" s="84"/>
+      <c r="AF35" s="84"/>
+      <c r="AG35" s="84"/>
+      <c r="AH35" s="84"/>
+      <c r="AI35" s="84"/>
+      <c r="AJ35" s="84"/>
+      <c r="AK35" s="84"/>
+      <c r="AL35" s="84"/>
+      <c r="AM35" s="84"/>
+      <c r="AN35" s="84"/>
+      <c r="AO35" s="84"/>
+      <c r="AP35" s="85"/>
+      <c r="AQ35" s="86"/>
+      <c r="AR35" s="84"/>
+      <c r="AS35" s="84"/>
+      <c r="AT35" s="84"/>
+      <c r="AU35" s="84"/>
+      <c r="AV35" s="84"/>
+      <c r="AW35" s="84"/>
+      <c r="AX35" s="84"/>
+      <c r="AY35" s="84"/>
+      <c r="AZ35" s="84"/>
+      <c r="BA35" s="84"/>
+      <c r="BB35" s="84"/>
+      <c r="BC35" s="84"/>
+      <c r="BD35" s="84"/>
+      <c r="BE35" s="87"/>
     </row>
   </sheetData>
   <mergeCells count="133">
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="H35:N35"/>
-    <mergeCell ref="O35:AP35"/>
-    <mergeCell ref="AQ35:BE35"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="H33:N33"/>
-    <mergeCell ref="O33:AP33"/>
-    <mergeCell ref="AQ33:BE33"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="H34:N34"/>
-    <mergeCell ref="O34:AP34"/>
-    <mergeCell ref="AQ34:BE34"/>
+    <mergeCell ref="A1:BE1"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="H3:N3"/>
+    <mergeCell ref="O3:AP3"/>
+    <mergeCell ref="AQ3:BE3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="O4:AP4"/>
+    <mergeCell ref="AQ4:BE4"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="H7:N7"/>
+    <mergeCell ref="O7:AP7"/>
+    <mergeCell ref="AQ7:BE7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="H8:N8"/>
+    <mergeCell ref="O8:AP8"/>
+    <mergeCell ref="AQ8:BE8"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="O5:AP5"/>
+    <mergeCell ref="AQ5:BE5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="O6:AP6"/>
+    <mergeCell ref="AQ6:BE6"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="H11:N11"/>
+    <mergeCell ref="O11:AP11"/>
+    <mergeCell ref="AQ11:BE11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="H12:N12"/>
+    <mergeCell ref="O12:AP12"/>
+    <mergeCell ref="AQ12:BE12"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="O9:AP9"/>
+    <mergeCell ref="AQ9:BE9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="H10:N10"/>
+    <mergeCell ref="O10:AP10"/>
+    <mergeCell ref="AQ10:BE10"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="H15:N15"/>
+    <mergeCell ref="O15:AP15"/>
+    <mergeCell ref="AQ15:BE15"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="H16:N16"/>
+    <mergeCell ref="O16:AP16"/>
+    <mergeCell ref="AQ16:BE16"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="H13:N13"/>
+    <mergeCell ref="O13:AP13"/>
+    <mergeCell ref="AQ13:BE13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="H14:N14"/>
+    <mergeCell ref="O14:AP14"/>
+    <mergeCell ref="AQ14:BE14"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:AP19"/>
+    <mergeCell ref="AQ19:BE19"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:AP20"/>
+    <mergeCell ref="AQ20:BE20"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="H17:N17"/>
+    <mergeCell ref="O17:AP17"/>
+    <mergeCell ref="AQ17:BE17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:AP18"/>
+    <mergeCell ref="AQ18:BE18"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="H23:N23"/>
+    <mergeCell ref="O23:AP23"/>
+    <mergeCell ref="AQ23:BE23"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="H24:N24"/>
+    <mergeCell ref="O24:AP24"/>
+    <mergeCell ref="AQ24:BE24"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:AP21"/>
+    <mergeCell ref="AQ21:BE21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="H22:N22"/>
+    <mergeCell ref="O22:AP22"/>
+    <mergeCell ref="AQ22:BE22"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="H27:N27"/>
+    <mergeCell ref="O27:AP27"/>
+    <mergeCell ref="AQ27:BE27"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="H28:N28"/>
+    <mergeCell ref="O28:AP28"/>
+    <mergeCell ref="AQ28:BE28"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="H25:N25"/>
+    <mergeCell ref="O25:AP25"/>
+    <mergeCell ref="AQ25:BE25"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="H26:N26"/>
+    <mergeCell ref="O26:AP26"/>
+    <mergeCell ref="AQ26:BE26"/>
     <mergeCell ref="A31:G31"/>
     <mergeCell ref="H31:N31"/>
     <mergeCell ref="O31:AP31"/>
@@ -13707,111 +14040,18 @@
     <mergeCell ref="H30:N30"/>
     <mergeCell ref="O30:AP30"/>
     <mergeCell ref="AQ30:BE30"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="H27:N27"/>
-    <mergeCell ref="O27:AP27"/>
-    <mergeCell ref="AQ27:BE27"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="H28:N28"/>
-    <mergeCell ref="O28:AP28"/>
-    <mergeCell ref="AQ28:BE28"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="H25:N25"/>
-    <mergeCell ref="O25:AP25"/>
-    <mergeCell ref="AQ25:BE25"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="H26:N26"/>
-    <mergeCell ref="O26:AP26"/>
-    <mergeCell ref="AQ26:BE26"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="H23:N23"/>
-    <mergeCell ref="O23:AP23"/>
-    <mergeCell ref="AQ23:BE23"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="H24:N24"/>
-    <mergeCell ref="O24:AP24"/>
-    <mergeCell ref="AQ24:BE24"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:AP21"/>
-    <mergeCell ref="AQ21:BE21"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="H22:N22"/>
-    <mergeCell ref="O22:AP22"/>
-    <mergeCell ref="AQ22:BE22"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:AP19"/>
-    <mergeCell ref="AQ19:BE19"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:AP20"/>
-    <mergeCell ref="AQ20:BE20"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="H17:N17"/>
-    <mergeCell ref="O17:AP17"/>
-    <mergeCell ref="AQ17:BE17"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:AP18"/>
-    <mergeCell ref="AQ18:BE18"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="H15:N15"/>
-    <mergeCell ref="O15:AP15"/>
-    <mergeCell ref="AQ15:BE15"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="H16:N16"/>
-    <mergeCell ref="O16:AP16"/>
-    <mergeCell ref="AQ16:BE16"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="H13:N13"/>
-    <mergeCell ref="O13:AP13"/>
-    <mergeCell ref="AQ13:BE13"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="H14:N14"/>
-    <mergeCell ref="O14:AP14"/>
-    <mergeCell ref="AQ14:BE14"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="H11:N11"/>
-    <mergeCell ref="O11:AP11"/>
-    <mergeCell ref="AQ11:BE11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="H12:N12"/>
-    <mergeCell ref="O12:AP12"/>
-    <mergeCell ref="AQ12:BE12"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="H9:N9"/>
-    <mergeCell ref="O9:AP9"/>
-    <mergeCell ref="AQ9:BE9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="H10:N10"/>
-    <mergeCell ref="O10:AP10"/>
-    <mergeCell ref="AQ10:BE10"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="H7:N7"/>
-    <mergeCell ref="O7:AP7"/>
-    <mergeCell ref="AQ7:BE7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="H8:N8"/>
-    <mergeCell ref="O8:AP8"/>
-    <mergeCell ref="AQ8:BE8"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="H5:N5"/>
-    <mergeCell ref="O5:AP5"/>
-    <mergeCell ref="AQ5:BE5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="H6:N6"/>
-    <mergeCell ref="O6:AP6"/>
-    <mergeCell ref="AQ6:BE6"/>
-    <mergeCell ref="A1:BE1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="H3:N3"/>
-    <mergeCell ref="O3:AP3"/>
-    <mergeCell ref="AQ3:BE3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="H4:N4"/>
-    <mergeCell ref="O4:AP4"/>
-    <mergeCell ref="AQ4:BE4"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="H35:N35"/>
+    <mergeCell ref="O35:AP35"/>
+    <mergeCell ref="AQ35:BE35"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="H33:N33"/>
+    <mergeCell ref="O33:AP33"/>
+    <mergeCell ref="AQ33:BE33"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="H34:N34"/>
+    <mergeCell ref="O34:AP34"/>
+    <mergeCell ref="AQ34:BE34"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>

--- a/development/MS/spec/MSBB/Logic/MSBBLA0010_SlsSchdSrch.xlsx
+++ b/development/MS/spec/MSBB/Logic/MSBBLA0010_SlsSchdSrch.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\PJ\TK\dev\development\MS\spec\MSBB\Logic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C01B90B-16B3-4152-83A0-5AFE1485E054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0080CC63-6AE2-4FC6-B539-E3DE847D4442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="794" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="645">
   <si>
     <t>*</t>
   </si>
@@ -2070,12 +2070,6 @@
     <t>装備後売上日</t>
   </si>
   <si>
-    <t>prd_itm_cd</t>
-  </si>
-  <si>
-    <t>prd_itm_nm</t>
-  </si>
-  <si>
     <t>Product item cd.</t>
   </si>
   <si>
@@ -2152,15 +2146,6 @@
   </si>
   <si>
     <t>商談名</t>
-  </si>
-  <si>
-    <t>prd_itm_sub1</t>
-  </si>
-  <si>
-    <t>prd_itm_sub2</t>
-  </si>
-  <si>
-    <t>prd_itm_sub3</t>
   </si>
   <si>
     <t>#MA.ZOHO_SLS_SCHD_NO</t>
@@ -3008,93 +2993,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3156,6 +3054,93 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4717,17 +4702,17 @@
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
       <c r="D27" s="8" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="E27" s="29" t="s">
         <v>152</v>
       </c>
       <c r="F27" s="29"/>
       <c r="G27" s="42" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="H27" s="42" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="I27" s="8" t="s">
         <v>245</v>
@@ -4764,7 +4749,7 @@
         <v>432</v>
       </c>
       <c r="H28" s="42" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="I28" s="8" t="s">
         <v>245</v>
@@ -4801,7 +4786,7 @@
         <v>433</v>
       </c>
       <c r="H29" s="42" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="I29" s="8" t="s">
         <v>245</v>
@@ -4838,7 +4823,7 @@
         <v>456</v>
       </c>
       <c r="H30" s="42" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="I30" s="8" t="s">
         <v>245</v>
@@ -4873,7 +4858,7 @@
         <v>457</v>
       </c>
       <c r="H31" s="42" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="I31" s="8" t="s">
         <v>245</v>
@@ -4898,7 +4883,7 @@
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E32" s="29" t="s">
         <v>156</v>
@@ -4908,7 +4893,7 @@
         <v>440</v>
       </c>
       <c r="H32" s="42" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="I32" s="8" t="s">
         <v>245</v>
@@ -4943,7 +4928,7 @@
         <v>441</v>
       </c>
       <c r="H33" s="42" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="I33" s="8" t="s">
         <v>245</v>
@@ -4978,7 +4963,7 @@
         <v>440</v>
       </c>
       <c r="H34" s="42" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="I34" s="8" t="s">
         <v>245</v>
@@ -5013,7 +4998,7 @@
         <v>441</v>
       </c>
       <c r="H35" s="42" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="I35" s="8" t="s">
         <v>245</v>
@@ -5048,7 +5033,7 @@
         <v>440</v>
       </c>
       <c r="H36" s="42" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="I36" s="8" t="s">
         <v>245</v>
@@ -5083,7 +5068,7 @@
         <v>441</v>
       </c>
       <c r="H37" s="42" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="I37" s="8" t="s">
         <v>245</v>
@@ -5108,7 +5093,7 @@
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
       <c r="D38" s="8" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E38" s="29" t="s">
         <v>156</v>
@@ -5118,7 +5103,7 @@
         <v>440</v>
       </c>
       <c r="H38" s="42" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="I38" s="8" t="s">
         <v>245</v>
@@ -5143,7 +5128,7 @@
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
       <c r="D39" s="8" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E39" s="29" t="s">
         <v>157</v>
@@ -5153,7 +5138,7 @@
         <v>441</v>
       </c>
       <c r="H39" s="42" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="I39" s="8" t="s">
         <v>245</v>
@@ -5178,7 +5163,7 @@
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
       <c r="D40" s="8" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E40" s="29" t="s">
         <v>156</v>
@@ -5188,7 +5173,7 @@
         <v>440</v>
       </c>
       <c r="H40" s="42" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="I40" s="8" t="s">
         <v>245</v>
@@ -5213,7 +5198,7 @@
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
       <c r="D41" s="8" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E41" s="29" t="s">
         <v>157</v>
@@ -5223,7 +5208,7 @@
         <v>441</v>
       </c>
       <c r="H41" s="42" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="I41" s="8" t="s">
         <v>245</v>
@@ -5803,7 +5788,7 @@
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
       <c r="D57" s="8" t="s">
-        <v>581</v>
+        <v>634</v>
       </c>
       <c r="E57" s="29" t="s">
         <v>49</v>
@@ -5840,7 +5825,7 @@
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
       <c r="D58" s="8" t="s">
-        <v>609</v>
+        <v>642</v>
       </c>
       <c r="E58" s="29" t="s">
         <v>50</v>
@@ -5877,7 +5862,7 @@
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
       <c r="D59" s="8" t="s">
-        <v>610</v>
+        <v>643</v>
       </c>
       <c r="E59" s="29" t="s">
         <v>28</v>
@@ -5914,7 +5899,7 @@
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
       <c r="D60" s="8" t="s">
-        <v>611</v>
+        <v>644</v>
       </c>
       <c r="E60" s="29" t="s">
         <v>29</v>
@@ -5951,7 +5936,7 @@
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
       <c r="D61" s="8" t="s">
-        <v>582</v>
+        <v>635</v>
       </c>
       <c r="E61" s="29" t="s">
         <v>85</v>
@@ -9834,17 +9819,17 @@
       <c r="B167" s="8"/>
       <c r="C167" s="8"/>
       <c r="D167" s="8" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="E167" s="29" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="F167" s="29"/>
       <c r="G167" s="42" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="H167" s="42" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="I167" s="8" t="s">
         <v>246</v>
@@ -9874,14 +9859,14 @@
         <v>573</v>
       </c>
       <c r="E168" s="29" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="F168" s="29"/>
       <c r="G168" s="42" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="H168" s="42" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="I168" s="8" t="s">
         <v>246</v>
@@ -9911,14 +9896,14 @@
         <v>574</v>
       </c>
       <c r="E169" s="29" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="F169" s="29"/>
       <c r="G169" s="42" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="H169" s="42" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="I169" s="8" t="s">
         <v>246</v>
@@ -10019,17 +10004,17 @@
       <c r="B172" s="8"/>
       <c r="C172" s="8"/>
       <c r="D172" s="8" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="E172" s="29" t="s">
         <v>152</v>
       </c>
       <c r="F172" s="29"/>
       <c r="G172" s="42" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="H172" s="42" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="I172" s="8" t="s">
         <v>246</v>
@@ -10056,17 +10041,17 @@
       <c r="B173" s="8"/>
       <c r="C173" s="8"/>
       <c r="D173" s="8" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="E173" s="29" t="s">
         <v>153</v>
       </c>
       <c r="F173" s="29"/>
       <c r="G173" s="42" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="H173" s="42" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="I173" s="8" t="s">
         <v>246</v>
@@ -10389,17 +10374,17 @@
       <c r="B182" s="8"/>
       <c r="C182" s="8"/>
       <c r="D182" s="73" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="E182" s="29" t="s">
         <v>49</v>
       </c>
       <c r="F182" s="29"/>
       <c r="G182" s="42" t="s">
+        <v>581</v>
+      </c>
+      <c r="H182" s="42" t="s">
         <v>583</v>
-      </c>
-      <c r="H182" s="42" t="s">
-        <v>585</v>
       </c>
       <c r="I182" s="8" t="s">
         <v>246</v>
@@ -10426,7 +10411,7 @@
       <c r="B183" s="8"/>
       <c r="C183" s="8"/>
       <c r="D183" s="73" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="E183" s="29" t="s">
         <v>50</v>
@@ -10436,7 +10421,7 @@
         <v>452</v>
       </c>
       <c r="H183" s="42" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="I183" s="8" t="s">
         <v>246</v>
@@ -10463,7 +10448,7 @@
       <c r="B184" s="8"/>
       <c r="C184" s="8"/>
       <c r="D184" s="73" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="E184" s="29" t="s">
         <v>28</v>
@@ -10473,7 +10458,7 @@
         <v>453</v>
       </c>
       <c r="H184" s="42" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="I184" s="8" t="s">
         <v>246</v>
@@ -10500,7 +10485,7 @@
       <c r="B185" s="8"/>
       <c r="C185" s="8"/>
       <c r="D185" s="73" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="E185" s="29" t="s">
         <v>29</v>
@@ -10510,7 +10495,7 @@
         <v>454</v>
       </c>
       <c r="H185" s="42" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="I185" s="8" t="s">
         <v>246</v>
@@ -10537,17 +10522,17 @@
       <c r="B186" s="8"/>
       <c r="C186" s="8"/>
       <c r="D186" s="73" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="E186" s="29" t="s">
         <v>85</v>
       </c>
       <c r="F186" s="29"/>
       <c r="G186" s="42" t="s">
+        <v>582</v>
+      </c>
+      <c r="H186" s="42" t="s">
         <v>584</v>
-      </c>
-      <c r="H186" s="42" t="s">
-        <v>586</v>
       </c>
       <c r="I186" s="8" t="s">
         <v>246</v>
@@ -10574,7 +10559,7 @@
       <c r="B187" s="8"/>
       <c r="C187" s="8"/>
       <c r="D187" s="73" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="E187" s="29" t="s">
         <v>27</v>
@@ -10611,7 +10596,7 @@
       <c r="B188" s="8"/>
       <c r="C188" s="8"/>
       <c r="D188" s="73" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="E188" s="29" t="s">
         <v>27</v>
@@ -10648,17 +10633,17 @@
       <c r="B189" s="8"/>
       <c r="C189" s="8"/>
       <c r="D189" s="73" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="E189" s="29" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="F189" s="29"/>
       <c r="G189" s="42" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H189" s="42" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="I189" s="8" t="s">
         <v>246</v>
@@ -10685,17 +10670,17 @@
       <c r="B190" s="8"/>
       <c r="C190" s="8"/>
       <c r="D190" s="73" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="E190" s="29" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="F190" s="29"/>
       <c r="G190" s="42" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="H190" s="42" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="I190" s="8" t="s">
         <v>246</v>
@@ -10722,17 +10707,17 @@
       <c r="B191" s="8"/>
       <c r="C191" s="8"/>
       <c r="D191" s="73" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="E191" s="29" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="F191" s="29"/>
       <c r="G191" s="42" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="H191" s="42" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="I191" s="8" t="s">
         <v>246</v>
@@ -10769,7 +10754,7 @@
         <v>451</v>
       </c>
       <c r="H192" s="42" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="I192" s="8" t="s">
         <v>246</v>
@@ -10806,7 +10791,7 @@
         <v>452</v>
       </c>
       <c r="H193" s="42" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="I193" s="8" t="s">
         <v>246</v>
@@ -10843,7 +10828,7 @@
         <v>453</v>
       </c>
       <c r="H194" s="42" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="I194" s="8" t="s">
         <v>246</v>
@@ -10880,7 +10865,7 @@
         <v>454</v>
       </c>
       <c r="H195" s="42" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="I195" s="8" t="s">
         <v>246</v>
@@ -10917,7 +10902,7 @@
         <v>455</v>
       </c>
       <c r="H196" s="42" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="I196" s="8" t="s">
         <v>246</v>
@@ -10944,17 +10929,17 @@
       <c r="B197" s="8"/>
       <c r="C197" s="8"/>
       <c r="D197" s="73" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="E197" s="29" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="F197" s="29"/>
       <c r="G197" s="42" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="H197" s="42" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="I197" s="8" t="s">
         <v>246</v>
@@ -10981,17 +10966,17 @@
       <c r="B198" s="8"/>
       <c r="C198" s="8"/>
       <c r="D198" s="73" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="E198" s="29" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="F198" s="29"/>
       <c r="G198" s="42" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="H198" s="42" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="I198" s="8" t="s">
         <v>246</v>
@@ -11520,6 +11505,157 @@
     </row>
   </sheetData>
   <mergeCells count="175">
+    <mergeCell ref="R196:S196"/>
+    <mergeCell ref="T196:U196"/>
+    <mergeCell ref="R199:S199"/>
+    <mergeCell ref="T199:U199"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="T50:U50"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="T147:U147"/>
+    <mergeCell ref="R68:S68"/>
+    <mergeCell ref="T68:U68"/>
+    <mergeCell ref="R164:S164"/>
+    <mergeCell ref="T164:U164"/>
+    <mergeCell ref="R144:S144"/>
+    <mergeCell ref="T150:U150"/>
+    <mergeCell ref="R153:S153"/>
+    <mergeCell ref="T144:U144"/>
+    <mergeCell ref="R168:S168"/>
+    <mergeCell ref="T168:U168"/>
+    <mergeCell ref="R182:S182"/>
+    <mergeCell ref="R170:S170"/>
+    <mergeCell ref="T170:U170"/>
+    <mergeCell ref="R171:S171"/>
+    <mergeCell ref="T171:U171"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="R58:S58"/>
+    <mergeCell ref="T58:U58"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="T48:U48"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="T27:U27"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="T24:U24"/>
+    <mergeCell ref="T204:U204"/>
+    <mergeCell ref="R200:S200"/>
+    <mergeCell ref="T200:U200"/>
+    <mergeCell ref="R207:S207"/>
+    <mergeCell ref="T207:U207"/>
+    <mergeCell ref="R206:S206"/>
+    <mergeCell ref="T206:U206"/>
+    <mergeCell ref="R205:S205"/>
+    <mergeCell ref="T205:U205"/>
+    <mergeCell ref="R202:S202"/>
+    <mergeCell ref="T202:U202"/>
+    <mergeCell ref="R201:S201"/>
+    <mergeCell ref="T201:U201"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="T69:U69"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="R73:S73"/>
+    <mergeCell ref="T73:U73"/>
+    <mergeCell ref="T60:U60"/>
+    <mergeCell ref="T56:U56"/>
+    <mergeCell ref="R57:S57"/>
+    <mergeCell ref="T57:U57"/>
+    <mergeCell ref="T43:U43"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="T44:U44"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="T52:U52"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="T71:U71"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="R150:S150"/>
+    <mergeCell ref="T49:U49"/>
+    <mergeCell ref="T67:U67"/>
+    <mergeCell ref="T26:U26"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="R53:S53"/>
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="T53:U53"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="T45:U45"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="T42:U42"/>
+    <mergeCell ref="T51:U51"/>
+    <mergeCell ref="R60:S60"/>
+    <mergeCell ref="T66:U66"/>
+    <mergeCell ref="R147:S147"/>
+    <mergeCell ref="R209:S209"/>
+    <mergeCell ref="T209:U209"/>
+    <mergeCell ref="T172:U172"/>
+    <mergeCell ref="R172:S172"/>
+    <mergeCell ref="R173:S173"/>
+    <mergeCell ref="T173:U173"/>
+    <mergeCell ref="R176:S176"/>
+    <mergeCell ref="R178:S178"/>
+    <mergeCell ref="T178:U178"/>
+    <mergeCell ref="T176:U176"/>
+    <mergeCell ref="R177:S177"/>
+    <mergeCell ref="T177:U177"/>
+    <mergeCell ref="T182:U182"/>
+    <mergeCell ref="R179:S179"/>
+    <mergeCell ref="T179:U179"/>
+    <mergeCell ref="R188:S188"/>
+    <mergeCell ref="T188:U188"/>
+    <mergeCell ref="R186:S186"/>
+    <mergeCell ref="T186:U186"/>
+    <mergeCell ref="R208:S208"/>
+    <mergeCell ref="T208:U208"/>
+    <mergeCell ref="R203:S203"/>
+    <mergeCell ref="T203:U203"/>
+    <mergeCell ref="R204:S204"/>
+    <mergeCell ref="R174:S174"/>
+    <mergeCell ref="T174:U174"/>
+    <mergeCell ref="R175:S175"/>
+    <mergeCell ref="T175:U175"/>
+    <mergeCell ref="T153:U153"/>
+    <mergeCell ref="R156:S156"/>
+    <mergeCell ref="T156:U156"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="T162:U162"/>
+    <mergeCell ref="R162:S162"/>
+    <mergeCell ref="R159:S159"/>
+    <mergeCell ref="T159:U159"/>
+    <mergeCell ref="R141:S141"/>
+    <mergeCell ref="R67:S67"/>
+    <mergeCell ref="T141:U141"/>
+    <mergeCell ref="R71:S71"/>
+    <mergeCell ref="T138:U138"/>
+    <mergeCell ref="R62:S62"/>
+    <mergeCell ref="R70:S70"/>
+    <mergeCell ref="T70:U70"/>
+    <mergeCell ref="T62:U62"/>
+    <mergeCell ref="R63:S63"/>
+    <mergeCell ref="T63:U63"/>
+    <mergeCell ref="R64:S64"/>
+    <mergeCell ref="T64:U64"/>
+    <mergeCell ref="R65:S65"/>
+    <mergeCell ref="T65:U65"/>
+    <mergeCell ref="R66:S66"/>
     <mergeCell ref="R12:S12"/>
     <mergeCell ref="T12:U12"/>
     <mergeCell ref="R187:S187"/>
@@ -11544,157 +11680,6 @@
     <mergeCell ref="T166:U166"/>
     <mergeCell ref="R167:S167"/>
     <mergeCell ref="T167:U167"/>
-    <mergeCell ref="R67:S67"/>
-    <mergeCell ref="T141:U141"/>
-    <mergeCell ref="R71:S71"/>
-    <mergeCell ref="T138:U138"/>
-    <mergeCell ref="R62:S62"/>
-    <mergeCell ref="R70:S70"/>
-    <mergeCell ref="T70:U70"/>
-    <mergeCell ref="T62:U62"/>
-    <mergeCell ref="R63:S63"/>
-    <mergeCell ref="T63:U63"/>
-    <mergeCell ref="R64:S64"/>
-    <mergeCell ref="T64:U64"/>
-    <mergeCell ref="R65:S65"/>
-    <mergeCell ref="T65:U65"/>
-    <mergeCell ref="R66:S66"/>
-    <mergeCell ref="R174:S174"/>
-    <mergeCell ref="T174:U174"/>
-    <mergeCell ref="R175:S175"/>
-    <mergeCell ref="T175:U175"/>
-    <mergeCell ref="T153:U153"/>
-    <mergeCell ref="R156:S156"/>
-    <mergeCell ref="T156:U156"/>
-    <mergeCell ref="R72:S72"/>
-    <mergeCell ref="T162:U162"/>
-    <mergeCell ref="R162:S162"/>
-    <mergeCell ref="R159:S159"/>
-    <mergeCell ref="T159:U159"/>
-    <mergeCell ref="R141:S141"/>
-    <mergeCell ref="R209:S209"/>
-    <mergeCell ref="T209:U209"/>
-    <mergeCell ref="T172:U172"/>
-    <mergeCell ref="R172:S172"/>
-    <mergeCell ref="R173:S173"/>
-    <mergeCell ref="T173:U173"/>
-    <mergeCell ref="R176:S176"/>
-    <mergeCell ref="R178:S178"/>
-    <mergeCell ref="T178:U178"/>
-    <mergeCell ref="T176:U176"/>
-    <mergeCell ref="R177:S177"/>
-    <mergeCell ref="T177:U177"/>
-    <mergeCell ref="T182:U182"/>
-    <mergeCell ref="R179:S179"/>
-    <mergeCell ref="T179:U179"/>
-    <mergeCell ref="R188:S188"/>
-    <mergeCell ref="T188:U188"/>
-    <mergeCell ref="R186:S186"/>
-    <mergeCell ref="T186:U186"/>
-    <mergeCell ref="R208:S208"/>
-    <mergeCell ref="T208:U208"/>
-    <mergeCell ref="R203:S203"/>
-    <mergeCell ref="T203:U203"/>
-    <mergeCell ref="R204:S204"/>
-    <mergeCell ref="T15:U15"/>
-    <mergeCell ref="R150:S150"/>
-    <mergeCell ref="T49:U49"/>
-    <mergeCell ref="T67:U67"/>
-    <mergeCell ref="T26:U26"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="R53:S53"/>
-    <mergeCell ref="T11:U11"/>
-    <mergeCell ref="T53:U53"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="T45:U45"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="T42:U42"/>
-    <mergeCell ref="T51:U51"/>
-    <mergeCell ref="R60:S60"/>
-    <mergeCell ref="T66:U66"/>
-    <mergeCell ref="R147:S147"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="T69:U69"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="T28:U28"/>
-    <mergeCell ref="R73:S73"/>
-    <mergeCell ref="T73:U73"/>
-    <mergeCell ref="T60:U60"/>
-    <mergeCell ref="T56:U56"/>
-    <mergeCell ref="R57:S57"/>
-    <mergeCell ref="T57:U57"/>
-    <mergeCell ref="T43:U43"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="T44:U44"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="T52:U52"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="T25:U25"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="T71:U71"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="T204:U204"/>
-    <mergeCell ref="R200:S200"/>
-    <mergeCell ref="T200:U200"/>
-    <mergeCell ref="R207:S207"/>
-    <mergeCell ref="T207:U207"/>
-    <mergeCell ref="R206:S206"/>
-    <mergeCell ref="T206:U206"/>
-    <mergeCell ref="R205:S205"/>
-    <mergeCell ref="T205:U205"/>
-    <mergeCell ref="R202:S202"/>
-    <mergeCell ref="T202:U202"/>
-    <mergeCell ref="R201:S201"/>
-    <mergeCell ref="T201:U201"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="R58:S58"/>
-    <mergeCell ref="T58:U58"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="T48:U48"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="T27:U27"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="T24:U24"/>
-    <mergeCell ref="R196:S196"/>
-    <mergeCell ref="T196:U196"/>
-    <mergeCell ref="R199:S199"/>
-    <mergeCell ref="T199:U199"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="T50:U50"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="T147:U147"/>
-    <mergeCell ref="R68:S68"/>
-    <mergeCell ref="T68:U68"/>
-    <mergeCell ref="R164:S164"/>
-    <mergeCell ref="T164:U164"/>
-    <mergeCell ref="R144:S144"/>
-    <mergeCell ref="T150:U150"/>
-    <mergeCell ref="R153:S153"/>
-    <mergeCell ref="T144:U144"/>
-    <mergeCell ref="R168:S168"/>
-    <mergeCell ref="T168:U168"/>
-    <mergeCell ref="R182:S182"/>
-    <mergeCell ref="R170:S170"/>
-    <mergeCell ref="T170:U170"/>
-    <mergeCell ref="R171:S171"/>
-    <mergeCell ref="T171:U171"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.47244094488188981" right="0.43307086614173229" top="0.55118110236220474" bottom="0.59055118110236227" header="0.55118110236220474" footer="0.11811023622047245"/>
@@ -11848,65 +11833,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="78" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
-      <c r="V1" s="108"/>
-      <c r="W1" s="108"/>
-      <c r="X1" s="108"/>
-      <c r="Y1" s="108"/>
-      <c r="Z1" s="108"/>
-      <c r="AA1" s="108"/>
-      <c r="AB1" s="108"/>
-      <c r="AC1" s="108"/>
-      <c r="AD1" s="108"/>
-      <c r="AE1" s="108"/>
-      <c r="AF1" s="108"/>
-      <c r="AG1" s="108"/>
-      <c r="AH1" s="108"/>
-      <c r="AI1" s="108"/>
-      <c r="AJ1" s="108"/>
-      <c r="AK1" s="108"/>
-      <c r="AL1" s="108"/>
-      <c r="AM1" s="108"/>
-      <c r="AN1" s="108"/>
-      <c r="AO1" s="108"/>
-      <c r="AP1" s="108"/>
-      <c r="AQ1" s="108"/>
-      <c r="AR1" s="108"/>
-      <c r="AS1" s="108"/>
-      <c r="AT1" s="108"/>
-      <c r="AU1" s="108"/>
-      <c r="AV1" s="108"/>
-      <c r="AW1" s="108"/>
-      <c r="AX1" s="108"/>
-      <c r="AY1" s="108"/>
-      <c r="AZ1" s="108"/>
-      <c r="BA1" s="108"/>
-      <c r="BB1" s="108"/>
-      <c r="BC1" s="108"/>
-      <c r="BD1" s="108"/>
-      <c r="BE1" s="109"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
+      <c r="O1" s="79"/>
+      <c r="P1" s="79"/>
+      <c r="Q1" s="79"/>
+      <c r="R1" s="79"/>
+      <c r="S1" s="79"/>
+      <c r="T1" s="79"/>
+      <c r="U1" s="79"/>
+      <c r="V1" s="79"/>
+      <c r="W1" s="79"/>
+      <c r="X1" s="79"/>
+      <c r="Y1" s="79"/>
+      <c r="Z1" s="79"/>
+      <c r="AA1" s="79"/>
+      <c r="AB1" s="79"/>
+      <c r="AC1" s="79"/>
+      <c r="AD1" s="79"/>
+      <c r="AE1" s="79"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="79"/>
+      <c r="AH1" s="79"/>
+      <c r="AI1" s="79"/>
+      <c r="AJ1" s="79"/>
+      <c r="AK1" s="79"/>
+      <c r="AL1" s="79"/>
+      <c r="AM1" s="79"/>
+      <c r="AN1" s="79"/>
+      <c r="AO1" s="79"/>
+      <c r="AP1" s="79"/>
+      <c r="AQ1" s="79"/>
+      <c r="AR1" s="79"/>
+      <c r="AS1" s="79"/>
+      <c r="AT1" s="79"/>
+      <c r="AU1" s="79"/>
+      <c r="AV1" s="79"/>
+      <c r="AW1" s="79"/>
+      <c r="AX1" s="79"/>
+      <c r="AY1" s="79"/>
+      <c r="AZ1" s="79"/>
+      <c r="BA1" s="79"/>
+      <c r="BB1" s="79"/>
+      <c r="BC1" s="79"/>
+      <c r="BD1" s="79"/>
+      <c r="BE1" s="80"/>
     </row>
     <row r="2" spans="1:57" ht="12" customHeight="1" thickBot="1">
       <c r="A2" s="51"/>
@@ -11953,1981 +11938,2080 @@
       <c r="AP2" s="51"/>
     </row>
     <row r="3" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A3" s="110" t="s">
+      <c r="A3" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="111"/>
-      <c r="C3" s="111"/>
-      <c r="D3" s="111"/>
-      <c r="E3" s="111"/>
-      <c r="F3" s="111"/>
-      <c r="G3" s="112"/>
-      <c r="H3" s="113" t="s">
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="111"/>
-      <c r="J3" s="111"/>
-      <c r="K3" s="111"/>
-      <c r="L3" s="111"/>
-      <c r="M3" s="111"/>
-      <c r="N3" s="112"/>
-      <c r="O3" s="113" t="s">
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="83"/>
+      <c r="O3" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="114"/>
-      <c r="Q3" s="114"/>
-      <c r="R3" s="114"/>
-      <c r="S3" s="114"/>
-      <c r="T3" s="114"/>
-      <c r="U3" s="114"/>
-      <c r="V3" s="114"/>
-      <c r="W3" s="114"/>
-      <c r="X3" s="114"/>
-      <c r="Y3" s="114"/>
-      <c r="Z3" s="114"/>
-      <c r="AA3" s="114"/>
-      <c r="AB3" s="114"/>
-      <c r="AC3" s="114"/>
-      <c r="AD3" s="114"/>
-      <c r="AE3" s="114"/>
-      <c r="AF3" s="114"/>
-      <c r="AG3" s="114"/>
-      <c r="AH3" s="114"/>
-      <c r="AI3" s="114"/>
-      <c r="AJ3" s="114"/>
-      <c r="AK3" s="114"/>
-      <c r="AL3" s="114"/>
-      <c r="AM3" s="114"/>
-      <c r="AN3" s="114"/>
-      <c r="AO3" s="114"/>
-      <c r="AP3" s="115"/>
-      <c r="AQ3" s="113" t="s">
+      <c r="P3" s="85"/>
+      <c r="Q3" s="85"/>
+      <c r="R3" s="85"/>
+      <c r="S3" s="85"/>
+      <c r="T3" s="85"/>
+      <c r="U3" s="85"/>
+      <c r="V3" s="85"/>
+      <c r="W3" s="85"/>
+      <c r="X3" s="85"/>
+      <c r="Y3" s="85"/>
+      <c r="Z3" s="85"/>
+      <c r="AA3" s="85"/>
+      <c r="AB3" s="85"/>
+      <c r="AC3" s="85"/>
+      <c r="AD3" s="85"/>
+      <c r="AE3" s="85"/>
+      <c r="AF3" s="85"/>
+      <c r="AG3" s="85"/>
+      <c r="AH3" s="85"/>
+      <c r="AI3" s="85"/>
+      <c r="AJ3" s="85"/>
+      <c r="AK3" s="85"/>
+      <c r="AL3" s="85"/>
+      <c r="AM3" s="85"/>
+      <c r="AN3" s="85"/>
+      <c r="AO3" s="85"/>
+      <c r="AP3" s="86"/>
+      <c r="AQ3" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="AR3" s="116"/>
-      <c r="AS3" s="116"/>
-      <c r="AT3" s="116"/>
-      <c r="AU3" s="116"/>
-      <c r="AV3" s="116"/>
-      <c r="AW3" s="116"/>
-      <c r="AX3" s="116"/>
-      <c r="AY3" s="116"/>
-      <c r="AZ3" s="116"/>
-      <c r="BA3" s="116"/>
-      <c r="BB3" s="116"/>
-      <c r="BC3" s="116"/>
-      <c r="BD3" s="116"/>
-      <c r="BE3" s="117"/>
+      <c r="AR3" s="87"/>
+      <c r="AS3" s="87"/>
+      <c r="AT3" s="87"/>
+      <c r="AU3" s="87"/>
+      <c r="AV3" s="87"/>
+      <c r="AW3" s="87"/>
+      <c r="AX3" s="87"/>
+      <c r="AY3" s="87"/>
+      <c r="AZ3" s="87"/>
+      <c r="BA3" s="87"/>
+      <c r="BB3" s="87"/>
+      <c r="BC3" s="87"/>
+      <c r="BD3" s="87"/>
+      <c r="BE3" s="88"/>
     </row>
     <row r="4" spans="1:57" ht="15" customHeight="1">
-      <c r="A4" s="118">
+      <c r="A4" s="89">
         <v>1</v>
       </c>
-      <c r="B4" s="119"/>
-      <c r="C4" s="119"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="122"/>
-      <c r="J4" s="122"/>
-      <c r="K4" s="122"/>
-      <c r="L4" s="122"/>
-      <c r="M4" s="122"/>
-      <c r="N4" s="123"/>
-      <c r="O4" s="121" t="s">
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="92"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93"/>
+      <c r="M4" s="93"/>
+      <c r="N4" s="94"/>
+      <c r="O4" s="92" t="s">
         <v>19</v>
       </c>
-      <c r="P4" s="124"/>
-      <c r="Q4" s="124"/>
-      <c r="R4" s="124"/>
-      <c r="S4" s="124"/>
-      <c r="T4" s="124"/>
-      <c r="U4" s="124"/>
-      <c r="V4" s="124"/>
-      <c r="W4" s="124"/>
-      <c r="X4" s="124"/>
-      <c r="Y4" s="124"/>
-      <c r="Z4" s="124"/>
-      <c r="AA4" s="124"/>
-      <c r="AB4" s="124"/>
-      <c r="AC4" s="124"/>
-      <c r="AD4" s="124"/>
-      <c r="AE4" s="124"/>
-      <c r="AF4" s="124"/>
-      <c r="AG4" s="124"/>
-      <c r="AH4" s="124"/>
-      <c r="AI4" s="124"/>
-      <c r="AJ4" s="124"/>
-      <c r="AK4" s="124"/>
-      <c r="AL4" s="124"/>
-      <c r="AM4" s="124"/>
-      <c r="AN4" s="124"/>
-      <c r="AO4" s="124"/>
-      <c r="AP4" s="125"/>
-      <c r="AQ4" s="126"/>
-      <c r="AR4" s="124"/>
-      <c r="AS4" s="124"/>
-      <c r="AT4" s="124"/>
-      <c r="AU4" s="124"/>
-      <c r="AV4" s="124"/>
-      <c r="AW4" s="124"/>
-      <c r="AX4" s="124"/>
-      <c r="AY4" s="124"/>
-      <c r="AZ4" s="124"/>
-      <c r="BA4" s="124"/>
-      <c r="BB4" s="124"/>
-      <c r="BC4" s="124"/>
-      <c r="BD4" s="124"/>
-      <c r="BE4" s="127"/>
+      <c r="P4" s="95"/>
+      <c r="Q4" s="95"/>
+      <c r="R4" s="95"/>
+      <c r="S4" s="95"/>
+      <c r="T4" s="95"/>
+      <c r="U4" s="95"/>
+      <c r="V4" s="95"/>
+      <c r="W4" s="95"/>
+      <c r="X4" s="95"/>
+      <c r="Y4" s="95"/>
+      <c r="Z4" s="95"/>
+      <c r="AA4" s="95"/>
+      <c r="AB4" s="95"/>
+      <c r="AC4" s="95"/>
+      <c r="AD4" s="95"/>
+      <c r="AE4" s="95"/>
+      <c r="AF4" s="95"/>
+      <c r="AG4" s="95"/>
+      <c r="AH4" s="95"/>
+      <c r="AI4" s="95"/>
+      <c r="AJ4" s="95"/>
+      <c r="AK4" s="95"/>
+      <c r="AL4" s="95"/>
+      <c r="AM4" s="95"/>
+      <c r="AN4" s="95"/>
+      <c r="AO4" s="95"/>
+      <c r="AP4" s="96"/>
+      <c r="AQ4" s="97"/>
+      <c r="AR4" s="95"/>
+      <c r="AS4" s="95"/>
+      <c r="AT4" s="95"/>
+      <c r="AU4" s="95"/>
+      <c r="AV4" s="95"/>
+      <c r="AW4" s="95"/>
+      <c r="AX4" s="95"/>
+      <c r="AY4" s="95"/>
+      <c r="AZ4" s="95"/>
+      <c r="BA4" s="95"/>
+      <c r="BB4" s="95"/>
+      <c r="BC4" s="95"/>
+      <c r="BD4" s="95"/>
+      <c r="BE4" s="98"/>
     </row>
     <row r="5" spans="1:57" ht="15" customHeight="1">
-      <c r="A5" s="88">
+      <c r="A5" s="99">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="90"/>
-      <c r="H5" s="91"/>
-      <c r="I5" s="92"/>
-      <c r="J5" s="92"/>
-      <c r="K5" s="92"/>
-      <c r="L5" s="92"/>
-      <c r="M5" s="92"/>
-      <c r="N5" s="93"/>
-      <c r="O5" s="101" t="s">
+      <c r="B5" s="100"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="100"/>
+      <c r="E5" s="100"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="101"/>
+      <c r="H5" s="105"/>
+      <c r="I5" s="106"/>
+      <c r="J5" s="106"/>
+      <c r="K5" s="106"/>
+      <c r="L5" s="106"/>
+      <c r="M5" s="106"/>
+      <c r="N5" s="107"/>
+      <c r="O5" s="112" t="s">
         <v>567</v>
       </c>
-      <c r="P5" s="102"/>
-      <c r="Q5" s="102"/>
-      <c r="R5" s="102"/>
-      <c r="S5" s="102"/>
-      <c r="T5" s="102"/>
-      <c r="U5" s="102"/>
-      <c r="V5" s="102"/>
-      <c r="W5" s="102"/>
-      <c r="X5" s="102"/>
-      <c r="Y5" s="102"/>
-      <c r="Z5" s="102"/>
-      <c r="AA5" s="102"/>
-      <c r="AB5" s="102"/>
-      <c r="AC5" s="102"/>
-      <c r="AD5" s="102"/>
-      <c r="AE5" s="102"/>
-      <c r="AF5" s="102"/>
-      <c r="AG5" s="102"/>
-      <c r="AH5" s="102"/>
-      <c r="AI5" s="102"/>
-      <c r="AJ5" s="102"/>
-      <c r="AK5" s="102"/>
-      <c r="AL5" s="102"/>
-      <c r="AM5" s="102"/>
-      <c r="AN5" s="102"/>
-      <c r="AO5" s="102"/>
-      <c r="AP5" s="103"/>
-      <c r="AQ5" s="104" t="s">
+      <c r="P5" s="113"/>
+      <c r="Q5" s="113"/>
+      <c r="R5" s="113"/>
+      <c r="S5" s="113"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="113"/>
+      <c r="V5" s="113"/>
+      <c r="W5" s="113"/>
+      <c r="X5" s="113"/>
+      <c r="Y5" s="113"/>
+      <c r="Z5" s="113"/>
+      <c r="AA5" s="113"/>
+      <c r="AB5" s="113"/>
+      <c r="AC5" s="113"/>
+      <c r="AD5" s="113"/>
+      <c r="AE5" s="113"/>
+      <c r="AF5" s="113"/>
+      <c r="AG5" s="113"/>
+      <c r="AH5" s="113"/>
+      <c r="AI5" s="113"/>
+      <c r="AJ5" s="113"/>
+      <c r="AK5" s="113"/>
+      <c r="AL5" s="113"/>
+      <c r="AM5" s="113"/>
+      <c r="AN5" s="113"/>
+      <c r="AO5" s="113"/>
+      <c r="AP5" s="114"/>
+      <c r="AQ5" s="115" t="s">
         <v>568</v>
       </c>
-      <c r="AR5" s="105"/>
-      <c r="AS5" s="105"/>
-      <c r="AT5" s="105"/>
-      <c r="AU5" s="105"/>
-      <c r="AV5" s="105"/>
-      <c r="AW5" s="105"/>
-      <c r="AX5" s="105"/>
-      <c r="AY5" s="105"/>
-      <c r="AZ5" s="105"/>
-      <c r="BA5" s="105"/>
-      <c r="BB5" s="105"/>
-      <c r="BC5" s="105"/>
-      <c r="BD5" s="105"/>
-      <c r="BE5" s="106"/>
+      <c r="AR5" s="116"/>
+      <c r="AS5" s="116"/>
+      <c r="AT5" s="116"/>
+      <c r="AU5" s="116"/>
+      <c r="AV5" s="116"/>
+      <c r="AW5" s="116"/>
+      <c r="AX5" s="116"/>
+      <c r="AY5" s="116"/>
+      <c r="AZ5" s="116"/>
+      <c r="BA5" s="116"/>
+      <c r="BB5" s="116"/>
+      <c r="BC5" s="116"/>
+      <c r="BD5" s="116"/>
+      <c r="BE5" s="117"/>
     </row>
     <row r="6" spans="1:57" ht="15" customHeight="1">
-      <c r="A6" s="88"/>
-      <c r="B6" s="89"/>
-      <c r="C6" s="89"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="89"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="90"/>
-      <c r="H6" s="98"/>
-      <c r="I6" s="99"/>
-      <c r="J6" s="99"/>
-      <c r="K6" s="99"/>
-      <c r="L6" s="99"/>
-      <c r="M6" s="99"/>
-      <c r="N6" s="100"/>
-      <c r="O6" s="91"/>
-      <c r="P6" s="94"/>
-      <c r="Q6" s="94"/>
-      <c r="R6" s="94"/>
-      <c r="S6" s="94"/>
-      <c r="T6" s="94"/>
-      <c r="U6" s="94"/>
-      <c r="V6" s="94"/>
-      <c r="W6" s="94"/>
-      <c r="X6" s="94"/>
-      <c r="Y6" s="94"/>
-      <c r="Z6" s="94"/>
-      <c r="AA6" s="94"/>
-      <c r="AB6" s="94"/>
-      <c r="AC6" s="94"/>
-      <c r="AD6" s="94"/>
-      <c r="AE6" s="94"/>
-      <c r="AF6" s="94"/>
-      <c r="AG6" s="94"/>
-      <c r="AH6" s="94"/>
-      <c r="AI6" s="94"/>
-      <c r="AJ6" s="94"/>
-      <c r="AK6" s="94"/>
-      <c r="AL6" s="94"/>
-      <c r="AM6" s="94"/>
-      <c r="AN6" s="94"/>
-      <c r="AO6" s="94"/>
-      <c r="AP6" s="95"/>
-      <c r="AQ6" s="96"/>
-      <c r="AR6" s="94"/>
-      <c r="AS6" s="94"/>
-      <c r="AT6" s="94"/>
-      <c r="AU6" s="94"/>
-      <c r="AV6" s="94"/>
-      <c r="AW6" s="94"/>
-      <c r="AX6" s="94"/>
-      <c r="AY6" s="94"/>
-      <c r="AZ6" s="94"/>
-      <c r="BA6" s="94"/>
-      <c r="BB6" s="94"/>
-      <c r="BC6" s="94"/>
-      <c r="BD6" s="94"/>
-      <c r="BE6" s="97"/>
+      <c r="A6" s="99"/>
+      <c r="B6" s="100"/>
+      <c r="C6" s="100"/>
+      <c r="D6" s="100"/>
+      <c r="E6" s="100"/>
+      <c r="F6" s="100"/>
+      <c r="G6" s="101"/>
+      <c r="H6" s="102"/>
+      <c r="I6" s="103"/>
+      <c r="J6" s="103"/>
+      <c r="K6" s="103"/>
+      <c r="L6" s="103"/>
+      <c r="M6" s="103"/>
+      <c r="N6" s="104"/>
+      <c r="O6" s="105"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="109"/>
+      <c r="R6" s="109"/>
+      <c r="S6" s="109"/>
+      <c r="T6" s="109"/>
+      <c r="U6" s="109"/>
+      <c r="V6" s="109"/>
+      <c r="W6" s="109"/>
+      <c r="X6" s="109"/>
+      <c r="Y6" s="109"/>
+      <c r="Z6" s="109"/>
+      <c r="AA6" s="109"/>
+      <c r="AB6" s="109"/>
+      <c r="AC6" s="109"/>
+      <c r="AD6" s="109"/>
+      <c r="AE6" s="109"/>
+      <c r="AF6" s="109"/>
+      <c r="AG6" s="109"/>
+      <c r="AH6" s="109"/>
+      <c r="AI6" s="109"/>
+      <c r="AJ6" s="109"/>
+      <c r="AK6" s="109"/>
+      <c r="AL6" s="109"/>
+      <c r="AM6" s="109"/>
+      <c r="AN6" s="109"/>
+      <c r="AO6" s="109"/>
+      <c r="AP6" s="111"/>
+      <c r="AQ6" s="108"/>
+      <c r="AR6" s="109"/>
+      <c r="AS6" s="109"/>
+      <c r="AT6" s="109"/>
+      <c r="AU6" s="109"/>
+      <c r="AV6" s="109"/>
+      <c r="AW6" s="109"/>
+      <c r="AX6" s="109"/>
+      <c r="AY6" s="109"/>
+      <c r="AZ6" s="109"/>
+      <c r="BA6" s="109"/>
+      <c r="BB6" s="109"/>
+      <c r="BC6" s="109"/>
+      <c r="BD6" s="109"/>
+      <c r="BE6" s="110"/>
     </row>
     <row r="7" spans="1:57" ht="15" customHeight="1">
-      <c r="A7" s="88"/>
-      <c r="B7" s="89"/>
-      <c r="C7" s="89"/>
-      <c r="D7" s="89"/>
-      <c r="E7" s="89"/>
-      <c r="F7" s="89"/>
-      <c r="G7" s="90"/>
-      <c r="H7" s="98"/>
-      <c r="I7" s="99"/>
-      <c r="J7" s="99"/>
-      <c r="K7" s="99"/>
-      <c r="L7" s="99"/>
-      <c r="M7" s="99"/>
-      <c r="N7" s="100"/>
-      <c r="O7" s="91"/>
-      <c r="P7" s="92"/>
-      <c r="Q7" s="92"/>
-      <c r="R7" s="92"/>
-      <c r="S7" s="92"/>
-      <c r="T7" s="92"/>
-      <c r="U7" s="92"/>
-      <c r="V7" s="92"/>
-      <c r="W7" s="92"/>
-      <c r="X7" s="92"/>
-      <c r="Y7" s="92"/>
-      <c r="Z7" s="92"/>
-      <c r="AA7" s="92"/>
-      <c r="AB7" s="92"/>
-      <c r="AC7" s="92"/>
-      <c r="AD7" s="92"/>
-      <c r="AE7" s="92"/>
-      <c r="AF7" s="92"/>
-      <c r="AG7" s="92"/>
-      <c r="AH7" s="92"/>
-      <c r="AI7" s="92"/>
-      <c r="AJ7" s="92"/>
-      <c r="AK7" s="92"/>
-      <c r="AL7" s="92"/>
-      <c r="AM7" s="92"/>
-      <c r="AN7" s="92"/>
-      <c r="AO7" s="92"/>
-      <c r="AP7" s="93"/>
-      <c r="AQ7" s="96"/>
-      <c r="AR7" s="94"/>
-      <c r="AS7" s="94"/>
-      <c r="AT7" s="94"/>
-      <c r="AU7" s="94"/>
-      <c r="AV7" s="94"/>
-      <c r="AW7" s="94"/>
-      <c r="AX7" s="94"/>
-      <c r="AY7" s="94"/>
-      <c r="AZ7" s="94"/>
-      <c r="BA7" s="94"/>
-      <c r="BB7" s="94"/>
-      <c r="BC7" s="94"/>
-      <c r="BD7" s="94"/>
-      <c r="BE7" s="97"/>
+      <c r="A7" s="99"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="100"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="101"/>
+      <c r="H7" s="102"/>
+      <c r="I7" s="103"/>
+      <c r="J7" s="103"/>
+      <c r="K7" s="103"/>
+      <c r="L7" s="103"/>
+      <c r="M7" s="103"/>
+      <c r="N7" s="104"/>
+      <c r="O7" s="105"/>
+      <c r="P7" s="106"/>
+      <c r="Q7" s="106"/>
+      <c r="R7" s="106"/>
+      <c r="S7" s="106"/>
+      <c r="T7" s="106"/>
+      <c r="U7" s="106"/>
+      <c r="V7" s="106"/>
+      <c r="W7" s="106"/>
+      <c r="X7" s="106"/>
+      <c r="Y7" s="106"/>
+      <c r="Z7" s="106"/>
+      <c r="AA7" s="106"/>
+      <c r="AB7" s="106"/>
+      <c r="AC7" s="106"/>
+      <c r="AD7" s="106"/>
+      <c r="AE7" s="106"/>
+      <c r="AF7" s="106"/>
+      <c r="AG7" s="106"/>
+      <c r="AH7" s="106"/>
+      <c r="AI7" s="106"/>
+      <c r="AJ7" s="106"/>
+      <c r="AK7" s="106"/>
+      <c r="AL7" s="106"/>
+      <c r="AM7" s="106"/>
+      <c r="AN7" s="106"/>
+      <c r="AO7" s="106"/>
+      <c r="AP7" s="107"/>
+      <c r="AQ7" s="108"/>
+      <c r="AR7" s="109"/>
+      <c r="AS7" s="109"/>
+      <c r="AT7" s="109"/>
+      <c r="AU7" s="109"/>
+      <c r="AV7" s="109"/>
+      <c r="AW7" s="109"/>
+      <c r="AX7" s="109"/>
+      <c r="AY7" s="109"/>
+      <c r="AZ7" s="109"/>
+      <c r="BA7" s="109"/>
+      <c r="BB7" s="109"/>
+      <c r="BC7" s="109"/>
+      <c r="BD7" s="109"/>
+      <c r="BE7" s="110"/>
     </row>
     <row r="8" spans="1:57" ht="15" customHeight="1">
-      <c r="A8" s="88"/>
-      <c r="B8" s="89"/>
-      <c r="C8" s="89"/>
-      <c r="D8" s="89"/>
-      <c r="E8" s="89"/>
-      <c r="F8" s="89"/>
-      <c r="G8" s="90"/>
-      <c r="H8" s="91"/>
-      <c r="I8" s="92"/>
-      <c r="J8" s="92"/>
-      <c r="K8" s="92"/>
-      <c r="L8" s="92"/>
-      <c r="M8" s="92"/>
-      <c r="N8" s="93"/>
-      <c r="O8" s="91"/>
-      <c r="P8" s="94"/>
-      <c r="Q8" s="94"/>
-      <c r="R8" s="94"/>
-      <c r="S8" s="94"/>
-      <c r="T8" s="94"/>
-      <c r="U8" s="94"/>
-      <c r="V8" s="94"/>
-      <c r="W8" s="94"/>
-      <c r="X8" s="94"/>
-      <c r="Y8" s="94"/>
-      <c r="Z8" s="94"/>
-      <c r="AA8" s="94"/>
-      <c r="AB8" s="94"/>
-      <c r="AC8" s="94"/>
-      <c r="AD8" s="94"/>
-      <c r="AE8" s="94"/>
-      <c r="AF8" s="94"/>
-      <c r="AG8" s="94"/>
-      <c r="AH8" s="94"/>
-      <c r="AI8" s="94"/>
-      <c r="AJ8" s="94"/>
-      <c r="AK8" s="94"/>
-      <c r="AL8" s="94"/>
-      <c r="AM8" s="94"/>
-      <c r="AN8" s="94"/>
-      <c r="AO8" s="94"/>
-      <c r="AP8" s="95"/>
-      <c r="AQ8" s="96"/>
-      <c r="AR8" s="94"/>
-      <c r="AS8" s="94"/>
-      <c r="AT8" s="94"/>
-      <c r="AU8" s="94"/>
-      <c r="AV8" s="94"/>
-      <c r="AW8" s="94"/>
-      <c r="AX8" s="94"/>
-      <c r="AY8" s="94"/>
-      <c r="AZ8" s="94"/>
-      <c r="BA8" s="94"/>
-      <c r="BB8" s="94"/>
-      <c r="BC8" s="94"/>
-      <c r="BD8" s="94"/>
-      <c r="BE8" s="97"/>
+      <c r="A8" s="99"/>
+      <c r="B8" s="100"/>
+      <c r="C8" s="100"/>
+      <c r="D8" s="100"/>
+      <c r="E8" s="100"/>
+      <c r="F8" s="100"/>
+      <c r="G8" s="101"/>
+      <c r="H8" s="105"/>
+      <c r="I8" s="106"/>
+      <c r="J8" s="106"/>
+      <c r="K8" s="106"/>
+      <c r="L8" s="106"/>
+      <c r="M8" s="106"/>
+      <c r="N8" s="107"/>
+      <c r="O8" s="105"/>
+      <c r="P8" s="109"/>
+      <c r="Q8" s="109"/>
+      <c r="R8" s="109"/>
+      <c r="S8" s="109"/>
+      <c r="T8" s="109"/>
+      <c r="U8" s="109"/>
+      <c r="V8" s="109"/>
+      <c r="W8" s="109"/>
+      <c r="X8" s="109"/>
+      <c r="Y8" s="109"/>
+      <c r="Z8" s="109"/>
+      <c r="AA8" s="109"/>
+      <c r="AB8" s="109"/>
+      <c r="AC8" s="109"/>
+      <c r="AD8" s="109"/>
+      <c r="AE8" s="109"/>
+      <c r="AF8" s="109"/>
+      <c r="AG8" s="109"/>
+      <c r="AH8" s="109"/>
+      <c r="AI8" s="109"/>
+      <c r="AJ8" s="109"/>
+      <c r="AK8" s="109"/>
+      <c r="AL8" s="109"/>
+      <c r="AM8" s="109"/>
+      <c r="AN8" s="109"/>
+      <c r="AO8" s="109"/>
+      <c r="AP8" s="111"/>
+      <c r="AQ8" s="108"/>
+      <c r="AR8" s="109"/>
+      <c r="AS8" s="109"/>
+      <c r="AT8" s="109"/>
+      <c r="AU8" s="109"/>
+      <c r="AV8" s="109"/>
+      <c r="AW8" s="109"/>
+      <c r="AX8" s="109"/>
+      <c r="AY8" s="109"/>
+      <c r="AZ8" s="109"/>
+      <c r="BA8" s="109"/>
+      <c r="BB8" s="109"/>
+      <c r="BC8" s="109"/>
+      <c r="BD8" s="109"/>
+      <c r="BE8" s="110"/>
     </row>
     <row r="9" spans="1:57" ht="15" customHeight="1">
-      <c r="A9" s="88"/>
-      <c r="B9" s="89"/>
-      <c r="C9" s="89"/>
-      <c r="D9" s="89"/>
-      <c r="E9" s="89"/>
-      <c r="F9" s="89"/>
-      <c r="G9" s="90"/>
-      <c r="H9" s="91"/>
-      <c r="I9" s="92"/>
-      <c r="J9" s="92"/>
-      <c r="K9" s="92"/>
-      <c r="L9" s="92"/>
-      <c r="M9" s="92"/>
-      <c r="N9" s="93"/>
-      <c r="O9" s="91"/>
-      <c r="P9" s="94"/>
-      <c r="Q9" s="94"/>
-      <c r="R9" s="94"/>
-      <c r="S9" s="94"/>
-      <c r="T9" s="94"/>
-      <c r="U9" s="94"/>
-      <c r="V9" s="94"/>
-      <c r="W9" s="94"/>
-      <c r="X9" s="94"/>
-      <c r="Y9" s="94"/>
-      <c r="Z9" s="94"/>
-      <c r="AA9" s="94"/>
-      <c r="AB9" s="94"/>
-      <c r="AC9" s="94"/>
-      <c r="AD9" s="94"/>
-      <c r="AE9" s="94"/>
-      <c r="AF9" s="94"/>
-      <c r="AG9" s="94"/>
-      <c r="AH9" s="94"/>
-      <c r="AI9" s="94"/>
-      <c r="AJ9" s="94"/>
-      <c r="AK9" s="94"/>
-      <c r="AL9" s="94"/>
-      <c r="AM9" s="94"/>
-      <c r="AN9" s="94"/>
-      <c r="AO9" s="94"/>
-      <c r="AP9" s="95"/>
-      <c r="AQ9" s="96"/>
-      <c r="AR9" s="94"/>
-      <c r="AS9" s="94"/>
-      <c r="AT9" s="94"/>
-      <c r="AU9" s="94"/>
-      <c r="AV9" s="94"/>
-      <c r="AW9" s="94"/>
-      <c r="AX9" s="94"/>
-      <c r="AY9" s="94"/>
-      <c r="AZ9" s="94"/>
-      <c r="BA9" s="94"/>
-      <c r="BB9" s="94"/>
-      <c r="BC9" s="94"/>
-      <c r="BD9" s="94"/>
-      <c r="BE9" s="97"/>
+      <c r="A9" s="99"/>
+      <c r="B9" s="100"/>
+      <c r="C9" s="100"/>
+      <c r="D9" s="100"/>
+      <c r="E9" s="100"/>
+      <c r="F9" s="100"/>
+      <c r="G9" s="101"/>
+      <c r="H9" s="105"/>
+      <c r="I9" s="106"/>
+      <c r="J9" s="106"/>
+      <c r="K9" s="106"/>
+      <c r="L9" s="106"/>
+      <c r="M9" s="106"/>
+      <c r="N9" s="107"/>
+      <c r="O9" s="105"/>
+      <c r="P9" s="109"/>
+      <c r="Q9" s="109"/>
+      <c r="R9" s="109"/>
+      <c r="S9" s="109"/>
+      <c r="T9" s="109"/>
+      <c r="U9" s="109"/>
+      <c r="V9" s="109"/>
+      <c r="W9" s="109"/>
+      <c r="X9" s="109"/>
+      <c r="Y9" s="109"/>
+      <c r="Z9" s="109"/>
+      <c r="AA9" s="109"/>
+      <c r="AB9" s="109"/>
+      <c r="AC9" s="109"/>
+      <c r="AD9" s="109"/>
+      <c r="AE9" s="109"/>
+      <c r="AF9" s="109"/>
+      <c r="AG9" s="109"/>
+      <c r="AH9" s="109"/>
+      <c r="AI9" s="109"/>
+      <c r="AJ9" s="109"/>
+      <c r="AK9" s="109"/>
+      <c r="AL9" s="109"/>
+      <c r="AM9" s="109"/>
+      <c r="AN9" s="109"/>
+      <c r="AO9" s="109"/>
+      <c r="AP9" s="111"/>
+      <c r="AQ9" s="108"/>
+      <c r="AR9" s="109"/>
+      <c r="AS9" s="109"/>
+      <c r="AT9" s="109"/>
+      <c r="AU9" s="109"/>
+      <c r="AV9" s="109"/>
+      <c r="AW9" s="109"/>
+      <c r="AX9" s="109"/>
+      <c r="AY9" s="109"/>
+      <c r="AZ9" s="109"/>
+      <c r="BA9" s="109"/>
+      <c r="BB9" s="109"/>
+      <c r="BC9" s="109"/>
+      <c r="BD9" s="109"/>
+      <c r="BE9" s="110"/>
     </row>
     <row r="10" spans="1:57" ht="15" customHeight="1">
-      <c r="A10" s="88"/>
-      <c r="B10" s="89"/>
-      <c r="C10" s="89"/>
-      <c r="D10" s="89"/>
-      <c r="E10" s="89"/>
-      <c r="F10" s="89"/>
-      <c r="G10" s="90"/>
-      <c r="H10" s="91"/>
-      <c r="I10" s="92"/>
-      <c r="J10" s="92"/>
-      <c r="K10" s="92"/>
-      <c r="L10" s="92"/>
-      <c r="M10" s="92"/>
-      <c r="N10" s="93"/>
-      <c r="O10" s="91"/>
-      <c r="P10" s="94"/>
-      <c r="Q10" s="94"/>
-      <c r="R10" s="94"/>
-      <c r="S10" s="94"/>
-      <c r="T10" s="94"/>
-      <c r="U10" s="94"/>
-      <c r="V10" s="94"/>
-      <c r="W10" s="94"/>
-      <c r="X10" s="94"/>
-      <c r="Y10" s="94"/>
-      <c r="Z10" s="94"/>
-      <c r="AA10" s="94"/>
-      <c r="AB10" s="94"/>
-      <c r="AC10" s="94"/>
-      <c r="AD10" s="94"/>
-      <c r="AE10" s="94"/>
-      <c r="AF10" s="94"/>
-      <c r="AG10" s="94"/>
-      <c r="AH10" s="94"/>
-      <c r="AI10" s="94"/>
-      <c r="AJ10" s="94"/>
-      <c r="AK10" s="94"/>
-      <c r="AL10" s="94"/>
-      <c r="AM10" s="94"/>
-      <c r="AN10" s="94"/>
-      <c r="AO10" s="94"/>
-      <c r="AP10" s="95"/>
-      <c r="AQ10" s="96"/>
-      <c r="AR10" s="94"/>
-      <c r="AS10" s="94"/>
-      <c r="AT10" s="94"/>
-      <c r="AU10" s="94"/>
-      <c r="AV10" s="94"/>
-      <c r="AW10" s="94"/>
-      <c r="AX10" s="94"/>
-      <c r="AY10" s="94"/>
-      <c r="AZ10" s="94"/>
-      <c r="BA10" s="94"/>
-      <c r="BB10" s="94"/>
-      <c r="BC10" s="94"/>
-      <c r="BD10" s="94"/>
-      <c r="BE10" s="97"/>
+      <c r="A10" s="99"/>
+      <c r="B10" s="100"/>
+      <c r="C10" s="100"/>
+      <c r="D10" s="100"/>
+      <c r="E10" s="100"/>
+      <c r="F10" s="100"/>
+      <c r="G10" s="101"/>
+      <c r="H10" s="105"/>
+      <c r="I10" s="106"/>
+      <c r="J10" s="106"/>
+      <c r="K10" s="106"/>
+      <c r="L10" s="106"/>
+      <c r="M10" s="106"/>
+      <c r="N10" s="107"/>
+      <c r="O10" s="105"/>
+      <c r="P10" s="109"/>
+      <c r="Q10" s="109"/>
+      <c r="R10" s="109"/>
+      <c r="S10" s="109"/>
+      <c r="T10" s="109"/>
+      <c r="U10" s="109"/>
+      <c r="V10" s="109"/>
+      <c r="W10" s="109"/>
+      <c r="X10" s="109"/>
+      <c r="Y10" s="109"/>
+      <c r="Z10" s="109"/>
+      <c r="AA10" s="109"/>
+      <c r="AB10" s="109"/>
+      <c r="AC10" s="109"/>
+      <c r="AD10" s="109"/>
+      <c r="AE10" s="109"/>
+      <c r="AF10" s="109"/>
+      <c r="AG10" s="109"/>
+      <c r="AH10" s="109"/>
+      <c r="AI10" s="109"/>
+      <c r="AJ10" s="109"/>
+      <c r="AK10" s="109"/>
+      <c r="AL10" s="109"/>
+      <c r="AM10" s="109"/>
+      <c r="AN10" s="109"/>
+      <c r="AO10" s="109"/>
+      <c r="AP10" s="111"/>
+      <c r="AQ10" s="108"/>
+      <c r="AR10" s="109"/>
+      <c r="AS10" s="109"/>
+      <c r="AT10" s="109"/>
+      <c r="AU10" s="109"/>
+      <c r="AV10" s="109"/>
+      <c r="AW10" s="109"/>
+      <c r="AX10" s="109"/>
+      <c r="AY10" s="109"/>
+      <c r="AZ10" s="109"/>
+      <c r="BA10" s="109"/>
+      <c r="BB10" s="109"/>
+      <c r="BC10" s="109"/>
+      <c r="BD10" s="109"/>
+      <c r="BE10" s="110"/>
     </row>
     <row r="11" spans="1:57" ht="15" customHeight="1">
-      <c r="A11" s="88"/>
-      <c r="B11" s="89"/>
-      <c r="C11" s="89"/>
-      <c r="D11" s="89"/>
-      <c r="E11" s="89"/>
-      <c r="F11" s="89"/>
-      <c r="G11" s="90"/>
-      <c r="H11" s="91"/>
-      <c r="I11" s="92"/>
-      <c r="J11" s="92"/>
-      <c r="K11" s="92"/>
-      <c r="L11" s="92"/>
-      <c r="M11" s="92"/>
-      <c r="N11" s="93"/>
-      <c r="O11" s="91"/>
-      <c r="P11" s="94"/>
-      <c r="Q11" s="94"/>
-      <c r="R11" s="94"/>
-      <c r="S11" s="94"/>
-      <c r="T11" s="94"/>
-      <c r="U11" s="94"/>
-      <c r="V11" s="94"/>
-      <c r="W11" s="94"/>
-      <c r="X11" s="94"/>
-      <c r="Y11" s="94"/>
-      <c r="Z11" s="94"/>
-      <c r="AA11" s="94"/>
-      <c r="AB11" s="94"/>
-      <c r="AC11" s="94"/>
-      <c r="AD11" s="94"/>
-      <c r="AE11" s="94"/>
-      <c r="AF11" s="94"/>
-      <c r="AG11" s="94"/>
-      <c r="AH11" s="94"/>
-      <c r="AI11" s="94"/>
-      <c r="AJ11" s="94"/>
-      <c r="AK11" s="94"/>
-      <c r="AL11" s="94"/>
-      <c r="AM11" s="94"/>
-      <c r="AN11" s="94"/>
-      <c r="AO11" s="94"/>
-      <c r="AP11" s="95"/>
-      <c r="AQ11" s="96"/>
-      <c r="AR11" s="94"/>
-      <c r="AS11" s="94"/>
-      <c r="AT11" s="94"/>
-      <c r="AU11" s="94"/>
-      <c r="AV11" s="94"/>
-      <c r="AW11" s="94"/>
-      <c r="AX11" s="94"/>
-      <c r="AY11" s="94"/>
-      <c r="AZ11" s="94"/>
-      <c r="BA11" s="94"/>
-      <c r="BB11" s="94"/>
-      <c r="BC11" s="94"/>
-      <c r="BD11" s="94"/>
-      <c r="BE11" s="97"/>
+      <c r="A11" s="99"/>
+      <c r="B11" s="100"/>
+      <c r="C11" s="100"/>
+      <c r="D11" s="100"/>
+      <c r="E11" s="100"/>
+      <c r="F11" s="100"/>
+      <c r="G11" s="101"/>
+      <c r="H11" s="105"/>
+      <c r="I11" s="106"/>
+      <c r="J11" s="106"/>
+      <c r="K11" s="106"/>
+      <c r="L11" s="106"/>
+      <c r="M11" s="106"/>
+      <c r="N11" s="107"/>
+      <c r="O11" s="105"/>
+      <c r="P11" s="109"/>
+      <c r="Q11" s="109"/>
+      <c r="R11" s="109"/>
+      <c r="S11" s="109"/>
+      <c r="T11" s="109"/>
+      <c r="U11" s="109"/>
+      <c r="V11" s="109"/>
+      <c r="W11" s="109"/>
+      <c r="X11" s="109"/>
+      <c r="Y11" s="109"/>
+      <c r="Z11" s="109"/>
+      <c r="AA11" s="109"/>
+      <c r="AB11" s="109"/>
+      <c r="AC11" s="109"/>
+      <c r="AD11" s="109"/>
+      <c r="AE11" s="109"/>
+      <c r="AF11" s="109"/>
+      <c r="AG11" s="109"/>
+      <c r="AH11" s="109"/>
+      <c r="AI11" s="109"/>
+      <c r="AJ11" s="109"/>
+      <c r="AK11" s="109"/>
+      <c r="AL11" s="109"/>
+      <c r="AM11" s="109"/>
+      <c r="AN11" s="109"/>
+      <c r="AO11" s="109"/>
+      <c r="AP11" s="111"/>
+      <c r="AQ11" s="108"/>
+      <c r="AR11" s="109"/>
+      <c r="AS11" s="109"/>
+      <c r="AT11" s="109"/>
+      <c r="AU11" s="109"/>
+      <c r="AV11" s="109"/>
+      <c r="AW11" s="109"/>
+      <c r="AX11" s="109"/>
+      <c r="AY11" s="109"/>
+      <c r="AZ11" s="109"/>
+      <c r="BA11" s="109"/>
+      <c r="BB11" s="109"/>
+      <c r="BC11" s="109"/>
+      <c r="BD11" s="109"/>
+      <c r="BE11" s="110"/>
     </row>
     <row r="12" spans="1:57" ht="15" customHeight="1">
-      <c r="A12" s="88"/>
-      <c r="B12" s="89"/>
-      <c r="C12" s="89"/>
-      <c r="D12" s="89"/>
-      <c r="E12" s="89"/>
-      <c r="F12" s="89"/>
-      <c r="G12" s="90"/>
-      <c r="H12" s="91"/>
-      <c r="I12" s="92"/>
-      <c r="J12" s="92"/>
-      <c r="K12" s="92"/>
-      <c r="L12" s="92"/>
-      <c r="M12" s="92"/>
-      <c r="N12" s="93"/>
-      <c r="O12" s="91"/>
-      <c r="P12" s="94"/>
-      <c r="Q12" s="94"/>
-      <c r="R12" s="94"/>
-      <c r="S12" s="94"/>
-      <c r="T12" s="94"/>
-      <c r="U12" s="94"/>
-      <c r="V12" s="94"/>
-      <c r="W12" s="94"/>
-      <c r="X12" s="94"/>
-      <c r="Y12" s="94"/>
-      <c r="Z12" s="94"/>
-      <c r="AA12" s="94"/>
-      <c r="AB12" s="94"/>
-      <c r="AC12" s="94"/>
-      <c r="AD12" s="94"/>
-      <c r="AE12" s="94"/>
-      <c r="AF12" s="94"/>
-      <c r="AG12" s="94"/>
-      <c r="AH12" s="94"/>
-      <c r="AI12" s="94"/>
-      <c r="AJ12" s="94"/>
-      <c r="AK12" s="94"/>
-      <c r="AL12" s="94"/>
-      <c r="AM12" s="94"/>
-      <c r="AN12" s="94"/>
-      <c r="AO12" s="94"/>
-      <c r="AP12" s="95"/>
-      <c r="AQ12" s="96"/>
-      <c r="AR12" s="94"/>
-      <c r="AS12" s="94"/>
-      <c r="AT12" s="94"/>
-      <c r="AU12" s="94"/>
-      <c r="AV12" s="94"/>
-      <c r="AW12" s="94"/>
-      <c r="AX12" s="94"/>
-      <c r="AY12" s="94"/>
-      <c r="AZ12" s="94"/>
-      <c r="BA12" s="94"/>
-      <c r="BB12" s="94"/>
-      <c r="BC12" s="94"/>
-      <c r="BD12" s="94"/>
-      <c r="BE12" s="97"/>
+      <c r="A12" s="99"/>
+      <c r="B12" s="100"/>
+      <c r="C12" s="100"/>
+      <c r="D12" s="100"/>
+      <c r="E12" s="100"/>
+      <c r="F12" s="100"/>
+      <c r="G12" s="101"/>
+      <c r="H12" s="105"/>
+      <c r="I12" s="106"/>
+      <c r="J12" s="106"/>
+      <c r="K12" s="106"/>
+      <c r="L12" s="106"/>
+      <c r="M12" s="106"/>
+      <c r="N12" s="107"/>
+      <c r="O12" s="105"/>
+      <c r="P12" s="109"/>
+      <c r="Q12" s="109"/>
+      <c r="R12" s="109"/>
+      <c r="S12" s="109"/>
+      <c r="T12" s="109"/>
+      <c r="U12" s="109"/>
+      <c r="V12" s="109"/>
+      <c r="W12" s="109"/>
+      <c r="X12" s="109"/>
+      <c r="Y12" s="109"/>
+      <c r="Z12" s="109"/>
+      <c r="AA12" s="109"/>
+      <c r="AB12" s="109"/>
+      <c r="AC12" s="109"/>
+      <c r="AD12" s="109"/>
+      <c r="AE12" s="109"/>
+      <c r="AF12" s="109"/>
+      <c r="AG12" s="109"/>
+      <c r="AH12" s="109"/>
+      <c r="AI12" s="109"/>
+      <c r="AJ12" s="109"/>
+      <c r="AK12" s="109"/>
+      <c r="AL12" s="109"/>
+      <c r="AM12" s="109"/>
+      <c r="AN12" s="109"/>
+      <c r="AO12" s="109"/>
+      <c r="AP12" s="111"/>
+      <c r="AQ12" s="108"/>
+      <c r="AR12" s="109"/>
+      <c r="AS12" s="109"/>
+      <c r="AT12" s="109"/>
+      <c r="AU12" s="109"/>
+      <c r="AV12" s="109"/>
+      <c r="AW12" s="109"/>
+      <c r="AX12" s="109"/>
+      <c r="AY12" s="109"/>
+      <c r="AZ12" s="109"/>
+      <c r="BA12" s="109"/>
+      <c r="BB12" s="109"/>
+      <c r="BC12" s="109"/>
+      <c r="BD12" s="109"/>
+      <c r="BE12" s="110"/>
     </row>
     <row r="13" spans="1:57" ht="15" customHeight="1">
-      <c r="A13" s="88"/>
-      <c r="B13" s="89"/>
-      <c r="C13" s="89"/>
-      <c r="D13" s="89"/>
-      <c r="E13" s="89"/>
-      <c r="F13" s="89"/>
-      <c r="G13" s="90"/>
-      <c r="H13" s="91"/>
-      <c r="I13" s="92"/>
-      <c r="J13" s="92"/>
-      <c r="K13" s="92"/>
-      <c r="L13" s="92"/>
-      <c r="M13" s="92"/>
-      <c r="N13" s="93"/>
-      <c r="O13" s="91"/>
-      <c r="P13" s="94"/>
-      <c r="Q13" s="94"/>
-      <c r="R13" s="94"/>
-      <c r="S13" s="94"/>
-      <c r="T13" s="94"/>
-      <c r="U13" s="94"/>
-      <c r="V13" s="94"/>
-      <c r="W13" s="94"/>
-      <c r="X13" s="94"/>
-      <c r="Y13" s="94"/>
-      <c r="Z13" s="94"/>
-      <c r="AA13" s="94"/>
-      <c r="AB13" s="94"/>
-      <c r="AC13" s="94"/>
-      <c r="AD13" s="94"/>
-      <c r="AE13" s="94"/>
-      <c r="AF13" s="94"/>
-      <c r="AG13" s="94"/>
-      <c r="AH13" s="94"/>
-      <c r="AI13" s="94"/>
-      <c r="AJ13" s="94"/>
-      <c r="AK13" s="94"/>
-      <c r="AL13" s="94"/>
-      <c r="AM13" s="94"/>
-      <c r="AN13" s="94"/>
-      <c r="AO13" s="94"/>
-      <c r="AP13" s="95"/>
-      <c r="AQ13" s="96"/>
-      <c r="AR13" s="94"/>
-      <c r="AS13" s="94"/>
-      <c r="AT13" s="94"/>
-      <c r="AU13" s="94"/>
-      <c r="AV13" s="94"/>
-      <c r="AW13" s="94"/>
-      <c r="AX13" s="94"/>
-      <c r="AY13" s="94"/>
-      <c r="AZ13" s="94"/>
-      <c r="BA13" s="94"/>
-      <c r="BB13" s="94"/>
-      <c r="BC13" s="94"/>
-      <c r="BD13" s="94"/>
-      <c r="BE13" s="97"/>
+      <c r="A13" s="99"/>
+      <c r="B13" s="100"/>
+      <c r="C13" s="100"/>
+      <c r="D13" s="100"/>
+      <c r="E13" s="100"/>
+      <c r="F13" s="100"/>
+      <c r="G13" s="101"/>
+      <c r="H13" s="105"/>
+      <c r="I13" s="106"/>
+      <c r="J13" s="106"/>
+      <c r="K13" s="106"/>
+      <c r="L13" s="106"/>
+      <c r="M13" s="106"/>
+      <c r="N13" s="107"/>
+      <c r="O13" s="105"/>
+      <c r="P13" s="109"/>
+      <c r="Q13" s="109"/>
+      <c r="R13" s="109"/>
+      <c r="S13" s="109"/>
+      <c r="T13" s="109"/>
+      <c r="U13" s="109"/>
+      <c r="V13" s="109"/>
+      <c r="W13" s="109"/>
+      <c r="X13" s="109"/>
+      <c r="Y13" s="109"/>
+      <c r="Z13" s="109"/>
+      <c r="AA13" s="109"/>
+      <c r="AB13" s="109"/>
+      <c r="AC13" s="109"/>
+      <c r="AD13" s="109"/>
+      <c r="AE13" s="109"/>
+      <c r="AF13" s="109"/>
+      <c r="AG13" s="109"/>
+      <c r="AH13" s="109"/>
+      <c r="AI13" s="109"/>
+      <c r="AJ13" s="109"/>
+      <c r="AK13" s="109"/>
+      <c r="AL13" s="109"/>
+      <c r="AM13" s="109"/>
+      <c r="AN13" s="109"/>
+      <c r="AO13" s="109"/>
+      <c r="AP13" s="111"/>
+      <c r="AQ13" s="108"/>
+      <c r="AR13" s="109"/>
+      <c r="AS13" s="109"/>
+      <c r="AT13" s="109"/>
+      <c r="AU13" s="109"/>
+      <c r="AV13" s="109"/>
+      <c r="AW13" s="109"/>
+      <c r="AX13" s="109"/>
+      <c r="AY13" s="109"/>
+      <c r="AZ13" s="109"/>
+      <c r="BA13" s="109"/>
+      <c r="BB13" s="109"/>
+      <c r="BC13" s="109"/>
+      <c r="BD13" s="109"/>
+      <c r="BE13" s="110"/>
     </row>
     <row r="14" spans="1:57" ht="15" customHeight="1">
-      <c r="A14" s="88"/>
-      <c r="B14" s="89"/>
-      <c r="C14" s="89"/>
-      <c r="D14" s="89"/>
-      <c r="E14" s="89"/>
-      <c r="F14" s="89"/>
-      <c r="G14" s="90"/>
-      <c r="H14" s="91"/>
-      <c r="I14" s="92"/>
-      <c r="J14" s="92"/>
-      <c r="K14" s="92"/>
-      <c r="L14" s="92"/>
-      <c r="M14" s="92"/>
-      <c r="N14" s="93"/>
-      <c r="O14" s="91"/>
-      <c r="P14" s="94"/>
-      <c r="Q14" s="94"/>
-      <c r="R14" s="94"/>
-      <c r="S14" s="94"/>
-      <c r="T14" s="94"/>
-      <c r="U14" s="94"/>
-      <c r="V14" s="94"/>
-      <c r="W14" s="94"/>
-      <c r="X14" s="94"/>
-      <c r="Y14" s="94"/>
-      <c r="Z14" s="94"/>
-      <c r="AA14" s="94"/>
-      <c r="AB14" s="94"/>
-      <c r="AC14" s="94"/>
-      <c r="AD14" s="94"/>
-      <c r="AE14" s="94"/>
-      <c r="AF14" s="94"/>
-      <c r="AG14" s="94"/>
-      <c r="AH14" s="94"/>
-      <c r="AI14" s="94"/>
-      <c r="AJ14" s="94"/>
-      <c r="AK14" s="94"/>
-      <c r="AL14" s="94"/>
-      <c r="AM14" s="94"/>
-      <c r="AN14" s="94"/>
-      <c r="AO14" s="94"/>
-      <c r="AP14" s="95"/>
-      <c r="AQ14" s="96"/>
-      <c r="AR14" s="94"/>
-      <c r="AS14" s="94"/>
-      <c r="AT14" s="94"/>
-      <c r="AU14" s="94"/>
-      <c r="AV14" s="94"/>
-      <c r="AW14" s="94"/>
-      <c r="AX14" s="94"/>
-      <c r="AY14" s="94"/>
-      <c r="AZ14" s="94"/>
-      <c r="BA14" s="94"/>
-      <c r="BB14" s="94"/>
-      <c r="BC14" s="94"/>
-      <c r="BD14" s="94"/>
-      <c r="BE14" s="97"/>
+      <c r="A14" s="99"/>
+      <c r="B14" s="100"/>
+      <c r="C14" s="100"/>
+      <c r="D14" s="100"/>
+      <c r="E14" s="100"/>
+      <c r="F14" s="100"/>
+      <c r="G14" s="101"/>
+      <c r="H14" s="105"/>
+      <c r="I14" s="106"/>
+      <c r="J14" s="106"/>
+      <c r="K14" s="106"/>
+      <c r="L14" s="106"/>
+      <c r="M14" s="106"/>
+      <c r="N14" s="107"/>
+      <c r="O14" s="105"/>
+      <c r="P14" s="109"/>
+      <c r="Q14" s="109"/>
+      <c r="R14" s="109"/>
+      <c r="S14" s="109"/>
+      <c r="T14" s="109"/>
+      <c r="U14" s="109"/>
+      <c r="V14" s="109"/>
+      <c r="W14" s="109"/>
+      <c r="X14" s="109"/>
+      <c r="Y14" s="109"/>
+      <c r="Z14" s="109"/>
+      <c r="AA14" s="109"/>
+      <c r="AB14" s="109"/>
+      <c r="AC14" s="109"/>
+      <c r="AD14" s="109"/>
+      <c r="AE14" s="109"/>
+      <c r="AF14" s="109"/>
+      <c r="AG14" s="109"/>
+      <c r="AH14" s="109"/>
+      <c r="AI14" s="109"/>
+      <c r="AJ14" s="109"/>
+      <c r="AK14" s="109"/>
+      <c r="AL14" s="109"/>
+      <c r="AM14" s="109"/>
+      <c r="AN14" s="109"/>
+      <c r="AO14" s="109"/>
+      <c r="AP14" s="111"/>
+      <c r="AQ14" s="108"/>
+      <c r="AR14" s="109"/>
+      <c r="AS14" s="109"/>
+      <c r="AT14" s="109"/>
+      <c r="AU14" s="109"/>
+      <c r="AV14" s="109"/>
+      <c r="AW14" s="109"/>
+      <c r="AX14" s="109"/>
+      <c r="AY14" s="109"/>
+      <c r="AZ14" s="109"/>
+      <c r="BA14" s="109"/>
+      <c r="BB14" s="109"/>
+      <c r="BC14" s="109"/>
+      <c r="BD14" s="109"/>
+      <c r="BE14" s="110"/>
     </row>
     <row r="15" spans="1:57" ht="15" customHeight="1">
-      <c r="A15" s="88"/>
-      <c r="B15" s="89"/>
-      <c r="C15" s="89"/>
-      <c r="D15" s="89"/>
-      <c r="E15" s="89"/>
-      <c r="F15" s="89"/>
-      <c r="G15" s="90"/>
-      <c r="H15" s="91"/>
-      <c r="I15" s="92"/>
-      <c r="J15" s="92"/>
-      <c r="K15" s="92"/>
-      <c r="L15" s="92"/>
-      <c r="M15" s="92"/>
-      <c r="N15" s="93"/>
-      <c r="O15" s="91"/>
-      <c r="P15" s="94"/>
-      <c r="Q15" s="94"/>
-      <c r="R15" s="94"/>
-      <c r="S15" s="94"/>
-      <c r="T15" s="94"/>
-      <c r="U15" s="94"/>
-      <c r="V15" s="94"/>
-      <c r="W15" s="94"/>
-      <c r="X15" s="94"/>
-      <c r="Y15" s="94"/>
-      <c r="Z15" s="94"/>
-      <c r="AA15" s="94"/>
-      <c r="AB15" s="94"/>
-      <c r="AC15" s="94"/>
-      <c r="AD15" s="94"/>
-      <c r="AE15" s="94"/>
-      <c r="AF15" s="94"/>
-      <c r="AG15" s="94"/>
-      <c r="AH15" s="94"/>
-      <c r="AI15" s="94"/>
-      <c r="AJ15" s="94"/>
-      <c r="AK15" s="94"/>
-      <c r="AL15" s="94"/>
-      <c r="AM15" s="94"/>
-      <c r="AN15" s="94"/>
-      <c r="AO15" s="94"/>
-      <c r="AP15" s="95"/>
-      <c r="AQ15" s="96"/>
-      <c r="AR15" s="94"/>
-      <c r="AS15" s="94"/>
-      <c r="AT15" s="94"/>
-      <c r="AU15" s="94"/>
-      <c r="AV15" s="94"/>
-      <c r="AW15" s="94"/>
-      <c r="AX15" s="94"/>
-      <c r="AY15" s="94"/>
-      <c r="AZ15" s="94"/>
-      <c r="BA15" s="94"/>
-      <c r="BB15" s="94"/>
-      <c r="BC15" s="94"/>
-      <c r="BD15" s="94"/>
-      <c r="BE15" s="97"/>
+      <c r="A15" s="99"/>
+      <c r="B15" s="100"/>
+      <c r="C15" s="100"/>
+      <c r="D15" s="100"/>
+      <c r="E15" s="100"/>
+      <c r="F15" s="100"/>
+      <c r="G15" s="101"/>
+      <c r="H15" s="105"/>
+      <c r="I15" s="106"/>
+      <c r="J15" s="106"/>
+      <c r="K15" s="106"/>
+      <c r="L15" s="106"/>
+      <c r="M15" s="106"/>
+      <c r="N15" s="107"/>
+      <c r="O15" s="105"/>
+      <c r="P15" s="109"/>
+      <c r="Q15" s="109"/>
+      <c r="R15" s="109"/>
+      <c r="S15" s="109"/>
+      <c r="T15" s="109"/>
+      <c r="U15" s="109"/>
+      <c r="V15" s="109"/>
+      <c r="W15" s="109"/>
+      <c r="X15" s="109"/>
+      <c r="Y15" s="109"/>
+      <c r="Z15" s="109"/>
+      <c r="AA15" s="109"/>
+      <c r="AB15" s="109"/>
+      <c r="AC15" s="109"/>
+      <c r="AD15" s="109"/>
+      <c r="AE15" s="109"/>
+      <c r="AF15" s="109"/>
+      <c r="AG15" s="109"/>
+      <c r="AH15" s="109"/>
+      <c r="AI15" s="109"/>
+      <c r="AJ15" s="109"/>
+      <c r="AK15" s="109"/>
+      <c r="AL15" s="109"/>
+      <c r="AM15" s="109"/>
+      <c r="AN15" s="109"/>
+      <c r="AO15" s="109"/>
+      <c r="AP15" s="111"/>
+      <c r="AQ15" s="108"/>
+      <c r="AR15" s="109"/>
+      <c r="AS15" s="109"/>
+      <c r="AT15" s="109"/>
+      <c r="AU15" s="109"/>
+      <c r="AV15" s="109"/>
+      <c r="AW15" s="109"/>
+      <c r="AX15" s="109"/>
+      <c r="AY15" s="109"/>
+      <c r="AZ15" s="109"/>
+      <c r="BA15" s="109"/>
+      <c r="BB15" s="109"/>
+      <c r="BC15" s="109"/>
+      <c r="BD15" s="109"/>
+      <c r="BE15" s="110"/>
     </row>
     <row r="16" spans="1:57" ht="15" customHeight="1">
-      <c r="A16" s="88"/>
-      <c r="B16" s="89"/>
-      <c r="C16" s="89"/>
-      <c r="D16" s="89"/>
-      <c r="E16" s="89"/>
-      <c r="F16" s="89"/>
-      <c r="G16" s="90"/>
-      <c r="H16" s="91"/>
-      <c r="I16" s="92"/>
-      <c r="J16" s="92"/>
-      <c r="K16" s="92"/>
-      <c r="L16" s="92"/>
-      <c r="M16" s="92"/>
-      <c r="N16" s="93"/>
-      <c r="O16" s="91"/>
-      <c r="P16" s="94"/>
-      <c r="Q16" s="94"/>
-      <c r="R16" s="94"/>
-      <c r="S16" s="94"/>
-      <c r="T16" s="94"/>
-      <c r="U16" s="94"/>
-      <c r="V16" s="94"/>
-      <c r="W16" s="94"/>
-      <c r="X16" s="94"/>
-      <c r="Y16" s="94"/>
-      <c r="Z16" s="94"/>
-      <c r="AA16" s="94"/>
-      <c r="AB16" s="94"/>
-      <c r="AC16" s="94"/>
-      <c r="AD16" s="94"/>
-      <c r="AE16" s="94"/>
-      <c r="AF16" s="94"/>
-      <c r="AG16" s="94"/>
-      <c r="AH16" s="94"/>
-      <c r="AI16" s="94"/>
-      <c r="AJ16" s="94"/>
-      <c r="AK16" s="94"/>
-      <c r="AL16" s="94"/>
-      <c r="AM16" s="94"/>
-      <c r="AN16" s="94"/>
-      <c r="AO16" s="94"/>
-      <c r="AP16" s="95"/>
-      <c r="AQ16" s="96"/>
-      <c r="AR16" s="94"/>
-      <c r="AS16" s="94"/>
-      <c r="AT16" s="94"/>
-      <c r="AU16" s="94"/>
-      <c r="AV16" s="94"/>
-      <c r="AW16" s="94"/>
-      <c r="AX16" s="94"/>
-      <c r="AY16" s="94"/>
-      <c r="AZ16" s="94"/>
-      <c r="BA16" s="94"/>
-      <c r="BB16" s="94"/>
-      <c r="BC16" s="94"/>
-      <c r="BD16" s="94"/>
-      <c r="BE16" s="97"/>
+      <c r="A16" s="99"/>
+      <c r="B16" s="100"/>
+      <c r="C16" s="100"/>
+      <c r="D16" s="100"/>
+      <c r="E16" s="100"/>
+      <c r="F16" s="100"/>
+      <c r="G16" s="101"/>
+      <c r="H16" s="105"/>
+      <c r="I16" s="106"/>
+      <c r="J16" s="106"/>
+      <c r="K16" s="106"/>
+      <c r="L16" s="106"/>
+      <c r="M16" s="106"/>
+      <c r="N16" s="107"/>
+      <c r="O16" s="105"/>
+      <c r="P16" s="109"/>
+      <c r="Q16" s="109"/>
+      <c r="R16" s="109"/>
+      <c r="S16" s="109"/>
+      <c r="T16" s="109"/>
+      <c r="U16" s="109"/>
+      <c r="V16" s="109"/>
+      <c r="W16" s="109"/>
+      <c r="X16" s="109"/>
+      <c r="Y16" s="109"/>
+      <c r="Z16" s="109"/>
+      <c r="AA16" s="109"/>
+      <c r="AB16" s="109"/>
+      <c r="AC16" s="109"/>
+      <c r="AD16" s="109"/>
+      <c r="AE16" s="109"/>
+      <c r="AF16" s="109"/>
+      <c r="AG16" s="109"/>
+      <c r="AH16" s="109"/>
+      <c r="AI16" s="109"/>
+      <c r="AJ16" s="109"/>
+      <c r="AK16" s="109"/>
+      <c r="AL16" s="109"/>
+      <c r="AM16" s="109"/>
+      <c r="AN16" s="109"/>
+      <c r="AO16" s="109"/>
+      <c r="AP16" s="111"/>
+      <c r="AQ16" s="108"/>
+      <c r="AR16" s="109"/>
+      <c r="AS16" s="109"/>
+      <c r="AT16" s="109"/>
+      <c r="AU16" s="109"/>
+      <c r="AV16" s="109"/>
+      <c r="AW16" s="109"/>
+      <c r="AX16" s="109"/>
+      <c r="AY16" s="109"/>
+      <c r="AZ16" s="109"/>
+      <c r="BA16" s="109"/>
+      <c r="BB16" s="109"/>
+      <c r="BC16" s="109"/>
+      <c r="BD16" s="109"/>
+      <c r="BE16" s="110"/>
     </row>
     <row r="17" spans="1:57" ht="15" customHeight="1">
-      <c r="A17" s="88"/>
-      <c r="B17" s="89"/>
-      <c r="C17" s="89"/>
-      <c r="D17" s="89"/>
-      <c r="E17" s="89"/>
-      <c r="F17" s="89"/>
-      <c r="G17" s="90"/>
-      <c r="H17" s="91"/>
-      <c r="I17" s="92"/>
-      <c r="J17" s="92"/>
-      <c r="K17" s="92"/>
-      <c r="L17" s="92"/>
-      <c r="M17" s="92"/>
-      <c r="N17" s="93"/>
-      <c r="O17" s="91"/>
-      <c r="P17" s="94"/>
-      <c r="Q17" s="94"/>
-      <c r="R17" s="94"/>
-      <c r="S17" s="94"/>
-      <c r="T17" s="94"/>
-      <c r="U17" s="94"/>
-      <c r="V17" s="94"/>
-      <c r="W17" s="94"/>
-      <c r="X17" s="94"/>
-      <c r="Y17" s="94"/>
-      <c r="Z17" s="94"/>
-      <c r="AA17" s="94"/>
-      <c r="AB17" s="94"/>
-      <c r="AC17" s="94"/>
-      <c r="AD17" s="94"/>
-      <c r="AE17" s="94"/>
-      <c r="AF17" s="94"/>
-      <c r="AG17" s="94"/>
-      <c r="AH17" s="94"/>
-      <c r="AI17" s="94"/>
-      <c r="AJ17" s="94"/>
-      <c r="AK17" s="94"/>
-      <c r="AL17" s="94"/>
-      <c r="AM17" s="94"/>
-      <c r="AN17" s="94"/>
-      <c r="AO17" s="94"/>
-      <c r="AP17" s="95"/>
-      <c r="AQ17" s="96"/>
-      <c r="AR17" s="94"/>
-      <c r="AS17" s="94"/>
-      <c r="AT17" s="94"/>
-      <c r="AU17" s="94"/>
-      <c r="AV17" s="94"/>
-      <c r="AW17" s="94"/>
-      <c r="AX17" s="94"/>
-      <c r="AY17" s="94"/>
-      <c r="AZ17" s="94"/>
-      <c r="BA17" s="94"/>
-      <c r="BB17" s="94"/>
-      <c r="BC17" s="94"/>
-      <c r="BD17" s="94"/>
-      <c r="BE17" s="97"/>
+      <c r="A17" s="99"/>
+      <c r="B17" s="100"/>
+      <c r="C17" s="100"/>
+      <c r="D17" s="100"/>
+      <c r="E17" s="100"/>
+      <c r="F17" s="100"/>
+      <c r="G17" s="101"/>
+      <c r="H17" s="105"/>
+      <c r="I17" s="106"/>
+      <c r="J17" s="106"/>
+      <c r="K17" s="106"/>
+      <c r="L17" s="106"/>
+      <c r="M17" s="106"/>
+      <c r="N17" s="107"/>
+      <c r="O17" s="105"/>
+      <c r="P17" s="109"/>
+      <c r="Q17" s="109"/>
+      <c r="R17" s="109"/>
+      <c r="S17" s="109"/>
+      <c r="T17" s="109"/>
+      <c r="U17" s="109"/>
+      <c r="V17" s="109"/>
+      <c r="W17" s="109"/>
+      <c r="X17" s="109"/>
+      <c r="Y17" s="109"/>
+      <c r="Z17" s="109"/>
+      <c r="AA17" s="109"/>
+      <c r="AB17" s="109"/>
+      <c r="AC17" s="109"/>
+      <c r="AD17" s="109"/>
+      <c r="AE17" s="109"/>
+      <c r="AF17" s="109"/>
+      <c r="AG17" s="109"/>
+      <c r="AH17" s="109"/>
+      <c r="AI17" s="109"/>
+      <c r="AJ17" s="109"/>
+      <c r="AK17" s="109"/>
+      <c r="AL17" s="109"/>
+      <c r="AM17" s="109"/>
+      <c r="AN17" s="109"/>
+      <c r="AO17" s="109"/>
+      <c r="AP17" s="111"/>
+      <c r="AQ17" s="108"/>
+      <c r="AR17" s="109"/>
+      <c r="AS17" s="109"/>
+      <c r="AT17" s="109"/>
+      <c r="AU17" s="109"/>
+      <c r="AV17" s="109"/>
+      <c r="AW17" s="109"/>
+      <c r="AX17" s="109"/>
+      <c r="AY17" s="109"/>
+      <c r="AZ17" s="109"/>
+      <c r="BA17" s="109"/>
+      <c r="BB17" s="109"/>
+      <c r="BC17" s="109"/>
+      <c r="BD17" s="109"/>
+      <c r="BE17" s="110"/>
     </row>
     <row r="18" spans="1:57" ht="15" customHeight="1">
-      <c r="A18" s="88"/>
-      <c r="B18" s="89"/>
-      <c r="C18" s="89"/>
-      <c r="D18" s="89"/>
-      <c r="E18" s="89"/>
-      <c r="F18" s="89"/>
-      <c r="G18" s="90"/>
-      <c r="H18" s="91"/>
-      <c r="I18" s="92"/>
-      <c r="J18" s="92"/>
-      <c r="K18" s="92"/>
-      <c r="L18" s="92"/>
-      <c r="M18" s="92"/>
-      <c r="N18" s="93"/>
-      <c r="O18" s="91"/>
-      <c r="P18" s="94"/>
-      <c r="Q18" s="94"/>
-      <c r="R18" s="94"/>
-      <c r="S18" s="94"/>
-      <c r="T18" s="94"/>
-      <c r="U18" s="94"/>
-      <c r="V18" s="94"/>
-      <c r="W18" s="94"/>
-      <c r="X18" s="94"/>
-      <c r="Y18" s="94"/>
-      <c r="Z18" s="94"/>
-      <c r="AA18" s="94"/>
-      <c r="AB18" s="94"/>
-      <c r="AC18" s="94"/>
-      <c r="AD18" s="94"/>
-      <c r="AE18" s="94"/>
-      <c r="AF18" s="94"/>
-      <c r="AG18" s="94"/>
-      <c r="AH18" s="94"/>
-      <c r="AI18" s="94"/>
-      <c r="AJ18" s="94"/>
-      <c r="AK18" s="94"/>
-      <c r="AL18" s="94"/>
-      <c r="AM18" s="94"/>
-      <c r="AN18" s="94"/>
-      <c r="AO18" s="94"/>
-      <c r="AP18" s="95"/>
-      <c r="AQ18" s="96"/>
-      <c r="AR18" s="94"/>
-      <c r="AS18" s="94"/>
-      <c r="AT18" s="94"/>
-      <c r="AU18" s="94"/>
-      <c r="AV18" s="94"/>
-      <c r="AW18" s="94"/>
-      <c r="AX18" s="94"/>
-      <c r="AY18" s="94"/>
-      <c r="AZ18" s="94"/>
-      <c r="BA18" s="94"/>
-      <c r="BB18" s="94"/>
-      <c r="BC18" s="94"/>
-      <c r="BD18" s="94"/>
-      <c r="BE18" s="97"/>
+      <c r="A18" s="99"/>
+      <c r="B18" s="100"/>
+      <c r="C18" s="100"/>
+      <c r="D18" s="100"/>
+      <c r="E18" s="100"/>
+      <c r="F18" s="100"/>
+      <c r="G18" s="101"/>
+      <c r="H18" s="105"/>
+      <c r="I18" s="106"/>
+      <c r="J18" s="106"/>
+      <c r="K18" s="106"/>
+      <c r="L18" s="106"/>
+      <c r="M18" s="106"/>
+      <c r="N18" s="107"/>
+      <c r="O18" s="105"/>
+      <c r="P18" s="109"/>
+      <c r="Q18" s="109"/>
+      <c r="R18" s="109"/>
+      <c r="S18" s="109"/>
+      <c r="T18" s="109"/>
+      <c r="U18" s="109"/>
+      <c r="V18" s="109"/>
+      <c r="W18" s="109"/>
+      <c r="X18" s="109"/>
+      <c r="Y18" s="109"/>
+      <c r="Z18" s="109"/>
+      <c r="AA18" s="109"/>
+      <c r="AB18" s="109"/>
+      <c r="AC18" s="109"/>
+      <c r="AD18" s="109"/>
+      <c r="AE18" s="109"/>
+      <c r="AF18" s="109"/>
+      <c r="AG18" s="109"/>
+      <c r="AH18" s="109"/>
+      <c r="AI18" s="109"/>
+      <c r="AJ18" s="109"/>
+      <c r="AK18" s="109"/>
+      <c r="AL18" s="109"/>
+      <c r="AM18" s="109"/>
+      <c r="AN18" s="109"/>
+      <c r="AO18" s="109"/>
+      <c r="AP18" s="111"/>
+      <c r="AQ18" s="108"/>
+      <c r="AR18" s="109"/>
+      <c r="AS18" s="109"/>
+      <c r="AT18" s="109"/>
+      <c r="AU18" s="109"/>
+      <c r="AV18" s="109"/>
+      <c r="AW18" s="109"/>
+      <c r="AX18" s="109"/>
+      <c r="AY18" s="109"/>
+      <c r="AZ18" s="109"/>
+      <c r="BA18" s="109"/>
+      <c r="BB18" s="109"/>
+      <c r="BC18" s="109"/>
+      <c r="BD18" s="109"/>
+      <c r="BE18" s="110"/>
     </row>
     <row r="19" spans="1:57" ht="15" customHeight="1">
-      <c r="A19" s="88"/>
-      <c r="B19" s="89"/>
-      <c r="C19" s="89"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="90"/>
-      <c r="H19" s="91"/>
-      <c r="I19" s="92"/>
-      <c r="J19" s="92"/>
-      <c r="K19" s="92"/>
-      <c r="L19" s="92"/>
-      <c r="M19" s="92"/>
-      <c r="N19" s="93"/>
-      <c r="O19" s="91"/>
-      <c r="P19" s="94"/>
-      <c r="Q19" s="94"/>
-      <c r="R19" s="94"/>
-      <c r="S19" s="94"/>
-      <c r="T19" s="94"/>
-      <c r="U19" s="94"/>
-      <c r="V19" s="94"/>
-      <c r="W19" s="94"/>
-      <c r="X19" s="94"/>
-      <c r="Y19" s="94"/>
-      <c r="Z19" s="94"/>
-      <c r="AA19" s="94"/>
-      <c r="AB19" s="94"/>
-      <c r="AC19" s="94"/>
-      <c r="AD19" s="94"/>
-      <c r="AE19" s="94"/>
-      <c r="AF19" s="94"/>
-      <c r="AG19" s="94"/>
-      <c r="AH19" s="94"/>
-      <c r="AI19" s="94"/>
-      <c r="AJ19" s="94"/>
-      <c r="AK19" s="94"/>
-      <c r="AL19" s="94"/>
-      <c r="AM19" s="94"/>
-      <c r="AN19" s="94"/>
-      <c r="AO19" s="94"/>
-      <c r="AP19" s="95"/>
-      <c r="AQ19" s="96"/>
-      <c r="AR19" s="94"/>
-      <c r="AS19" s="94"/>
-      <c r="AT19" s="94"/>
-      <c r="AU19" s="94"/>
-      <c r="AV19" s="94"/>
-      <c r="AW19" s="94"/>
-      <c r="AX19" s="94"/>
-      <c r="AY19" s="94"/>
-      <c r="AZ19" s="94"/>
-      <c r="BA19" s="94"/>
-      <c r="BB19" s="94"/>
-      <c r="BC19" s="94"/>
-      <c r="BD19" s="94"/>
-      <c r="BE19" s="97"/>
+      <c r="A19" s="99"/>
+      <c r="B19" s="100"/>
+      <c r="C19" s="100"/>
+      <c r="D19" s="100"/>
+      <c r="E19" s="100"/>
+      <c r="F19" s="100"/>
+      <c r="G19" s="101"/>
+      <c r="H19" s="105"/>
+      <c r="I19" s="106"/>
+      <c r="J19" s="106"/>
+      <c r="K19" s="106"/>
+      <c r="L19" s="106"/>
+      <c r="M19" s="106"/>
+      <c r="N19" s="107"/>
+      <c r="O19" s="105"/>
+      <c r="P19" s="109"/>
+      <c r="Q19" s="109"/>
+      <c r="R19" s="109"/>
+      <c r="S19" s="109"/>
+      <c r="T19" s="109"/>
+      <c r="U19" s="109"/>
+      <c r="V19" s="109"/>
+      <c r="W19" s="109"/>
+      <c r="X19" s="109"/>
+      <c r="Y19" s="109"/>
+      <c r="Z19" s="109"/>
+      <c r="AA19" s="109"/>
+      <c r="AB19" s="109"/>
+      <c r="AC19" s="109"/>
+      <c r="AD19" s="109"/>
+      <c r="AE19" s="109"/>
+      <c r="AF19" s="109"/>
+      <c r="AG19" s="109"/>
+      <c r="AH19" s="109"/>
+      <c r="AI19" s="109"/>
+      <c r="AJ19" s="109"/>
+      <c r="AK19" s="109"/>
+      <c r="AL19" s="109"/>
+      <c r="AM19" s="109"/>
+      <c r="AN19" s="109"/>
+      <c r="AO19" s="109"/>
+      <c r="AP19" s="111"/>
+      <c r="AQ19" s="108"/>
+      <c r="AR19" s="109"/>
+      <c r="AS19" s="109"/>
+      <c r="AT19" s="109"/>
+      <c r="AU19" s="109"/>
+      <c r="AV19" s="109"/>
+      <c r="AW19" s="109"/>
+      <c r="AX19" s="109"/>
+      <c r="AY19" s="109"/>
+      <c r="AZ19" s="109"/>
+      <c r="BA19" s="109"/>
+      <c r="BB19" s="109"/>
+      <c r="BC19" s="109"/>
+      <c r="BD19" s="109"/>
+      <c r="BE19" s="110"/>
     </row>
     <row r="20" spans="1:57" ht="15" customHeight="1">
-      <c r="A20" s="88"/>
-      <c r="B20" s="89"/>
-      <c r="C20" s="89"/>
-      <c r="D20" s="89"/>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="90"/>
-      <c r="H20" s="91"/>
-      <c r="I20" s="92"/>
-      <c r="J20" s="92"/>
-      <c r="K20" s="92"/>
-      <c r="L20" s="92"/>
-      <c r="M20" s="92"/>
-      <c r="N20" s="93"/>
-      <c r="O20" s="91"/>
-      <c r="P20" s="94"/>
-      <c r="Q20" s="94"/>
-      <c r="R20" s="94"/>
-      <c r="S20" s="94"/>
-      <c r="T20" s="94"/>
-      <c r="U20" s="94"/>
-      <c r="V20" s="94"/>
-      <c r="W20" s="94"/>
-      <c r="X20" s="94"/>
-      <c r="Y20" s="94"/>
-      <c r="Z20" s="94"/>
-      <c r="AA20" s="94"/>
-      <c r="AB20" s="94"/>
-      <c r="AC20" s="94"/>
-      <c r="AD20" s="94"/>
-      <c r="AE20" s="94"/>
-      <c r="AF20" s="94"/>
-      <c r="AG20" s="94"/>
-      <c r="AH20" s="94"/>
-      <c r="AI20" s="94"/>
-      <c r="AJ20" s="94"/>
-      <c r="AK20" s="94"/>
-      <c r="AL20" s="94"/>
-      <c r="AM20" s="94"/>
-      <c r="AN20" s="94"/>
-      <c r="AO20" s="94"/>
-      <c r="AP20" s="95"/>
-      <c r="AQ20" s="96"/>
-      <c r="AR20" s="94"/>
-      <c r="AS20" s="94"/>
-      <c r="AT20" s="94"/>
-      <c r="AU20" s="94"/>
-      <c r="AV20" s="94"/>
-      <c r="AW20" s="94"/>
-      <c r="AX20" s="94"/>
-      <c r="AY20" s="94"/>
-      <c r="AZ20" s="94"/>
-      <c r="BA20" s="94"/>
-      <c r="BB20" s="94"/>
-      <c r="BC20" s="94"/>
-      <c r="BD20" s="94"/>
-      <c r="BE20" s="97"/>
+      <c r="A20" s="99"/>
+      <c r="B20" s="100"/>
+      <c r="C20" s="100"/>
+      <c r="D20" s="100"/>
+      <c r="E20" s="100"/>
+      <c r="F20" s="100"/>
+      <c r="G20" s="101"/>
+      <c r="H20" s="105"/>
+      <c r="I20" s="106"/>
+      <c r="J20" s="106"/>
+      <c r="K20" s="106"/>
+      <c r="L20" s="106"/>
+      <c r="M20" s="106"/>
+      <c r="N20" s="107"/>
+      <c r="O20" s="105"/>
+      <c r="P20" s="109"/>
+      <c r="Q20" s="109"/>
+      <c r="R20" s="109"/>
+      <c r="S20" s="109"/>
+      <c r="T20" s="109"/>
+      <c r="U20" s="109"/>
+      <c r="V20" s="109"/>
+      <c r="W20" s="109"/>
+      <c r="X20" s="109"/>
+      <c r="Y20" s="109"/>
+      <c r="Z20" s="109"/>
+      <c r="AA20" s="109"/>
+      <c r="AB20" s="109"/>
+      <c r="AC20" s="109"/>
+      <c r="AD20" s="109"/>
+      <c r="AE20" s="109"/>
+      <c r="AF20" s="109"/>
+      <c r="AG20" s="109"/>
+      <c r="AH20" s="109"/>
+      <c r="AI20" s="109"/>
+      <c r="AJ20" s="109"/>
+      <c r="AK20" s="109"/>
+      <c r="AL20" s="109"/>
+      <c r="AM20" s="109"/>
+      <c r="AN20" s="109"/>
+      <c r="AO20" s="109"/>
+      <c r="AP20" s="111"/>
+      <c r="AQ20" s="108"/>
+      <c r="AR20" s="109"/>
+      <c r="AS20" s="109"/>
+      <c r="AT20" s="109"/>
+      <c r="AU20" s="109"/>
+      <c r="AV20" s="109"/>
+      <c r="AW20" s="109"/>
+      <c r="AX20" s="109"/>
+      <c r="AY20" s="109"/>
+      <c r="AZ20" s="109"/>
+      <c r="BA20" s="109"/>
+      <c r="BB20" s="109"/>
+      <c r="BC20" s="109"/>
+      <c r="BD20" s="109"/>
+      <c r="BE20" s="110"/>
     </row>
     <row r="21" spans="1:57" ht="15" customHeight="1">
-      <c r="A21" s="88"/>
-      <c r="B21" s="89"/>
-      <c r="C21" s="89"/>
-      <c r="D21" s="89"/>
-      <c r="E21" s="89"/>
-      <c r="F21" s="89"/>
-      <c r="G21" s="90"/>
-      <c r="H21" s="91"/>
-      <c r="I21" s="92"/>
-      <c r="J21" s="92"/>
-      <c r="K21" s="92"/>
-      <c r="L21" s="92"/>
-      <c r="M21" s="92"/>
-      <c r="N21" s="93"/>
-      <c r="O21" s="91"/>
-      <c r="P21" s="94"/>
-      <c r="Q21" s="94"/>
-      <c r="R21" s="94"/>
-      <c r="S21" s="94"/>
-      <c r="T21" s="94"/>
-      <c r="U21" s="94"/>
-      <c r="V21" s="94"/>
-      <c r="W21" s="94"/>
-      <c r="X21" s="94"/>
-      <c r="Y21" s="94"/>
-      <c r="Z21" s="94"/>
-      <c r="AA21" s="94"/>
-      <c r="AB21" s="94"/>
-      <c r="AC21" s="94"/>
-      <c r="AD21" s="94"/>
-      <c r="AE21" s="94"/>
-      <c r="AF21" s="94"/>
-      <c r="AG21" s="94"/>
-      <c r="AH21" s="94"/>
-      <c r="AI21" s="94"/>
-      <c r="AJ21" s="94"/>
-      <c r="AK21" s="94"/>
-      <c r="AL21" s="94"/>
-      <c r="AM21" s="94"/>
-      <c r="AN21" s="94"/>
-      <c r="AO21" s="94"/>
-      <c r="AP21" s="95"/>
-      <c r="AQ21" s="96"/>
-      <c r="AR21" s="94"/>
-      <c r="AS21" s="94"/>
-      <c r="AT21" s="94"/>
-      <c r="AU21" s="94"/>
-      <c r="AV21" s="94"/>
-      <c r="AW21" s="94"/>
-      <c r="AX21" s="94"/>
-      <c r="AY21" s="94"/>
-      <c r="AZ21" s="94"/>
-      <c r="BA21" s="94"/>
-      <c r="BB21" s="94"/>
-      <c r="BC21" s="94"/>
-      <c r="BD21" s="94"/>
-      <c r="BE21" s="97"/>
+      <c r="A21" s="99"/>
+      <c r="B21" s="100"/>
+      <c r="C21" s="100"/>
+      <c r="D21" s="100"/>
+      <c r="E21" s="100"/>
+      <c r="F21" s="100"/>
+      <c r="G21" s="101"/>
+      <c r="H21" s="105"/>
+      <c r="I21" s="106"/>
+      <c r="J21" s="106"/>
+      <c r="K21" s="106"/>
+      <c r="L21" s="106"/>
+      <c r="M21" s="106"/>
+      <c r="N21" s="107"/>
+      <c r="O21" s="105"/>
+      <c r="P21" s="109"/>
+      <c r="Q21" s="109"/>
+      <c r="R21" s="109"/>
+      <c r="S21" s="109"/>
+      <c r="T21" s="109"/>
+      <c r="U21" s="109"/>
+      <c r="V21" s="109"/>
+      <c r="W21" s="109"/>
+      <c r="X21" s="109"/>
+      <c r="Y21" s="109"/>
+      <c r="Z21" s="109"/>
+      <c r="AA21" s="109"/>
+      <c r="AB21" s="109"/>
+      <c r="AC21" s="109"/>
+      <c r="AD21" s="109"/>
+      <c r="AE21" s="109"/>
+      <c r="AF21" s="109"/>
+      <c r="AG21" s="109"/>
+      <c r="AH21" s="109"/>
+      <c r="AI21" s="109"/>
+      <c r="AJ21" s="109"/>
+      <c r="AK21" s="109"/>
+      <c r="AL21" s="109"/>
+      <c r="AM21" s="109"/>
+      <c r="AN21" s="109"/>
+      <c r="AO21" s="109"/>
+      <c r="AP21" s="111"/>
+      <c r="AQ21" s="108"/>
+      <c r="AR21" s="109"/>
+      <c r="AS21" s="109"/>
+      <c r="AT21" s="109"/>
+      <c r="AU21" s="109"/>
+      <c r="AV21" s="109"/>
+      <c r="AW21" s="109"/>
+      <c r="AX21" s="109"/>
+      <c r="AY21" s="109"/>
+      <c r="AZ21" s="109"/>
+      <c r="BA21" s="109"/>
+      <c r="BB21" s="109"/>
+      <c r="BC21" s="109"/>
+      <c r="BD21" s="109"/>
+      <c r="BE21" s="110"/>
     </row>
     <row r="22" spans="1:57" ht="15" customHeight="1">
-      <c r="A22" s="88"/>
-      <c r="B22" s="89"/>
-      <c r="C22" s="89"/>
-      <c r="D22" s="89"/>
-      <c r="E22" s="89"/>
-      <c r="F22" s="89"/>
-      <c r="G22" s="90"/>
-      <c r="H22" s="91"/>
-      <c r="I22" s="92"/>
-      <c r="J22" s="92"/>
-      <c r="K22" s="92"/>
-      <c r="L22" s="92"/>
-      <c r="M22" s="92"/>
-      <c r="N22" s="93"/>
-      <c r="O22" s="91"/>
-      <c r="P22" s="94"/>
-      <c r="Q22" s="94"/>
-      <c r="R22" s="94"/>
-      <c r="S22" s="94"/>
-      <c r="T22" s="94"/>
-      <c r="U22" s="94"/>
-      <c r="V22" s="94"/>
-      <c r="W22" s="94"/>
-      <c r="X22" s="94"/>
-      <c r="Y22" s="94"/>
-      <c r="Z22" s="94"/>
-      <c r="AA22" s="94"/>
-      <c r="AB22" s="94"/>
-      <c r="AC22" s="94"/>
-      <c r="AD22" s="94"/>
-      <c r="AE22" s="94"/>
-      <c r="AF22" s="94"/>
-      <c r="AG22" s="94"/>
-      <c r="AH22" s="94"/>
-      <c r="AI22" s="94"/>
-      <c r="AJ22" s="94"/>
-      <c r="AK22" s="94"/>
-      <c r="AL22" s="94"/>
-      <c r="AM22" s="94"/>
-      <c r="AN22" s="94"/>
-      <c r="AO22" s="94"/>
-      <c r="AP22" s="95"/>
-      <c r="AQ22" s="96"/>
-      <c r="AR22" s="94"/>
-      <c r="AS22" s="94"/>
-      <c r="AT22" s="94"/>
-      <c r="AU22" s="94"/>
-      <c r="AV22" s="94"/>
-      <c r="AW22" s="94"/>
-      <c r="AX22" s="94"/>
-      <c r="AY22" s="94"/>
-      <c r="AZ22" s="94"/>
-      <c r="BA22" s="94"/>
-      <c r="BB22" s="94"/>
-      <c r="BC22" s="94"/>
-      <c r="BD22" s="94"/>
-      <c r="BE22" s="97"/>
+      <c r="A22" s="99"/>
+      <c r="B22" s="100"/>
+      <c r="C22" s="100"/>
+      <c r="D22" s="100"/>
+      <c r="E22" s="100"/>
+      <c r="F22" s="100"/>
+      <c r="G22" s="101"/>
+      <c r="H22" s="105"/>
+      <c r="I22" s="106"/>
+      <c r="J22" s="106"/>
+      <c r="K22" s="106"/>
+      <c r="L22" s="106"/>
+      <c r="M22" s="106"/>
+      <c r="N22" s="107"/>
+      <c r="O22" s="105"/>
+      <c r="P22" s="109"/>
+      <c r="Q22" s="109"/>
+      <c r="R22" s="109"/>
+      <c r="S22" s="109"/>
+      <c r="T22" s="109"/>
+      <c r="U22" s="109"/>
+      <c r="V22" s="109"/>
+      <c r="W22" s="109"/>
+      <c r="X22" s="109"/>
+      <c r="Y22" s="109"/>
+      <c r="Z22" s="109"/>
+      <c r="AA22" s="109"/>
+      <c r="AB22" s="109"/>
+      <c r="AC22" s="109"/>
+      <c r="AD22" s="109"/>
+      <c r="AE22" s="109"/>
+      <c r="AF22" s="109"/>
+      <c r="AG22" s="109"/>
+      <c r="AH22" s="109"/>
+      <c r="AI22" s="109"/>
+      <c r="AJ22" s="109"/>
+      <c r="AK22" s="109"/>
+      <c r="AL22" s="109"/>
+      <c r="AM22" s="109"/>
+      <c r="AN22" s="109"/>
+      <c r="AO22" s="109"/>
+      <c r="AP22" s="111"/>
+      <c r="AQ22" s="108"/>
+      <c r="AR22" s="109"/>
+      <c r="AS22" s="109"/>
+      <c r="AT22" s="109"/>
+      <c r="AU22" s="109"/>
+      <c r="AV22" s="109"/>
+      <c r="AW22" s="109"/>
+      <c r="AX22" s="109"/>
+      <c r="AY22" s="109"/>
+      <c r="AZ22" s="109"/>
+      <c r="BA22" s="109"/>
+      <c r="BB22" s="109"/>
+      <c r="BC22" s="109"/>
+      <c r="BD22" s="109"/>
+      <c r="BE22" s="110"/>
     </row>
     <row r="23" spans="1:57" ht="15" customHeight="1">
-      <c r="A23" s="88"/>
-      <c r="B23" s="89"/>
-      <c r="C23" s="89"/>
-      <c r="D23" s="89"/>
-      <c r="E23" s="89"/>
-      <c r="F23" s="89"/>
-      <c r="G23" s="90"/>
-      <c r="H23" s="91"/>
-      <c r="I23" s="92"/>
-      <c r="J23" s="92"/>
-      <c r="K23" s="92"/>
-      <c r="L23" s="92"/>
-      <c r="M23" s="92"/>
-      <c r="N23" s="93"/>
-      <c r="O23" s="91"/>
-      <c r="P23" s="94"/>
-      <c r="Q23" s="94"/>
-      <c r="R23" s="94"/>
-      <c r="S23" s="94"/>
-      <c r="T23" s="94"/>
-      <c r="U23" s="94"/>
-      <c r="V23" s="94"/>
-      <c r="W23" s="94"/>
-      <c r="X23" s="94"/>
-      <c r="Y23" s="94"/>
-      <c r="Z23" s="94"/>
-      <c r="AA23" s="94"/>
-      <c r="AB23" s="94"/>
-      <c r="AC23" s="94"/>
-      <c r="AD23" s="94"/>
-      <c r="AE23" s="94"/>
-      <c r="AF23" s="94"/>
-      <c r="AG23" s="94"/>
-      <c r="AH23" s="94"/>
-      <c r="AI23" s="94"/>
-      <c r="AJ23" s="94"/>
-      <c r="AK23" s="94"/>
-      <c r="AL23" s="94"/>
-      <c r="AM23" s="94"/>
-      <c r="AN23" s="94"/>
-      <c r="AO23" s="94"/>
-      <c r="AP23" s="95"/>
-      <c r="AQ23" s="96"/>
-      <c r="AR23" s="94"/>
-      <c r="AS23" s="94"/>
-      <c r="AT23" s="94"/>
-      <c r="AU23" s="94"/>
-      <c r="AV23" s="94"/>
-      <c r="AW23" s="94"/>
-      <c r="AX23" s="94"/>
-      <c r="AY23" s="94"/>
-      <c r="AZ23" s="94"/>
-      <c r="BA23" s="94"/>
-      <c r="BB23" s="94"/>
-      <c r="BC23" s="94"/>
-      <c r="BD23" s="94"/>
-      <c r="BE23" s="97"/>
+      <c r="A23" s="99"/>
+      <c r="B23" s="100"/>
+      <c r="C23" s="100"/>
+      <c r="D23" s="100"/>
+      <c r="E23" s="100"/>
+      <c r="F23" s="100"/>
+      <c r="G23" s="101"/>
+      <c r="H23" s="105"/>
+      <c r="I23" s="106"/>
+      <c r="J23" s="106"/>
+      <c r="K23" s="106"/>
+      <c r="L23" s="106"/>
+      <c r="M23" s="106"/>
+      <c r="N23" s="107"/>
+      <c r="O23" s="105"/>
+      <c r="P23" s="109"/>
+      <c r="Q23" s="109"/>
+      <c r="R23" s="109"/>
+      <c r="S23" s="109"/>
+      <c r="T23" s="109"/>
+      <c r="U23" s="109"/>
+      <c r="V23" s="109"/>
+      <c r="W23" s="109"/>
+      <c r="X23" s="109"/>
+      <c r="Y23" s="109"/>
+      <c r="Z23" s="109"/>
+      <c r="AA23" s="109"/>
+      <c r="AB23" s="109"/>
+      <c r="AC23" s="109"/>
+      <c r="AD23" s="109"/>
+      <c r="AE23" s="109"/>
+      <c r="AF23" s="109"/>
+      <c r="AG23" s="109"/>
+      <c r="AH23" s="109"/>
+      <c r="AI23" s="109"/>
+      <c r="AJ23" s="109"/>
+      <c r="AK23" s="109"/>
+      <c r="AL23" s="109"/>
+      <c r="AM23" s="109"/>
+      <c r="AN23" s="109"/>
+      <c r="AO23" s="109"/>
+      <c r="AP23" s="111"/>
+      <c r="AQ23" s="108"/>
+      <c r="AR23" s="109"/>
+      <c r="AS23" s="109"/>
+      <c r="AT23" s="109"/>
+      <c r="AU23" s="109"/>
+      <c r="AV23" s="109"/>
+      <c r="AW23" s="109"/>
+      <c r="AX23" s="109"/>
+      <c r="AY23" s="109"/>
+      <c r="AZ23" s="109"/>
+      <c r="BA23" s="109"/>
+      <c r="BB23" s="109"/>
+      <c r="BC23" s="109"/>
+      <c r="BD23" s="109"/>
+      <c r="BE23" s="110"/>
     </row>
     <row r="24" spans="1:57" ht="15" customHeight="1">
-      <c r="A24" s="88"/>
-      <c r="B24" s="89"/>
-      <c r="C24" s="89"/>
-      <c r="D24" s="89"/>
-      <c r="E24" s="89"/>
-      <c r="F24" s="89"/>
-      <c r="G24" s="90"/>
-      <c r="H24" s="91"/>
-      <c r="I24" s="92"/>
-      <c r="J24" s="92"/>
-      <c r="K24" s="92"/>
-      <c r="L24" s="92"/>
-      <c r="M24" s="92"/>
-      <c r="N24" s="93"/>
-      <c r="O24" s="91"/>
-      <c r="P24" s="94"/>
-      <c r="Q24" s="94"/>
-      <c r="R24" s="94"/>
-      <c r="S24" s="94"/>
-      <c r="T24" s="94"/>
-      <c r="U24" s="94"/>
-      <c r="V24" s="94"/>
-      <c r="W24" s="94"/>
-      <c r="X24" s="94"/>
-      <c r="Y24" s="94"/>
-      <c r="Z24" s="94"/>
-      <c r="AA24" s="94"/>
-      <c r="AB24" s="94"/>
-      <c r="AC24" s="94"/>
-      <c r="AD24" s="94"/>
-      <c r="AE24" s="94"/>
-      <c r="AF24" s="94"/>
-      <c r="AG24" s="94"/>
-      <c r="AH24" s="94"/>
-      <c r="AI24" s="94"/>
-      <c r="AJ24" s="94"/>
-      <c r="AK24" s="94"/>
-      <c r="AL24" s="94"/>
-      <c r="AM24" s="94"/>
-      <c r="AN24" s="94"/>
-      <c r="AO24" s="94"/>
-      <c r="AP24" s="95"/>
-      <c r="AQ24" s="96"/>
-      <c r="AR24" s="94"/>
-      <c r="AS24" s="94"/>
-      <c r="AT24" s="94"/>
-      <c r="AU24" s="94"/>
-      <c r="AV24" s="94"/>
-      <c r="AW24" s="94"/>
-      <c r="AX24" s="94"/>
-      <c r="AY24" s="94"/>
-      <c r="AZ24" s="94"/>
-      <c r="BA24" s="94"/>
-      <c r="BB24" s="94"/>
-      <c r="BC24" s="94"/>
-      <c r="BD24" s="94"/>
-      <c r="BE24" s="97"/>
+      <c r="A24" s="99"/>
+      <c r="B24" s="100"/>
+      <c r="C24" s="100"/>
+      <c r="D24" s="100"/>
+      <c r="E24" s="100"/>
+      <c r="F24" s="100"/>
+      <c r="G24" s="101"/>
+      <c r="H24" s="105"/>
+      <c r="I24" s="106"/>
+      <c r="J24" s="106"/>
+      <c r="K24" s="106"/>
+      <c r="L24" s="106"/>
+      <c r="M24" s="106"/>
+      <c r="N24" s="107"/>
+      <c r="O24" s="105"/>
+      <c r="P24" s="109"/>
+      <c r="Q24" s="109"/>
+      <c r="R24" s="109"/>
+      <c r="S24" s="109"/>
+      <c r="T24" s="109"/>
+      <c r="U24" s="109"/>
+      <c r="V24" s="109"/>
+      <c r="W24" s="109"/>
+      <c r="X24" s="109"/>
+      <c r="Y24" s="109"/>
+      <c r="Z24" s="109"/>
+      <c r="AA24" s="109"/>
+      <c r="AB24" s="109"/>
+      <c r="AC24" s="109"/>
+      <c r="AD24" s="109"/>
+      <c r="AE24" s="109"/>
+      <c r="AF24" s="109"/>
+      <c r="AG24" s="109"/>
+      <c r="AH24" s="109"/>
+      <c r="AI24" s="109"/>
+      <c r="AJ24" s="109"/>
+      <c r="AK24" s="109"/>
+      <c r="AL24" s="109"/>
+      <c r="AM24" s="109"/>
+      <c r="AN24" s="109"/>
+      <c r="AO24" s="109"/>
+      <c r="AP24" s="111"/>
+      <c r="AQ24" s="108"/>
+      <c r="AR24" s="109"/>
+      <c r="AS24" s="109"/>
+      <c r="AT24" s="109"/>
+      <c r="AU24" s="109"/>
+      <c r="AV24" s="109"/>
+      <c r="AW24" s="109"/>
+      <c r="AX24" s="109"/>
+      <c r="AY24" s="109"/>
+      <c r="AZ24" s="109"/>
+      <c r="BA24" s="109"/>
+      <c r="BB24" s="109"/>
+      <c r="BC24" s="109"/>
+      <c r="BD24" s="109"/>
+      <c r="BE24" s="110"/>
     </row>
     <row r="25" spans="1:57" ht="15" customHeight="1">
-      <c r="A25" s="88"/>
-      <c r="B25" s="89"/>
-      <c r="C25" s="89"/>
-      <c r="D25" s="89"/>
-      <c r="E25" s="89"/>
-      <c r="F25" s="89"/>
-      <c r="G25" s="90"/>
-      <c r="H25" s="91"/>
-      <c r="I25" s="92"/>
-      <c r="J25" s="92"/>
-      <c r="K25" s="92"/>
-      <c r="L25" s="92"/>
-      <c r="M25" s="92"/>
-      <c r="N25" s="93"/>
-      <c r="O25" s="91"/>
-      <c r="P25" s="94"/>
-      <c r="Q25" s="94"/>
-      <c r="R25" s="94"/>
-      <c r="S25" s="94"/>
-      <c r="T25" s="94"/>
-      <c r="U25" s="94"/>
-      <c r="V25" s="94"/>
-      <c r="W25" s="94"/>
-      <c r="X25" s="94"/>
-      <c r="Y25" s="94"/>
-      <c r="Z25" s="94"/>
-      <c r="AA25" s="94"/>
-      <c r="AB25" s="94"/>
-      <c r="AC25" s="94"/>
-      <c r="AD25" s="94"/>
-      <c r="AE25" s="94"/>
-      <c r="AF25" s="94"/>
-      <c r="AG25" s="94"/>
-      <c r="AH25" s="94"/>
-      <c r="AI25" s="94"/>
-      <c r="AJ25" s="94"/>
-      <c r="AK25" s="94"/>
-      <c r="AL25" s="94"/>
-      <c r="AM25" s="94"/>
-      <c r="AN25" s="94"/>
-      <c r="AO25" s="94"/>
-      <c r="AP25" s="95"/>
-      <c r="AQ25" s="96"/>
-      <c r="AR25" s="94"/>
-      <c r="AS25" s="94"/>
-      <c r="AT25" s="94"/>
-      <c r="AU25" s="94"/>
-      <c r="AV25" s="94"/>
-      <c r="AW25" s="94"/>
-      <c r="AX25" s="94"/>
-      <c r="AY25" s="94"/>
-      <c r="AZ25" s="94"/>
-      <c r="BA25" s="94"/>
-      <c r="BB25" s="94"/>
-      <c r="BC25" s="94"/>
-      <c r="BD25" s="94"/>
-      <c r="BE25" s="97"/>
+      <c r="A25" s="99"/>
+      <c r="B25" s="100"/>
+      <c r="C25" s="100"/>
+      <c r="D25" s="100"/>
+      <c r="E25" s="100"/>
+      <c r="F25" s="100"/>
+      <c r="G25" s="101"/>
+      <c r="H25" s="105"/>
+      <c r="I25" s="106"/>
+      <c r="J25" s="106"/>
+      <c r="K25" s="106"/>
+      <c r="L25" s="106"/>
+      <c r="M25" s="106"/>
+      <c r="N25" s="107"/>
+      <c r="O25" s="105"/>
+      <c r="P25" s="109"/>
+      <c r="Q25" s="109"/>
+      <c r="R25" s="109"/>
+      <c r="S25" s="109"/>
+      <c r="T25" s="109"/>
+      <c r="U25" s="109"/>
+      <c r="V25" s="109"/>
+      <c r="W25" s="109"/>
+      <c r="X25" s="109"/>
+      <c r="Y25" s="109"/>
+      <c r="Z25" s="109"/>
+      <c r="AA25" s="109"/>
+      <c r="AB25" s="109"/>
+      <c r="AC25" s="109"/>
+      <c r="AD25" s="109"/>
+      <c r="AE25" s="109"/>
+      <c r="AF25" s="109"/>
+      <c r="AG25" s="109"/>
+      <c r="AH25" s="109"/>
+      <c r="AI25" s="109"/>
+      <c r="AJ25" s="109"/>
+      <c r="AK25" s="109"/>
+      <c r="AL25" s="109"/>
+      <c r="AM25" s="109"/>
+      <c r="AN25" s="109"/>
+      <c r="AO25" s="109"/>
+      <c r="AP25" s="111"/>
+      <c r="AQ25" s="108"/>
+      <c r="AR25" s="109"/>
+      <c r="AS25" s="109"/>
+      <c r="AT25" s="109"/>
+      <c r="AU25" s="109"/>
+      <c r="AV25" s="109"/>
+      <c r="AW25" s="109"/>
+      <c r="AX25" s="109"/>
+      <c r="AY25" s="109"/>
+      <c r="AZ25" s="109"/>
+      <c r="BA25" s="109"/>
+      <c r="BB25" s="109"/>
+      <c r="BC25" s="109"/>
+      <c r="BD25" s="109"/>
+      <c r="BE25" s="110"/>
     </row>
     <row r="26" spans="1:57" ht="15" customHeight="1">
-      <c r="A26" s="88"/>
-      <c r="B26" s="89"/>
-      <c r="C26" s="89"/>
-      <c r="D26" s="89"/>
-      <c r="E26" s="89"/>
-      <c r="F26" s="89"/>
-      <c r="G26" s="90"/>
-      <c r="H26" s="91"/>
-      <c r="I26" s="92"/>
-      <c r="J26" s="92"/>
-      <c r="K26" s="92"/>
-      <c r="L26" s="92"/>
-      <c r="M26" s="92"/>
-      <c r="N26" s="93"/>
-      <c r="O26" s="91"/>
-      <c r="P26" s="94"/>
-      <c r="Q26" s="94"/>
-      <c r="R26" s="94"/>
-      <c r="S26" s="94"/>
-      <c r="T26" s="94"/>
-      <c r="U26" s="94"/>
-      <c r="V26" s="94"/>
-      <c r="W26" s="94"/>
-      <c r="X26" s="94"/>
-      <c r="Y26" s="94"/>
-      <c r="Z26" s="94"/>
-      <c r="AA26" s="94"/>
-      <c r="AB26" s="94"/>
-      <c r="AC26" s="94"/>
-      <c r="AD26" s="94"/>
-      <c r="AE26" s="94"/>
-      <c r="AF26" s="94"/>
-      <c r="AG26" s="94"/>
-      <c r="AH26" s="94"/>
-      <c r="AI26" s="94"/>
-      <c r="AJ26" s="94"/>
-      <c r="AK26" s="94"/>
-      <c r="AL26" s="94"/>
-      <c r="AM26" s="94"/>
-      <c r="AN26" s="94"/>
-      <c r="AO26" s="94"/>
-      <c r="AP26" s="95"/>
-      <c r="AQ26" s="96"/>
-      <c r="AR26" s="94"/>
-      <c r="AS26" s="94"/>
-      <c r="AT26" s="94"/>
-      <c r="AU26" s="94"/>
-      <c r="AV26" s="94"/>
-      <c r="AW26" s="94"/>
-      <c r="AX26" s="94"/>
-      <c r="AY26" s="94"/>
-      <c r="AZ26" s="94"/>
-      <c r="BA26" s="94"/>
-      <c r="BB26" s="94"/>
-      <c r="BC26" s="94"/>
-      <c r="BD26" s="94"/>
-      <c r="BE26" s="97"/>
+      <c r="A26" s="99"/>
+      <c r="B26" s="100"/>
+      <c r="C26" s="100"/>
+      <c r="D26" s="100"/>
+      <c r="E26" s="100"/>
+      <c r="F26" s="100"/>
+      <c r="G26" s="101"/>
+      <c r="H26" s="105"/>
+      <c r="I26" s="106"/>
+      <c r="J26" s="106"/>
+      <c r="K26" s="106"/>
+      <c r="L26" s="106"/>
+      <c r="M26" s="106"/>
+      <c r="N26" s="107"/>
+      <c r="O26" s="105"/>
+      <c r="P26" s="109"/>
+      <c r="Q26" s="109"/>
+      <c r="R26" s="109"/>
+      <c r="S26" s="109"/>
+      <c r="T26" s="109"/>
+      <c r="U26" s="109"/>
+      <c r="V26" s="109"/>
+      <c r="W26" s="109"/>
+      <c r="X26" s="109"/>
+      <c r="Y26" s="109"/>
+      <c r="Z26" s="109"/>
+      <c r="AA26" s="109"/>
+      <c r="AB26" s="109"/>
+      <c r="AC26" s="109"/>
+      <c r="AD26" s="109"/>
+      <c r="AE26" s="109"/>
+      <c r="AF26" s="109"/>
+      <c r="AG26" s="109"/>
+      <c r="AH26" s="109"/>
+      <c r="AI26" s="109"/>
+      <c r="AJ26" s="109"/>
+      <c r="AK26" s="109"/>
+      <c r="AL26" s="109"/>
+      <c r="AM26" s="109"/>
+      <c r="AN26" s="109"/>
+      <c r="AO26" s="109"/>
+      <c r="AP26" s="111"/>
+      <c r="AQ26" s="108"/>
+      <c r="AR26" s="109"/>
+      <c r="AS26" s="109"/>
+      <c r="AT26" s="109"/>
+      <c r="AU26" s="109"/>
+      <c r="AV26" s="109"/>
+      <c r="AW26" s="109"/>
+      <c r="AX26" s="109"/>
+      <c r="AY26" s="109"/>
+      <c r="AZ26" s="109"/>
+      <c r="BA26" s="109"/>
+      <c r="BB26" s="109"/>
+      <c r="BC26" s="109"/>
+      <c r="BD26" s="109"/>
+      <c r="BE26" s="110"/>
     </row>
     <row r="27" spans="1:57" ht="15" customHeight="1">
-      <c r="A27" s="88"/>
-      <c r="B27" s="89"/>
-      <c r="C27" s="89"/>
-      <c r="D27" s="89"/>
-      <c r="E27" s="89"/>
-      <c r="F27" s="89"/>
-      <c r="G27" s="90"/>
-      <c r="H27" s="91"/>
-      <c r="I27" s="92"/>
-      <c r="J27" s="92"/>
-      <c r="K27" s="92"/>
-      <c r="L27" s="92"/>
-      <c r="M27" s="92"/>
-      <c r="N27" s="93"/>
-      <c r="O27" s="91"/>
-      <c r="P27" s="94"/>
-      <c r="Q27" s="94"/>
-      <c r="R27" s="94"/>
-      <c r="S27" s="94"/>
-      <c r="T27" s="94"/>
-      <c r="U27" s="94"/>
-      <c r="V27" s="94"/>
-      <c r="W27" s="94"/>
-      <c r="X27" s="94"/>
-      <c r="Y27" s="94"/>
-      <c r="Z27" s="94"/>
-      <c r="AA27" s="94"/>
-      <c r="AB27" s="94"/>
-      <c r="AC27" s="94"/>
-      <c r="AD27" s="94"/>
-      <c r="AE27" s="94"/>
-      <c r="AF27" s="94"/>
-      <c r="AG27" s="94"/>
-      <c r="AH27" s="94"/>
-      <c r="AI27" s="94"/>
-      <c r="AJ27" s="94"/>
-      <c r="AK27" s="94"/>
-      <c r="AL27" s="94"/>
-      <c r="AM27" s="94"/>
-      <c r="AN27" s="94"/>
-      <c r="AO27" s="94"/>
-      <c r="AP27" s="95"/>
-      <c r="AQ27" s="96"/>
-      <c r="AR27" s="94"/>
-      <c r="AS27" s="94"/>
-      <c r="AT27" s="94"/>
-      <c r="AU27" s="94"/>
-      <c r="AV27" s="94"/>
-      <c r="AW27" s="94"/>
-      <c r="AX27" s="94"/>
-      <c r="AY27" s="94"/>
-      <c r="AZ27" s="94"/>
-      <c r="BA27" s="94"/>
-      <c r="BB27" s="94"/>
-      <c r="BC27" s="94"/>
-      <c r="BD27" s="94"/>
-      <c r="BE27" s="97"/>
+      <c r="A27" s="99"/>
+      <c r="B27" s="100"/>
+      <c r="C27" s="100"/>
+      <c r="D27" s="100"/>
+      <c r="E27" s="100"/>
+      <c r="F27" s="100"/>
+      <c r="G27" s="101"/>
+      <c r="H27" s="105"/>
+      <c r="I27" s="106"/>
+      <c r="J27" s="106"/>
+      <c r="K27" s="106"/>
+      <c r="L27" s="106"/>
+      <c r="M27" s="106"/>
+      <c r="N27" s="107"/>
+      <c r="O27" s="105"/>
+      <c r="P27" s="109"/>
+      <c r="Q27" s="109"/>
+      <c r="R27" s="109"/>
+      <c r="S27" s="109"/>
+      <c r="T27" s="109"/>
+      <c r="U27" s="109"/>
+      <c r="V27" s="109"/>
+      <c r="W27" s="109"/>
+      <c r="X27" s="109"/>
+      <c r="Y27" s="109"/>
+      <c r="Z27" s="109"/>
+      <c r="AA27" s="109"/>
+      <c r="AB27" s="109"/>
+      <c r="AC27" s="109"/>
+      <c r="AD27" s="109"/>
+      <c r="AE27" s="109"/>
+      <c r="AF27" s="109"/>
+      <c r="AG27" s="109"/>
+      <c r="AH27" s="109"/>
+      <c r="AI27" s="109"/>
+      <c r="AJ27" s="109"/>
+      <c r="AK27" s="109"/>
+      <c r="AL27" s="109"/>
+      <c r="AM27" s="109"/>
+      <c r="AN27" s="109"/>
+      <c r="AO27" s="109"/>
+      <c r="AP27" s="111"/>
+      <c r="AQ27" s="108"/>
+      <c r="AR27" s="109"/>
+      <c r="AS27" s="109"/>
+      <c r="AT27" s="109"/>
+      <c r="AU27" s="109"/>
+      <c r="AV27" s="109"/>
+      <c r="AW27" s="109"/>
+      <c r="AX27" s="109"/>
+      <c r="AY27" s="109"/>
+      <c r="AZ27" s="109"/>
+      <c r="BA27" s="109"/>
+      <c r="BB27" s="109"/>
+      <c r="BC27" s="109"/>
+      <c r="BD27" s="109"/>
+      <c r="BE27" s="110"/>
     </row>
     <row r="28" spans="1:57" ht="15" customHeight="1">
-      <c r="A28" s="88"/>
-      <c r="B28" s="89"/>
-      <c r="C28" s="89"/>
-      <c r="D28" s="89"/>
-      <c r="E28" s="89"/>
-      <c r="F28" s="89"/>
-      <c r="G28" s="90"/>
-      <c r="H28" s="91"/>
-      <c r="I28" s="92"/>
-      <c r="J28" s="92"/>
-      <c r="K28" s="92"/>
-      <c r="L28" s="92"/>
-      <c r="M28" s="92"/>
-      <c r="N28" s="93"/>
-      <c r="O28" s="91"/>
-      <c r="P28" s="94"/>
-      <c r="Q28" s="94"/>
-      <c r="R28" s="94"/>
-      <c r="S28" s="94"/>
-      <c r="T28" s="94"/>
-      <c r="U28" s="94"/>
-      <c r="V28" s="94"/>
-      <c r="W28" s="94"/>
-      <c r="X28" s="94"/>
-      <c r="Y28" s="94"/>
-      <c r="Z28" s="94"/>
-      <c r="AA28" s="94"/>
-      <c r="AB28" s="94"/>
-      <c r="AC28" s="94"/>
-      <c r="AD28" s="94"/>
-      <c r="AE28" s="94"/>
-      <c r="AF28" s="94"/>
-      <c r="AG28" s="94"/>
-      <c r="AH28" s="94"/>
-      <c r="AI28" s="94"/>
-      <c r="AJ28" s="94"/>
-      <c r="AK28" s="94"/>
-      <c r="AL28" s="94"/>
-      <c r="AM28" s="94"/>
-      <c r="AN28" s="94"/>
-      <c r="AO28" s="94"/>
-      <c r="AP28" s="95"/>
-      <c r="AQ28" s="96"/>
-      <c r="AR28" s="94"/>
-      <c r="AS28" s="94"/>
-      <c r="AT28" s="94"/>
-      <c r="AU28" s="94"/>
-      <c r="AV28" s="94"/>
-      <c r="AW28" s="94"/>
-      <c r="AX28" s="94"/>
-      <c r="AY28" s="94"/>
-      <c r="AZ28" s="94"/>
-      <c r="BA28" s="94"/>
-      <c r="BB28" s="94"/>
-      <c r="BC28" s="94"/>
-      <c r="BD28" s="94"/>
-      <c r="BE28" s="97"/>
+      <c r="A28" s="99"/>
+      <c r="B28" s="100"/>
+      <c r="C28" s="100"/>
+      <c r="D28" s="100"/>
+      <c r="E28" s="100"/>
+      <c r="F28" s="100"/>
+      <c r="G28" s="101"/>
+      <c r="H28" s="105"/>
+      <c r="I28" s="106"/>
+      <c r="J28" s="106"/>
+      <c r="K28" s="106"/>
+      <c r="L28" s="106"/>
+      <c r="M28" s="106"/>
+      <c r="N28" s="107"/>
+      <c r="O28" s="105"/>
+      <c r="P28" s="109"/>
+      <c r="Q28" s="109"/>
+      <c r="R28" s="109"/>
+      <c r="S28" s="109"/>
+      <c r="T28" s="109"/>
+      <c r="U28" s="109"/>
+      <c r="V28" s="109"/>
+      <c r="W28" s="109"/>
+      <c r="X28" s="109"/>
+      <c r="Y28" s="109"/>
+      <c r="Z28" s="109"/>
+      <c r="AA28" s="109"/>
+      <c r="AB28" s="109"/>
+      <c r="AC28" s="109"/>
+      <c r="AD28" s="109"/>
+      <c r="AE28" s="109"/>
+      <c r="AF28" s="109"/>
+      <c r="AG28" s="109"/>
+      <c r="AH28" s="109"/>
+      <c r="AI28" s="109"/>
+      <c r="AJ28" s="109"/>
+      <c r="AK28" s="109"/>
+      <c r="AL28" s="109"/>
+      <c r="AM28" s="109"/>
+      <c r="AN28" s="109"/>
+      <c r="AO28" s="109"/>
+      <c r="AP28" s="111"/>
+      <c r="AQ28" s="108"/>
+      <c r="AR28" s="109"/>
+      <c r="AS28" s="109"/>
+      <c r="AT28" s="109"/>
+      <c r="AU28" s="109"/>
+      <c r="AV28" s="109"/>
+      <c r="AW28" s="109"/>
+      <c r="AX28" s="109"/>
+      <c r="AY28" s="109"/>
+      <c r="AZ28" s="109"/>
+      <c r="BA28" s="109"/>
+      <c r="BB28" s="109"/>
+      <c r="BC28" s="109"/>
+      <c r="BD28" s="109"/>
+      <c r="BE28" s="110"/>
     </row>
     <row r="29" spans="1:57" ht="15" customHeight="1">
-      <c r="A29" s="88"/>
-      <c r="B29" s="89"/>
-      <c r="C29" s="89"/>
-      <c r="D29" s="89"/>
-      <c r="E29" s="89"/>
-      <c r="F29" s="89"/>
-      <c r="G29" s="90"/>
-      <c r="H29" s="91"/>
-      <c r="I29" s="92"/>
-      <c r="J29" s="92"/>
-      <c r="K29" s="92"/>
-      <c r="L29" s="92"/>
-      <c r="M29" s="92"/>
-      <c r="N29" s="93"/>
-      <c r="O29" s="91"/>
-      <c r="P29" s="94"/>
-      <c r="Q29" s="94"/>
-      <c r="R29" s="94"/>
-      <c r="S29" s="94"/>
-      <c r="T29" s="94"/>
-      <c r="U29" s="94"/>
-      <c r="V29" s="94"/>
-      <c r="W29" s="94"/>
-      <c r="X29" s="94"/>
-      <c r="Y29" s="94"/>
-      <c r="Z29" s="94"/>
-      <c r="AA29" s="94"/>
-      <c r="AB29" s="94"/>
-      <c r="AC29" s="94"/>
-      <c r="AD29" s="94"/>
-      <c r="AE29" s="94"/>
-      <c r="AF29" s="94"/>
-      <c r="AG29" s="94"/>
-      <c r="AH29" s="94"/>
-      <c r="AI29" s="94"/>
-      <c r="AJ29" s="94"/>
-      <c r="AK29" s="94"/>
-      <c r="AL29" s="94"/>
-      <c r="AM29" s="94"/>
-      <c r="AN29" s="94"/>
-      <c r="AO29" s="94"/>
-      <c r="AP29" s="95"/>
-      <c r="AQ29" s="96"/>
-      <c r="AR29" s="94"/>
-      <c r="AS29" s="94"/>
-      <c r="AT29" s="94"/>
-      <c r="AU29" s="94"/>
-      <c r="AV29" s="94"/>
-      <c r="AW29" s="94"/>
-      <c r="AX29" s="94"/>
-      <c r="AY29" s="94"/>
-      <c r="AZ29" s="94"/>
-      <c r="BA29" s="94"/>
-      <c r="BB29" s="94"/>
-      <c r="BC29" s="94"/>
-      <c r="BD29" s="94"/>
-      <c r="BE29" s="97"/>
+      <c r="A29" s="99"/>
+      <c r="B29" s="100"/>
+      <c r="C29" s="100"/>
+      <c r="D29" s="100"/>
+      <c r="E29" s="100"/>
+      <c r="F29" s="100"/>
+      <c r="G29" s="101"/>
+      <c r="H29" s="105"/>
+      <c r="I29" s="106"/>
+      <c r="J29" s="106"/>
+      <c r="K29" s="106"/>
+      <c r="L29" s="106"/>
+      <c r="M29" s="106"/>
+      <c r="N29" s="107"/>
+      <c r="O29" s="105"/>
+      <c r="P29" s="109"/>
+      <c r="Q29" s="109"/>
+      <c r="R29" s="109"/>
+      <c r="S29" s="109"/>
+      <c r="T29" s="109"/>
+      <c r="U29" s="109"/>
+      <c r="V29" s="109"/>
+      <c r="W29" s="109"/>
+      <c r="X29" s="109"/>
+      <c r="Y29" s="109"/>
+      <c r="Z29" s="109"/>
+      <c r="AA29" s="109"/>
+      <c r="AB29" s="109"/>
+      <c r="AC29" s="109"/>
+      <c r="AD29" s="109"/>
+      <c r="AE29" s="109"/>
+      <c r="AF29" s="109"/>
+      <c r="AG29" s="109"/>
+      <c r="AH29" s="109"/>
+      <c r="AI29" s="109"/>
+      <c r="AJ29" s="109"/>
+      <c r="AK29" s="109"/>
+      <c r="AL29" s="109"/>
+      <c r="AM29" s="109"/>
+      <c r="AN29" s="109"/>
+      <c r="AO29" s="109"/>
+      <c r="AP29" s="111"/>
+      <c r="AQ29" s="108"/>
+      <c r="AR29" s="109"/>
+      <c r="AS29" s="109"/>
+      <c r="AT29" s="109"/>
+      <c r="AU29" s="109"/>
+      <c r="AV29" s="109"/>
+      <c r="AW29" s="109"/>
+      <c r="AX29" s="109"/>
+      <c r="AY29" s="109"/>
+      <c r="AZ29" s="109"/>
+      <c r="BA29" s="109"/>
+      <c r="BB29" s="109"/>
+      <c r="BC29" s="109"/>
+      <c r="BD29" s="109"/>
+      <c r="BE29" s="110"/>
     </row>
     <row r="30" spans="1:57" ht="15" customHeight="1">
-      <c r="A30" s="88"/>
-      <c r="B30" s="89"/>
-      <c r="C30" s="89"/>
-      <c r="D30" s="89"/>
-      <c r="E30" s="89"/>
-      <c r="F30" s="89"/>
-      <c r="G30" s="90"/>
-      <c r="H30" s="91"/>
-      <c r="I30" s="92"/>
-      <c r="J30" s="92"/>
-      <c r="K30" s="92"/>
-      <c r="L30" s="92"/>
-      <c r="M30" s="92"/>
-      <c r="N30" s="93"/>
-      <c r="O30" s="91"/>
-      <c r="P30" s="94"/>
-      <c r="Q30" s="94"/>
-      <c r="R30" s="94"/>
-      <c r="S30" s="94"/>
-      <c r="T30" s="94"/>
-      <c r="U30" s="94"/>
-      <c r="V30" s="94"/>
-      <c r="W30" s="94"/>
-      <c r="X30" s="94"/>
-      <c r="Y30" s="94"/>
-      <c r="Z30" s="94"/>
-      <c r="AA30" s="94"/>
-      <c r="AB30" s="94"/>
-      <c r="AC30" s="94"/>
-      <c r="AD30" s="94"/>
-      <c r="AE30" s="94"/>
-      <c r="AF30" s="94"/>
-      <c r="AG30" s="94"/>
-      <c r="AH30" s="94"/>
-      <c r="AI30" s="94"/>
-      <c r="AJ30" s="94"/>
-      <c r="AK30" s="94"/>
-      <c r="AL30" s="94"/>
-      <c r="AM30" s="94"/>
-      <c r="AN30" s="94"/>
-      <c r="AO30" s="94"/>
-      <c r="AP30" s="95"/>
-      <c r="AQ30" s="96"/>
-      <c r="AR30" s="94"/>
-      <c r="AS30" s="94"/>
-      <c r="AT30" s="94"/>
-      <c r="AU30" s="94"/>
-      <c r="AV30" s="94"/>
-      <c r="AW30" s="94"/>
-      <c r="AX30" s="94"/>
-      <c r="AY30" s="94"/>
-      <c r="AZ30" s="94"/>
-      <c r="BA30" s="94"/>
-      <c r="BB30" s="94"/>
-      <c r="BC30" s="94"/>
-      <c r="BD30" s="94"/>
-      <c r="BE30" s="97"/>
+      <c r="A30" s="99"/>
+      <c r="B30" s="100"/>
+      <c r="C30" s="100"/>
+      <c r="D30" s="100"/>
+      <c r="E30" s="100"/>
+      <c r="F30" s="100"/>
+      <c r="G30" s="101"/>
+      <c r="H30" s="105"/>
+      <c r="I30" s="106"/>
+      <c r="J30" s="106"/>
+      <c r="K30" s="106"/>
+      <c r="L30" s="106"/>
+      <c r="M30" s="106"/>
+      <c r="N30" s="107"/>
+      <c r="O30" s="105"/>
+      <c r="P30" s="109"/>
+      <c r="Q30" s="109"/>
+      <c r="R30" s="109"/>
+      <c r="S30" s="109"/>
+      <c r="T30" s="109"/>
+      <c r="U30" s="109"/>
+      <c r="V30" s="109"/>
+      <c r="W30" s="109"/>
+      <c r="X30" s="109"/>
+      <c r="Y30" s="109"/>
+      <c r="Z30" s="109"/>
+      <c r="AA30" s="109"/>
+      <c r="AB30" s="109"/>
+      <c r="AC30" s="109"/>
+      <c r="AD30" s="109"/>
+      <c r="AE30" s="109"/>
+      <c r="AF30" s="109"/>
+      <c r="AG30" s="109"/>
+      <c r="AH30" s="109"/>
+      <c r="AI30" s="109"/>
+      <c r="AJ30" s="109"/>
+      <c r="AK30" s="109"/>
+      <c r="AL30" s="109"/>
+      <c r="AM30" s="109"/>
+      <c r="AN30" s="109"/>
+      <c r="AO30" s="109"/>
+      <c r="AP30" s="111"/>
+      <c r="AQ30" s="108"/>
+      <c r="AR30" s="109"/>
+      <c r="AS30" s="109"/>
+      <c r="AT30" s="109"/>
+      <c r="AU30" s="109"/>
+      <c r="AV30" s="109"/>
+      <c r="AW30" s="109"/>
+      <c r="AX30" s="109"/>
+      <c r="AY30" s="109"/>
+      <c r="AZ30" s="109"/>
+      <c r="BA30" s="109"/>
+      <c r="BB30" s="109"/>
+      <c r="BC30" s="109"/>
+      <c r="BD30" s="109"/>
+      <c r="BE30" s="110"/>
     </row>
     <row r="31" spans="1:57" ht="15" customHeight="1">
-      <c r="A31" s="88"/>
-      <c r="B31" s="89"/>
-      <c r="C31" s="89"/>
-      <c r="D31" s="89"/>
-      <c r="E31" s="89"/>
-      <c r="F31" s="89"/>
-      <c r="G31" s="90"/>
-      <c r="H31" s="91"/>
-      <c r="I31" s="92"/>
-      <c r="J31" s="92"/>
-      <c r="K31" s="92"/>
-      <c r="L31" s="92"/>
-      <c r="M31" s="92"/>
-      <c r="N31" s="93"/>
-      <c r="O31" s="91"/>
-      <c r="P31" s="94"/>
-      <c r="Q31" s="94"/>
-      <c r="R31" s="94"/>
-      <c r="S31" s="94"/>
-      <c r="T31" s="94"/>
-      <c r="U31" s="94"/>
-      <c r="V31" s="94"/>
-      <c r="W31" s="94"/>
-      <c r="X31" s="94"/>
-      <c r="Y31" s="94"/>
-      <c r="Z31" s="94"/>
-      <c r="AA31" s="94"/>
-      <c r="AB31" s="94"/>
-      <c r="AC31" s="94"/>
-      <c r="AD31" s="94"/>
-      <c r="AE31" s="94"/>
-      <c r="AF31" s="94"/>
-      <c r="AG31" s="94"/>
-      <c r="AH31" s="94"/>
-      <c r="AI31" s="94"/>
-      <c r="AJ31" s="94"/>
-      <c r="AK31" s="94"/>
-      <c r="AL31" s="94"/>
-      <c r="AM31" s="94"/>
-      <c r="AN31" s="94"/>
-      <c r="AO31" s="94"/>
-      <c r="AP31" s="95"/>
-      <c r="AQ31" s="96"/>
-      <c r="AR31" s="94"/>
-      <c r="AS31" s="94"/>
-      <c r="AT31" s="94"/>
-      <c r="AU31" s="94"/>
-      <c r="AV31" s="94"/>
-      <c r="AW31" s="94"/>
-      <c r="AX31" s="94"/>
-      <c r="AY31" s="94"/>
-      <c r="AZ31" s="94"/>
-      <c r="BA31" s="94"/>
-      <c r="BB31" s="94"/>
-      <c r="BC31" s="94"/>
-      <c r="BD31" s="94"/>
-      <c r="BE31" s="97"/>
+      <c r="A31" s="99"/>
+      <c r="B31" s="100"/>
+      <c r="C31" s="100"/>
+      <c r="D31" s="100"/>
+      <c r="E31" s="100"/>
+      <c r="F31" s="100"/>
+      <c r="G31" s="101"/>
+      <c r="H31" s="105"/>
+      <c r="I31" s="106"/>
+      <c r="J31" s="106"/>
+      <c r="K31" s="106"/>
+      <c r="L31" s="106"/>
+      <c r="M31" s="106"/>
+      <c r="N31" s="107"/>
+      <c r="O31" s="105"/>
+      <c r="P31" s="109"/>
+      <c r="Q31" s="109"/>
+      <c r="R31" s="109"/>
+      <c r="S31" s="109"/>
+      <c r="T31" s="109"/>
+      <c r="U31" s="109"/>
+      <c r="V31" s="109"/>
+      <c r="W31" s="109"/>
+      <c r="X31" s="109"/>
+      <c r="Y31" s="109"/>
+      <c r="Z31" s="109"/>
+      <c r="AA31" s="109"/>
+      <c r="AB31" s="109"/>
+      <c r="AC31" s="109"/>
+      <c r="AD31" s="109"/>
+      <c r="AE31" s="109"/>
+      <c r="AF31" s="109"/>
+      <c r="AG31" s="109"/>
+      <c r="AH31" s="109"/>
+      <c r="AI31" s="109"/>
+      <c r="AJ31" s="109"/>
+      <c r="AK31" s="109"/>
+      <c r="AL31" s="109"/>
+      <c r="AM31" s="109"/>
+      <c r="AN31" s="109"/>
+      <c r="AO31" s="109"/>
+      <c r="AP31" s="111"/>
+      <c r="AQ31" s="108"/>
+      <c r="AR31" s="109"/>
+      <c r="AS31" s="109"/>
+      <c r="AT31" s="109"/>
+      <c r="AU31" s="109"/>
+      <c r="AV31" s="109"/>
+      <c r="AW31" s="109"/>
+      <c r="AX31" s="109"/>
+      <c r="AY31" s="109"/>
+      <c r="AZ31" s="109"/>
+      <c r="BA31" s="109"/>
+      <c r="BB31" s="109"/>
+      <c r="BC31" s="109"/>
+      <c r="BD31" s="109"/>
+      <c r="BE31" s="110"/>
     </row>
     <row r="32" spans="1:57" ht="15" customHeight="1">
-      <c r="A32" s="88"/>
-      <c r="B32" s="89"/>
-      <c r="C32" s="89"/>
-      <c r="D32" s="89"/>
-      <c r="E32" s="89"/>
-      <c r="F32" s="89"/>
-      <c r="G32" s="90"/>
-      <c r="H32" s="91"/>
-      <c r="I32" s="92"/>
-      <c r="J32" s="92"/>
-      <c r="K32" s="92"/>
-      <c r="L32" s="92"/>
-      <c r="M32" s="92"/>
-      <c r="N32" s="93"/>
-      <c r="O32" s="91"/>
-      <c r="P32" s="94"/>
-      <c r="Q32" s="94"/>
-      <c r="R32" s="94"/>
-      <c r="S32" s="94"/>
-      <c r="T32" s="94"/>
-      <c r="U32" s="94"/>
-      <c r="V32" s="94"/>
-      <c r="W32" s="94"/>
-      <c r="X32" s="94"/>
-      <c r="Y32" s="94"/>
-      <c r="Z32" s="94"/>
-      <c r="AA32" s="94"/>
-      <c r="AB32" s="94"/>
-      <c r="AC32" s="94"/>
-      <c r="AD32" s="94"/>
-      <c r="AE32" s="94"/>
-      <c r="AF32" s="94"/>
-      <c r="AG32" s="94"/>
-      <c r="AH32" s="94"/>
-      <c r="AI32" s="94"/>
-      <c r="AJ32" s="94"/>
-      <c r="AK32" s="94"/>
-      <c r="AL32" s="94"/>
-      <c r="AM32" s="94"/>
-      <c r="AN32" s="94"/>
-      <c r="AO32" s="94"/>
-      <c r="AP32" s="95"/>
-      <c r="AQ32" s="96"/>
-      <c r="AR32" s="94"/>
-      <c r="AS32" s="94"/>
-      <c r="AT32" s="94"/>
-      <c r="AU32" s="94"/>
-      <c r="AV32" s="94"/>
-      <c r="AW32" s="94"/>
-      <c r="AX32" s="94"/>
-      <c r="AY32" s="94"/>
-      <c r="AZ32" s="94"/>
-      <c r="BA32" s="94"/>
-      <c r="BB32" s="94"/>
-      <c r="BC32" s="94"/>
-      <c r="BD32" s="94"/>
-      <c r="BE32" s="97"/>
+      <c r="A32" s="99"/>
+      <c r="B32" s="100"/>
+      <c r="C32" s="100"/>
+      <c r="D32" s="100"/>
+      <c r="E32" s="100"/>
+      <c r="F32" s="100"/>
+      <c r="G32" s="101"/>
+      <c r="H32" s="105"/>
+      <c r="I32" s="106"/>
+      <c r="J32" s="106"/>
+      <c r="K32" s="106"/>
+      <c r="L32" s="106"/>
+      <c r="M32" s="106"/>
+      <c r="N32" s="107"/>
+      <c r="O32" s="105"/>
+      <c r="P32" s="109"/>
+      <c r="Q32" s="109"/>
+      <c r="R32" s="109"/>
+      <c r="S32" s="109"/>
+      <c r="T32" s="109"/>
+      <c r="U32" s="109"/>
+      <c r="V32" s="109"/>
+      <c r="W32" s="109"/>
+      <c r="X32" s="109"/>
+      <c r="Y32" s="109"/>
+      <c r="Z32" s="109"/>
+      <c r="AA32" s="109"/>
+      <c r="AB32" s="109"/>
+      <c r="AC32" s="109"/>
+      <c r="AD32" s="109"/>
+      <c r="AE32" s="109"/>
+      <c r="AF32" s="109"/>
+      <c r="AG32" s="109"/>
+      <c r="AH32" s="109"/>
+      <c r="AI32" s="109"/>
+      <c r="AJ32" s="109"/>
+      <c r="AK32" s="109"/>
+      <c r="AL32" s="109"/>
+      <c r="AM32" s="109"/>
+      <c r="AN32" s="109"/>
+      <c r="AO32" s="109"/>
+      <c r="AP32" s="111"/>
+      <c r="AQ32" s="108"/>
+      <c r="AR32" s="109"/>
+      <c r="AS32" s="109"/>
+      <c r="AT32" s="109"/>
+      <c r="AU32" s="109"/>
+      <c r="AV32" s="109"/>
+      <c r="AW32" s="109"/>
+      <c r="AX32" s="109"/>
+      <c r="AY32" s="109"/>
+      <c r="AZ32" s="109"/>
+      <c r="BA32" s="109"/>
+      <c r="BB32" s="109"/>
+      <c r="BC32" s="109"/>
+      <c r="BD32" s="109"/>
+      <c r="BE32" s="110"/>
     </row>
     <row r="33" spans="1:57" ht="15" customHeight="1">
-      <c r="A33" s="88"/>
-      <c r="B33" s="89"/>
-      <c r="C33" s="89"/>
-      <c r="D33" s="89"/>
-      <c r="E33" s="89"/>
-      <c r="F33" s="89"/>
-      <c r="G33" s="90"/>
-      <c r="H33" s="91"/>
-      <c r="I33" s="92"/>
-      <c r="J33" s="92"/>
-      <c r="K33" s="92"/>
-      <c r="L33" s="92"/>
-      <c r="M33" s="92"/>
-      <c r="N33" s="93"/>
-      <c r="O33" s="91"/>
-      <c r="P33" s="94"/>
-      <c r="Q33" s="94"/>
-      <c r="R33" s="94"/>
-      <c r="S33" s="94"/>
-      <c r="T33" s="94"/>
-      <c r="U33" s="94"/>
-      <c r="V33" s="94"/>
-      <c r="W33" s="94"/>
-      <c r="X33" s="94"/>
-      <c r="Y33" s="94"/>
-      <c r="Z33" s="94"/>
-      <c r="AA33" s="94"/>
-      <c r="AB33" s="94"/>
-      <c r="AC33" s="94"/>
-      <c r="AD33" s="94"/>
-      <c r="AE33" s="94"/>
-      <c r="AF33" s="94"/>
-      <c r="AG33" s="94"/>
-      <c r="AH33" s="94"/>
-      <c r="AI33" s="94"/>
-      <c r="AJ33" s="94"/>
-      <c r="AK33" s="94"/>
-      <c r="AL33" s="94"/>
-      <c r="AM33" s="94"/>
-      <c r="AN33" s="94"/>
-      <c r="AO33" s="94"/>
-      <c r="AP33" s="95"/>
-      <c r="AQ33" s="96"/>
-      <c r="AR33" s="94"/>
-      <c r="AS33" s="94"/>
-      <c r="AT33" s="94"/>
-      <c r="AU33" s="94"/>
-      <c r="AV33" s="94"/>
-      <c r="AW33" s="94"/>
-      <c r="AX33" s="94"/>
-      <c r="AY33" s="94"/>
-      <c r="AZ33" s="94"/>
-      <c r="BA33" s="94"/>
-      <c r="BB33" s="94"/>
-      <c r="BC33" s="94"/>
-      <c r="BD33" s="94"/>
-      <c r="BE33" s="97"/>
+      <c r="A33" s="99"/>
+      <c r="B33" s="100"/>
+      <c r="C33" s="100"/>
+      <c r="D33" s="100"/>
+      <c r="E33" s="100"/>
+      <c r="F33" s="100"/>
+      <c r="G33" s="101"/>
+      <c r="H33" s="105"/>
+      <c r="I33" s="106"/>
+      <c r="J33" s="106"/>
+      <c r="K33" s="106"/>
+      <c r="L33" s="106"/>
+      <c r="M33" s="106"/>
+      <c r="N33" s="107"/>
+      <c r="O33" s="105"/>
+      <c r="P33" s="109"/>
+      <c r="Q33" s="109"/>
+      <c r="R33" s="109"/>
+      <c r="S33" s="109"/>
+      <c r="T33" s="109"/>
+      <c r="U33" s="109"/>
+      <c r="V33" s="109"/>
+      <c r="W33" s="109"/>
+      <c r="X33" s="109"/>
+      <c r="Y33" s="109"/>
+      <c r="Z33" s="109"/>
+      <c r="AA33" s="109"/>
+      <c r="AB33" s="109"/>
+      <c r="AC33" s="109"/>
+      <c r="AD33" s="109"/>
+      <c r="AE33" s="109"/>
+      <c r="AF33" s="109"/>
+      <c r="AG33" s="109"/>
+      <c r="AH33" s="109"/>
+      <c r="AI33" s="109"/>
+      <c r="AJ33" s="109"/>
+      <c r="AK33" s="109"/>
+      <c r="AL33" s="109"/>
+      <c r="AM33" s="109"/>
+      <c r="AN33" s="109"/>
+      <c r="AO33" s="109"/>
+      <c r="AP33" s="111"/>
+      <c r="AQ33" s="108"/>
+      <c r="AR33" s="109"/>
+      <c r="AS33" s="109"/>
+      <c r="AT33" s="109"/>
+      <c r="AU33" s="109"/>
+      <c r="AV33" s="109"/>
+      <c r="AW33" s="109"/>
+      <c r="AX33" s="109"/>
+      <c r="AY33" s="109"/>
+      <c r="AZ33" s="109"/>
+      <c r="BA33" s="109"/>
+      <c r="BB33" s="109"/>
+      <c r="BC33" s="109"/>
+      <c r="BD33" s="109"/>
+      <c r="BE33" s="110"/>
     </row>
     <row r="34" spans="1:57" ht="15" customHeight="1">
-      <c r="A34" s="88"/>
-      <c r="B34" s="89"/>
-      <c r="C34" s="89"/>
-      <c r="D34" s="89"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="89"/>
-      <c r="G34" s="90"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="92"/>
-      <c r="J34" s="92"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="92"/>
-      <c r="M34" s="92"/>
-      <c r="N34" s="93"/>
-      <c r="O34" s="91"/>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="94"/>
-      <c r="S34" s="94"/>
-      <c r="T34" s="94"/>
-      <c r="U34" s="94"/>
-      <c r="V34" s="94"/>
-      <c r="W34" s="94"/>
-      <c r="X34" s="94"/>
-      <c r="Y34" s="94"/>
-      <c r="Z34" s="94"/>
-      <c r="AA34" s="94"/>
-      <c r="AB34" s="94"/>
-      <c r="AC34" s="94"/>
-      <c r="AD34" s="94"/>
-      <c r="AE34" s="94"/>
-      <c r="AF34" s="94"/>
-      <c r="AG34" s="94"/>
-      <c r="AH34" s="94"/>
-      <c r="AI34" s="94"/>
-      <c r="AJ34" s="94"/>
-      <c r="AK34" s="94"/>
-      <c r="AL34" s="94"/>
-      <c r="AM34" s="94"/>
-      <c r="AN34" s="94"/>
-      <c r="AO34" s="94"/>
-      <c r="AP34" s="95"/>
-      <c r="AQ34" s="96"/>
-      <c r="AR34" s="94"/>
-      <c r="AS34" s="94"/>
-      <c r="AT34" s="94"/>
-      <c r="AU34" s="94"/>
-      <c r="AV34" s="94"/>
-      <c r="AW34" s="94"/>
-      <c r="AX34" s="94"/>
-      <c r="AY34" s="94"/>
-      <c r="AZ34" s="94"/>
-      <c r="BA34" s="94"/>
-      <c r="BB34" s="94"/>
-      <c r="BC34" s="94"/>
-      <c r="BD34" s="94"/>
-      <c r="BE34" s="97"/>
+      <c r="A34" s="99"/>
+      <c r="B34" s="100"/>
+      <c r="C34" s="100"/>
+      <c r="D34" s="100"/>
+      <c r="E34" s="100"/>
+      <c r="F34" s="100"/>
+      <c r="G34" s="101"/>
+      <c r="H34" s="105"/>
+      <c r="I34" s="106"/>
+      <c r="J34" s="106"/>
+      <c r="K34" s="106"/>
+      <c r="L34" s="106"/>
+      <c r="M34" s="106"/>
+      <c r="N34" s="107"/>
+      <c r="O34" s="105"/>
+      <c r="P34" s="109"/>
+      <c r="Q34" s="109"/>
+      <c r="R34" s="109"/>
+      <c r="S34" s="109"/>
+      <c r="T34" s="109"/>
+      <c r="U34" s="109"/>
+      <c r="V34" s="109"/>
+      <c r="W34" s="109"/>
+      <c r="X34" s="109"/>
+      <c r="Y34" s="109"/>
+      <c r="Z34" s="109"/>
+      <c r="AA34" s="109"/>
+      <c r="AB34" s="109"/>
+      <c r="AC34" s="109"/>
+      <c r="AD34" s="109"/>
+      <c r="AE34" s="109"/>
+      <c r="AF34" s="109"/>
+      <c r="AG34" s="109"/>
+      <c r="AH34" s="109"/>
+      <c r="AI34" s="109"/>
+      <c r="AJ34" s="109"/>
+      <c r="AK34" s="109"/>
+      <c r="AL34" s="109"/>
+      <c r="AM34" s="109"/>
+      <c r="AN34" s="109"/>
+      <c r="AO34" s="109"/>
+      <c r="AP34" s="111"/>
+      <c r="AQ34" s="108"/>
+      <c r="AR34" s="109"/>
+      <c r="AS34" s="109"/>
+      <c r="AT34" s="109"/>
+      <c r="AU34" s="109"/>
+      <c r="AV34" s="109"/>
+      <c r="AW34" s="109"/>
+      <c r="AX34" s="109"/>
+      <c r="AY34" s="109"/>
+      <c r="AZ34" s="109"/>
+      <c r="BA34" s="109"/>
+      <c r="BB34" s="109"/>
+      <c r="BC34" s="109"/>
+      <c r="BD34" s="109"/>
+      <c r="BE34" s="110"/>
     </row>
     <row r="35" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="78"/>
-      <c r="B35" s="79"/>
-      <c r="C35" s="79"/>
-      <c r="D35" s="79"/>
-      <c r="E35" s="79"/>
-      <c r="F35" s="79"/>
-      <c r="G35" s="80"/>
-      <c r="H35" s="81"/>
-      <c r="I35" s="82"/>
-      <c r="J35" s="82"/>
-      <c r="K35" s="82"/>
-      <c r="L35" s="82"/>
-      <c r="M35" s="82"/>
-      <c r="N35" s="83"/>
-      <c r="O35" s="81"/>
-      <c r="P35" s="84"/>
-      <c r="Q35" s="84"/>
-      <c r="R35" s="84"/>
-      <c r="S35" s="84"/>
-      <c r="T35" s="84"/>
-      <c r="U35" s="84"/>
-      <c r="V35" s="84"/>
-      <c r="W35" s="84"/>
-      <c r="X35" s="84"/>
-      <c r="Y35" s="84"/>
-      <c r="Z35" s="84"/>
-      <c r="AA35" s="84"/>
-      <c r="AB35" s="84"/>
-      <c r="AC35" s="84"/>
-      <c r="AD35" s="84"/>
-      <c r="AE35" s="84"/>
-      <c r="AF35" s="84"/>
-      <c r="AG35" s="84"/>
-      <c r="AH35" s="84"/>
-      <c r="AI35" s="84"/>
-      <c r="AJ35" s="84"/>
-      <c r="AK35" s="84"/>
-      <c r="AL35" s="84"/>
-      <c r="AM35" s="84"/>
-      <c r="AN35" s="84"/>
-      <c r="AO35" s="84"/>
-      <c r="AP35" s="85"/>
-      <c r="AQ35" s="86"/>
-      <c r="AR35" s="84"/>
-      <c r="AS35" s="84"/>
-      <c r="AT35" s="84"/>
-      <c r="AU35" s="84"/>
-      <c r="AV35" s="84"/>
-      <c r="AW35" s="84"/>
-      <c r="AX35" s="84"/>
-      <c r="AY35" s="84"/>
-      <c r="AZ35" s="84"/>
-      <c r="BA35" s="84"/>
-      <c r="BB35" s="84"/>
-      <c r="BC35" s="84"/>
-      <c r="BD35" s="84"/>
-      <c r="BE35" s="87"/>
+      <c r="A35" s="118"/>
+      <c r="B35" s="119"/>
+      <c r="C35" s="119"/>
+      <c r="D35" s="119"/>
+      <c r="E35" s="119"/>
+      <c r="F35" s="119"/>
+      <c r="G35" s="120"/>
+      <c r="H35" s="121"/>
+      <c r="I35" s="122"/>
+      <c r="J35" s="122"/>
+      <c r="K35" s="122"/>
+      <c r="L35" s="122"/>
+      <c r="M35" s="122"/>
+      <c r="N35" s="123"/>
+      <c r="O35" s="121"/>
+      <c r="P35" s="124"/>
+      <c r="Q35" s="124"/>
+      <c r="R35" s="124"/>
+      <c r="S35" s="124"/>
+      <c r="T35" s="124"/>
+      <c r="U35" s="124"/>
+      <c r="V35" s="124"/>
+      <c r="W35" s="124"/>
+      <c r="X35" s="124"/>
+      <c r="Y35" s="124"/>
+      <c r="Z35" s="124"/>
+      <c r="AA35" s="124"/>
+      <c r="AB35" s="124"/>
+      <c r="AC35" s="124"/>
+      <c r="AD35" s="124"/>
+      <c r="AE35" s="124"/>
+      <c r="AF35" s="124"/>
+      <c r="AG35" s="124"/>
+      <c r="AH35" s="124"/>
+      <c r="AI35" s="124"/>
+      <c r="AJ35" s="124"/>
+      <c r="AK35" s="124"/>
+      <c r="AL35" s="124"/>
+      <c r="AM35" s="124"/>
+      <c r="AN35" s="124"/>
+      <c r="AO35" s="124"/>
+      <c r="AP35" s="125"/>
+      <c r="AQ35" s="126"/>
+      <c r="AR35" s="124"/>
+      <c r="AS35" s="124"/>
+      <c r="AT35" s="124"/>
+      <c r="AU35" s="124"/>
+      <c r="AV35" s="124"/>
+      <c r="AW35" s="124"/>
+      <c r="AX35" s="124"/>
+      <c r="AY35" s="124"/>
+      <c r="AZ35" s="124"/>
+      <c r="BA35" s="124"/>
+      <c r="BB35" s="124"/>
+      <c r="BC35" s="124"/>
+      <c r="BD35" s="124"/>
+      <c r="BE35" s="127"/>
     </row>
   </sheetData>
   <mergeCells count="133">
-    <mergeCell ref="A1:BE1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="H3:N3"/>
-    <mergeCell ref="O3:AP3"/>
-    <mergeCell ref="AQ3:BE3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="H4:N4"/>
-    <mergeCell ref="O4:AP4"/>
-    <mergeCell ref="AQ4:BE4"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="H35:N35"/>
+    <mergeCell ref="O35:AP35"/>
+    <mergeCell ref="AQ35:BE35"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="H33:N33"/>
+    <mergeCell ref="O33:AP33"/>
+    <mergeCell ref="AQ33:BE33"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="H34:N34"/>
+    <mergeCell ref="O34:AP34"/>
+    <mergeCell ref="AQ34:BE34"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="H31:N31"/>
+    <mergeCell ref="O31:AP31"/>
+    <mergeCell ref="AQ31:BE31"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="H32:N32"/>
+    <mergeCell ref="O32:AP32"/>
+    <mergeCell ref="AQ32:BE32"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="H29:N29"/>
+    <mergeCell ref="O29:AP29"/>
+    <mergeCell ref="AQ29:BE29"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="H30:N30"/>
+    <mergeCell ref="O30:AP30"/>
+    <mergeCell ref="AQ30:BE30"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="H27:N27"/>
+    <mergeCell ref="O27:AP27"/>
+    <mergeCell ref="AQ27:BE27"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="H28:N28"/>
+    <mergeCell ref="O28:AP28"/>
+    <mergeCell ref="AQ28:BE28"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="H25:N25"/>
+    <mergeCell ref="O25:AP25"/>
+    <mergeCell ref="AQ25:BE25"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="H26:N26"/>
+    <mergeCell ref="O26:AP26"/>
+    <mergeCell ref="AQ26:BE26"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="H23:N23"/>
+    <mergeCell ref="O23:AP23"/>
+    <mergeCell ref="AQ23:BE23"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="H24:N24"/>
+    <mergeCell ref="O24:AP24"/>
+    <mergeCell ref="AQ24:BE24"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:AP21"/>
+    <mergeCell ref="AQ21:BE21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="H22:N22"/>
+    <mergeCell ref="O22:AP22"/>
+    <mergeCell ref="AQ22:BE22"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:AP19"/>
+    <mergeCell ref="AQ19:BE19"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:AP20"/>
+    <mergeCell ref="AQ20:BE20"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="H17:N17"/>
+    <mergeCell ref="O17:AP17"/>
+    <mergeCell ref="AQ17:BE17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:AP18"/>
+    <mergeCell ref="AQ18:BE18"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="H15:N15"/>
+    <mergeCell ref="O15:AP15"/>
+    <mergeCell ref="AQ15:BE15"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="H16:N16"/>
+    <mergeCell ref="O16:AP16"/>
+    <mergeCell ref="AQ16:BE16"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="H13:N13"/>
+    <mergeCell ref="O13:AP13"/>
+    <mergeCell ref="AQ13:BE13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="H14:N14"/>
+    <mergeCell ref="O14:AP14"/>
+    <mergeCell ref="AQ14:BE14"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="H11:N11"/>
+    <mergeCell ref="O11:AP11"/>
+    <mergeCell ref="AQ11:BE11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="H12:N12"/>
+    <mergeCell ref="O12:AP12"/>
+    <mergeCell ref="AQ12:BE12"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="O9:AP9"/>
+    <mergeCell ref="AQ9:BE9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="H10:N10"/>
+    <mergeCell ref="O10:AP10"/>
+    <mergeCell ref="AQ10:BE10"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="H7:N7"/>
     <mergeCell ref="O7:AP7"/>
@@ -13944,114 +14028,15 @@
     <mergeCell ref="H6:N6"/>
     <mergeCell ref="O6:AP6"/>
     <mergeCell ref="AQ6:BE6"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="H11:N11"/>
-    <mergeCell ref="O11:AP11"/>
-    <mergeCell ref="AQ11:BE11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="H12:N12"/>
-    <mergeCell ref="O12:AP12"/>
-    <mergeCell ref="AQ12:BE12"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="H9:N9"/>
-    <mergeCell ref="O9:AP9"/>
-    <mergeCell ref="AQ9:BE9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="H10:N10"/>
-    <mergeCell ref="O10:AP10"/>
-    <mergeCell ref="AQ10:BE10"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="H15:N15"/>
-    <mergeCell ref="O15:AP15"/>
-    <mergeCell ref="AQ15:BE15"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="H16:N16"/>
-    <mergeCell ref="O16:AP16"/>
-    <mergeCell ref="AQ16:BE16"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="H13:N13"/>
-    <mergeCell ref="O13:AP13"/>
-    <mergeCell ref="AQ13:BE13"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="H14:N14"/>
-    <mergeCell ref="O14:AP14"/>
-    <mergeCell ref="AQ14:BE14"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:AP19"/>
-    <mergeCell ref="AQ19:BE19"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:AP20"/>
-    <mergeCell ref="AQ20:BE20"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="H17:N17"/>
-    <mergeCell ref="O17:AP17"/>
-    <mergeCell ref="AQ17:BE17"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:AP18"/>
-    <mergeCell ref="AQ18:BE18"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="H23:N23"/>
-    <mergeCell ref="O23:AP23"/>
-    <mergeCell ref="AQ23:BE23"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="H24:N24"/>
-    <mergeCell ref="O24:AP24"/>
-    <mergeCell ref="AQ24:BE24"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:AP21"/>
-    <mergeCell ref="AQ21:BE21"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="H22:N22"/>
-    <mergeCell ref="O22:AP22"/>
-    <mergeCell ref="AQ22:BE22"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="H27:N27"/>
-    <mergeCell ref="O27:AP27"/>
-    <mergeCell ref="AQ27:BE27"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="H28:N28"/>
-    <mergeCell ref="O28:AP28"/>
-    <mergeCell ref="AQ28:BE28"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="H25:N25"/>
-    <mergeCell ref="O25:AP25"/>
-    <mergeCell ref="AQ25:BE25"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="H26:N26"/>
-    <mergeCell ref="O26:AP26"/>
-    <mergeCell ref="AQ26:BE26"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="H31:N31"/>
-    <mergeCell ref="O31:AP31"/>
-    <mergeCell ref="AQ31:BE31"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="H32:N32"/>
-    <mergeCell ref="O32:AP32"/>
-    <mergeCell ref="AQ32:BE32"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="H29:N29"/>
-    <mergeCell ref="O29:AP29"/>
-    <mergeCell ref="AQ29:BE29"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="H30:N30"/>
-    <mergeCell ref="O30:AP30"/>
-    <mergeCell ref="AQ30:BE30"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="H35:N35"/>
-    <mergeCell ref="O35:AP35"/>
-    <mergeCell ref="AQ35:BE35"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="H33:N33"/>
-    <mergeCell ref="O33:AP33"/>
-    <mergeCell ref="AQ33:BE33"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="H34:N34"/>
-    <mergeCell ref="O34:AP34"/>
-    <mergeCell ref="AQ34:BE34"/>
+    <mergeCell ref="A1:BE1"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="H3:N3"/>
+    <mergeCell ref="O3:AP3"/>
+    <mergeCell ref="AQ3:BE3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="O4:AP4"/>
+    <mergeCell ref="AQ4:BE4"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
